--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I2" t="str">
-        <v>257.0</v>
+        <v>246.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H3">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I3" t="str">
-        <v>492.0</v>
+        <v>481.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H4">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I4" t="str">
-        <v>946.0</v>
+        <v>947.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H5">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="I5" t="str">
-        <v>1388.0</v>
+        <v>1382.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="H6">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="I6" t="str">
-        <v>2251.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="I7" t="str">
-        <v>463.0</v>
+        <v>453.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H8">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="I8" t="str">
-        <v>1147.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H9">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I9" t="str">
-        <v>702.0</v>
+        <v>705.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I10" t="str">
-        <v>938.0</v>
+        <v>918.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="H11">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="I11" t="str">
-        <v>478.0</v>
+        <v>471.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H12">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="I12" t="str">
-        <v>271.0</v>
+        <v>264.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H13">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="I13" t="str">
-        <v>474.0</v>
+        <v>473.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H14">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I14" t="str">
-        <v>924.0</v>
+        <v>900.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="H15">
-        <v>249</v>
+        <v>199</v>
       </c>
       <c r="I15" t="str">
-        <v>1382.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H16">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I16" t="str">
-        <v>2276.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H17">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="I17" t="str">
-        <v>469.0</v>
+        <v>457.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H18">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="I18" t="str">
-        <v>1126.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1106,10 +1106,10 @@
         <v>132</v>
       </c>
       <c r="H19">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I19" t="str">
-        <v>676.0</v>
+        <v>698.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="H20">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I20" t="str">
-        <v>911.0</v>
+        <v>905.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="H21">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="I21" t="str">
-        <v>454.0</v>
+        <v>457.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="H22">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I22" t="str">
-        <v>245.0</v>
+        <v>242.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H23">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I23" t="str">
-        <v>474.0</v>
+        <v>469.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H24">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I24" t="str">
-        <v>946.0</v>
+        <v>914.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H25">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="I25" t="str">
-        <v>1387.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H26">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I26" t="str">
-        <v>2272.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H27">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="I27" t="str">
-        <v>462.0</v>
+        <v>493.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H28">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I28" t="str">
-        <v>1154.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H29">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="I29" t="str">
-        <v>701.0</v>
+        <v>721.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H30">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I30" t="str">
-        <v>937.0</v>
+        <v>946.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H31">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I31" t="str">
-        <v>454.0</v>
+        <v>468.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H32">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="I32" t="str">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H33">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I33" t="str">
-        <v>457.0</v>
+        <v>451.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="H34">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="I34" t="str">
-        <v>900.0</v>
+        <v>906.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,10 +1711,10 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="H35">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="I35" t="str">
         <v>1353.0</v>
@@ -1752,10 +1752,10 @@
         <v>261</v>
       </c>
       <c r="H36">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I36" t="str">
-        <v>2259.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H37">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I37" t="str">
-        <v>484.0</v>
+        <v>496.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H38">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I38" t="str">
-        <v>1142.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="I39" t="str">
-        <v>707.0</v>
+        <v>708.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="H40">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I40" t="str">
-        <v>925.0</v>
+        <v>949.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
+        <v>126</v>
+      </c>
+      <c r="H41">
         <v>130</v>
       </c>
-      <c r="H41">
-        <v>145</v>
-      </c>
       <c r="I41" t="str">
-        <v>469.0</v>
+        <v>485.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H42">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="I42" t="str">
-        <v>261.0</v>
+        <v>267.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H43">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="I43" t="str">
-        <v>488.0</v>
+        <v>470.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="H44">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="I44" t="str">
-        <v>920.0</v>
+        <v>936.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H45">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I45" t="str">
-        <v>1363.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="H46">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="I46" t="str">
-        <v>2274.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H47">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="I47" t="str">
-        <v>462.0</v>
+        <v>498.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H48">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="I48" t="str">
-        <v>1174.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H49">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I49" t="str">
-        <v>691.0</v>
+        <v>707.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H50">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="I50" t="str">
-        <v>936.0</v>
+        <v>917.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H51">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I51" t="str">
-        <v>462.0</v>
+        <v>487.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H52">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="I52" t="str">
-        <v>235.0</v>
+        <v>253.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H53">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I53" t="str">
-        <v>451.0</v>
+        <v>477.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H54">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="I54" t="str">
-        <v>917.0</v>
+        <v>925.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H55">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="I55" t="str">
-        <v>1352.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="H56">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="I56" t="str">
-        <v>2280.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H57">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="I57" t="str">
-        <v>474.0</v>
+        <v>498.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H58">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="I58" t="str">
-        <v>1171.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="H59">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I59" t="str">
-        <v>709.0</v>
+        <v>678.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H60">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="I60" t="str">
-        <v>903.0</v>
+        <v>936.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="H61">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="I61" t="str">
-        <v>456.0</v>
+        <v>458.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H62">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I62" t="str">
-        <v>233.0</v>
+        <v>266.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H63">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I63" t="str">
-        <v>468.0</v>
+        <v>479.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="H64">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I64" t="str">
-        <v>927.0</v>
+        <v>920.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H65">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="I65" t="str">
-        <v>1368.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H66">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="I66" t="str">
-        <v>2279.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H67">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="I67" t="str">
-        <v>476.0</v>
+        <v>484.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H68">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="I68" t="str">
-        <v>1166.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H69">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I69" t="str">
-        <v>686.0</v>
+        <v>703.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H70">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I70" t="str">
-        <v>948.0</v>
+        <v>927.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="H71">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I71" t="str">
-        <v>470.0</v>
+        <v>497.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,10 +3117,10 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H72">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I72" t="str">
         <v>260.0</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H73">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I73" t="str">
-        <v>463.0</v>
+        <v>461.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="H74">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I74" t="str">
-        <v>949.0</v>
+        <v>917.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H75">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I75" t="str">
-        <v>1372.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="H76">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="I76" t="str">
-        <v>2271.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H77">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="I77" t="str">
-        <v>465.0</v>
+        <v>496.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="H78">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="I78" t="str">
-        <v>1132.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H79">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="I79" t="str">
-        <v>716.0</v>
+        <v>696.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H80">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="I80" t="str">
-        <v>948.0</v>
+        <v>901.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="H81">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I81" t="str">
-        <v>459.0</v>
+        <v>494.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3500,10 +3500,10 @@
         <v>97</v>
       </c>
       <c r="H82">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I82" t="str">
-        <v>253.0</v>
+        <v>229.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H83">
         <v>155</v>
       </c>
       <c r="I83" t="str">
-        <v>470.0</v>
+        <v>491.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H84">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I84" t="str">
-        <v>925.0</v>
+        <v>905.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="H85">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="I85" t="str">
-        <v>1362.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="H86">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I86" t="str">
-        <v>2258.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="H87">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I87" t="str">
-        <v>465.0</v>
+        <v>483.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
+        <v>163</v>
+      </c>
+      <c r="H88">
         <v>175</v>
       </c>
-      <c r="H88">
-        <v>199</v>
-      </c>
       <c r="I88" t="str">
-        <v>1130.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="H89">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="I89" t="str">
-        <v>697.0</v>
+        <v>707.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H90">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I90" t="str">
-        <v>949.0</v>
+        <v>943.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H91">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I91" t="str">
-        <v>497.0</v>
+        <v>479.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H92">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="I92" t="str">
-        <v>274.0</v>
+        <v>262.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H93">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I93" t="str">
-        <v>489.0</v>
+        <v>496.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3956,10 +3956,10 @@
         <v>149</v>
       </c>
       <c r="H94">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="I94" t="str">
-        <v>947.0</v>
+        <v>948.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3994,10 +3994,10 @@
         <v>205</v>
       </c>
       <c r="H95">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I95" t="str">
-        <v>1369.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H96">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="I96" t="str">
-        <v>2294.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H97">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I97" t="str">
-        <v>494.0</v>
+        <v>460.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H98">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I98" t="str">
-        <v>1141.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H99">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="I99" t="str">
-        <v>723.0</v>
+        <v>682.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H100">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I100" t="str">
-        <v>916.0</v>
+        <v>949.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H101">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="I101" t="str">
-        <v>485.0</v>
+        <v>462.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H102">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I102" t="str">
-        <v>229.0</v>
+        <v>265.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
+        <v>117</v>
+      </c>
+      <c r="H103">
         <v>119</v>
       </c>
-      <c r="H103">
-        <v>152</v>
-      </c>
       <c r="I103" t="str">
-        <v>482.0</v>
+        <v>487.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H104">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="I104" t="str">
-        <v>928.0</v>
+        <v>925.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H105">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="I105" t="str">
-        <v>1392.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H106">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="I106" t="str">
-        <v>2270.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H107">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I107" t="str">
-        <v>487.0</v>
+        <v>498.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H108">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="I108" t="str">
-        <v>1138.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H109">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="I109" t="str">
-        <v>690.0</v>
+        <v>695.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H110">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I110" t="str">
-        <v>944.0</v>
+        <v>909.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="H111">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="I111" t="str">
-        <v>466.0</v>
+        <v>464.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H112">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I112" t="str">
-        <v>254.0</v>
+        <v>274.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H113">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I113" t="str">
-        <v>458.0</v>
+        <v>456.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="H114">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I114" t="str">
-        <v>914.0</v>
+        <v>943.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H115">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I115" t="str">
-        <v>1381.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="H116">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="I116" t="str">
-        <v>2298.0</v>
+        <v>2284.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="H117">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I117" t="str">
-        <v>487.0</v>
+        <v>474.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H118">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I118" t="str">
-        <v>1130.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H119">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I119" t="str">
-        <v>690.0</v>
+        <v>688.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H120">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I120" t="str">
-        <v>904.0</v>
+        <v>910.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H121">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="I121" t="str">
-        <v>466.0</v>
+        <v>498.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5020,10 +5020,10 @@
         <v>98</v>
       </c>
       <c r="H122">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I122" t="str">
-        <v>256.0</v>
+        <v>258.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H123">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I123" t="str">
-        <v>485.0</v>
+        <v>487.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="H124">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="I124" t="str">
-        <v>929.0</v>
+        <v>900.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H125">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="I125" t="str">
-        <v>1356.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H126">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="I126" t="str">
-        <v>2252.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H127">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I127" t="str">
-        <v>494.0</v>
+        <v>491.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,10 +5245,10 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H128">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I128" t="str">
         <v>1130.0</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H129">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I129" t="str">
-        <v>714.0</v>
+        <v>686.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="H130">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="I130" t="str">
-        <v>927.0</v>
+        <v>905.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H131">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="I131" t="str">
-        <v>453.0</v>
+        <v>479.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H132">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I132" t="str">
-        <v>248.0</v>
+        <v>236.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H133">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="I133" t="str">
-        <v>461.0</v>
+        <v>476.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H134">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I134" t="str">
-        <v>929.0</v>
+        <v>904.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H135">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="I135" t="str">
-        <v>1399.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="H136">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I136" t="str">
-        <v>2273.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H137">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I137" t="str">
-        <v>491.0</v>
+        <v>459.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H138">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="I138" t="str">
-        <v>1151.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="H139">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I139" t="str">
-        <v>682.0</v>
+        <v>708.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H140">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I140" t="str">
-        <v>916.0</v>
+        <v>906.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H141">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I141" t="str">
-        <v>489.0</v>
+        <v>460.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H142">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="I142" t="str">
-        <v>246.0</v>
+        <v>259.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H143">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="I143" t="str">
-        <v>485.0</v>
+        <v>454.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="H144">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I144" t="str">
-        <v>903.0</v>
+        <v>914.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H145">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="I145" t="str">
-        <v>1353.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H146">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="I146" t="str">
-        <v>2284.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H147">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="I147" t="str">
-        <v>486.0</v>
+        <v>476.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H148">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="I148" t="str">
-        <v>1131.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H149">
         <v>166</v>
       </c>
       <c r="I149" t="str">
-        <v>681.0</v>
+        <v>715.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H150">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I150" t="str">
-        <v>904.0</v>
+        <v>926.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H151">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="I151" t="str">
-        <v>451.0</v>
+        <v>453.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H152">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="I152" t="str">
-        <v>271.0</v>
+        <v>260.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H153">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I153" t="str">
-        <v>477.0</v>
+        <v>458.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H154">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I154" t="str">
-        <v>900.0</v>
+        <v>911.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H155">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I155" t="str">
-        <v>1363.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="H156">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="I156" t="str">
-        <v>2262.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H157">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I157" t="str">
-        <v>475.0</v>
+        <v>470.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H158">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="I158" t="str">
-        <v>1131.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H159">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="I159" t="str">
-        <v>721.0</v>
+        <v>690.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H160">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I160" t="str">
-        <v>921.0</v>
+        <v>932.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H161">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I161" t="str">
-        <v>483.0</v>
+        <v>470.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H162">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I162" t="str">
-        <v>234.0</v>
+        <v>242.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H163">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I163" t="str">
-        <v>460.0</v>
+        <v>474.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="H164">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="I164" t="str">
-        <v>944.0</v>
+        <v>939.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H165">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I165" t="str">
-        <v>1375.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="H166">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="I166" t="str">
-        <v>2294.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="H167">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="I167" t="str">
-        <v>496.0</v>
+        <v>472.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H168">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I168" t="str">
-        <v>1136.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H169">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="I169" t="str">
-        <v>716.0</v>
+        <v>714.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H170">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="I170" t="str">
-        <v>922.0</v>
+        <v>933.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H171">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I171" t="str">
-        <v>454.0</v>
+        <v>452.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H172">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="I172" t="str">
-        <v>244.0</v>
+        <v>239.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H173">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="I173" t="str">
-        <v>487.0</v>
+        <v>454.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H174">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I174" t="str">
-        <v>906.0</v>
+        <v>910.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H175">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I175" t="str">
-        <v>1395.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H176">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I176" t="str">
-        <v>2288.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H177">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I177" t="str">
-        <v>484.0</v>
+        <v>455.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7148,10 +7148,10 @@
         <v>175</v>
       </c>
       <c r="H178">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="I178" t="str">
-        <v>1172.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H179">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I179" t="str">
-        <v>687.0</v>
+        <v>715.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H180">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I180" t="str">
-        <v>948.0</v>
+        <v>946.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H181">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="I181" t="str">
-        <v>482.0</v>
+        <v>477.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H182">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I182" t="str">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H183">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I183" t="str">
-        <v>468.0</v>
+        <v>477.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H184">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I184" t="str">
-        <v>947.0</v>
+        <v>919.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="H185">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="I185" t="str">
-        <v>1365.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H186">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="I186" t="str">
-        <v>2280.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H187">
         <v>146</v>
       </c>
       <c r="I187" t="str">
-        <v>481.0</v>
+        <v>461.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H188">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="I188" t="str">
-        <v>1156.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H189">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="I189" t="str">
-        <v>710.0</v>
+        <v>691.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H190">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="I190" t="str">
-        <v>930.0</v>
+        <v>912.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H191">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="I191" t="str">
-        <v>499.0</v>
+        <v>493.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H192">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I192" t="str">
-        <v>269.0</v>
+        <v>264.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H193">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I193" t="str">
-        <v>452.0</v>
+        <v>475.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H194">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I194" t="str">
-        <v>933.0</v>
+        <v>948.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H195">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="I195" t="str">
-        <v>1374.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="H196">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="I196" t="str">
-        <v>2293.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H197">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="I197" t="str">
-        <v>487.0</v>
+        <v>457.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H198">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I198" t="str">
-        <v>1163.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H199">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="I199" t="str">
-        <v>701.0</v>
+        <v>722.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H200">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I200" t="str">
-        <v>949.0</v>
+        <v>917.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="H201">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="I201" t="str">
-        <v>477.0</v>
+        <v>489.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H202">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="I202" t="str">
-        <v>265.0</v>
+        <v>230.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="H203">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="I203" t="str">
-        <v>478.0</v>
+        <v>463.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="H204">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="I204" t="str">
-        <v>912.0</v>
+        <v>936.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H205">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I205" t="str">
-        <v>1358.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H206">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="I206" t="str">
-        <v>2261.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H207">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I207" t="str">
-        <v>479.0</v>
+        <v>458.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H208">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="I208" t="str">
-        <v>1139.0</v>
+        <v>1145.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H209">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I209" t="str">
-        <v>694.0</v>
+        <v>718.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H210">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I210" t="str">
-        <v>915.0</v>
+        <v>919.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H211">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I211" t="str">
-        <v>476.0</v>
+        <v>469.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H212">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I212" t="str">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H213">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I213" t="str">
-        <v>498.0</v>
+        <v>466.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H214">
         <v>185</v>
       </c>
       <c r="I214" t="str">
-        <v>910.0</v>
+        <v>920.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="H215">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I215" t="str">
-        <v>1387.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="H216">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="I216" t="str">
-        <v>2290.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H217">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I217" t="str">
-        <v>453.0</v>
+        <v>494.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
+        <v>162</v>
+      </c>
+      <c r="H218">
         <v>178</v>
       </c>
-      <c r="H218">
-        <v>197</v>
-      </c>
       <c r="I218" t="str">
-        <v>1174.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H219">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I219" t="str">
-        <v>714.0</v>
+        <v>716.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H220">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I220" t="str">
-        <v>920.0</v>
+        <v>945.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="H221">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I221" t="str">
-        <v>493.0</v>
+        <v>463.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H222">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="I222" t="str">
-        <v>226.0</v>
+        <v>264.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H223">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="I223" t="str">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H224">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I224" t="str">
-        <v>905.0</v>
+        <v>908.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H225">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I225" t="str">
-        <v>1359.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H226">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I226" t="str">
-        <v>2260.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H227">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="I227" t="str">
-        <v>456.0</v>
+        <v>466.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H228">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="I228" t="str">
-        <v>1142.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H229">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="I229" t="str">
-        <v>720.0</v>
+        <v>676.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H230">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I230" t="str">
-        <v>929.0</v>
+        <v>936.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H231">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="I231" t="str">
-        <v>470.0</v>
+        <v>453.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9200,10 +9200,10 @@
         <v>95</v>
       </c>
       <c r="H232">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="I232" t="str">
-        <v>257.0</v>
+        <v>267.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="H233">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I233" t="str">
-        <v>484.0</v>
+        <v>488.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H234">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I234" t="str">
-        <v>948.0</v>
+        <v>933.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H235">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="I235" t="str">
-        <v>1397.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="H236">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I236" t="str">
-        <v>2274.0</v>
+        <v>2262.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="H237">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="I237" t="str">
-        <v>475.0</v>
+        <v>470.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H238">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I238" t="str">
-        <v>1145.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H239">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="I239" t="str">
-        <v>719.0</v>
+        <v>695.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H240">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="I240" t="str">
-        <v>936.0</v>
+        <v>934.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H241">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="I241" t="str">
-        <v>465.0</v>
+        <v>459.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H242">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="I242" t="str">
-        <v>245.0</v>
+        <v>228.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H243">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I243" t="str">
-        <v>470.0</v>
+        <v>461.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H244">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="I244" t="str">
-        <v>908.0</v>
+        <v>937.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H245">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="I245" t="str">
-        <v>1355.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H246">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="I246" t="str">
-        <v>2256.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H247">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="I247" t="str">
-        <v>460.0</v>
+        <v>468.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="H248">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="I248" t="str">
-        <v>1132.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="H249">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="I249" t="str">
-        <v>701.0</v>
+        <v>721.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H250">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="I250" t="str">
-        <v>923.0</v>
+        <v>922.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H251">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I251" t="str">
-        <v>475.0</v>
+        <v>482.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H252">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I252" t="str">
-        <v>261.0</v>
+        <v>253.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H253">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I253" t="str">
-        <v>483.0</v>
+        <v>477.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="H254">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I254" t="str">
-        <v>913.0</v>
+        <v>926.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="H255">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="I255" t="str">
-        <v>1371.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H256">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I256" t="str">
-        <v>2265.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H257">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="I257" t="str">
-        <v>465.0</v>
+        <v>484.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H258">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I258" t="str">
-        <v>1173.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H259">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I259" t="str">
-        <v>723.0</v>
+        <v>701.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H260">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I260" t="str">
-        <v>940.0</v>
+        <v>900.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H261">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="I261" t="str">
-        <v>460.0</v>
+        <v>482.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H262">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="I262" t="str">
-        <v>233.0</v>
+        <v>250.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H263">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I263" t="str">
-        <v>451.0</v>
+        <v>469.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H264">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="I264" t="str">
-        <v>934.0</v>
+        <v>918.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H265">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="I265" t="str">
-        <v>1369.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H266">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="I266" t="str">
-        <v>2276.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H267">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="I267" t="str">
-        <v>492.0</v>
+        <v>486.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H268">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I268" t="str">
-        <v>1157.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H269">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I269" t="str">
-        <v>718.0</v>
+        <v>686.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="H270">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I270" t="str">
-        <v>928.0</v>
+        <v>941.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="H271">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I271" t="str">
-        <v>481.0</v>
+        <v>484.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="H272">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="I272" t="str">
-        <v>239.0</v>
+        <v>231.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H273">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="I273" t="str">
-        <v>464.0</v>
+        <v>483.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H274">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I274" t="str">
-        <v>930.0</v>
+        <v>935.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="H275">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="I275" t="str">
-        <v>1377.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="H276">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="I276" t="str">
-        <v>2290.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H277">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="I277" t="str">
-        <v>486.0</v>
+        <v>450.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="H278">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I278" t="str">
-        <v>1149.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H279">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="I279" t="str">
-        <v>675.0</v>
+        <v>705.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11024,10 +11024,10 @@
         <v>98</v>
       </c>
       <c r="H280">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="I280" t="str">
-        <v>932.0</v>
+        <v>914.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H281">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I281" t="str">
-        <v>487.0</v>
+        <v>457.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H282">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I282" t="str">
-        <v>231.0</v>
+        <v>261.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H283">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I283" t="str">
-        <v>459.0</v>
+        <v>464.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="H284">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="I284" t="str">
-        <v>914.0</v>
+        <v>939.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="H285">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I285" t="str">
-        <v>1365.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H286">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I286" t="str">
-        <v>2299.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H287">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I287" t="str">
-        <v>488.0</v>
+        <v>486.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="H288">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="I288" t="str">
-        <v>1168.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H289">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I289" t="str">
-        <v>717.0</v>
+        <v>675.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11404,10 +11404,10 @@
         <v>110</v>
       </c>
       <c r="H290">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="I290" t="str">
-        <v>936.0</v>
+        <v>925.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H291">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I291" t="str">
-        <v>499.0</v>
+        <v>487.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H292">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="I292" t="str">
-        <v>270.0</v>
+        <v>241.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H293">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="I293" t="str">
-        <v>490.0</v>
+        <v>482.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H294">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="I294" t="str">
-        <v>922.0</v>
+        <v>949.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H295">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="I295" t="str">
-        <v>1377.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="H296">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="I296" t="str">
-        <v>2294.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H297">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="I297" t="str">
-        <v>473.0</v>
+        <v>470.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H298">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I298" t="str">
-        <v>1144.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="H299">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I299" t="str">
-        <v>690.0</v>
+        <v>679.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H300">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I300" t="str">
-        <v>934.0</v>
+        <v>938.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H301">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I301" t="str">
-        <v>478.0</v>
+        <v>472.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H2">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="I2" t="str">
-        <v>246.0</v>
+        <v>236.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="H3">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="I3" t="str">
-        <v>481.0</v>
+        <v>463.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H4">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I4" t="str">
-        <v>947.0</v>
+        <v>946.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H5">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="I5" t="str">
-        <v>1382.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H6">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="I6" t="str">
-        <v>2297.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H7">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="I7" t="str">
-        <v>453.0</v>
+        <v>485.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H8">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="I8" t="str">
-        <v>1169.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H9">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="I9" t="str">
-        <v>705.0</v>
+        <v>685.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H10">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="I10" t="str">
-        <v>918.0</v>
+        <v>906.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H11">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I11" t="str">
-        <v>471.0</v>
+        <v>497.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H12">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I12" t="str">
-        <v>264.0</v>
+        <v>248.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H13">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="I13" t="str">
-        <v>473.0</v>
+        <v>468.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H14">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="I14" t="str">
-        <v>900.0</v>
+        <v>906.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="H15">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I15" t="str">
-        <v>1369.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H16">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I16" t="str">
-        <v>2283.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H17">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="I17" t="str">
-        <v>457.0</v>
+        <v>495.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="H18">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="I18" t="str">
-        <v>1144.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H19">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="I19" t="str">
-        <v>698.0</v>
+        <v>715.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H20">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="I20" t="str">
-        <v>905.0</v>
+        <v>940.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H21">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I21" t="str">
-        <v>457.0</v>
+        <v>464.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H22">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="I22" t="str">
-        <v>242.0</v>
+        <v>236.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H23">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="I23" t="str">
-        <v>469.0</v>
+        <v>488.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H24">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="I24" t="str">
-        <v>914.0</v>
+        <v>941.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H25">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="I25" t="str">
-        <v>1363.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H26">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="I26" t="str">
-        <v>2278.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H27">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="I27" t="str">
-        <v>493.0</v>
+        <v>473.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H28">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I28" t="str">
-        <v>1167.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H29">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="I29" t="str">
-        <v>721.0</v>
+        <v>715.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H30">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I30" t="str">
-        <v>946.0</v>
+        <v>948.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H31">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="I31" t="str">
-        <v>468.0</v>
+        <v>466.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H32">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="I32" t="str">
-        <v>239.0</v>
+        <v>249.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H33">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I33" t="str">
-        <v>451.0</v>
+        <v>459.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H34">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I34" t="str">
-        <v>906.0</v>
+        <v>927.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="H35">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="I35" t="str">
-        <v>1353.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H36">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="I36" t="str">
-        <v>2276.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H37">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="I37" t="str">
-        <v>496.0</v>
+        <v>468.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H38">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="I38" t="str">
-        <v>1169.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H39">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="I39" t="str">
-        <v>708.0</v>
+        <v>695.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H40">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I40" t="str">
-        <v>949.0</v>
+        <v>930.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H41">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I41" t="str">
-        <v>485.0</v>
+        <v>457.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H42">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I42" t="str">
-        <v>267.0</v>
+        <v>251.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H43">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I43" t="str">
-        <v>470.0</v>
+        <v>451.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2056,10 +2056,10 @@
         <v>145</v>
       </c>
       <c r="H44">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="I44" t="str">
-        <v>936.0</v>
+        <v>941.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H45">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I45" t="str">
-        <v>1362.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H46">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="I46" t="str">
-        <v>2290.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H47">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I47" t="str">
-        <v>498.0</v>
+        <v>490.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H48">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="I48" t="str">
-        <v>1170.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H49">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="I49" t="str">
-        <v>707.0</v>
+        <v>701.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H50">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="I50" t="str">
-        <v>917.0</v>
+        <v>928.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H51">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I51" t="str">
-        <v>487.0</v>
+        <v>492.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H52">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I52" t="str">
-        <v>253.0</v>
+        <v>228.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H53">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I53" t="str">
-        <v>477.0</v>
+        <v>497.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H54">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I54" t="str">
-        <v>925.0</v>
+        <v>942.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H55">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I55" t="str">
-        <v>1397.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H56">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="I56" t="str">
-        <v>2279.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H57">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="I57" t="str">
-        <v>498.0</v>
+        <v>482.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="H58">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I58" t="str">
-        <v>1136.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H59">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="I59" t="str">
-        <v>678.0</v>
+        <v>721.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H60">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="I60" t="str">
-        <v>936.0</v>
+        <v>917.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H61">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="I61" t="str">
-        <v>458.0</v>
+        <v>486.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H62">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I62" t="str">
-        <v>266.0</v>
+        <v>226.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H63">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I63" t="str">
-        <v>479.0</v>
+        <v>459.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H64">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I64" t="str">
-        <v>920.0</v>
+        <v>917.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H65">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="I65" t="str">
-        <v>1370.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H66">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I66" t="str">
-        <v>2256.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H67">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="I67" t="str">
-        <v>484.0</v>
+        <v>475.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H68">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="I68" t="str">
-        <v>1168.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H69">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I69" t="str">
-        <v>703.0</v>
+        <v>712.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H70">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I70" t="str">
-        <v>927.0</v>
+        <v>904.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H71">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="I71" t="str">
-        <v>497.0</v>
+        <v>450.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H72">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I72" t="str">
-        <v>260.0</v>
+        <v>252.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H73">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="I73" t="str">
-        <v>461.0</v>
+        <v>486.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H74">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I74" t="str">
-        <v>917.0</v>
+        <v>914.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="H75">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="I75" t="str">
-        <v>1394.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H76">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="I76" t="str">
-        <v>2285.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H77">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="I77" t="str">
-        <v>496.0</v>
+        <v>479.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H78">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="I78" t="str">
-        <v>1127.0</v>
+        <v>1128.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="H79">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I79" t="str">
-        <v>696.0</v>
+        <v>684.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="H80">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="I80" t="str">
-        <v>901.0</v>
+        <v>910.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H81">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I81" t="str">
-        <v>494.0</v>
+        <v>457.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H82">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="I82" t="str">
-        <v>229.0</v>
+        <v>249.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H83">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I83" t="str">
-        <v>491.0</v>
+        <v>465.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="H84">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I84" t="str">
-        <v>905.0</v>
+        <v>936.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="H85">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="I85" t="str">
-        <v>1375.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="H86">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="I86" t="str">
-        <v>2299.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3690,10 +3690,10 @@
         <v>128</v>
       </c>
       <c r="H87">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="I87" t="str">
-        <v>483.0</v>
+        <v>487.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H88">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I88" t="str">
-        <v>1163.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H89">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I89" t="str">
-        <v>707.0</v>
+        <v>697.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
+        <v>106</v>
+      </c>
+      <c r="H90">
         <v>109</v>
       </c>
-      <c r="H90">
-        <v>119</v>
-      </c>
       <c r="I90" t="str">
-        <v>943.0</v>
+        <v>912.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H91">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I91" t="str">
-        <v>479.0</v>
+        <v>484.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H92">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="I92" t="str">
-        <v>262.0</v>
+        <v>274.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H93">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="I93" t="str">
-        <v>496.0</v>
+        <v>454.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="H94">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="I94" t="str">
-        <v>948.0</v>
+        <v>940.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H95">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="I95" t="str">
-        <v>1375.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,10 +4029,10 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H96">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="I96" t="str">
         <v>2297.0</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H97">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I97" t="str">
-        <v>460.0</v>
+        <v>465.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H98">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I98" t="str">
-        <v>1131.0</v>
+        <v>1134.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H99">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I99" t="str">
-        <v>682.0</v>
+        <v>675.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4184,10 +4184,10 @@
         <v>100</v>
       </c>
       <c r="H100">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I100" t="str">
-        <v>949.0</v>
+        <v>941.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H101">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="I101" t="str">
-        <v>462.0</v>
+        <v>468.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H102">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="I102" t="str">
-        <v>265.0</v>
+        <v>269.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H103">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="I103" t="str">
-        <v>487.0</v>
+        <v>458.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H104">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I104" t="str">
-        <v>925.0</v>
+        <v>919.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H105">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="I105" t="str">
-        <v>1389.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H106">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="I106" t="str">
-        <v>2285.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H107">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I107" t="str">
-        <v>498.0</v>
+        <v>453.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H108">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="I108" t="str">
-        <v>1150.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H109">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I109" t="str">
-        <v>695.0</v>
+        <v>682.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H110">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I110" t="str">
-        <v>909.0</v>
+        <v>916.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="H111">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="I111" t="str">
-        <v>464.0</v>
+        <v>497.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H112">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I112" t="str">
-        <v>274.0</v>
+        <v>262.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H113">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="I113" t="str">
-        <v>456.0</v>
+        <v>470.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="H114">
         <v>176</v>
       </c>
       <c r="I114" t="str">
-        <v>943.0</v>
+        <v>911.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H115">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I115" t="str">
-        <v>1360.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H116">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="I116" t="str">
-        <v>2284.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H117">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I117" t="str">
-        <v>474.0</v>
+        <v>484.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H118">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="I118" t="str">
-        <v>1136.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="H119">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I119" t="str">
-        <v>688.0</v>
+        <v>711.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H120">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="I120" t="str">
-        <v>910.0</v>
+        <v>914.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H121">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="I121" t="str">
-        <v>498.0</v>
+        <v>460.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H122">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="I122" t="str">
-        <v>258.0</v>
+        <v>228.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H123">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I123" t="str">
-        <v>487.0</v>
+        <v>479.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H124">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I124" t="str">
-        <v>900.0</v>
+        <v>909.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H125">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="I125" t="str">
-        <v>1357.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="H126">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="I126" t="str">
-        <v>2278.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H127">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="I127" t="str">
-        <v>491.0</v>
+        <v>469.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H128">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I128" t="str">
-        <v>1130.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H129">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I129" t="str">
-        <v>686.0</v>
+        <v>697.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H130">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="I130" t="str">
-        <v>905.0</v>
+        <v>923.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H131">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="I131" t="str">
-        <v>479.0</v>
+        <v>459.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H132">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I132" t="str">
-        <v>236.0</v>
+        <v>230.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H133">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="I133" t="str">
-        <v>476.0</v>
+        <v>469.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5476,10 +5476,10 @@
         <v>162</v>
       </c>
       <c r="H134">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I134" t="str">
-        <v>904.0</v>
+        <v>919.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H135">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I135" t="str">
-        <v>1365.0</v>
+        <v>1398.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H136">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="I136" t="str">
-        <v>2288.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H137">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I137" t="str">
-        <v>459.0</v>
+        <v>462.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H138">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="I138" t="str">
-        <v>1167.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="H139">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="I139" t="str">
-        <v>708.0</v>
+        <v>698.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H140">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I140" t="str">
-        <v>906.0</v>
+        <v>900.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H141">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I141" t="str">
-        <v>460.0</v>
+        <v>463.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H142">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="I142" t="str">
-        <v>259.0</v>
+        <v>245.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H143">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I143" t="str">
-        <v>454.0</v>
+        <v>496.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H144">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I144" t="str">
-        <v>914.0</v>
+        <v>918.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="H145">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="I145" t="str">
-        <v>1373.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5935,7 +5935,7 @@
         <v>300</v>
       </c>
       <c r="I146" t="str">
-        <v>2295.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H147">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I147" t="str">
-        <v>476.0</v>
+        <v>495.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="H148">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="I148" t="str">
-        <v>1129.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H149">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I149" t="str">
-        <v>715.0</v>
+        <v>685.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H150">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="I150" t="str">
-        <v>926.0</v>
+        <v>938.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="H151">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I151" t="str">
-        <v>453.0</v>
+        <v>483.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H152">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="I152" t="str">
-        <v>260.0</v>
+        <v>241.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H153">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="I153" t="str">
-        <v>458.0</v>
+        <v>465.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H154">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="I154" t="str">
-        <v>911.0</v>
+        <v>922.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H155">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="I155" t="str">
-        <v>1353.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H156">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I156" t="str">
-        <v>2299.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
+        <v>116</v>
+      </c>
+      <c r="H157">
         <v>121</v>
       </c>
-      <c r="H157">
-        <v>140</v>
-      </c>
       <c r="I157" t="str">
-        <v>470.0</v>
+        <v>466.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6388,10 +6388,10 @@
         <v>169</v>
       </c>
       <c r="H158">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="I158" t="str">
-        <v>1164.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H159">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I159" t="str">
-        <v>690.0</v>
+        <v>680.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H160">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="I160" t="str">
-        <v>932.0</v>
+        <v>906.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H161">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I161" t="str">
-        <v>470.0</v>
+        <v>495.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H162">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I162" t="str">
-        <v>242.0</v>
+        <v>254.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H163">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I163" t="str">
-        <v>474.0</v>
+        <v>452.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,10 +6613,10 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="H164">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I164" t="str">
         <v>939.0</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H165">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I165" t="str">
-        <v>1357.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H166">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="I166" t="str">
-        <v>2291.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H167">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="I167" t="str">
-        <v>472.0</v>
+        <v>469.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H168">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="I168" t="str">
-        <v>1174.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
+        <v>134</v>
+      </c>
+      <c r="H169">
         <v>143</v>
       </c>
-      <c r="H169">
-        <v>151</v>
-      </c>
       <c r="I169" t="str">
-        <v>714.0</v>
+        <v>707.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H170">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I170" t="str">
-        <v>933.0</v>
+        <v>918.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H171">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I171" t="str">
-        <v>452.0</v>
+        <v>465.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H172">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I172" t="str">
-        <v>239.0</v>
+        <v>251.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,10 +6955,10 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H173">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="I173" t="str">
         <v>454.0</v>
@@ -6996,10 +6996,10 @@
         <v>169</v>
       </c>
       <c r="H174">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I174" t="str">
-        <v>910.0</v>
+        <v>927.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H175">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="I175" t="str">
-        <v>1385.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="H176">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="I176" t="str">
-        <v>2259.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H177">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="I177" t="str">
-        <v>455.0</v>
+        <v>494.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H178">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I178" t="str">
-        <v>1173.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7186,10 +7186,10 @@
         <v>152</v>
       </c>
       <c r="H179">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="I179" t="str">
-        <v>715.0</v>
+        <v>692.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="H180">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="I180" t="str">
-        <v>946.0</v>
+        <v>906.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="H181">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I181" t="str">
-        <v>477.0</v>
+        <v>462.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H182">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="I182" t="str">
-        <v>256.0</v>
+        <v>269.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H183">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I183" t="str">
-        <v>477.0</v>
+        <v>483.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H184">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="I184" t="str">
-        <v>919.0</v>
+        <v>913.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H185">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I185" t="str">
-        <v>1394.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7452,10 +7452,10 @@
         <v>261</v>
       </c>
       <c r="H186">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="I186" t="str">
-        <v>2277.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="H187">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="I187" t="str">
-        <v>461.0</v>
+        <v>485.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H188">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="I188" t="str">
-        <v>1129.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,10 +7563,10 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H189">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I189" t="str">
         <v>691.0</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H190">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I190" t="str">
-        <v>912.0</v>
+        <v>918.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H191">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="I191" t="str">
-        <v>493.0</v>
+        <v>478.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H192">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="I192" t="str">
-        <v>264.0</v>
+        <v>271.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H193">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I193" t="str">
-        <v>475.0</v>
+        <v>479.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H194">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I194" t="str">
-        <v>948.0</v>
+        <v>900.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H195">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="I195" t="str">
-        <v>1397.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H196">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I196" t="str">
-        <v>2299.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H197">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="I197" t="str">
-        <v>457.0</v>
+        <v>490.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H198">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I198" t="str">
-        <v>1160.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="H199">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I199" t="str">
-        <v>722.0</v>
+        <v>723.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H200">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="I200" t="str">
-        <v>917.0</v>
+        <v>936.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H201">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I201" t="str">
-        <v>489.0</v>
+        <v>466.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H202">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I202" t="str">
-        <v>230.0</v>
+        <v>250.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H203">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I203" t="str">
-        <v>463.0</v>
+        <v>491.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H204">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I204" t="str">
-        <v>936.0</v>
+        <v>902.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H205">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="I205" t="str">
-        <v>1386.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H206">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I206" t="str">
-        <v>2276.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="H207">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="I207" t="str">
-        <v>458.0</v>
+        <v>490.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H208">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I208" t="str">
-        <v>1145.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H209">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="I209" t="str">
-        <v>718.0</v>
+        <v>723.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H210">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I210" t="str">
-        <v>919.0</v>
+        <v>945.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H211">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I211" t="str">
-        <v>469.0</v>
+        <v>492.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H212">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="I212" t="str">
-        <v>268.0</v>
+        <v>238.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H213">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I213" t="str">
-        <v>466.0</v>
+        <v>469.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
+        <v>146</v>
+      </c>
+      <c r="H214">
         <v>151</v>
       </c>
-      <c r="H214">
-        <v>185</v>
-      </c>
       <c r="I214" t="str">
-        <v>920.0</v>
+        <v>911.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H215">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I215" t="str">
-        <v>1366.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H216">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="I216" t="str">
-        <v>2260.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="H217">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I217" t="str">
-        <v>494.0</v>
+        <v>477.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H218">
         <v>178</v>
       </c>
       <c r="I218" t="str">
-        <v>1140.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="H219">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I219" t="str">
-        <v>716.0</v>
+        <v>683.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H220">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="I220" t="str">
-        <v>945.0</v>
+        <v>919.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H221">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I221" t="str">
-        <v>463.0</v>
+        <v>487.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H222">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I222" t="str">
-        <v>264.0</v>
+        <v>229.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8858,10 +8858,10 @@
         <v>122</v>
       </c>
       <c r="H223">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I223" t="str">
-        <v>469.0</v>
+        <v>465.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H224">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I224" t="str">
-        <v>908.0</v>
+        <v>919.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H225">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I225" t="str">
-        <v>1377.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="H226">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I226" t="str">
-        <v>2273.0</v>
+        <v>2262.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H227">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="I227" t="str">
-        <v>466.0</v>
+        <v>485.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="H228">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I228" t="str">
-        <v>1151.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H229">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="I229" t="str">
-        <v>676.0</v>
+        <v>699.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H230">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="I230" t="str">
-        <v>936.0</v>
+        <v>922.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H231">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="I231" t="str">
-        <v>453.0</v>
+        <v>490.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H232">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I232" t="str">
-        <v>267.0</v>
+        <v>265.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H233">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="I233" t="str">
-        <v>488.0</v>
+        <v>480.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H234">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I234" t="str">
-        <v>933.0</v>
+        <v>908.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H235">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="I235" t="str">
-        <v>1381.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,7 +9349,7 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="H236">
         <v>262</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="H237">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="I237" t="str">
-        <v>470.0</v>
+        <v>462.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="H238">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="I238" t="str">
-        <v>1153.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H239">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I239" t="str">
-        <v>695.0</v>
+        <v>675.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H240">
         <v>137</v>
       </c>
       <c r="I240" t="str">
-        <v>934.0</v>
+        <v>908.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H241">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="I241" t="str">
-        <v>459.0</v>
+        <v>497.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H242">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I242" t="str">
-        <v>228.0</v>
+        <v>226.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,10 +9615,10 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H243">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I243" t="str">
         <v>461.0</v>
@@ -9653,10 +9653,10 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="H244">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="I244" t="str">
         <v>937.0</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H245">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I245" t="str">
-        <v>1352.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H246">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="I246" t="str">
-        <v>2257.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H247">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I247" t="str">
-        <v>468.0</v>
+        <v>457.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H248">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="I248" t="str">
-        <v>1125.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H249">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="I249" t="str">
-        <v>721.0</v>
+        <v>688.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H250">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="I250" t="str">
-        <v>922.0</v>
+        <v>947.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="H251">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="I251" t="str">
-        <v>482.0</v>
+        <v>456.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H252">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="I252" t="str">
-        <v>253.0</v>
+        <v>264.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="H253">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I253" t="str">
-        <v>477.0</v>
+        <v>450.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,10 +10033,10 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H254">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I254" t="str">
         <v>926.0</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="H255">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="I255" t="str">
-        <v>1355.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="H256">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="I256" t="str">
-        <v>2260.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H257">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I257" t="str">
-        <v>484.0</v>
+        <v>474.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H258">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I258" t="str">
-        <v>1152.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H259">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I259" t="str">
-        <v>701.0</v>
+        <v>677.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H260">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="I260" t="str">
-        <v>900.0</v>
+        <v>918.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H261">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I261" t="str">
-        <v>482.0</v>
+        <v>480.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H262">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="I262" t="str">
-        <v>250.0</v>
+        <v>233.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10378,10 +10378,10 @@
         <v>116</v>
       </c>
       <c r="H263">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="I263" t="str">
-        <v>469.0</v>
+        <v>462.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H264">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="I264" t="str">
-        <v>918.0</v>
+        <v>937.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H265">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="I265" t="str">
-        <v>1371.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="H266">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="I266" t="str">
-        <v>2293.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H267">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="I267" t="str">
-        <v>486.0</v>
+        <v>491.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10568,10 +10568,10 @@
         <v>177</v>
       </c>
       <c r="H268">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I268" t="str">
-        <v>1172.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H269">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I269" t="str">
-        <v>686.0</v>
+        <v>714.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
+        <v>97</v>
+      </c>
+      <c r="H270">
         <v>112</v>
       </c>
-      <c r="H270">
-        <v>127</v>
-      </c>
       <c r="I270" t="str">
-        <v>941.0</v>
+        <v>924.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H271">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="I271" t="str">
-        <v>484.0</v>
+        <v>471.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H272">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I272" t="str">
-        <v>231.0</v>
+        <v>262.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H273">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="I273" t="str">
-        <v>483.0</v>
+        <v>499.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
+        <v>145</v>
+      </c>
+      <c r="H274">
         <v>158</v>
       </c>
-      <c r="H274">
-        <v>184</v>
-      </c>
       <c r="I274" t="str">
-        <v>935.0</v>
+        <v>916.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H275">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I275" t="str">
-        <v>1372.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H276">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="I276" t="str">
-        <v>2275.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H277">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I277" t="str">
-        <v>450.0</v>
+        <v>476.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10948,10 +10948,10 @@
         <v>174</v>
       </c>
       <c r="H278">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I278" t="str">
-        <v>1172.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H279">
         <v>161</v>
       </c>
       <c r="I279" t="str">
-        <v>705.0</v>
+        <v>718.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H280">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="I280" t="str">
-        <v>914.0</v>
+        <v>931.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H281">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="I281" t="str">
-        <v>457.0</v>
+        <v>486.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H282">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I282" t="str">
-        <v>261.0</v>
+        <v>230.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="H283">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I283" t="str">
-        <v>464.0</v>
+        <v>491.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H284">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="I284" t="str">
-        <v>939.0</v>
+        <v>915.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H285">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="I285" t="str">
-        <v>1357.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="H286">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I286" t="str">
-        <v>2271.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H287">
         <v>123</v>
       </c>
       <c r="I287" t="str">
-        <v>486.0</v>
+        <v>472.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="H288">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="I288" t="str">
-        <v>1130.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H289">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I289" t="str">
-        <v>675.0</v>
+        <v>724.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H290">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="I290" t="str">
-        <v>925.0</v>
+        <v>935.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H291">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I291" t="str">
-        <v>487.0</v>
+        <v>493.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H292">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="I292" t="str">
-        <v>241.0</v>
+        <v>252.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H293">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I293" t="str">
-        <v>482.0</v>
+        <v>464.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,10 +11553,10 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H294">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I294" t="str">
         <v>949.0</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H295">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="I295" t="str">
-        <v>1390.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="H296">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="I296" t="str">
-        <v>2286.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H297">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="I297" t="str">
-        <v>470.0</v>
+        <v>469.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="H298">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I298" t="str">
-        <v>1147.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="H299">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I299" t="str">
-        <v>679.0</v>
+        <v>712.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="H300">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="I300" t="str">
-        <v>938.0</v>
+        <v>924.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H301">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I301" t="str">
-        <v>472.0</v>
+        <v>491.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H2">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="I2" t="str">
-        <v>236.0</v>
+        <v>235.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H3">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="I3" t="str">
-        <v>463.0</v>
+        <v>497.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="H4">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="I4" t="str">
-        <v>946.0</v>
+        <v>941.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H5">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="I5" t="str">
-        <v>1399.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="H6">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="I6" t="str">
-        <v>2287.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H7">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I7" t="str">
-        <v>485.0</v>
+        <v>479.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H8">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I8" t="str">
-        <v>1137.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H9">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I9" t="str">
-        <v>685.0</v>
+        <v>690.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="I10" t="str">
-        <v>906.0</v>
+        <v>924.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H11">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I11" t="str">
-        <v>497.0</v>
+        <v>464.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H12">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I12" t="str">
-        <v>248.0</v>
+        <v>225.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H13">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I13" t="str">
-        <v>468.0</v>
+        <v>472.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H14">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="I14" t="str">
-        <v>906.0</v>
+        <v>947.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H15">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="I15" t="str">
-        <v>1389.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H16">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I16" t="str">
-        <v>2256.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H17">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" t="str">
-        <v>495.0</v>
+        <v>463.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="H18">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="I18" t="str">
-        <v>1174.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="H19">
         <v>171</v>
       </c>
       <c r="I19" t="str">
-        <v>715.0</v>
+        <v>697.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H20">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="I20" t="str">
-        <v>940.0</v>
+        <v>900.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H21">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="I21" t="str">
-        <v>464.0</v>
+        <v>461.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H22">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I22" t="str">
-        <v>236.0</v>
+        <v>239.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H23">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I23" t="str">
-        <v>488.0</v>
+        <v>487.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="H24">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="I24" t="str">
-        <v>941.0</v>
+        <v>903.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H25">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I25" t="str">
-        <v>1350.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H26">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="I26" t="str">
-        <v>2283.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H27">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I27" t="str">
-        <v>473.0</v>
+        <v>461.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H28">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="I28" t="str">
-        <v>1165.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H29">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I29" t="str">
-        <v>715.0</v>
+        <v>703.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H30">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I30" t="str">
-        <v>948.0</v>
+        <v>941.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H31">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="I31" t="str">
-        <v>466.0</v>
+        <v>487.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H32">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="I32" t="str">
-        <v>249.0</v>
+        <v>238.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H33">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I33" t="str">
-        <v>459.0</v>
+        <v>478.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,10 +1673,10 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="H34">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I34" t="str">
         <v>927.0</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H35">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="I35" t="str">
-        <v>1380.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H36">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I36" t="str">
-        <v>2274.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H37">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="I37" t="str">
-        <v>468.0</v>
+        <v>488.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H38">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I38" t="str">
-        <v>1153.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H39">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="I39" t="str">
-        <v>695.0</v>
+        <v>701.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H40">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="I40" t="str">
-        <v>930.0</v>
+        <v>912.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1942,10 +1942,10 @@
         <v>128</v>
       </c>
       <c r="H41">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I41" t="str">
-        <v>457.0</v>
+        <v>475.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1980,10 +1980,10 @@
         <v>106</v>
       </c>
       <c r="H42">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I42" t="str">
-        <v>251.0</v>
+        <v>229.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H43">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I43" t="str">
-        <v>451.0</v>
+        <v>461.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H44">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="I44" t="str">
-        <v>941.0</v>
+        <v>943.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H45">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="I45" t="str">
-        <v>1381.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H46">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="I46" t="str">
-        <v>2276.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H47">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="I47" t="str">
-        <v>490.0</v>
+        <v>494.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H48">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I48" t="str">
-        <v>1173.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="H49">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I49" t="str">
-        <v>701.0</v>
+        <v>697.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H50">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I50" t="str">
-        <v>928.0</v>
+        <v>938.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H51">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I51" t="str">
-        <v>492.0</v>
+        <v>470.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H52">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="I52" t="str">
-        <v>228.0</v>
+        <v>232.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H53">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I53" t="str">
-        <v>497.0</v>
+        <v>493.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H54">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I54" t="str">
-        <v>942.0</v>
+        <v>910.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H55">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="I55" t="str">
-        <v>1354.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="H56">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="I56" t="str">
-        <v>2298.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H57">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I57" t="str">
-        <v>482.0</v>
+        <v>491.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H58">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="I58" t="str">
-        <v>1156.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H59">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I59" t="str">
-        <v>721.0</v>
+        <v>680.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="H60">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I60" t="str">
-        <v>917.0</v>
+        <v>916.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H61">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I61" t="str">
-        <v>486.0</v>
+        <v>481.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H62">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I62" t="str">
-        <v>226.0</v>
+        <v>228.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H63">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="I63" t="str">
-        <v>459.0</v>
+        <v>499.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H64">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="I64" t="str">
-        <v>917.0</v>
+        <v>941.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="H65">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="I65" t="str">
-        <v>1350.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H66">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="I66" t="str">
-        <v>2297.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="H67">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I67" t="str">
-        <v>475.0</v>
+        <v>493.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H68">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I68" t="str">
-        <v>1146.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H69">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I69" t="str">
-        <v>712.0</v>
+        <v>720.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H70">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="I70" t="str">
-        <v>904.0</v>
+        <v>928.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H71">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="I71" t="str">
-        <v>450.0</v>
+        <v>492.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H72">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="I72" t="str">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H73">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="I73" t="str">
-        <v>486.0</v>
+        <v>462.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H74">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="I74" t="str">
-        <v>914.0</v>
+        <v>938.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="H75">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="I75" t="str">
-        <v>1357.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H76">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="I76" t="str">
-        <v>2283.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H77">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="I77" t="str">
-        <v>479.0</v>
+        <v>460.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="H78">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="I78" t="str">
-        <v>1128.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="H79">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="I79" t="str">
-        <v>684.0</v>
+        <v>696.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H80">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I80" t="str">
-        <v>910.0</v>
+        <v>916.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H81">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I81" t="str">
-        <v>457.0</v>
+        <v>478.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H82">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="I82" t="str">
-        <v>249.0</v>
+        <v>268.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H83">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="I83" t="str">
-        <v>465.0</v>
+        <v>488.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H84">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I84" t="str">
-        <v>936.0</v>
+        <v>947.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H85">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I85" t="str">
-        <v>1374.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H86">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="I86" t="str">
-        <v>2270.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H87">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="I87" t="str">
-        <v>487.0</v>
+        <v>496.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H88">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="I88" t="str">
-        <v>1127.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H89">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I89" t="str">
-        <v>697.0</v>
+        <v>677.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H90">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I90" t="str">
-        <v>912.0</v>
+        <v>910.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H91">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="I91" t="str">
-        <v>484.0</v>
+        <v>451.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H92">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="I92" t="str">
-        <v>274.0</v>
+        <v>272.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H93">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="I93" t="str">
-        <v>454.0</v>
+        <v>458.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H94">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I94" t="str">
-        <v>940.0</v>
+        <v>924.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3994,10 +3994,10 @@
         <v>208</v>
       </c>
       <c r="H95">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="I95" t="str">
-        <v>1365.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="H96">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I96" t="str">
-        <v>2297.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H97">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="I97" t="str">
-        <v>465.0</v>
+        <v>478.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="H98">
         <v>195</v>
       </c>
       <c r="I98" t="str">
-        <v>1134.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H99">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="I99" t="str">
-        <v>675.0</v>
+        <v>723.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H100">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I100" t="str">
-        <v>941.0</v>
+        <v>919.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H101">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="I101" t="str">
-        <v>468.0</v>
+        <v>452.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="H102">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I102" t="str">
-        <v>269.0</v>
+        <v>239.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H103">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="I103" t="str">
-        <v>458.0</v>
+        <v>491.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H104">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I104" t="str">
-        <v>919.0</v>
+        <v>948.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H105">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I105" t="str">
-        <v>1378.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H106">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="I106" t="str">
-        <v>2298.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H107">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I107" t="str">
-        <v>453.0</v>
+        <v>473.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H108">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="I108" t="str">
-        <v>1172.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,10 +4523,10 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="H109">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="I109" t="str">
         <v>682.0</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H110">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I110" t="str">
-        <v>916.0</v>
+        <v>907.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H111">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="I111" t="str">
-        <v>497.0</v>
+        <v>484.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H112">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I112" t="str">
-        <v>262.0</v>
+        <v>250.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4678,10 +4678,10 @@
         <v>115</v>
       </c>
       <c r="H113">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="I113" t="str">
-        <v>470.0</v>
+        <v>498.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H114">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I114" t="str">
-        <v>911.0</v>
+        <v>927.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H115">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="I115" t="str">
-        <v>1399.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="H116">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I116" t="str">
-        <v>2271.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H117">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I117" t="str">
-        <v>484.0</v>
+        <v>457.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="H118">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="I118" t="str">
-        <v>1144.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H119">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I119" t="str">
-        <v>711.0</v>
+        <v>686.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H120">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I120" t="str">
-        <v>914.0</v>
+        <v>944.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H121">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I121" t="str">
-        <v>460.0</v>
+        <v>470.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H122">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="I122" t="str">
-        <v>228.0</v>
+        <v>256.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H123">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="I123" t="str">
-        <v>479.0</v>
+        <v>450.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H124">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="I124" t="str">
-        <v>909.0</v>
+        <v>949.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H125">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="I125" t="str">
-        <v>1385.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
+        <v>247</v>
+      </c>
+      <c r="H126">
         <v>264</v>
       </c>
-      <c r="H126">
-        <v>279</v>
-      </c>
       <c r="I126" t="str">
-        <v>2299.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H127">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I127" t="str">
-        <v>469.0</v>
+        <v>458.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H128">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I128" t="str">
-        <v>1168.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H129">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="I129" t="str">
-        <v>697.0</v>
+        <v>710.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H130">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I130" t="str">
-        <v>923.0</v>
+        <v>938.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H131">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="I131" t="str">
-        <v>459.0</v>
+        <v>452.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H132">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="I132" t="str">
-        <v>230.0</v>
+        <v>244.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H133">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I133" t="str">
-        <v>469.0</v>
+        <v>458.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="H134">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I134" t="str">
-        <v>919.0</v>
+        <v>923.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="H135">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="I135" t="str">
-        <v>1398.0</v>
+        <v>1383.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H136">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="I136" t="str">
-        <v>2267.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H137">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I137" t="str">
-        <v>462.0</v>
+        <v>458.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H138">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="I138" t="str">
-        <v>1169.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="H139">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="I139" t="str">
-        <v>698.0</v>
+        <v>722.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H140">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I140" t="str">
-        <v>900.0</v>
+        <v>947.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H141">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="I141" t="str">
-        <v>463.0</v>
+        <v>459.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H142">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I142" t="str">
-        <v>245.0</v>
+        <v>225.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H143">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I143" t="str">
-        <v>496.0</v>
+        <v>477.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="H144">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="I144" t="str">
-        <v>918.0</v>
+        <v>911.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H145">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="I145" t="str">
-        <v>1391.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H146">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="I146" t="str">
-        <v>2289.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H147">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I147" t="str">
-        <v>495.0</v>
+        <v>465.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H148">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I148" t="str">
-        <v>1146.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H149">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I149" t="str">
-        <v>685.0</v>
+        <v>676.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H150">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I150" t="str">
-        <v>938.0</v>
+        <v>900.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H151">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="I151" t="str">
-        <v>483.0</v>
+        <v>480.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="H152">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="I152" t="str">
-        <v>241.0</v>
+        <v>268.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H153">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I153" t="str">
-        <v>465.0</v>
+        <v>458.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H154">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="I154" t="str">
-        <v>922.0</v>
+        <v>906.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H155">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="I155" t="str">
-        <v>1371.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
+        <v>246</v>
+      </c>
+      <c r="H156">
         <v>253</v>
       </c>
-      <c r="H156">
-        <v>254</v>
-      </c>
       <c r="I156" t="str">
-        <v>2253.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H157">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I157" t="str">
-        <v>466.0</v>
+        <v>476.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H158">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I158" t="str">
-        <v>1166.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H159">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I159" t="str">
-        <v>680.0</v>
+        <v>698.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H160">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="I160" t="str">
-        <v>906.0</v>
+        <v>916.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="H161">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="I161" t="str">
-        <v>495.0</v>
+        <v>496.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H162">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="I162" t="str">
-        <v>254.0</v>
+        <v>260.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H163">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="I163" t="str">
-        <v>452.0</v>
+        <v>451.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H164">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="I164" t="str">
-        <v>939.0</v>
+        <v>947.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H165">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I165" t="str">
-        <v>1362.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H166">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="I166" t="str">
-        <v>2267.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H167">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="I167" t="str">
-        <v>469.0</v>
+        <v>464.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H168">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="I168" t="str">
-        <v>1131.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H169">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="I169" t="str">
-        <v>707.0</v>
+        <v>692.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H170">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="I170" t="str">
-        <v>918.0</v>
+        <v>929.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H171">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I171" t="str">
-        <v>465.0</v>
+        <v>463.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H172">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="I172" t="str">
-        <v>251.0</v>
+        <v>266.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H173">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="I173" t="str">
-        <v>454.0</v>
+        <v>487.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H174">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="I174" t="str">
-        <v>927.0</v>
+        <v>939.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="H175">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I175" t="str">
-        <v>1376.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="H176">
-        <v>298</v>
+        <v>255</v>
       </c>
       <c r="I176" t="str">
-        <v>2272.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H177">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I177" t="str">
-        <v>494.0</v>
+        <v>495.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H178">
         <v>206</v>
       </c>
       <c r="I178" t="str">
-        <v>1155.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="H179">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="I179" t="str">
-        <v>692.0</v>
+        <v>703.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H180">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="I180" t="str">
-        <v>906.0</v>
+        <v>921.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H181">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I181" t="str">
-        <v>462.0</v>
+        <v>452.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H182">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="I182" t="str">
-        <v>269.0</v>
+        <v>235.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H183">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="I183" t="str">
-        <v>483.0</v>
+        <v>475.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H184">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I184" t="str">
-        <v>913.0</v>
+        <v>901.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="H185">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I185" t="str">
-        <v>1371.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H186">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I186" t="str">
-        <v>2254.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H187">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I187" t="str">
-        <v>485.0</v>
+        <v>477.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H188">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I188" t="str">
-        <v>1141.0</v>
+        <v>1134.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="H189">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I189" t="str">
-        <v>691.0</v>
+        <v>723.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H190">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I190" t="str">
-        <v>918.0</v>
+        <v>935.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H191">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I191" t="str">
-        <v>478.0</v>
+        <v>476.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H192">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I192" t="str">
-        <v>271.0</v>
+        <v>259.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="H193">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I193" t="str">
-        <v>479.0</v>
+        <v>470.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H194">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I194" t="str">
-        <v>900.0</v>
+        <v>902.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="H195">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="I195" t="str">
-        <v>1365.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H196">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I196" t="str">
-        <v>2264.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H197">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="I197" t="str">
-        <v>490.0</v>
+        <v>488.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="H198">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I198" t="str">
-        <v>1144.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H199">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I199" t="str">
-        <v>723.0</v>
+        <v>699.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H200">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I200" t="str">
-        <v>936.0</v>
+        <v>939.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H201">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="I201" t="str">
-        <v>466.0</v>
+        <v>464.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="H202">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I202" t="str">
-        <v>250.0</v>
+        <v>228.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,10 +8095,10 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H203">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="I203" t="str">
         <v>491.0</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="H204">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="I204" t="str">
-        <v>902.0</v>
+        <v>906.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
+        <v>208</v>
+      </c>
+      <c r="H205">
         <v>209</v>
       </c>
-      <c r="H205">
-        <v>230</v>
-      </c>
       <c r="I205" t="str">
-        <v>1370.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="H206">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="I206" t="str">
-        <v>2279.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H207">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I207" t="str">
-        <v>490.0</v>
+        <v>460.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H208">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="I208" t="str">
-        <v>1172.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="H209">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I209" t="str">
-        <v>723.0</v>
+        <v>681.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H210">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I210" t="str">
-        <v>945.0</v>
+        <v>949.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H211">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I211" t="str">
-        <v>492.0</v>
+        <v>451.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H212">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I212" t="str">
-        <v>238.0</v>
+        <v>227.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H213">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="I213" t="str">
-        <v>469.0</v>
+        <v>457.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H214">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="I214" t="str">
-        <v>911.0</v>
+        <v>918.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H215">
         <v>213</v>
       </c>
       <c r="I215" t="str">
-        <v>1379.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H216">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="I216" t="str">
-        <v>2290.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="H217">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="I217" t="str">
-        <v>477.0</v>
+        <v>476.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H218">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I218" t="str">
-        <v>1169.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="H219">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I219" t="str">
-        <v>683.0</v>
+        <v>721.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H220">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I220" t="str">
-        <v>919.0</v>
+        <v>933.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H221">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I221" t="str">
-        <v>487.0</v>
+        <v>481.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H222">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I222" t="str">
-        <v>229.0</v>
+        <v>247.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H223">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I223" t="str">
-        <v>465.0</v>
+        <v>469.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="H224">
         <v>180</v>
       </c>
       <c r="I224" t="str">
-        <v>919.0</v>
+        <v>946.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H225">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="I225" t="str">
-        <v>1355.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="H226">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="I226" t="str">
-        <v>2262.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H227">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="I227" t="str">
-        <v>485.0</v>
+        <v>457.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H228">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="I228" t="str">
-        <v>1146.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="H229">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="I229" t="str">
-        <v>699.0</v>
+        <v>714.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H230">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I230" t="str">
-        <v>922.0</v>
+        <v>936.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9162,10 +9162,10 @@
         <v>141</v>
       </c>
       <c r="H231">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I231" t="str">
-        <v>490.0</v>
+        <v>488.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H232">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I232" t="str">
-        <v>265.0</v>
+        <v>264.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H233">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I233" t="str">
-        <v>480.0</v>
+        <v>492.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H234">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="I234" t="str">
-        <v>908.0</v>
+        <v>943.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="H235">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="I235" t="str">
-        <v>1354.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H236">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="I236" t="str">
-        <v>2262.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="H237">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="I237" t="str">
-        <v>462.0</v>
+        <v>488.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H238">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I238" t="str">
-        <v>1143.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="H239">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I239" t="str">
-        <v>675.0</v>
+        <v>703.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H240">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I240" t="str">
-        <v>908.0</v>
+        <v>917.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H241">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="I241" t="str">
-        <v>497.0</v>
+        <v>461.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H242">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I242" t="str">
-        <v>226.0</v>
+        <v>270.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H243">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I243" t="str">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="H244">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="I244" t="str">
-        <v>937.0</v>
+        <v>938.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H245">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="I245" t="str">
-        <v>1399.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H246">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="I246" t="str">
-        <v>2296.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H247">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I247" t="str">
-        <v>457.0</v>
+        <v>485.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H248">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="I248" t="str">
-        <v>1151.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="H249">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="I249" t="str">
-        <v>688.0</v>
+        <v>719.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="H250">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="I250" t="str">
-        <v>947.0</v>
+        <v>906.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H251">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="I251" t="str">
-        <v>456.0</v>
+        <v>475.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H252">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I252" t="str">
-        <v>264.0</v>
+        <v>271.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="H253">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="I253" t="str">
-        <v>450.0</v>
+        <v>466.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
+        <v>145</v>
+      </c>
+      <c r="H254">
         <v>149</v>
       </c>
-      <c r="H254">
-        <v>158</v>
-      </c>
       <c r="I254" t="str">
-        <v>926.0</v>
+        <v>944.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="H255">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="I255" t="str">
-        <v>1380.0</v>
+        <v>1383.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H256">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="I256" t="str">
-        <v>2282.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H257">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I257" t="str">
-        <v>474.0</v>
+        <v>452.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H258">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="I258" t="str">
-        <v>1174.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H259">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="I259" t="str">
-        <v>677.0</v>
+        <v>718.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H260">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I260" t="str">
-        <v>918.0</v>
+        <v>931.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="H261">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="I261" t="str">
-        <v>480.0</v>
+        <v>471.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H262">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I262" t="str">
-        <v>233.0</v>
+        <v>264.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H263">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I263" t="str">
-        <v>462.0</v>
+        <v>485.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="H264">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="I264" t="str">
-        <v>937.0</v>
+        <v>943.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H265">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="I265" t="str">
-        <v>1387.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H266">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I266" t="str">
-        <v>2283.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="H267">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="I267" t="str">
-        <v>491.0</v>
+        <v>481.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="H268">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I268" t="str">
-        <v>1165.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H269">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I269" t="str">
-        <v>714.0</v>
+        <v>700.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="H270">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="I270" t="str">
-        <v>924.0</v>
+        <v>909.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H271">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I271" t="str">
-        <v>471.0</v>
+        <v>493.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H272">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="I272" t="str">
-        <v>262.0</v>
+        <v>248.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H273">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="I273" t="str">
-        <v>499.0</v>
+        <v>467.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H274">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="I274" t="str">
-        <v>916.0</v>
+        <v>901.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H275">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="I275" t="str">
-        <v>1390.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H276">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I276" t="str">
-        <v>2252.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H277">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="I277" t="str">
-        <v>476.0</v>
+        <v>491.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H278">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="I278" t="str">
-        <v>1158.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H279">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="I279" t="str">
-        <v>718.0</v>
+        <v>685.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H280">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I280" t="str">
-        <v>931.0</v>
+        <v>941.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H281">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I281" t="str">
-        <v>486.0</v>
+        <v>467.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H282">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I282" t="str">
-        <v>230.0</v>
+        <v>258.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="H283">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="I283" t="str">
-        <v>491.0</v>
+        <v>470.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H284">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I284" t="str">
-        <v>915.0</v>
+        <v>942.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="H285">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="I285" t="str">
-        <v>1366.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H286">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="I286" t="str">
-        <v>2295.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H287">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="I287" t="str">
-        <v>472.0</v>
+        <v>455.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H288">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I288" t="str">
-        <v>1132.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H289">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I289" t="str">
-        <v>724.0</v>
+        <v>693.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H290">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="I290" t="str">
-        <v>935.0</v>
+        <v>907.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H291">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="I291" t="str">
-        <v>493.0</v>
+        <v>462.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="H292">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="I292" t="str">
-        <v>252.0</v>
+        <v>247.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H293">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I293" t="str">
-        <v>464.0</v>
+        <v>493.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="H294">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I294" t="str">
-        <v>949.0</v>
+        <v>903.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H295">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="I295" t="str">
-        <v>1392.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="H296">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="I296" t="str">
-        <v>2290.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11670,10 +11670,10 @@
         <v>119</v>
       </c>
       <c r="H297">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="I297" t="str">
-        <v>469.0</v>
+        <v>499.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="H298">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I298" t="str">
-        <v>1164.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H299">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I299" t="str">
-        <v>712.0</v>
+        <v>698.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="H300">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="I300" t="str">
-        <v>924.0</v>
+        <v>927.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H301">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I301" t="str">
-        <v>491.0</v>
+        <v>497.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H2">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I2" t="str">
-        <v>235.0</v>
+        <v>253.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H3">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="I3" t="str">
-        <v>497.0</v>
+        <v>482.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H4">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I4" t="str">
-        <v>941.0</v>
+        <v>948.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H5">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="I5" t="str">
-        <v>1352.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H6">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="I6" t="str">
-        <v>2257.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H7">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I7" t="str">
-        <v>479.0</v>
+        <v>453.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H8">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I8" t="str">
-        <v>1135.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H9">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I9" t="str">
-        <v>690.0</v>
+        <v>680.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I10" t="str">
-        <v>924.0</v>
+        <v>940.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,10 +799,10 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H11">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I11" t="str">
         <v>464.0</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H12">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="I12" t="str">
-        <v>225.0</v>
+        <v>272.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H13">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I13" t="str">
-        <v>472.0</v>
+        <v>499.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,10 +913,10 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H14">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I14" t="str">
         <v>947.0</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H15">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="I15" t="str">
-        <v>1376.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H16">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="I16" t="str">
-        <v>2255.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H17">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="I17" t="str">
-        <v>463.0</v>
+        <v>481.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H18">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="I18" t="str">
-        <v>1149.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H19">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="I19" t="str">
-        <v>697.0</v>
+        <v>689.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H20">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="I20" t="str">
-        <v>900.0</v>
+        <v>932.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H21">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="I21" t="str">
-        <v>461.0</v>
+        <v>494.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H22">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I22" t="str">
-        <v>239.0</v>
+        <v>249.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H23">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="I23" t="str">
-        <v>487.0</v>
+        <v>474.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="H24">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I24" t="str">
-        <v>903.0</v>
+        <v>948.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H25">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I25" t="str">
-        <v>1376.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="H26">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="I26" t="str">
-        <v>2293.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="H27">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="I27" t="str">
-        <v>461.0</v>
+        <v>491.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H28">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I28" t="str">
-        <v>1163.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H29">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="I29" t="str">
-        <v>703.0</v>
+        <v>716.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H30">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I30" t="str">
-        <v>941.0</v>
+        <v>933.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H31">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="I31" t="str">
-        <v>487.0</v>
+        <v>481.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="H32">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I32" t="str">
-        <v>238.0</v>
+        <v>257.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H33">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I33" t="str">
-        <v>478.0</v>
+        <v>473.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H34">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I34" t="str">
-        <v>927.0</v>
+        <v>901.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H35">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="I35" t="str">
-        <v>1362.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H36">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I36" t="str">
-        <v>2253.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H37">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="I37" t="str">
-        <v>488.0</v>
+        <v>459.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="H38">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I38" t="str">
-        <v>1146.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1866,10 +1866,10 @@
         <v>148</v>
       </c>
       <c r="H39">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="I39" t="str">
-        <v>701.0</v>
+        <v>682.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1904,10 +1904,10 @@
         <v>103</v>
       </c>
       <c r="H40">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I40" t="str">
-        <v>912.0</v>
+        <v>903.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H41">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="I41" t="str">
-        <v>475.0</v>
+        <v>451.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H42">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="I42" t="str">
-        <v>229.0</v>
+        <v>254.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H43">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I43" t="str">
-        <v>461.0</v>
+        <v>464.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H44">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="I44" t="str">
-        <v>943.0</v>
+        <v>926.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H45">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I45" t="str">
-        <v>1357.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2132,10 +2132,10 @@
         <v>255</v>
       </c>
       <c r="H46">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I46" t="str">
-        <v>2263.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H47">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I47" t="str">
-        <v>494.0</v>
+        <v>497.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H48">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" t="str">
-        <v>1129.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H49">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="I49" t="str">
-        <v>697.0</v>
+        <v>716.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H50">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="I50" t="str">
-        <v>938.0</v>
+        <v>916.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H51">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="I51" t="str">
-        <v>470.0</v>
+        <v>467.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H52">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="I52" t="str">
-        <v>232.0</v>
+        <v>265.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H53">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I53" t="str">
-        <v>493.0</v>
+        <v>495.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H54">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="I54" t="str">
-        <v>910.0</v>
+        <v>942.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H55">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="I55" t="str">
-        <v>1379.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H56">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="I56" t="str">
-        <v>2291.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H57">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I57" t="str">
-        <v>491.0</v>
+        <v>477.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="H58">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="I58" t="str">
-        <v>1143.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H59">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I59" t="str">
-        <v>680.0</v>
+        <v>712.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="H60">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="I60" t="str">
-        <v>916.0</v>
+        <v>926.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="H61">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="I61" t="str">
-        <v>481.0</v>
+        <v>499.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H62">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="I62" t="str">
-        <v>228.0</v>
+        <v>236.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H63">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I63" t="str">
-        <v>499.0</v>
+        <v>472.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H64">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="I64" t="str">
-        <v>941.0</v>
+        <v>944.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="H65">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="I65" t="str">
-        <v>1352.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H66">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I66" t="str">
-        <v>2281.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H67">
         <v>132</v>
       </c>
       <c r="I67" t="str">
-        <v>493.0</v>
+        <v>453.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="H68">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="I68" t="str">
-        <v>1153.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H69">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I69" t="str">
-        <v>720.0</v>
+        <v>698.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H70">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="I70" t="str">
-        <v>928.0</v>
+        <v>947.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H71">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I71" t="str">
-        <v>492.0</v>
+        <v>461.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H72">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="I72" t="str">
-        <v>254.0</v>
+        <v>236.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H73">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I73" t="str">
-        <v>462.0</v>
+        <v>485.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="H74">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="I74" t="str">
-        <v>938.0</v>
+        <v>927.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H75">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I75" t="str">
-        <v>1391.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H76">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I76" t="str">
-        <v>2292.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H77">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="I77" t="str">
-        <v>460.0</v>
+        <v>465.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H78">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I78" t="str">
-        <v>1167.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="H79">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="I79" t="str">
-        <v>696.0</v>
+        <v>710.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="H80">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="I80" t="str">
-        <v>916.0</v>
+        <v>948.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H81">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="I81" t="str">
-        <v>478.0</v>
+        <v>465.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H82">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="I82" t="str">
-        <v>268.0</v>
+        <v>265.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="H83">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I83" t="str">
-        <v>488.0</v>
+        <v>491.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H84">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="I84" t="str">
-        <v>947.0</v>
+        <v>909.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3614,10 +3614,10 @@
         <v>207</v>
       </c>
       <c r="H85">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I85" t="str">
-        <v>1372.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H86">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="I86" t="str">
-        <v>2260.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H87">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="I87" t="str">
-        <v>496.0</v>
+        <v>463.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H88">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="I88" t="str">
-        <v>1146.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H89">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I89" t="str">
-        <v>677.0</v>
+        <v>686.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H90">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="I90" t="str">
-        <v>910.0</v>
+        <v>917.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H91">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I91" t="str">
-        <v>451.0</v>
+        <v>463.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H92">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="I92" t="str">
-        <v>272.0</v>
+        <v>252.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H93">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="I93" t="str">
-        <v>458.0</v>
+        <v>491.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H94">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="I94" t="str">
-        <v>924.0</v>
+        <v>932.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H95">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="I95" t="str">
-        <v>1386.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H96">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I96" t="str">
-        <v>2265.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4070,10 +4070,10 @@
         <v>121</v>
       </c>
       <c r="H97">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="I97" t="str">
-        <v>478.0</v>
+        <v>452.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="H98">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="I98" t="str">
-        <v>1170.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="H99">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I99" t="str">
-        <v>723.0</v>
+        <v>691.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="H100">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I100" t="str">
-        <v>919.0</v>
+        <v>949.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H101">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I101" t="str">
-        <v>452.0</v>
+        <v>478.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H102">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I102" t="str">
-        <v>239.0</v>
+        <v>272.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H103">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I103" t="str">
-        <v>491.0</v>
+        <v>494.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H104">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="I104" t="str">
-        <v>948.0</v>
+        <v>917.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H105">
         <v>232</v>
       </c>
       <c r="I105" t="str">
-        <v>1392.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H106">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="I106" t="str">
-        <v>2281.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H107">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="I107" t="str">
-        <v>473.0</v>
+        <v>485.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="H108">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I108" t="str">
-        <v>1149.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H109">
-        <v>132</v>
+        <v>183</v>
       </c>
       <c r="I109" t="str">
-        <v>682.0</v>
+        <v>684.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="H110">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I110" t="str">
-        <v>907.0</v>
+        <v>947.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H111">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="I111" t="str">
-        <v>484.0</v>
+        <v>497.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H112">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="I112" t="str">
-        <v>250.0</v>
+        <v>258.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4678,10 +4678,10 @@
         <v>115</v>
       </c>
       <c r="H113">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="I113" t="str">
-        <v>498.0</v>
+        <v>477.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H114">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I114" t="str">
-        <v>927.0</v>
+        <v>945.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H115">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="I115" t="str">
-        <v>1376.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4792,10 +4792,10 @@
         <v>244</v>
       </c>
       <c r="H116">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="I116" t="str">
-        <v>2257.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H117">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="I117" t="str">
-        <v>457.0</v>
+        <v>464.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H118">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I118" t="str">
-        <v>1156.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H119">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I119" t="str">
-        <v>686.0</v>
+        <v>705.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H120">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="I120" t="str">
-        <v>944.0</v>
+        <v>932.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="H121">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="I121" t="str">
-        <v>470.0</v>
+        <v>499.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H122">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I122" t="str">
-        <v>256.0</v>
+        <v>260.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H123">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I123" t="str">
-        <v>450.0</v>
+        <v>453.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H124">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="I124" t="str">
-        <v>949.0</v>
+        <v>926.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="H125">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="I125" t="str">
-        <v>1361.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="H126">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I126" t="str">
-        <v>2257.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H127">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="I127" t="str">
-        <v>458.0</v>
+        <v>497.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H128">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="I128" t="str">
-        <v>1138.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H129">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I129" t="str">
-        <v>710.0</v>
+        <v>720.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="H130">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I130" t="str">
-        <v>938.0</v>
+        <v>929.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H131">
         <v>145</v>
       </c>
       <c r="I131" t="str">
-        <v>452.0</v>
+        <v>475.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H132">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="I132" t="str">
-        <v>244.0</v>
+        <v>274.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H133">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="I133" t="str">
-        <v>458.0</v>
+        <v>468.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H134">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="I134" t="str">
-        <v>923.0</v>
+        <v>944.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H135">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="I135" t="str">
-        <v>1383.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H136">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="I136" t="str">
-        <v>2261.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H137">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I137" t="str">
-        <v>458.0</v>
+        <v>455.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H138">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I138" t="str">
-        <v>1135.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H139">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I139" t="str">
-        <v>722.0</v>
+        <v>719.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H140">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I140" t="str">
-        <v>947.0</v>
+        <v>926.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="H141">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I141" t="str">
-        <v>459.0</v>
+        <v>475.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H142">
         <v>124</v>
       </c>
       <c r="I142" t="str">
-        <v>225.0</v>
+        <v>252.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H143">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="I143" t="str">
-        <v>477.0</v>
+        <v>476.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="H144">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="I144" t="str">
-        <v>911.0</v>
+        <v>905.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="H145">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="I145" t="str">
-        <v>1353.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H146">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="I146" t="str">
-        <v>2290.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H147">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="I147" t="str">
-        <v>465.0</v>
+        <v>497.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H148">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="I148" t="str">
-        <v>1153.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H149">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I149" t="str">
-        <v>676.0</v>
+        <v>678.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H150">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I150" t="str">
-        <v>900.0</v>
+        <v>938.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H151">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="I151" t="str">
-        <v>480.0</v>
+        <v>494.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H152">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="I152" t="str">
-        <v>268.0</v>
+        <v>235.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H153">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I153" t="str">
-        <v>458.0</v>
+        <v>495.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H154">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="I154" t="str">
-        <v>906.0</v>
+        <v>920.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H155">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I155" t="str">
-        <v>1394.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H156">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I156" t="str">
-        <v>2268.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H157">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="I157" t="str">
-        <v>476.0</v>
+        <v>486.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H158">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="I158" t="str">
-        <v>1157.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H159">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I159" t="str">
-        <v>698.0</v>
+        <v>682.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H160">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I160" t="str">
-        <v>916.0</v>
+        <v>930.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H161">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I161" t="str">
-        <v>496.0</v>
+        <v>465.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,10 +6537,10 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="H162">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I162" t="str">
         <v>260.0</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H163">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I163" t="str">
-        <v>451.0</v>
+        <v>485.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H164">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="I164" t="str">
-        <v>947.0</v>
+        <v>909.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H165">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I165" t="str">
-        <v>1365.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H166">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I166" t="str">
-        <v>2272.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H167">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="I167" t="str">
-        <v>464.0</v>
+        <v>498.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H168">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I168" t="str">
-        <v>1155.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H169">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I169" t="str">
-        <v>692.0</v>
+        <v>701.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="H170">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I170" t="str">
-        <v>929.0</v>
+        <v>908.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H171">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="I171" t="str">
-        <v>463.0</v>
+        <v>489.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H172">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I172" t="str">
-        <v>266.0</v>
+        <v>230.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H173">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I173" t="str">
-        <v>487.0</v>
+        <v>482.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H174">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="I174" t="str">
-        <v>939.0</v>
+        <v>903.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H175">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="I175" t="str">
-        <v>1391.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7072,10 +7072,10 @@
         <v>247</v>
       </c>
       <c r="H176">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="I176" t="str">
-        <v>2287.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H177">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="I177" t="str">
-        <v>495.0</v>
+        <v>490.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H178">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I178" t="str">
-        <v>1168.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H179">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="I179" t="str">
-        <v>703.0</v>
+        <v>701.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H180">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="I180" t="str">
-        <v>921.0</v>
+        <v>903.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H181">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I181" t="str">
-        <v>452.0</v>
+        <v>499.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="H182">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I182" t="str">
-        <v>235.0</v>
+        <v>251.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H183">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="I183" t="str">
-        <v>475.0</v>
+        <v>498.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="H184">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="I184" t="str">
-        <v>901.0</v>
+        <v>917.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="H185">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="I185" t="str">
-        <v>1375.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H186">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I186" t="str">
-        <v>2288.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H187">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I187" t="str">
-        <v>477.0</v>
+        <v>479.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H188">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I188" t="str">
-        <v>1134.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H189">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="I189" t="str">
-        <v>723.0</v>
+        <v>719.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H190">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I190" t="str">
-        <v>935.0</v>
+        <v>946.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H191">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I191" t="str">
-        <v>476.0</v>
+        <v>474.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H192">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I192" t="str">
-        <v>259.0</v>
+        <v>242.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="H193">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="I193" t="str">
-        <v>470.0</v>
+        <v>491.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H194">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I194" t="str">
-        <v>902.0</v>
+        <v>906.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="H195">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="I195" t="str">
-        <v>1367.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H196">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="I196" t="str">
-        <v>2252.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H197">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I197" t="str">
-        <v>488.0</v>
+        <v>452.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
+        <v>167</v>
+      </c>
+      <c r="H198">
         <v>169</v>
       </c>
-      <c r="H198">
-        <v>197</v>
-      </c>
       <c r="I198" t="str">
-        <v>1141.0</v>
+        <v>1134.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H199">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I199" t="str">
-        <v>699.0</v>
+        <v>688.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H200">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="I200" t="str">
-        <v>939.0</v>
+        <v>905.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H201">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="I201" t="str">
-        <v>464.0</v>
+        <v>491.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H202">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="I202" t="str">
-        <v>228.0</v>
+        <v>249.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="H203">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="I203" t="str">
-        <v>491.0</v>
+        <v>455.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H204">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="I204" t="str">
-        <v>906.0</v>
+        <v>923.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H205">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I205" t="str">
-        <v>1384.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H206">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I206" t="str">
-        <v>2261.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H207">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I207" t="str">
-        <v>460.0</v>
+        <v>479.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H208">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="I208" t="str">
-        <v>1159.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H209">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I209" t="str">
-        <v>681.0</v>
+        <v>677.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H210">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="I210" t="str">
-        <v>949.0</v>
+        <v>913.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H211">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I211" t="str">
-        <v>451.0</v>
+        <v>468.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H212">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="I212" t="str">
-        <v>227.0</v>
+        <v>225.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H213">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="I213" t="str">
-        <v>457.0</v>
+        <v>478.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H214">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I214" t="str">
-        <v>918.0</v>
+        <v>938.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="H215">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="I215" t="str">
-        <v>1366.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H216">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="I216" t="str">
-        <v>2298.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H217">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="I217" t="str">
-        <v>476.0</v>
+        <v>477.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H218">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="I218" t="str">
-        <v>1152.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H219">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="I219" t="str">
-        <v>721.0</v>
+        <v>709.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H220">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="I220" t="str">
-        <v>933.0</v>
+        <v>923.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H221">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="I221" t="str">
-        <v>481.0</v>
+        <v>490.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H222">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="I222" t="str">
-        <v>247.0</v>
+        <v>236.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,10 +8855,10 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H223">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I223" t="str">
         <v>469.0</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H224">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I224" t="str">
-        <v>946.0</v>
+        <v>930.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="H225">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I225" t="str">
-        <v>1384.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H226">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="I226" t="str">
-        <v>2299.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H227">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I227" t="str">
-        <v>457.0</v>
+        <v>488.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H228">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I228" t="str">
-        <v>1171.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H229">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I229" t="str">
-        <v>714.0</v>
+        <v>699.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H230">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="I230" t="str">
-        <v>936.0</v>
+        <v>914.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H231">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="I231" t="str">
-        <v>488.0</v>
+        <v>451.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H232">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="I232" t="str">
-        <v>264.0</v>
+        <v>250.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H233">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="I233" t="str">
-        <v>492.0</v>
+        <v>465.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H234">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I234" t="str">
-        <v>943.0</v>
+        <v>912.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="H235">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I235" t="str">
-        <v>1352.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="H236">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="I236" t="str">
-        <v>2266.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H237">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I237" t="str">
-        <v>488.0</v>
+        <v>464.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="H238">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="I238" t="str">
-        <v>1130.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="H239">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="I239" t="str">
-        <v>703.0</v>
+        <v>677.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="H240">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I240" t="str">
-        <v>917.0</v>
+        <v>941.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H241">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="I241" t="str">
-        <v>461.0</v>
+        <v>486.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="H242">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="I242" t="str">
-        <v>270.0</v>
+        <v>247.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H243">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="I243" t="str">
-        <v>463.0</v>
+        <v>473.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="H244">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="I244" t="str">
-        <v>938.0</v>
+        <v>907.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H245">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I245" t="str">
-        <v>1352.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H246">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="I246" t="str">
-        <v>2285.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H247">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I247" t="str">
-        <v>485.0</v>
+        <v>480.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H248">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="I248" t="str">
-        <v>1142.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H249">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="I249" t="str">
-        <v>719.0</v>
+        <v>689.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H250">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="I250" t="str">
-        <v>906.0</v>
+        <v>932.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H251">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I251" t="str">
-        <v>475.0</v>
+        <v>456.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H252">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="I252" t="str">
-        <v>271.0</v>
+        <v>246.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H253">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="I253" t="str">
-        <v>466.0</v>
+        <v>460.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,10 +10033,10 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H254">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I254" t="str">
         <v>944.0</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="H255">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="I255" t="str">
-        <v>1383.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="H256">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="I256" t="str">
-        <v>2293.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H257">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I257" t="str">
-        <v>452.0</v>
+        <v>470.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="H258">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="I258" t="str">
-        <v>1161.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H259">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="I259" t="str">
-        <v>718.0</v>
+        <v>700.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H260">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="I260" t="str">
-        <v>931.0</v>
+        <v>932.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="H261">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="I261" t="str">
-        <v>471.0</v>
+        <v>468.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H262">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I262" t="str">
-        <v>264.0</v>
+        <v>247.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H263">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I263" t="str">
-        <v>485.0</v>
+        <v>494.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H264">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I264" t="str">
-        <v>943.0</v>
+        <v>939.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,10 +10451,10 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H265">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I265" t="str">
         <v>1371.0</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="H266">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="I266" t="str">
-        <v>2294.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="H267">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="I267" t="str">
-        <v>481.0</v>
+        <v>492.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H268">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I268" t="str">
-        <v>1150.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H269">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I269" t="str">
-        <v>700.0</v>
+        <v>722.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H270">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I270" t="str">
-        <v>909.0</v>
+        <v>937.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H271">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="I271" t="str">
-        <v>493.0</v>
+        <v>466.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H272">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="I272" t="str">
-        <v>248.0</v>
+        <v>238.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10758,10 +10758,10 @@
         <v>123</v>
       </c>
       <c r="H273">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I273" t="str">
-        <v>467.0</v>
+        <v>472.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H274">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="I274" t="str">
-        <v>901.0</v>
+        <v>922.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="H275">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="I275" t="str">
-        <v>1379.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H276">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I276" t="str">
-        <v>2295.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H277">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="I277" t="str">
-        <v>491.0</v>
+        <v>497.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H278">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="I278" t="str">
-        <v>1126.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="H279">
         <v>169</v>
       </c>
       <c r="I279" t="str">
-        <v>685.0</v>
+        <v>682.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H280">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="I280" t="str">
-        <v>941.0</v>
+        <v>912.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H281">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I281" t="str">
-        <v>467.0</v>
+        <v>463.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H282">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I282" t="str">
-        <v>258.0</v>
+        <v>270.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H283">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I283" t="str">
-        <v>470.0</v>
+        <v>457.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H284">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="I284" t="str">
-        <v>942.0</v>
+        <v>922.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="H285">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I285" t="str">
-        <v>1372.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H286">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I286" t="str">
-        <v>2256.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H287">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I287" t="str">
-        <v>455.0</v>
+        <v>457.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H288">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="I288" t="str">
-        <v>1154.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="H289">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="I289" t="str">
-        <v>693.0</v>
+        <v>719.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H290">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="I290" t="str">
-        <v>907.0</v>
+        <v>921.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H291">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I291" t="str">
-        <v>462.0</v>
+        <v>472.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H292">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I292" t="str">
-        <v>247.0</v>
+        <v>225.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11518,10 +11518,10 @@
         <v>114</v>
       </c>
       <c r="H293">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I293" t="str">
-        <v>493.0</v>
+        <v>470.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="H294">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I294" t="str">
-        <v>903.0</v>
+        <v>936.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="H295">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="I295" t="str">
-        <v>1362.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H296">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I296" t="str">
-        <v>2274.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H297">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="I297" t="str">
-        <v>499.0</v>
+        <v>451.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H298">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="I298" t="str">
-        <v>1157.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="H299">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I299" t="str">
-        <v>698.0</v>
+        <v>702.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H300">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="I300" t="str">
-        <v>927.0</v>
+        <v>915.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H301">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="I301" t="str">
-        <v>497.0</v>
+        <v>481.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H2">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I2" t="str">
-        <v>253.0</v>
+        <v>272.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H3">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="I3" t="str">
-        <v>482.0</v>
+        <v>466.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="H4">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I4" t="str">
-        <v>948.0</v>
+        <v>930.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H5">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="I5" t="str">
-        <v>1350.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="H6">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="I6" t="str">
-        <v>2250.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H7">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I7" t="str">
-        <v>453.0</v>
+        <v>463.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H8">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="I8" t="str">
-        <v>1151.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H9">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I9" t="str">
-        <v>680.0</v>
+        <v>685.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="H10">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I10" t="str">
-        <v>940.0</v>
+        <v>902.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H11">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I11" t="str">
-        <v>464.0</v>
+        <v>476.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H12">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="I12" t="str">
-        <v>272.0</v>
+        <v>231.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H13">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I13" t="str">
-        <v>499.0</v>
+        <v>458.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H14">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="I14" t="str">
-        <v>947.0</v>
+        <v>939.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H15">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="I15" t="str">
-        <v>1367.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H16">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="I16" t="str">
-        <v>2297.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H17">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I17" t="str">
-        <v>481.0</v>
+        <v>492.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="H18">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="I18" t="str">
-        <v>1146.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H19">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="I19" t="str">
-        <v>689.0</v>
+        <v>716.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H20">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I20" t="str">
-        <v>932.0</v>
+        <v>924.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="H21">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="I21" t="str">
-        <v>494.0</v>
+        <v>455.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I22" t="str">
-        <v>249.0</v>
+        <v>230.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H23">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I23" t="str">
-        <v>474.0</v>
+        <v>491.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H24">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I24" t="str">
-        <v>948.0</v>
+        <v>900.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H25">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I25" t="str">
-        <v>1381.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="H26">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="I26" t="str">
-        <v>2251.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H27">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="I27" t="str">
-        <v>491.0</v>
+        <v>482.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H28">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="I28" t="str">
-        <v>1139.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H29">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I29" t="str">
-        <v>716.0</v>
+        <v>699.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H30">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I30" t="str">
-        <v>933.0</v>
+        <v>949.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H31">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I31" t="str">
-        <v>481.0</v>
+        <v>486.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="H32">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="I32" t="str">
-        <v>257.0</v>
+        <v>266.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H33">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I33" t="str">
-        <v>473.0</v>
+        <v>493.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H34">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="I34" t="str">
-        <v>901.0</v>
+        <v>933.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H35">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="I35" t="str">
-        <v>1399.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H36">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="I36" t="str">
-        <v>2269.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="H37">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="I37" t="str">
-        <v>459.0</v>
+        <v>498.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H38">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="I38" t="str">
-        <v>1174.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H39">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="I39" t="str">
-        <v>682.0</v>
+        <v>712.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H40">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I40" t="str">
-        <v>903.0</v>
+        <v>924.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H41">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="I41" t="str">
-        <v>451.0</v>
+        <v>497.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H42">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I42" t="str">
-        <v>254.0</v>
+        <v>250.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H43">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I43" t="str">
-        <v>464.0</v>
+        <v>481.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="H44">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I44" t="str">
-        <v>926.0</v>
+        <v>913.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H45">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I45" t="str">
-        <v>1389.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H46">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="I46" t="str">
-        <v>2260.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H47">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I47" t="str">
-        <v>497.0</v>
+        <v>471.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H48">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I48" t="str">
-        <v>1127.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="H49">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="I49" t="str">
-        <v>716.0</v>
+        <v>709.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H50">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="I50" t="str">
-        <v>916.0</v>
+        <v>912.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="H51">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="I51" t="str">
-        <v>467.0</v>
+        <v>470.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H52">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="I52" t="str">
-        <v>265.0</v>
+        <v>229.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H53">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I53" t="str">
-        <v>495.0</v>
+        <v>473.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H54">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I54" t="str">
-        <v>942.0</v>
+        <v>909.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,10 +2471,10 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H55">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="I55" t="str">
         <v>1350.0</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H56">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="I56" t="str">
-        <v>2296.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H57">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I57" t="str">
-        <v>477.0</v>
+        <v>455.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H58">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I58" t="str">
-        <v>1160.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H59">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="I59" t="str">
-        <v>712.0</v>
+        <v>677.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H60">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="I60" t="str">
-        <v>926.0</v>
+        <v>933.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="H61">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="I61" t="str">
-        <v>499.0</v>
+        <v>483.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H62">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="I62" t="str">
-        <v>236.0</v>
+        <v>266.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H63">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="I63" t="str">
-        <v>472.0</v>
+        <v>480.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H64">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="I64" t="str">
-        <v>944.0</v>
+        <v>942.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="H65">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I65" t="str">
-        <v>1374.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H66">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="I66" t="str">
-        <v>2298.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H67">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="I67" t="str">
-        <v>453.0</v>
+        <v>484.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H68">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I68" t="str">
-        <v>1142.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H69">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="I69" t="str">
-        <v>698.0</v>
+        <v>703.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3044,10 +3044,10 @@
         <v>103</v>
       </c>
       <c r="H70">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="I70" t="str">
-        <v>947.0</v>
+        <v>917.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H71">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I71" t="str">
-        <v>461.0</v>
+        <v>490.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H72">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I72" t="str">
-        <v>236.0</v>
+        <v>231.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H73">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="I73" t="str">
-        <v>485.0</v>
+        <v>475.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="H74">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I74" t="str">
-        <v>927.0</v>
+        <v>947.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="H75">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="I75" t="str">
-        <v>1360.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="H76">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I76" t="str">
-        <v>2295.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H77">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="I77" t="str">
-        <v>465.0</v>
+        <v>491.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H78">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I78" t="str">
-        <v>1126.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="H79">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="I79" t="str">
-        <v>710.0</v>
+        <v>707.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="H80">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I80" t="str">
-        <v>948.0</v>
+        <v>921.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H81">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="I81" t="str">
-        <v>465.0</v>
+        <v>498.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H82">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="I82" t="str">
-        <v>265.0</v>
+        <v>225.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H83">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="I83" t="str">
-        <v>491.0</v>
+        <v>489.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H84">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I84" t="str">
-        <v>909.0</v>
+        <v>937.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H85">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I85" t="str">
-        <v>1364.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H86">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="I86" t="str">
-        <v>2270.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H87">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="I87" t="str">
-        <v>463.0</v>
+        <v>475.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H88">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="I88" t="str">
-        <v>1136.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3766,10 +3766,10 @@
         <v>130</v>
       </c>
       <c r="H89">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="I89" t="str">
-        <v>686.0</v>
+        <v>708.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H90">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I90" t="str">
-        <v>917.0</v>
+        <v>913.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="H91">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I91" t="str">
-        <v>463.0</v>
+        <v>496.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H92">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="I92" t="str">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H93">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="I93" t="str">
-        <v>491.0</v>
+        <v>455.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H94">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="I94" t="str">
-        <v>932.0</v>
+        <v>943.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H95">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I95" t="str">
-        <v>1391.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H96">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="I96" t="str">
-        <v>2277.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H97">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I97" t="str">
-        <v>452.0</v>
+        <v>490.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H98">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I98" t="str">
-        <v>1132.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H99">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I99" t="str">
-        <v>691.0</v>
+        <v>720.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H100">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="I100" t="str">
-        <v>949.0</v>
+        <v>948.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H101">
         <v>149</v>
       </c>
       <c r="I101" t="str">
-        <v>478.0</v>
+        <v>475.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H102">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="I102" t="str">
-        <v>272.0</v>
+        <v>240.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H103">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I103" t="str">
-        <v>494.0</v>
+        <v>475.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H104">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I104" t="str">
-        <v>917.0</v>
+        <v>936.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H105">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="I105" t="str">
-        <v>1391.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H106">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I106" t="str">
-        <v>2280.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,10 +4447,10 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="H107">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="I107" t="str">
         <v>485.0</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="H108">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="I108" t="str">
-        <v>1141.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="H109">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="I109" t="str">
-        <v>684.0</v>
+        <v>721.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H110">
         <v>133</v>
       </c>
       <c r="I110" t="str">
-        <v>947.0</v>
+        <v>913.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H111">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="I111" t="str">
-        <v>497.0</v>
+        <v>490.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H112">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="I112" t="str">
-        <v>258.0</v>
+        <v>227.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="H113">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I113" t="str">
-        <v>477.0</v>
+        <v>474.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H114">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I114" t="str">
-        <v>945.0</v>
+        <v>909.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="H115">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="I115" t="str">
-        <v>1368.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H116">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="I116" t="str">
-        <v>2281.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H117">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="I117" t="str">
-        <v>464.0</v>
+        <v>484.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H118">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I118" t="str">
-        <v>1142.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H119">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I119" t="str">
-        <v>705.0</v>
+        <v>708.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H120">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I120" t="str">
-        <v>932.0</v>
+        <v>941.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
+        <v>128</v>
+      </c>
+      <c r="H121">
         <v>137</v>
       </c>
-      <c r="H121">
-        <v>162</v>
-      </c>
       <c r="I121" t="str">
-        <v>499.0</v>
+        <v>471.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H122">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I122" t="str">
-        <v>260.0</v>
+        <v>252.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H123">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I123" t="str">
-        <v>453.0</v>
+        <v>490.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H124">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I124" t="str">
-        <v>926.0</v>
+        <v>912.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H125">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="I125" t="str">
-        <v>1386.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H126">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="I126" t="str">
-        <v>2292.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H127">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I127" t="str">
-        <v>497.0</v>
+        <v>458.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="H128">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I128" t="str">
-        <v>1131.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="H129">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="I129" t="str">
-        <v>720.0</v>
+        <v>690.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H130">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I130" t="str">
-        <v>929.0</v>
+        <v>905.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H131">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I131" t="str">
-        <v>475.0</v>
+        <v>493.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H132">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="I132" t="str">
-        <v>274.0</v>
+        <v>238.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H133">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I133" t="str">
-        <v>468.0</v>
+        <v>459.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H134">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I134" t="str">
-        <v>944.0</v>
+        <v>916.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H135">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="I135" t="str">
-        <v>1392.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H136">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="I136" t="str">
-        <v>2271.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H137">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I137" t="str">
-        <v>455.0</v>
+        <v>484.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H138">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I138" t="str">
-        <v>1164.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H139">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I139" t="str">
-        <v>719.0</v>
+        <v>702.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H140">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I140" t="str">
-        <v>926.0</v>
+        <v>931.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="H141">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="I141" t="str">
-        <v>475.0</v>
+        <v>494.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H142">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I142" t="str">
-        <v>252.0</v>
+        <v>270.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H143">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I143" t="str">
-        <v>476.0</v>
+        <v>454.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H144">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I144" t="str">
-        <v>905.0</v>
+        <v>912.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="H145">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="I145" t="str">
-        <v>1363.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="H146">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="I146" t="str">
-        <v>2269.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
+        <v>105</v>
+      </c>
+      <c r="H147">
         <v>113</v>
       </c>
-      <c r="H147">
-        <v>149</v>
-      </c>
       <c r="I147" t="str">
-        <v>497.0</v>
+        <v>485.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H148">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="I148" t="str">
-        <v>1155.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H149">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I149" t="str">
-        <v>678.0</v>
+        <v>719.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H150">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="I150" t="str">
-        <v>938.0</v>
+        <v>943.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H151">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="I151" t="str">
-        <v>494.0</v>
+        <v>453.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="H152">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I152" t="str">
-        <v>235.0</v>
+        <v>270.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="H153">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I153" t="str">
-        <v>495.0</v>
+        <v>468.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="H154">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="I154" t="str">
-        <v>920.0</v>
+        <v>904.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H155">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I155" t="str">
-        <v>1361.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="H156">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I156" t="str">
-        <v>2293.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="H157">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="I157" t="str">
-        <v>486.0</v>
+        <v>492.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H158">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="I158" t="str">
-        <v>1174.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H159">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="I159" t="str">
-        <v>682.0</v>
+        <v>699.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H160">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I160" t="str">
-        <v>930.0</v>
+        <v>938.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="H161">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="I161" t="str">
-        <v>465.0</v>
+        <v>471.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="H162">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="I162" t="str">
-        <v>260.0</v>
+        <v>238.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H163">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="I163" t="str">
-        <v>485.0</v>
+        <v>489.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6616,10 +6616,10 @@
         <v>152</v>
       </c>
       <c r="H164">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I164" t="str">
-        <v>909.0</v>
+        <v>939.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H165">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I165" t="str">
-        <v>1370.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H166">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="I166" t="str">
-        <v>2255.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="H167">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="I167" t="str">
-        <v>498.0</v>
+        <v>492.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H168">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I168" t="str">
-        <v>1140.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H169">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="I169" t="str">
-        <v>701.0</v>
+        <v>682.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H170">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I170" t="str">
-        <v>908.0</v>
+        <v>903.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H171">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="I171" t="str">
-        <v>489.0</v>
+        <v>453.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H172">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I172" t="str">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H173">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="I173" t="str">
-        <v>482.0</v>
+        <v>470.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H174">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="I174" t="str">
-        <v>903.0</v>
+        <v>922.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="H175">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="I175" t="str">
-        <v>1392.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7072,10 +7072,10 @@
         <v>247</v>
       </c>
       <c r="H176">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="I176" t="str">
-        <v>2292.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H177">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I177" t="str">
-        <v>490.0</v>
+        <v>471.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="H178">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="I178" t="str">
-        <v>1136.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H179">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I179" t="str">
-        <v>701.0</v>
+        <v>676.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H180">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I180" t="str">
-        <v>903.0</v>
+        <v>932.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H181">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="I181" t="str">
-        <v>499.0</v>
+        <v>463.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H182">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I182" t="str">
-        <v>251.0</v>
+        <v>247.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H183">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="I183" t="str">
-        <v>498.0</v>
+        <v>458.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H184">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="I184" t="str">
-        <v>917.0</v>
+        <v>947.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
+        <v>195</v>
+      </c>
+      <c r="H185">
         <v>210</v>
       </c>
-      <c r="H185">
-        <v>213</v>
-      </c>
       <c r="I185" t="str">
-        <v>1395.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H186">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I186" t="str">
-        <v>2294.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H187">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I187" t="str">
-        <v>479.0</v>
+        <v>468.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="H188">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="I188" t="str">
-        <v>1169.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
+        <v>132</v>
+      </c>
+      <c r="H189">
         <v>143</v>
       </c>
-      <c r="H189">
-        <v>182</v>
-      </c>
       <c r="I189" t="str">
-        <v>719.0</v>
+        <v>696.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H190">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I190" t="str">
-        <v>946.0</v>
+        <v>918.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H191">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I191" t="str">
-        <v>474.0</v>
+        <v>485.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7680,10 +7680,10 @@
         <v>98</v>
       </c>
       <c r="H192">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="I192" t="str">
-        <v>242.0</v>
+        <v>266.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H193">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I193" t="str">
-        <v>491.0</v>
+        <v>485.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="H194">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="I194" t="str">
-        <v>906.0</v>
+        <v>940.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H195">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="I195" t="str">
-        <v>1355.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H196">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I196" t="str">
-        <v>2286.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H197">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="I197" t="str">
-        <v>452.0</v>
+        <v>470.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H198">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I198" t="str">
-        <v>1134.0</v>
+        <v>1128.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H199">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="I199" t="str">
-        <v>688.0</v>
+        <v>696.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H200">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="I200" t="str">
-        <v>905.0</v>
+        <v>944.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H201">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I201" t="str">
-        <v>491.0</v>
+        <v>454.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H202">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="I202" t="str">
-        <v>249.0</v>
+        <v>272.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8101,7 +8101,7 @@
         <v>167</v>
       </c>
       <c r="I203" t="str">
-        <v>455.0</v>
+        <v>484.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="H204">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="I204" t="str">
-        <v>923.0</v>
+        <v>920.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H205">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="I205" t="str">
-        <v>1394.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="H206">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="I206" t="str">
-        <v>2263.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H207">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I207" t="str">
-        <v>479.0</v>
+        <v>486.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H208">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I208" t="str">
-        <v>1125.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="H209">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="I209" t="str">
-        <v>677.0</v>
+        <v>707.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="H210">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="I210" t="str">
-        <v>913.0</v>
+        <v>920.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,10 +8399,10 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H211">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="I211" t="str">
         <v>468.0</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="H212">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="I212" t="str">
-        <v>225.0</v>
+        <v>268.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H213">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I213" t="str">
-        <v>478.0</v>
+        <v>479.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H214">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I214" t="str">
-        <v>938.0</v>
+        <v>942.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H215">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I215" t="str">
-        <v>1384.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H216">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I216" t="str">
-        <v>2255.0</v>
+        <v>2262.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H217">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="I217" t="str">
-        <v>477.0</v>
+        <v>485.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H218">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="I218" t="str">
-        <v>1164.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H219">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="I219" t="str">
-        <v>709.0</v>
+        <v>679.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H220">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I220" t="str">
-        <v>923.0</v>
+        <v>922.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8782,10 +8782,10 @@
         <v>128</v>
       </c>
       <c r="H221">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="I221" t="str">
-        <v>490.0</v>
+        <v>481.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H222">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="I222" t="str">
-        <v>236.0</v>
+        <v>269.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H223">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I223" t="str">
-        <v>469.0</v>
+        <v>481.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H224">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="I224" t="str">
-        <v>930.0</v>
+        <v>932.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H225">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I225" t="str">
-        <v>1394.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8972,10 +8972,10 @@
         <v>259</v>
       </c>
       <c r="H226">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="I226" t="str">
-        <v>2277.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H227">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="I227" t="str">
-        <v>488.0</v>
+        <v>475.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H228">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I228" t="str">
-        <v>1130.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H229">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I229" t="str">
-        <v>699.0</v>
+        <v>684.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H230">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I230" t="str">
-        <v>914.0</v>
+        <v>912.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H231">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="I231" t="str">
-        <v>451.0</v>
+        <v>469.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H232">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I232" t="str">
-        <v>250.0</v>
+        <v>264.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9238,10 +9238,10 @@
         <v>130</v>
       </c>
       <c r="H233">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="I233" t="str">
-        <v>465.0</v>
+        <v>459.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H234">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="I234" t="str">
-        <v>912.0</v>
+        <v>924.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H235">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="I235" t="str">
-        <v>1357.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="H236">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="I236" t="str">
-        <v>2291.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H237">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I237" t="str">
-        <v>464.0</v>
+        <v>451.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H238">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="I238" t="str">
-        <v>1147.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H239">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="I239" t="str">
-        <v>677.0</v>
+        <v>722.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="H240">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I240" t="str">
-        <v>941.0</v>
+        <v>938.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H241">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="I241" t="str">
-        <v>486.0</v>
+        <v>475.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H242">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="I242" t="str">
-        <v>247.0</v>
+        <v>270.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="H243">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="I243" t="str">
-        <v>473.0</v>
+        <v>459.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H244">
         <v>182</v>
       </c>
       <c r="I244" t="str">
-        <v>907.0</v>
+        <v>910.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="H245">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I245" t="str">
-        <v>1351.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H246">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="I246" t="str">
-        <v>2264.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9770,10 +9770,10 @@
         <v>111</v>
       </c>
       <c r="H247">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I247" t="str">
-        <v>480.0</v>
+        <v>461.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H248">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I248" t="str">
-        <v>1166.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H249">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I249" t="str">
-        <v>689.0</v>
+        <v>690.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H250">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="I250" t="str">
-        <v>932.0</v>
+        <v>903.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H251">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I251" t="str">
-        <v>456.0</v>
+        <v>497.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H252">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="I252" t="str">
-        <v>246.0</v>
+        <v>254.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H253">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I253" t="str">
-        <v>460.0</v>
+        <v>493.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H254">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="I254" t="str">
-        <v>944.0</v>
+        <v>910.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="H255">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="I255" t="str">
-        <v>1357.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="H256">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="I256" t="str">
-        <v>2291.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H257">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I257" t="str">
-        <v>470.0</v>
+        <v>480.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H258">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I258" t="str">
-        <v>1160.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H259">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="I259" t="str">
-        <v>700.0</v>
+        <v>687.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H260">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I260" t="str">
-        <v>932.0</v>
+        <v>919.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H261">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I261" t="str">
-        <v>468.0</v>
+        <v>459.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H262">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I262" t="str">
-        <v>247.0</v>
+        <v>274.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H263">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="I263" t="str">
-        <v>494.0</v>
+        <v>470.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10416,10 +10416,10 @@
         <v>162</v>
       </c>
       <c r="H264">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I264" t="str">
-        <v>939.0</v>
+        <v>904.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="H265">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="I265" t="str">
-        <v>1371.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H266">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="I266" t="str">
-        <v>2265.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H267">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I267" t="str">
-        <v>492.0</v>
+        <v>451.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H268">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="I268" t="str">
-        <v>1136.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H269">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="I269" t="str">
-        <v>722.0</v>
+        <v>702.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H270">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I270" t="str">
-        <v>937.0</v>
+        <v>919.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H271">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="I271" t="str">
-        <v>466.0</v>
+        <v>473.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H272">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="I272" t="str">
-        <v>238.0</v>
+        <v>229.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H273">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="I273" t="str">
-        <v>472.0</v>
+        <v>490.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H274">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="I274" t="str">
-        <v>922.0</v>
+        <v>940.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H275">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="I275" t="str">
-        <v>1381.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H276">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="I276" t="str">
-        <v>2299.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H277">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I277" t="str">
-        <v>497.0</v>
+        <v>491.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H278">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="I278" t="str">
-        <v>1161.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="H279">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I279" t="str">
-        <v>682.0</v>
+        <v>707.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H280">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I280" t="str">
-        <v>912.0</v>
+        <v>901.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H281">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I281" t="str">
-        <v>463.0</v>
+        <v>465.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H282">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="I282" t="str">
-        <v>270.0</v>
+        <v>237.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H283">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="I283" t="str">
-        <v>457.0</v>
+        <v>458.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H284">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I284" t="str">
-        <v>922.0</v>
+        <v>923.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H285">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="I285" t="str">
-        <v>1373.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="H286">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="I286" t="str">
-        <v>2286.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H287">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I287" t="str">
-        <v>457.0</v>
+        <v>494.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="H288">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="I288" t="str">
-        <v>1146.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H289">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="I289" t="str">
-        <v>719.0</v>
+        <v>720.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H290">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I290" t="str">
-        <v>921.0</v>
+        <v>910.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H291">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I291" t="str">
-        <v>472.0</v>
+        <v>460.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H292">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I292" t="str">
-        <v>225.0</v>
+        <v>271.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="H293">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="I293" t="str">
-        <v>470.0</v>
+        <v>476.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H294">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I294" t="str">
-        <v>936.0</v>
+        <v>945.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,10 +11591,10 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H295">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="I295" t="str">
         <v>1360.0</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="H296">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I296" t="str">
-        <v>2290.0</v>
+        <v>2262.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H297">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="I297" t="str">
-        <v>451.0</v>
+        <v>484.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H298">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="I298" t="str">
-        <v>1132.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H299">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="I299" t="str">
-        <v>702.0</v>
+        <v>722.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H300">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I300" t="str">
-        <v>915.0</v>
+        <v>933.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H301">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="I301" t="str">
-        <v>481.0</v>
+        <v>485.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="H2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I2" t="str">
-        <v>272.0</v>
+        <v>237.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H3">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I3" t="str">
-        <v>466.0</v>
+        <v>496.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H4">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="I4" t="str">
-        <v>930.0</v>
+        <v>909.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H5">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="I5" t="str">
-        <v>1387.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="H6">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="I6" t="str">
-        <v>2277.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I7" t="str">
-        <v>463.0</v>
+        <v>479.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8">
         <v>189</v>
       </c>
       <c r="I8" t="str">
-        <v>1140.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H9">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I9" t="str">
-        <v>685.0</v>
+        <v>693.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H10">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="I10" t="str">
-        <v>902.0</v>
+        <v>936.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H11">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I11" t="str">
-        <v>476.0</v>
+        <v>453.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H12">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I12" t="str">
-        <v>231.0</v>
+        <v>239.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H13">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="I13" t="str">
-        <v>458.0</v>
+        <v>496.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="H14">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="I14" t="str">
-        <v>939.0</v>
+        <v>918.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H15">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="I15" t="str">
-        <v>1387.0</v>
+        <v>1398.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H16">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="I16" t="str">
-        <v>2263.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="H17">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="I17" t="str">
-        <v>492.0</v>
+        <v>479.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H18">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="I18" t="str">
-        <v>1131.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H19">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="I19" t="str">
-        <v>716.0</v>
+        <v>690.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H20">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I20" t="str">
-        <v>924.0</v>
+        <v>936.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="H21">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="I21" t="str">
-        <v>455.0</v>
+        <v>485.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H22">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I22" t="str">
-        <v>230.0</v>
+        <v>273.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H23">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I23" t="str">
-        <v>491.0</v>
+        <v>461.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H24">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="I24" t="str">
-        <v>900.0</v>
+        <v>935.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="H25">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="I25" t="str">
-        <v>1350.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H26">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="I26" t="str">
-        <v>2286.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H27">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="I27" t="str">
-        <v>482.0</v>
+        <v>466.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H28">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="I28" t="str">
-        <v>1173.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H29">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="I29" t="str">
-        <v>699.0</v>
+        <v>695.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H30">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="I30" t="str">
-        <v>949.0</v>
+        <v>930.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H31">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I31" t="str">
-        <v>486.0</v>
+        <v>493.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="H32">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="I32" t="str">
-        <v>266.0</v>
+        <v>247.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H33">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="I33" t="str">
-        <v>493.0</v>
+        <v>484.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H34">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="I34" t="str">
-        <v>933.0</v>
+        <v>937.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H35">
         <v>226</v>
       </c>
       <c r="I35" t="str">
-        <v>1391.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H36">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="I36" t="str">
-        <v>2297.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H37">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I37" t="str">
-        <v>498.0</v>
+        <v>477.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H38">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I38" t="str">
-        <v>1160.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H39">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I39" t="str">
-        <v>712.0</v>
+        <v>693.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H40">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I40" t="str">
-        <v>924.0</v>
+        <v>931.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="H41">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="I41" t="str">
-        <v>497.0</v>
+        <v>450.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H42">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="I42" t="str">
-        <v>250.0</v>
+        <v>255.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H43">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="I43" t="str">
-        <v>481.0</v>
+        <v>450.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H44">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="I44" t="str">
-        <v>913.0</v>
+        <v>931.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H45">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="I45" t="str">
-        <v>1366.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H46">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I46" t="str">
-        <v>2290.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="H47">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I47" t="str">
-        <v>471.0</v>
+        <v>497.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="H48">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I48" t="str">
-        <v>1156.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="H49">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="I49" t="str">
-        <v>709.0</v>
+        <v>721.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H50">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="I50" t="str">
-        <v>912.0</v>
+        <v>933.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H51">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I51" t="str">
-        <v>470.0</v>
+        <v>459.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="H52">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="I52" t="str">
-        <v>229.0</v>
+        <v>237.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2398,10 +2398,10 @@
         <v>130</v>
       </c>
       <c r="H53">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I53" t="str">
-        <v>473.0</v>
+        <v>455.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H54">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="I54" t="str">
-        <v>909.0</v>
+        <v>922.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H55">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="I55" t="str">
-        <v>1350.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="H56">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="I56" t="str">
-        <v>2257.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="H57">
         <v>131</v>
       </c>
       <c r="I57" t="str">
-        <v>455.0</v>
+        <v>466.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H58">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="I58" t="str">
-        <v>1166.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H59">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I59" t="str">
-        <v>677.0</v>
+        <v>712.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H60">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="I60" t="str">
-        <v>933.0</v>
+        <v>934.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H61">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="I61" t="str">
-        <v>483.0</v>
+        <v>453.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H62">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="I62" t="str">
-        <v>266.0</v>
+        <v>244.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H63">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I63" t="str">
-        <v>480.0</v>
+        <v>476.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H64">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="I64" t="str">
-        <v>942.0</v>
+        <v>949.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H65">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="I65" t="str">
-        <v>1384.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="H66">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="I66" t="str">
-        <v>2276.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H67">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="I67" t="str">
-        <v>484.0</v>
+        <v>488.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H68">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I68" t="str">
-        <v>1167.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H69">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="I69" t="str">
-        <v>703.0</v>
+        <v>694.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H70">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I70" t="str">
-        <v>917.0</v>
+        <v>925.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H71">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="I71" t="str">
-        <v>490.0</v>
+        <v>454.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H72">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I72" t="str">
-        <v>231.0</v>
+        <v>226.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H73">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="I73" t="str">
-        <v>475.0</v>
+        <v>463.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H74">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="I74" t="str">
-        <v>947.0</v>
+        <v>911.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H75">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I75" t="str">
-        <v>1361.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H76">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I76" t="str">
-        <v>2289.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H77">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="I77" t="str">
-        <v>491.0</v>
+        <v>497.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H78">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="I78" t="str">
-        <v>1131.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H79">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I79" t="str">
-        <v>707.0</v>
+        <v>705.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H80">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="I80" t="str">
-        <v>921.0</v>
+        <v>949.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H81">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I81" t="str">
-        <v>498.0</v>
+        <v>468.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H82">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="I82" t="str">
-        <v>225.0</v>
+        <v>262.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H83">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I83" t="str">
-        <v>489.0</v>
+        <v>457.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H84">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="I84" t="str">
-        <v>937.0</v>
+        <v>903.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="H85">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="I85" t="str">
-        <v>1396.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="H86">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I86" t="str">
-        <v>2290.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H87">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I87" t="str">
-        <v>475.0</v>
+        <v>450.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H88">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I88" t="str">
-        <v>1159.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="H89">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="I89" t="str">
-        <v>708.0</v>
+        <v>716.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H90">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="I90" t="str">
-        <v>913.0</v>
+        <v>941.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="H91">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I91" t="str">
-        <v>496.0</v>
+        <v>478.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H92">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I92" t="str">
-        <v>253.0</v>
+        <v>270.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="H93">
         <v>142</v>
       </c>
       <c r="I93" t="str">
-        <v>455.0</v>
+        <v>461.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H94">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I94" t="str">
-        <v>943.0</v>
+        <v>938.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H95">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="I95" t="str">
-        <v>1384.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H96">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="I96" t="str">
-        <v>2294.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H97">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="I97" t="str">
-        <v>490.0</v>
+        <v>497.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H98">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="I98" t="str">
-        <v>1126.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H99">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I99" t="str">
-        <v>720.0</v>
+        <v>700.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H100">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I100" t="str">
-        <v>948.0</v>
+        <v>913.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="H101">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="I101" t="str">
-        <v>475.0</v>
+        <v>483.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H102">
         <v>110</v>
       </c>
       <c r="I102" t="str">
-        <v>240.0</v>
+        <v>243.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H103">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I103" t="str">
-        <v>475.0</v>
+        <v>492.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H104">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I104" t="str">
-        <v>936.0</v>
+        <v>930.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H105">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="I105" t="str">
-        <v>1385.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H106">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="I106" t="str">
-        <v>2272.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H107">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I107" t="str">
-        <v>485.0</v>
+        <v>473.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H108">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I108" t="str">
-        <v>1161.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H109">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I109" t="str">
-        <v>721.0</v>
+        <v>719.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H110">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I110" t="str">
-        <v>913.0</v>
+        <v>947.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H111">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I111" t="str">
-        <v>490.0</v>
+        <v>497.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H112">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="I112" t="str">
-        <v>227.0</v>
+        <v>250.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="H113">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I113" t="str">
-        <v>474.0</v>
+        <v>451.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="H114">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I114" t="str">
-        <v>909.0</v>
+        <v>930.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H115">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I115" t="str">
-        <v>1379.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H116">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="I116" t="str">
-        <v>2258.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H117">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I117" t="str">
-        <v>484.0</v>
+        <v>472.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H118">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="I118" t="str">
-        <v>1156.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H119">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I119" t="str">
-        <v>708.0</v>
+        <v>721.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H120">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="I120" t="str">
-        <v>941.0</v>
+        <v>918.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H121">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="I121" t="str">
-        <v>471.0</v>
+        <v>499.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H122">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="I122" t="str">
-        <v>252.0</v>
+        <v>227.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="H123">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="I123" t="str">
-        <v>490.0</v>
+        <v>466.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5096,10 +5096,10 @@
         <v>167</v>
       </c>
       <c r="H124">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I124" t="str">
-        <v>912.0</v>
+        <v>911.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H125">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I125" t="str">
-        <v>1394.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H126">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="I126" t="str">
-        <v>2297.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H127">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="I127" t="str">
-        <v>458.0</v>
+        <v>493.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H128">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I128" t="str">
-        <v>1155.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H129">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I129" t="str">
-        <v>690.0</v>
+        <v>708.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H130">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I130" t="str">
-        <v>905.0</v>
+        <v>908.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H131">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="I131" t="str">
-        <v>493.0</v>
+        <v>470.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H132">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="I132" t="str">
-        <v>238.0</v>
+        <v>236.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H133">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="I133" t="str">
-        <v>459.0</v>
+        <v>485.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H134">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="I134" t="str">
-        <v>916.0</v>
+        <v>902.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H135">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I135" t="str">
-        <v>1359.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="H136">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I136" t="str">
-        <v>2276.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H137">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="I137" t="str">
-        <v>484.0</v>
+        <v>488.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="H138">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="I138" t="str">
-        <v>1132.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="H139">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I139" t="str">
-        <v>702.0</v>
+        <v>715.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H140">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="I140" t="str">
-        <v>931.0</v>
+        <v>912.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H141">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="I141" t="str">
-        <v>494.0</v>
+        <v>486.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H142">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I142" t="str">
-        <v>270.0</v>
+        <v>250.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H143">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="I143" t="str">
-        <v>454.0</v>
+        <v>459.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="H144">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="I144" t="str">
-        <v>912.0</v>
+        <v>938.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H145">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="I145" t="str">
-        <v>1369.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,10 +5929,10 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H146">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="I146" t="str">
         <v>2263.0</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H147">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="I147" t="str">
-        <v>485.0</v>
+        <v>492.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="H148">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="I148" t="str">
-        <v>1140.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H149">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I149" t="str">
-        <v>719.0</v>
+        <v>688.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H150">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I150" t="str">
-        <v>943.0</v>
+        <v>918.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H151">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I151" t="str">
-        <v>453.0</v>
+        <v>493.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H152">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="I152" t="str">
-        <v>270.0</v>
+        <v>230.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H153">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I153" t="str">
-        <v>468.0</v>
+        <v>472.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="H154">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="I154" t="str">
-        <v>904.0</v>
+        <v>942.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H155">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="I155" t="str">
-        <v>1381.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H156">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="I156" t="str">
-        <v>2259.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="H157">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="I157" t="str">
-        <v>492.0</v>
+        <v>456.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H158">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="I158" t="str">
-        <v>1130.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H159">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="I159" t="str">
-        <v>699.0</v>
+        <v>716.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="H160">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I160" t="str">
-        <v>938.0</v>
+        <v>928.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H161">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I161" t="str">
-        <v>471.0</v>
+        <v>492.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H162">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="I162" t="str">
-        <v>238.0</v>
+        <v>251.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="H163">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="I163" t="str">
-        <v>489.0</v>
+        <v>498.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H164">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="I164" t="str">
-        <v>939.0</v>
+        <v>909.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H165">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="I165" t="str">
-        <v>1357.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H166">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="I166" t="str">
-        <v>2263.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,10 +6727,10 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H167">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="I167" t="str">
         <v>492.0</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H168">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I168" t="str">
-        <v>1174.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="H169">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="I169" t="str">
-        <v>682.0</v>
+        <v>695.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H170">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I170" t="str">
-        <v>903.0</v>
+        <v>907.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H171">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="I171" t="str">
-        <v>453.0</v>
+        <v>472.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H172">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I172" t="str">
-        <v>231.0</v>
+        <v>242.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H173">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="I173" t="str">
-        <v>470.0</v>
+        <v>483.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="H174">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I174" t="str">
-        <v>922.0</v>
+        <v>948.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="H175">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="I175" t="str">
-        <v>1371.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H176">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I176" t="str">
-        <v>2277.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H177">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="I177" t="str">
-        <v>471.0</v>
+        <v>459.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H178">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="I178" t="str">
-        <v>1147.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,10 +7183,10 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H179">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="I179" t="str">
         <v>676.0</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H180">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I180" t="str">
-        <v>932.0</v>
+        <v>929.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H181">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="I181" t="str">
-        <v>463.0</v>
+        <v>451.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H182">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="I182" t="str">
-        <v>247.0</v>
+        <v>246.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H183">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I183" t="str">
-        <v>458.0</v>
+        <v>465.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="H184">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="I184" t="str">
-        <v>947.0</v>
+        <v>927.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H185">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I185" t="str">
-        <v>1350.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="H186">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="I186" t="str">
-        <v>2266.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H187">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="I187" t="str">
-        <v>468.0</v>
+        <v>462.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H188">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="I188" t="str">
-        <v>1156.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H189">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I189" t="str">
-        <v>696.0</v>
+        <v>716.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H190">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I190" t="str">
-        <v>918.0</v>
+        <v>913.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,10 +7639,10 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H191">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="I191" t="str">
         <v>485.0</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H192">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I192" t="str">
-        <v>266.0</v>
+        <v>237.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H193">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I193" t="str">
-        <v>485.0</v>
+        <v>474.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="H194">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="I194" t="str">
-        <v>940.0</v>
+        <v>925.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H195">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="I195" t="str">
-        <v>1372.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="H196">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I196" t="str">
-        <v>2296.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="H197">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I197" t="str">
-        <v>470.0</v>
+        <v>462.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H198">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I198" t="str">
-        <v>1128.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H199">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I199" t="str">
-        <v>696.0</v>
+        <v>712.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H200">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I200" t="str">
-        <v>944.0</v>
+        <v>932.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H201">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I201" t="str">
-        <v>454.0</v>
+        <v>473.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H202">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="I202" t="str">
-        <v>272.0</v>
+        <v>259.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H203">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I203" t="str">
-        <v>484.0</v>
+        <v>489.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="H204">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="I204" t="str">
-        <v>920.0</v>
+        <v>925.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H205">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="I205" t="str">
-        <v>1381.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H206">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="I206" t="str">
-        <v>2291.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H207">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I207" t="str">
-        <v>486.0</v>
+        <v>460.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="H208">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="I208" t="str">
-        <v>1168.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H209">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I209" t="str">
-        <v>707.0</v>
+        <v>705.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="H210">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I210" t="str">
-        <v>920.0</v>
+        <v>906.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="H211">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="I211" t="str">
-        <v>468.0</v>
+        <v>455.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H212">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="I212" t="str">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H213">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I213" t="str">
-        <v>479.0</v>
+        <v>494.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="H214">
         <v>182</v>
       </c>
       <c r="I214" t="str">
-        <v>942.0</v>
+        <v>900.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H215">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I215" t="str">
-        <v>1397.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H216">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I216" t="str">
-        <v>2262.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H217">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="I217" t="str">
-        <v>485.0</v>
+        <v>475.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H218">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I218" t="str">
-        <v>1168.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H219">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I219" t="str">
-        <v>679.0</v>
+        <v>698.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H220">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="I220" t="str">
-        <v>922.0</v>
+        <v>935.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H221">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I221" t="str">
-        <v>481.0</v>
+        <v>464.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H222">
         <v>113</v>
       </c>
       <c r="I222" t="str">
-        <v>269.0</v>
+        <v>234.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H223">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="I223" t="str">
-        <v>481.0</v>
+        <v>499.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="H224">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="I224" t="str">
-        <v>932.0</v>
+        <v>911.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="H225">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="I225" t="str">
-        <v>1369.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="H226">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="I226" t="str">
-        <v>2257.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H227">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I227" t="str">
-        <v>475.0</v>
+        <v>471.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H228">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="I228" t="str">
-        <v>1143.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9086,10 +9086,10 @@
         <v>139</v>
       </c>
       <c r="H229">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="I229" t="str">
-        <v>684.0</v>
+        <v>705.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H230">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="I230" t="str">
-        <v>912.0</v>
+        <v>931.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H231">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="I231" t="str">
-        <v>469.0</v>
+        <v>487.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="H232">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="I232" t="str">
-        <v>264.0</v>
+        <v>244.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H233">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I233" t="str">
-        <v>459.0</v>
+        <v>453.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H234">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="I234" t="str">
-        <v>924.0</v>
+        <v>923.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H235">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="I235" t="str">
-        <v>1369.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="H236">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="I236" t="str">
-        <v>2280.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H237">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="I237" t="str">
-        <v>451.0</v>
+        <v>475.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H238">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I238" t="str">
-        <v>1167.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H239">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="I239" t="str">
-        <v>722.0</v>
+        <v>683.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H240">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I240" t="str">
-        <v>938.0</v>
+        <v>924.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H241">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I241" t="str">
-        <v>475.0</v>
+        <v>483.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H242">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="I242" t="str">
-        <v>270.0</v>
+        <v>228.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H243">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="I243" t="str">
-        <v>459.0</v>
+        <v>475.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="H244">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="I244" t="str">
-        <v>910.0</v>
+        <v>901.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="H245">
         <v>221</v>
       </c>
       <c r="I245" t="str">
-        <v>1365.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H246">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="I246" t="str">
-        <v>2267.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H247">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="I247" t="str">
-        <v>461.0</v>
+        <v>468.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H248">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I248" t="str">
-        <v>1136.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="H249">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="I249" t="str">
-        <v>690.0</v>
+        <v>681.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H250">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I250" t="str">
-        <v>903.0</v>
+        <v>923.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H251">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="I251" t="str">
-        <v>497.0</v>
+        <v>451.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H252">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I252" t="str">
-        <v>254.0</v>
+        <v>250.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9998,10 +9998,10 @@
         <v>123</v>
       </c>
       <c r="H253">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="I253" t="str">
-        <v>493.0</v>
+        <v>481.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H254">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I254" t="str">
-        <v>910.0</v>
+        <v>919.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H255">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="I255" t="str">
-        <v>1351.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="H256">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I256" t="str">
-        <v>2294.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H257">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I257" t="str">
-        <v>480.0</v>
+        <v>470.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H258">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I258" t="str">
-        <v>1168.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H259">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I259" t="str">
-        <v>687.0</v>
+        <v>682.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H260">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="I260" t="str">
-        <v>919.0</v>
+        <v>937.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H261">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="I261" t="str">
-        <v>459.0</v>
+        <v>496.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H262">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I262" t="str">
-        <v>274.0</v>
+        <v>244.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H263">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="I263" t="str">
-        <v>470.0</v>
+        <v>476.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H264">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I264" t="str">
-        <v>904.0</v>
+        <v>913.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="H265">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="I265" t="str">
-        <v>1351.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H266">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="I266" t="str">
-        <v>2290.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="H267">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I267" t="str">
-        <v>451.0</v>
+        <v>492.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="H268">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="I268" t="str">
-        <v>1171.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H269">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I269" t="str">
-        <v>702.0</v>
+        <v>678.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H270">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="I270" t="str">
-        <v>919.0</v>
+        <v>908.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H271">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="I271" t="str">
-        <v>473.0</v>
+        <v>462.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H272">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="I272" t="str">
-        <v>229.0</v>
+        <v>263.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H273">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="I273" t="str">
-        <v>490.0</v>
+        <v>457.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H274">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="I274" t="str">
-        <v>940.0</v>
+        <v>912.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H275">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="I275" t="str">
-        <v>1370.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H276">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="I276" t="str">
-        <v>2285.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="H277">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="I277" t="str">
-        <v>491.0</v>
+        <v>475.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H278">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I278" t="str">
-        <v>1166.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H279">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="I279" t="str">
-        <v>707.0</v>
+        <v>696.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H280">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="I280" t="str">
-        <v>901.0</v>
+        <v>945.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="H281">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="I281" t="str">
-        <v>465.0</v>
+        <v>486.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H282">
         <v>125</v>
       </c>
       <c r="I282" t="str">
-        <v>237.0</v>
+        <v>233.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,10 +11135,10 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H283">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="I283" t="str">
         <v>458.0</v>
@@ -11176,10 +11176,10 @@
         <v>152</v>
       </c>
       <c r="H284">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="I284" t="str">
-        <v>923.0</v>
+        <v>918.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11214,10 +11214,10 @@
         <v>200</v>
       </c>
       <c r="H285">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="I285" t="str">
-        <v>1387.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H286">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="I286" t="str">
-        <v>2265.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="H287">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="I287" t="str">
-        <v>494.0</v>
+        <v>465.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H288">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I288" t="str">
-        <v>1127.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="H289">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I289" t="str">
-        <v>720.0</v>
+        <v>712.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H290">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I290" t="str">
-        <v>910.0</v>
+        <v>901.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H291">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I291" t="str">
-        <v>460.0</v>
+        <v>474.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H292">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="I292" t="str">
-        <v>271.0</v>
+        <v>269.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H293">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I293" t="str">
-        <v>476.0</v>
+        <v>460.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H294">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="I294" t="str">
-        <v>945.0</v>
+        <v>917.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H295">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="I295" t="str">
-        <v>1360.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="H296">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="I296" t="str">
-        <v>2262.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11670,10 +11670,10 @@
         <v>124</v>
       </c>
       <c r="H297">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I297" t="str">
-        <v>484.0</v>
+        <v>459.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H298">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I298" t="str">
-        <v>1156.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="H299">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="I299" t="str">
-        <v>722.0</v>
+        <v>705.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
+        <v>103</v>
+      </c>
+      <c r="H300">
         <v>104</v>
       </c>
-      <c r="H300">
-        <v>122</v>
-      </c>
       <c r="I300" t="str">
-        <v>933.0</v>
+        <v>937.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H301">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="I301" t="str">
-        <v>485.0</v>
+        <v>460.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H2">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="I2" t="str">
-        <v>237.0</v>
+        <v>255.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="H3">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="I3" t="str">
-        <v>496.0</v>
+        <v>477.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H4">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="I4" t="str">
-        <v>909.0</v>
+        <v>919.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H5">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="I5" t="str">
-        <v>1376.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H6">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="I6" t="str">
-        <v>2251.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="H7">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="I7" t="str">
-        <v>479.0</v>
+        <v>491.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H8">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="I8" t="str">
-        <v>1167.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H9">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I9" t="str">
-        <v>693.0</v>
+        <v>719.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
+        <v>98</v>
+      </c>
+      <c r="H10">
         <v>113</v>
       </c>
-      <c r="H10">
-        <v>142</v>
-      </c>
       <c r="I10" t="str">
-        <v>936.0</v>
+        <v>902.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H11">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="I11" t="str">
-        <v>453.0</v>
+        <v>452.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H12">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="I12" t="str">
-        <v>239.0</v>
+        <v>245.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="H13">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="I13" t="str">
-        <v>496.0</v>
+        <v>468.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="H14">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="I14" t="str">
-        <v>918.0</v>
+        <v>935.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="H15">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="I15" t="str">
-        <v>1398.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H16">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="I16" t="str">
-        <v>2273.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="H17">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="I17" t="str">
-        <v>479.0</v>
+        <v>481.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I18" t="str">
-        <v>1144.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H19">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I19" t="str">
-        <v>690.0</v>
+        <v>717.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H20">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I20" t="str">
-        <v>936.0</v>
+        <v>930.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H21">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I21" t="str">
-        <v>485.0</v>
+        <v>463.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H22">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I22" t="str">
-        <v>273.0</v>
+        <v>254.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="H23">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="I23" t="str">
-        <v>461.0</v>
+        <v>471.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H24">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="I24" t="str">
-        <v>935.0</v>
+        <v>941.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H25">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="I25" t="str">
-        <v>1358.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="H26">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="I26" t="str">
-        <v>2271.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H27">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="I27" t="str">
-        <v>466.0</v>
+        <v>458.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H28">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="I28" t="str">
-        <v>1160.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H29">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="I29" t="str">
-        <v>695.0</v>
+        <v>722.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H30">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="I30" t="str">
-        <v>930.0</v>
+        <v>901.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H31">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I31" t="str">
-        <v>493.0</v>
+        <v>499.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H32">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I32" t="str">
-        <v>247.0</v>
+        <v>225.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H33">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="I33" t="str">
-        <v>484.0</v>
+        <v>455.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H34">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="I34" t="str">
-        <v>937.0</v>
+        <v>903.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H35">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="I35" t="str">
-        <v>1357.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H36">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="I36" t="str">
-        <v>2275.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H37">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I37" t="str">
-        <v>477.0</v>
+        <v>464.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H38">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I38" t="str">
-        <v>1169.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H39">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I39" t="str">
-        <v>693.0</v>
+        <v>723.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1904,10 +1904,10 @@
         <v>106</v>
       </c>
       <c r="H40">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="I40" t="str">
-        <v>931.0</v>
+        <v>920.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H41">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="I41" t="str">
-        <v>450.0</v>
+        <v>475.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H42">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="I42" t="str">
-        <v>255.0</v>
+        <v>260.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="H43">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="I43" t="str">
-        <v>450.0</v>
+        <v>486.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H44">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I44" t="str">
-        <v>931.0</v>
+        <v>941.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="H45">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I45" t="str">
-        <v>1376.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="H46">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="I46" t="str">
-        <v>2297.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H47">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="I47" t="str">
-        <v>497.0</v>
+        <v>457.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="H48">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="I48" t="str">
-        <v>1167.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H49">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I49" t="str">
-        <v>721.0</v>
+        <v>677.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="H50">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="I50" t="str">
-        <v>933.0</v>
+        <v>936.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H51">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I51" t="str">
-        <v>459.0</v>
+        <v>497.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H52">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I52" t="str">
-        <v>237.0</v>
+        <v>248.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H53">
         <v>132</v>
       </c>
       <c r="I53" t="str">
-        <v>455.0</v>
+        <v>459.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H54">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="I54" t="str">
-        <v>922.0</v>
+        <v>939.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H55">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I55" t="str">
-        <v>1355.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="H56">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="I56" t="str">
-        <v>2291.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H57">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I57" t="str">
-        <v>466.0</v>
+        <v>460.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="H58">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="I58" t="str">
-        <v>1139.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H59">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I59" t="str">
-        <v>712.0</v>
+        <v>690.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H60">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="I60" t="str">
-        <v>934.0</v>
+        <v>903.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="H61">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="I61" t="str">
-        <v>453.0</v>
+        <v>481.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H62">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="I62" t="str">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="H63">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="I63" t="str">
-        <v>476.0</v>
+        <v>489.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H64">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="I64" t="str">
-        <v>949.0</v>
+        <v>918.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H65">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="I65" t="str">
-        <v>1395.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H66">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="I66" t="str">
-        <v>2269.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
+        <v>113</v>
+      </c>
+      <c r="H67">
         <v>129</v>
       </c>
-      <c r="H67">
-        <v>148</v>
-      </c>
       <c r="I67" t="str">
-        <v>488.0</v>
+        <v>472.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H68">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I68" t="str">
-        <v>1162.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H69">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="I69" t="str">
-        <v>694.0</v>
+        <v>682.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H70">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="I70" t="str">
-        <v>925.0</v>
+        <v>943.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H71">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I71" t="str">
-        <v>454.0</v>
+        <v>452.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H72">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="I72" t="str">
-        <v>226.0</v>
+        <v>269.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H73">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I73" t="str">
-        <v>463.0</v>
+        <v>484.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H74">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="I74" t="str">
-        <v>911.0</v>
+        <v>943.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H75">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I75" t="str">
-        <v>1373.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="H76">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I76" t="str">
-        <v>2267.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H77">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I77" t="str">
-        <v>497.0</v>
+        <v>452.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H78">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I78" t="str">
-        <v>1141.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H79">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="I79" t="str">
-        <v>705.0</v>
+        <v>683.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H80">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="I80" t="str">
-        <v>949.0</v>
+        <v>947.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H81">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="I81" t="str">
-        <v>468.0</v>
+        <v>492.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H82">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="I82" t="str">
-        <v>262.0</v>
+        <v>244.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H83">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I83" t="str">
-        <v>457.0</v>
+        <v>468.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H84">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="I84" t="str">
-        <v>903.0</v>
+        <v>914.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H85">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I85" t="str">
-        <v>1397.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="H86">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I86" t="str">
-        <v>2282.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H87">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I87" t="str">
-        <v>450.0</v>
+        <v>459.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H88">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I88" t="str">
-        <v>1138.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H89">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="I89" t="str">
-        <v>716.0</v>
+        <v>711.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H90">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I90" t="str">
-        <v>941.0</v>
+        <v>923.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3842,10 +3842,10 @@
         <v>125</v>
       </c>
       <c r="H91">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="I91" t="str">
-        <v>478.0</v>
+        <v>489.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H92">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I92" t="str">
-        <v>270.0</v>
+        <v>234.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H93">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="I93" t="str">
-        <v>461.0</v>
+        <v>477.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H94">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I94" t="str">
-        <v>938.0</v>
+        <v>943.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H95">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I95" t="str">
-        <v>1392.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="H96">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="I96" t="str">
-        <v>2298.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H97">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I97" t="str">
-        <v>497.0</v>
+        <v>484.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H98">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="I98" t="str">
-        <v>1168.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H99">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I99" t="str">
-        <v>700.0</v>
+        <v>682.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H100">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="I100" t="str">
-        <v>913.0</v>
+        <v>915.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="H101">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="I101" t="str">
-        <v>483.0</v>
+        <v>497.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H102">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I102" t="str">
-        <v>243.0</v>
+        <v>246.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H103">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="I103" t="str">
-        <v>492.0</v>
+        <v>480.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H104">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I104" t="str">
-        <v>930.0</v>
+        <v>938.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H105">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="I105" t="str">
-        <v>1369.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H106">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I106" t="str">
-        <v>2269.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H107">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="I107" t="str">
-        <v>473.0</v>
+        <v>452.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="H108">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="I108" t="str">
-        <v>1150.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H109">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="I109" t="str">
-        <v>719.0</v>
+        <v>710.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H110">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="I110" t="str">
-        <v>947.0</v>
+        <v>926.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H111">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="I111" t="str">
-        <v>497.0</v>
+        <v>485.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H112">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I112" t="str">
-        <v>250.0</v>
+        <v>232.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H113">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I113" t="str">
-        <v>451.0</v>
+        <v>460.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H114">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="I114" t="str">
-        <v>930.0</v>
+        <v>909.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H115">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="I115" t="str">
-        <v>1366.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H116">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="I116" t="str">
-        <v>2274.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H117">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="I117" t="str">
-        <v>472.0</v>
+        <v>469.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H118">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I118" t="str">
-        <v>1170.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H119">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I119" t="str">
-        <v>721.0</v>
+        <v>720.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="H120">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="I120" t="str">
-        <v>918.0</v>
+        <v>928.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H121">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="I121" t="str">
-        <v>499.0</v>
+        <v>466.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H122">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I122" t="str">
-        <v>227.0</v>
+        <v>252.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H123">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I123" t="str">
-        <v>466.0</v>
+        <v>471.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="H124">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="I124" t="str">
-        <v>911.0</v>
+        <v>907.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H125">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I125" t="str">
-        <v>1368.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H126">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="I126" t="str">
-        <v>2266.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H127">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="I127" t="str">
-        <v>493.0</v>
+        <v>454.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H128">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="I128" t="str">
-        <v>1152.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H129">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I129" t="str">
-        <v>708.0</v>
+        <v>719.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H130">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="I130" t="str">
-        <v>908.0</v>
+        <v>921.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="H131">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="I131" t="str">
-        <v>470.0</v>
+        <v>451.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H132">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I132" t="str">
-        <v>236.0</v>
+        <v>233.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H133">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="I133" t="str">
-        <v>485.0</v>
+        <v>467.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="H134">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="I134" t="str">
-        <v>902.0</v>
+        <v>944.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="H135">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I135" t="str">
-        <v>1375.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5552,10 +5552,10 @@
         <v>261</v>
       </c>
       <c r="H136">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="I136" t="str">
-        <v>2266.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H137">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="I137" t="str">
-        <v>488.0</v>
+        <v>484.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H138">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="I138" t="str">
-        <v>1142.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H139">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="I139" t="str">
-        <v>715.0</v>
+        <v>704.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="H140">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="I140" t="str">
-        <v>912.0</v>
+        <v>945.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H141">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I141" t="str">
-        <v>486.0</v>
+        <v>463.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H142">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I142" t="str">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H143">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="I143" t="str">
-        <v>459.0</v>
+        <v>491.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H144">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I144" t="str">
-        <v>938.0</v>
+        <v>911.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H145">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="I145" t="str">
-        <v>1388.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H146">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="I146" t="str">
-        <v>2263.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H147">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I147" t="str">
-        <v>492.0</v>
+        <v>499.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H148">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I148" t="str">
-        <v>1160.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H149">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="I149" t="str">
-        <v>688.0</v>
+        <v>708.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H150">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="I150" t="str">
-        <v>918.0</v>
+        <v>929.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H151">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="I151" t="str">
-        <v>493.0</v>
+        <v>497.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H152">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I152" t="str">
-        <v>230.0</v>
+        <v>229.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H153">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I153" t="str">
-        <v>472.0</v>
+        <v>475.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H154">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="I154" t="str">
-        <v>942.0</v>
+        <v>910.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H155">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="I155" t="str">
-        <v>1364.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="H156">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="I156" t="str">
-        <v>2286.0</v>
+        <v>2284.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H157">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I157" t="str">
-        <v>456.0</v>
+        <v>453.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="H158">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="I158" t="str">
-        <v>1139.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="H159">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="I159" t="str">
-        <v>716.0</v>
+        <v>681.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H160">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="I160" t="str">
-        <v>928.0</v>
+        <v>905.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H161">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I161" t="str">
-        <v>492.0</v>
+        <v>475.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H162">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="I162" t="str">
-        <v>251.0</v>
+        <v>270.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H163">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="I163" t="str">
-        <v>498.0</v>
+        <v>460.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H164">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="I164" t="str">
-        <v>909.0</v>
+        <v>928.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H165">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="I165" t="str">
-        <v>1396.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="H166">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="I166" t="str">
-        <v>2265.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,10 +6727,10 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H167">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I167" t="str">
         <v>492.0</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="H168">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I168" t="str">
-        <v>1159.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H169">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I169" t="str">
-        <v>695.0</v>
+        <v>697.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H170">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I170" t="str">
-        <v>907.0</v>
+        <v>921.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,10 +6879,10 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H171">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="I171" t="str">
         <v>472.0</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H172">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="I172" t="str">
-        <v>242.0</v>
+        <v>265.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="H173">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I173" t="str">
-        <v>483.0</v>
+        <v>495.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H174">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="I174" t="str">
-        <v>948.0</v>
+        <v>930.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H175">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="I175" t="str">
-        <v>1365.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="H176">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I176" t="str">
-        <v>2278.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H177">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="I177" t="str">
-        <v>459.0</v>
+        <v>472.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H178">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="I178" t="str">
-        <v>1127.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7186,10 +7186,10 @@
         <v>148</v>
       </c>
       <c r="H179">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I179" t="str">
-        <v>676.0</v>
+        <v>709.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H180">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="I180" t="str">
-        <v>929.0</v>
+        <v>917.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H181">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="I181" t="str">
-        <v>451.0</v>
+        <v>486.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="H182">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="I182" t="str">
-        <v>246.0</v>
+        <v>231.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H183">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="I183" t="str">
-        <v>465.0</v>
+        <v>480.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="H184">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="I184" t="str">
-        <v>927.0</v>
+        <v>921.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="H185">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="I185" t="str">
-        <v>1369.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="H186">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="I186" t="str">
-        <v>2289.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H187">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I187" t="str">
-        <v>462.0</v>
+        <v>468.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H188">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I188" t="str">
-        <v>1150.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H189">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I189" t="str">
-        <v>716.0</v>
+        <v>710.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,10 +7601,10 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H190">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="I190" t="str">
         <v>913.0</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="H191">
         <v>166</v>
       </c>
       <c r="I191" t="str">
-        <v>485.0</v>
+        <v>454.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H192">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="I192" t="str">
-        <v>237.0</v>
+        <v>248.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H193">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I193" t="str">
-        <v>474.0</v>
+        <v>452.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H194">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I194" t="str">
-        <v>925.0</v>
+        <v>946.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H195">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="I195" t="str">
-        <v>1376.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H196">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="I196" t="str">
-        <v>2273.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H197">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="I197" t="str">
-        <v>462.0</v>
+        <v>456.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H198">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="I198" t="str">
-        <v>1168.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H199">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="I199" t="str">
-        <v>712.0</v>
+        <v>721.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H200">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I200" t="str">
-        <v>932.0</v>
+        <v>916.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="H201">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I201" t="str">
-        <v>473.0</v>
+        <v>496.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H202">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="I202" t="str">
-        <v>259.0</v>
+        <v>244.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H203">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I203" t="str">
-        <v>489.0</v>
+        <v>487.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,10 +8133,10 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="H204">
-        <v>208</v>
+        <v>149</v>
       </c>
       <c r="I204" t="str">
         <v>925.0</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H205">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I205" t="str">
-        <v>1353.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H206">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="I206" t="str">
-        <v>2274.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H207">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="I207" t="str">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H208">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="I208" t="str">
-        <v>1170.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H209">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I209" t="str">
-        <v>705.0</v>
+        <v>719.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H210">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="I210" t="str">
-        <v>906.0</v>
+        <v>931.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8402,10 +8402,10 @@
         <v>123</v>
       </c>
       <c r="H211">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I211" t="str">
-        <v>455.0</v>
+        <v>453.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H212">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="I212" t="str">
-        <v>269.0</v>
+        <v>263.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,10 +8475,10 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H213">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I213" t="str">
         <v>494.0</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="H214">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I214" t="str">
-        <v>900.0</v>
+        <v>910.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H215">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I215" t="str">
-        <v>1373.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H216">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="I216" t="str">
-        <v>2268.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H217">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="I217" t="str">
-        <v>475.0</v>
+        <v>479.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H218">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="I218" t="str">
-        <v>1160.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H219">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="I219" t="str">
-        <v>698.0</v>
+        <v>686.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="H220">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I220" t="str">
-        <v>935.0</v>
+        <v>940.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="H221">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="I221" t="str">
-        <v>464.0</v>
+        <v>473.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H222">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="I222" t="str">
-        <v>234.0</v>
+        <v>262.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="H223">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="I223" t="str">
-        <v>499.0</v>
+        <v>474.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H224">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I224" t="str">
-        <v>911.0</v>
+        <v>920.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H225">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="I225" t="str">
-        <v>1387.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="H226">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="I226" t="str">
-        <v>2256.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H227">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I227" t="str">
-        <v>471.0</v>
+        <v>489.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="H228">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I228" t="str">
-        <v>1137.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H229">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="I229" t="str">
-        <v>705.0</v>
+        <v>679.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H230">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I230" t="str">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H231">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I231" t="str">
-        <v>487.0</v>
+        <v>456.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H232">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I232" t="str">
-        <v>244.0</v>
+        <v>266.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H233">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="I233" t="str">
-        <v>453.0</v>
+        <v>467.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H234">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I234" t="str">
-        <v>923.0</v>
+        <v>949.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H235">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I235" t="str">
-        <v>1366.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="H236">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="I236" t="str">
-        <v>2266.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H237">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I237" t="str">
-        <v>475.0</v>
+        <v>490.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H238">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="I238" t="str">
-        <v>1150.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H239">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="I239" t="str">
-        <v>683.0</v>
+        <v>691.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H240">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="I240" t="str">
-        <v>924.0</v>
+        <v>946.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H241">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I241" t="str">
-        <v>483.0</v>
+        <v>450.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="H242">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="I242" t="str">
-        <v>228.0</v>
+        <v>226.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H243">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="I243" t="str">
-        <v>475.0</v>
+        <v>477.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H244">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="I244" t="str">
-        <v>901.0</v>
+        <v>902.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H245">
         <v>221</v>
       </c>
       <c r="I245" t="str">
-        <v>1374.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H246">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I246" t="str">
-        <v>2283.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H247">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="I247" t="str">
-        <v>468.0</v>
+        <v>499.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H248">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="I248" t="str">
-        <v>1125.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="H249">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="I249" t="str">
-        <v>681.0</v>
+        <v>715.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H250">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="I250" t="str">
-        <v>923.0</v>
+        <v>924.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H251">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="I251" t="str">
-        <v>451.0</v>
+        <v>464.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H252">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I252" t="str">
-        <v>250.0</v>
+        <v>244.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H253">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="I253" t="str">
-        <v>481.0</v>
+        <v>479.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H254">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I254" t="str">
-        <v>919.0</v>
+        <v>922.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H255">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="I255" t="str">
-        <v>1371.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H256">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="I256" t="str">
-        <v>2269.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="H257">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I257" t="str">
-        <v>470.0</v>
+        <v>475.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H258">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I258" t="str">
-        <v>1171.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H259">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="I259" t="str">
-        <v>682.0</v>
+        <v>717.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H260">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="I260" t="str">
-        <v>937.0</v>
+        <v>905.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H261">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I261" t="str">
-        <v>496.0</v>
+        <v>455.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="H262">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I262" t="str">
-        <v>244.0</v>
+        <v>251.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="H263">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="I263" t="str">
-        <v>476.0</v>
+        <v>451.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H264">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I264" t="str">
-        <v>913.0</v>
+        <v>937.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H265">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I265" t="str">
-        <v>1372.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="H266">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I266" t="str">
-        <v>2289.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H267">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="I267" t="str">
-        <v>492.0</v>
+        <v>467.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H268">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I268" t="str">
-        <v>1169.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H269">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="I269" t="str">
-        <v>678.0</v>
+        <v>704.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
+        <v>105</v>
+      </c>
+      <c r="H270">
         <v>112</v>
       </c>
-      <c r="H270">
-        <v>122</v>
-      </c>
       <c r="I270" t="str">
-        <v>908.0</v>
+        <v>936.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H271">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="I271" t="str">
-        <v>462.0</v>
+        <v>469.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,10 +10717,10 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H272">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="I272" t="str">
         <v>263.0</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H273">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I273" t="str">
-        <v>457.0</v>
+        <v>494.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="H274">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="I274" t="str">
-        <v>912.0</v>
+        <v>914.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H275">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I275" t="str">
-        <v>1375.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H276">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="I276" t="str">
-        <v>2283.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,10 +10907,10 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="H277">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="I277" t="str">
         <v>475.0</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H278">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I278" t="str">
-        <v>1133.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H279">
         <v>173</v>
       </c>
       <c r="I279" t="str">
-        <v>696.0</v>
+        <v>711.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="H280">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="I280" t="str">
-        <v>945.0</v>
+        <v>927.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H281">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="I281" t="str">
-        <v>486.0</v>
+        <v>460.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H282">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="I282" t="str">
-        <v>233.0</v>
+        <v>260.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H283">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="I283" t="str">
-        <v>458.0</v>
+        <v>498.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H284">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="I284" t="str">
-        <v>918.0</v>
+        <v>919.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="H285">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="I285" t="str">
-        <v>1350.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="H286">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="I286" t="str">
-        <v>2279.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="H287">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I287" t="str">
-        <v>465.0</v>
+        <v>493.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H288">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="I288" t="str">
-        <v>1150.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="H289">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I289" t="str">
-        <v>712.0</v>
+        <v>694.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H290">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I290" t="str">
-        <v>901.0</v>
+        <v>943.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="H291">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="I291" t="str">
-        <v>474.0</v>
+        <v>496.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="H292">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I292" t="str">
-        <v>269.0</v>
+        <v>245.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H293">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I293" t="str">
-        <v>460.0</v>
+        <v>463.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H294">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I294" t="str">
-        <v>917.0</v>
+        <v>941.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H295">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I295" t="str">
-        <v>1350.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="H296">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I296" t="str">
-        <v>2282.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H297">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="I297" t="str">
-        <v>459.0</v>
+        <v>476.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="H298">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="I298" t="str">
-        <v>1138.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H299">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="I299" t="str">
-        <v>705.0</v>
+        <v>692.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H300">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="I300" t="str">
-        <v>937.0</v>
+        <v>918.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H301">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="I301" t="str">
-        <v>460.0</v>
+        <v>455.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H2">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I2" t="str">
-        <v>255.0</v>
+        <v>260.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="H3">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="I3" t="str">
-        <v>477.0</v>
+        <v>479.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="H4">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="I4" t="str">
-        <v>919.0</v>
+        <v>900.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="H5">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I5" t="str">
-        <v>1374.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="H6">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="I6" t="str">
-        <v>2273.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H7">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I7" t="str">
-        <v>491.0</v>
+        <v>496.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H8">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="I8" t="str">
-        <v>1149.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H9">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I9" t="str">
-        <v>719.0</v>
+        <v>717.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H10">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I10" t="str">
-        <v>902.0</v>
+        <v>907.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H11">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="I11" t="str">
-        <v>452.0</v>
+        <v>465.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H12">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="I12" t="str">
-        <v>245.0</v>
+        <v>232.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="I13" t="str">
-        <v>468.0</v>
+        <v>459.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H14">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="I14" t="str">
-        <v>935.0</v>
+        <v>934.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H15">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="I15" t="str">
-        <v>1369.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H16">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="I16" t="str">
-        <v>2296.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="H17">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I17" t="str">
-        <v>481.0</v>
+        <v>471.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="H18">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I18" t="str">
-        <v>1135.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,10 +1103,10 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H19">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I19" t="str">
         <v>717.0</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H20">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I20" t="str">
-        <v>930.0</v>
+        <v>936.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="H21">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="I21" t="str">
-        <v>463.0</v>
+        <v>457.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H22">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I22" t="str">
-        <v>254.0</v>
+        <v>257.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H23">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I23" t="str">
-        <v>471.0</v>
+        <v>465.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1296,10 +1296,10 @@
         <v>166</v>
       </c>
       <c r="H24">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="I24" t="str">
-        <v>941.0</v>
+        <v>926.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="H25">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="I25" t="str">
-        <v>1378.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H26">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I26" t="str">
-        <v>2257.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H27">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="I27" t="str">
-        <v>458.0</v>
+        <v>460.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H28">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="I28" t="str">
-        <v>1143.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H29">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="I29" t="str">
-        <v>722.0</v>
+        <v>684.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="H30">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="I30" t="str">
-        <v>901.0</v>
+        <v>923.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H31">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="I31" t="str">
-        <v>499.0</v>
+        <v>481.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H32">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I32" t="str">
-        <v>225.0</v>
+        <v>258.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H33">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I33" t="str">
-        <v>455.0</v>
+        <v>466.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H34">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I34" t="str">
-        <v>903.0</v>
+        <v>913.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="H35">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="I35" t="str">
-        <v>1366.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H36">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="I36" t="str">
-        <v>2252.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H37">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I37" t="str">
-        <v>464.0</v>
+        <v>497.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1828,7 +1828,7 @@
         <v>164</v>
       </c>
       <c r="H38">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I38" t="str">
         <v>1135.0</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H39">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="I39" t="str">
-        <v>723.0</v>
+        <v>694.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H40">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="I40" t="str">
-        <v>920.0</v>
+        <v>949.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="H41">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="I41" t="str">
-        <v>475.0</v>
+        <v>483.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
+        <v>90</v>
+      </c>
+      <c r="H42">
         <v>95</v>
       </c>
-      <c r="H42">
-        <v>123</v>
-      </c>
       <c r="I42" t="str">
-        <v>260.0</v>
+        <v>232.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,10 +2015,10 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="H43">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="I43" t="str">
         <v>486.0</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H44">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I44" t="str">
-        <v>941.0</v>
+        <v>933.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H45">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I45" t="str">
-        <v>1390.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H46">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="I46" t="str">
-        <v>2264.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H47">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="I47" t="str">
-        <v>457.0</v>
+        <v>489.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="H48">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I48" t="str">
-        <v>1161.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H49">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I49" t="str">
-        <v>677.0</v>
+        <v>700.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H50">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="I50" t="str">
-        <v>936.0</v>
+        <v>930.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H51">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I51" t="str">
-        <v>497.0</v>
+        <v>488.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H52">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I52" t="str">
-        <v>248.0</v>
+        <v>240.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="H53">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I53" t="str">
-        <v>459.0</v>
+        <v>460.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H54">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="I54" t="str">
-        <v>939.0</v>
+        <v>927.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H55">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="I55" t="str">
-        <v>1378.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="H56">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I56" t="str">
-        <v>2257.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H57">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I57" t="str">
-        <v>460.0</v>
+        <v>463.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H58">
         <v>168</v>
       </c>
       <c r="I58" t="str">
-        <v>1143.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H59">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I59" t="str">
-        <v>690.0</v>
+        <v>710.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H60">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I60" t="str">
-        <v>903.0</v>
+        <v>908.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H61">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I61" t="str">
-        <v>481.0</v>
+        <v>472.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H62">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I62" t="str">
-        <v>245.0</v>
+        <v>266.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H63">
         <v>125</v>
       </c>
       <c r="I63" t="str">
-        <v>489.0</v>
+        <v>485.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="H64">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="I64" t="str">
-        <v>918.0</v>
+        <v>921.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H65">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="I65" t="str">
-        <v>1387.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H66">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I66" t="str">
-        <v>2296.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H67">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="I67" t="str">
-        <v>472.0</v>
+        <v>464.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H68">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="I68" t="str">
-        <v>1135.0</v>
+        <v>1128.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H69">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="I69" t="str">
-        <v>682.0</v>
+        <v>695.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3044,7 +3044,7 @@
         <v>114</v>
       </c>
       <c r="H70">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="I70" t="str">
         <v>943.0</v>
@@ -3079,10 +3079,10 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="H71">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I71" t="str">
         <v>452.0</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H72">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I72" t="str">
-        <v>269.0</v>
+        <v>261.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H73">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I73" t="str">
-        <v>484.0</v>
+        <v>488.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="H74">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="I74" t="str">
-        <v>943.0</v>
+        <v>915.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H75">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I75" t="str">
-        <v>1355.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="H76">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="I76" t="str">
-        <v>2299.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H77">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I77" t="str">
-        <v>452.0</v>
+        <v>498.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H78">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="I78" t="str">
-        <v>1148.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H79">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="I79" t="str">
-        <v>683.0</v>
+        <v>712.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H80">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="I80" t="str">
-        <v>947.0</v>
+        <v>926.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H81">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I81" t="str">
-        <v>492.0</v>
+        <v>491.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H82">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="I82" t="str">
-        <v>244.0</v>
+        <v>225.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H83">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="I83" t="str">
-        <v>468.0</v>
+        <v>472.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H84">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="I84" t="str">
-        <v>914.0</v>
+        <v>911.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="H85">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I85" t="str">
-        <v>1370.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="H86">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="I86" t="str">
-        <v>2293.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H87">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I87" t="str">
-        <v>459.0</v>
+        <v>490.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H88">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I88" t="str">
-        <v>1135.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H89">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="I89" t="str">
-        <v>711.0</v>
+        <v>677.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H90">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I90" t="str">
-        <v>923.0</v>
+        <v>919.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="H91">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="I91" t="str">
-        <v>489.0</v>
+        <v>455.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H92">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I92" t="str">
-        <v>234.0</v>
+        <v>228.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H93">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I93" t="str">
-        <v>477.0</v>
+        <v>486.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H94">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I94" t="str">
-        <v>943.0</v>
+        <v>909.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="H95">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="I95" t="str">
-        <v>1379.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H96">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="I96" t="str">
-        <v>2290.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H97">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="I97" t="str">
-        <v>484.0</v>
+        <v>490.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="H98">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I98" t="str">
-        <v>1161.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H99">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="I99" t="str">
-        <v>682.0</v>
+        <v>677.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H100">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="I100" t="str">
-        <v>915.0</v>
+        <v>934.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H101">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I101" t="str">
-        <v>497.0</v>
+        <v>486.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4260,10 +4260,10 @@
         <v>100</v>
       </c>
       <c r="H102">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I102" t="str">
-        <v>246.0</v>
+        <v>266.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H103">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I103" t="str">
-        <v>480.0</v>
+        <v>463.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H104">
         <v>172</v>
       </c>
       <c r="I104" t="str">
-        <v>938.0</v>
+        <v>926.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="H105">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="I105" t="str">
-        <v>1356.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="H106">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="I106" t="str">
-        <v>2283.0</v>
+        <v>2284.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H107">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="I107" t="str">
-        <v>452.0</v>
+        <v>465.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H108">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I108" t="str">
-        <v>1140.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H109">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="I109" t="str">
-        <v>710.0</v>
+        <v>678.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H110">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I110" t="str">
-        <v>926.0</v>
+        <v>946.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H111">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="I111" t="str">
-        <v>485.0</v>
+        <v>478.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H112">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I112" t="str">
-        <v>232.0</v>
+        <v>238.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H113">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I113" t="str">
-        <v>460.0</v>
+        <v>450.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H114">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="I114" t="str">
-        <v>909.0</v>
+        <v>928.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H115">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="I115" t="str">
-        <v>1379.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H116">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="I116" t="str">
-        <v>2257.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H117">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="I117" t="str">
-        <v>469.0</v>
+        <v>455.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="H118">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="I118" t="str">
-        <v>1141.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H119">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="I119" t="str">
-        <v>720.0</v>
+        <v>680.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H120">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I120" t="str">
-        <v>928.0</v>
+        <v>949.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H121">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I121" t="str">
-        <v>466.0</v>
+        <v>461.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H122">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="I122" t="str">
-        <v>252.0</v>
+        <v>240.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="H123">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I123" t="str">
-        <v>471.0</v>
+        <v>493.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="H124">
         <v>161</v>
       </c>
       <c r="I124" t="str">
-        <v>907.0</v>
+        <v>934.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H125">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="I125" t="str">
-        <v>1373.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5172,10 +5172,10 @@
         <v>250</v>
       </c>
       <c r="H126">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="I126" t="str">
-        <v>2279.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="H127">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="I127" t="str">
-        <v>454.0</v>
+        <v>499.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H128">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I128" t="str">
-        <v>1167.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H129">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I129" t="str">
-        <v>719.0</v>
+        <v>687.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H130">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="I130" t="str">
-        <v>921.0</v>
+        <v>936.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H131">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="I131" t="str">
-        <v>451.0</v>
+        <v>474.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H132">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I132" t="str">
-        <v>233.0</v>
+        <v>245.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H133">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I133" t="str">
-        <v>467.0</v>
+        <v>466.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="H134">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="I134" t="str">
-        <v>944.0</v>
+        <v>904.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H135">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I135" t="str">
-        <v>1381.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H136">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="I136" t="str">
-        <v>2290.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H137">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="I137" t="str">
-        <v>484.0</v>
+        <v>468.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H138">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="I138" t="str">
-        <v>1166.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="H139">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="I139" t="str">
-        <v>704.0</v>
+        <v>689.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="H140">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="I140" t="str">
-        <v>945.0</v>
+        <v>925.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H141">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="I141" t="str">
-        <v>463.0</v>
+        <v>469.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H142">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I142" t="str">
-        <v>251.0</v>
+        <v>236.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H143">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="I143" t="str">
-        <v>491.0</v>
+        <v>485.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H144">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I144" t="str">
-        <v>911.0</v>
+        <v>916.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H145">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="I145" t="str">
-        <v>1353.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="H146">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I146" t="str">
-        <v>2258.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H147">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="I147" t="str">
-        <v>499.0</v>
+        <v>465.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H148">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I148" t="str">
-        <v>1143.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="H149">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="I149" t="str">
-        <v>708.0</v>
+        <v>712.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H150">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="I150" t="str">
-        <v>929.0</v>
+        <v>924.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="H151">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="I151" t="str">
-        <v>497.0</v>
+        <v>470.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H152">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I152" t="str">
-        <v>229.0</v>
+        <v>271.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H153">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="I153" t="str">
-        <v>475.0</v>
+        <v>483.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H154">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="I154" t="str">
-        <v>910.0</v>
+        <v>903.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H155">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="I155" t="str">
-        <v>1367.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H156">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="I156" t="str">
-        <v>2284.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H157">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I157" t="str">
-        <v>453.0</v>
+        <v>489.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H158">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I158" t="str">
-        <v>1144.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="H159">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I159" t="str">
-        <v>681.0</v>
+        <v>710.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="H160">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="I160" t="str">
-        <v>905.0</v>
+        <v>916.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H161">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I161" t="str">
-        <v>475.0</v>
+        <v>459.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H162">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I162" t="str">
-        <v>270.0</v>
+        <v>246.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H163">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="I163" t="str">
-        <v>460.0</v>
+        <v>470.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H164">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I164" t="str">
-        <v>928.0</v>
+        <v>925.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,7 +6651,7 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="H165">
         <v>236</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H166">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="I166" t="str">
-        <v>2261.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H167">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="I167" t="str">
-        <v>492.0</v>
+        <v>496.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="H168">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I168" t="str">
-        <v>1152.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H169">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="I169" t="str">
-        <v>697.0</v>
+        <v>715.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H170">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I170" t="str">
-        <v>921.0</v>
+        <v>912.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H171">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="I171" t="str">
-        <v>472.0</v>
+        <v>499.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H172">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I172" t="str">
-        <v>265.0</v>
+        <v>257.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H173">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I173" t="str">
-        <v>495.0</v>
+        <v>460.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H174">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="I174" t="str">
-        <v>930.0</v>
+        <v>902.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H175">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="I175" t="str">
-        <v>1377.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H176">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="I176" t="str">
-        <v>2274.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H177">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I177" t="str">
-        <v>472.0</v>
+        <v>492.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H178">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="I178" t="str">
-        <v>1150.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H179">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="I179" t="str">
-        <v>709.0</v>
+        <v>675.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H180">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="I180" t="str">
-        <v>917.0</v>
+        <v>945.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H181">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I181" t="str">
-        <v>486.0</v>
+        <v>455.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="H182">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="I182" t="str">
-        <v>231.0</v>
+        <v>263.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H183">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="I183" t="str">
-        <v>480.0</v>
+        <v>486.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="H184">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I184" t="str">
-        <v>921.0</v>
+        <v>923.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H185">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="I185" t="str">
-        <v>1373.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="H186">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="I186" t="str">
-        <v>2282.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H187">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="I187" t="str">
-        <v>468.0</v>
+        <v>470.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="H188">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I188" t="str">
-        <v>1154.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H189">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I189" t="str">
-        <v>710.0</v>
+        <v>686.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H190">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="I190" t="str">
-        <v>913.0</v>
+        <v>923.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H191">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I191" t="str">
-        <v>454.0</v>
+        <v>460.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H192">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="I192" t="str">
-        <v>248.0</v>
+        <v>236.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H193">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="I193" t="str">
-        <v>452.0</v>
+        <v>495.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H194">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="I194" t="str">
-        <v>946.0</v>
+        <v>943.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H195">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="I195" t="str">
-        <v>1369.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H196">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="I196" t="str">
-        <v>2275.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H197">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="I197" t="str">
-        <v>456.0</v>
+        <v>474.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="H198">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="I198" t="str">
-        <v>1160.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="H199">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I199" t="str">
-        <v>721.0</v>
+        <v>685.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H200">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I200" t="str">
-        <v>916.0</v>
+        <v>938.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H201">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="I201" t="str">
-        <v>496.0</v>
+        <v>479.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H202">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="I202" t="str">
-        <v>244.0</v>
+        <v>266.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H203">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="I203" t="str">
-        <v>487.0</v>
+        <v>468.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="H204">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="I204" t="str">
-        <v>925.0</v>
+        <v>922.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8174,10 +8174,10 @@
         <v>197</v>
       </c>
       <c r="H205">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I205" t="str">
-        <v>1354.0</v>
+        <v>1383.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H206">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="I206" t="str">
-        <v>2259.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H207">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I207" t="str">
-        <v>462.0</v>
+        <v>469.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H208">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I208" t="str">
-        <v>1164.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="H209">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I209" t="str">
-        <v>719.0</v>
+        <v>703.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,10 +8361,10 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H210">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I210" t="str">
         <v>931.0</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H211">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I211" t="str">
-        <v>453.0</v>
+        <v>491.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H212">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="I212" t="str">
-        <v>263.0</v>
+        <v>229.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H213">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I213" t="str">
-        <v>494.0</v>
+        <v>488.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H214">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I214" t="str">
-        <v>910.0</v>
+        <v>935.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="H215">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I215" t="str">
-        <v>1356.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H216">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="I216" t="str">
-        <v>2270.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H217">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="I217" t="str">
-        <v>479.0</v>
+        <v>480.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H218">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="I218" t="str">
-        <v>1132.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="H219">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="I219" t="str">
-        <v>686.0</v>
+        <v>675.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H220">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I220" t="str">
-        <v>940.0</v>
+        <v>944.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H221">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="I221" t="str">
-        <v>473.0</v>
+        <v>489.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H222">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I222" t="str">
-        <v>262.0</v>
+        <v>266.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
+        <v>125</v>
+      </c>
+      <c r="H223">
         <v>130</v>
       </c>
-      <c r="H223">
-        <v>160</v>
-      </c>
       <c r="I223" t="str">
-        <v>474.0</v>
+        <v>477.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H224">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I224" t="str">
-        <v>920.0</v>
+        <v>944.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="H225">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="I225" t="str">
-        <v>1379.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H226">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="I226" t="str">
-        <v>2266.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H227">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="I227" t="str">
-        <v>489.0</v>
+        <v>462.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H228">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="I228" t="str">
-        <v>1130.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H229">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I229" t="str">
-        <v>679.0</v>
+        <v>687.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H230">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="I230" t="str">
-        <v>933.0</v>
+        <v>905.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H231">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I231" t="str">
-        <v>456.0</v>
+        <v>490.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H232">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I232" t="str">
-        <v>266.0</v>
+        <v>241.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H233">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I233" t="str">
-        <v>467.0</v>
+        <v>470.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H234">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="I234" t="str">
-        <v>949.0</v>
+        <v>921.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H235">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I235" t="str">
-        <v>1369.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H236">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="I236" t="str">
-        <v>2254.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H237">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I237" t="str">
-        <v>490.0</v>
+        <v>471.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H238">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="I238" t="str">
-        <v>1160.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H239">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I239" t="str">
-        <v>691.0</v>
+        <v>693.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H240">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I240" t="str">
-        <v>946.0</v>
+        <v>947.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H241">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I241" t="str">
-        <v>450.0</v>
+        <v>494.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H242">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I242" t="str">
-        <v>226.0</v>
+        <v>239.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H243">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="I243" t="str">
-        <v>477.0</v>
+        <v>494.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="H244">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I244" t="str">
-        <v>902.0</v>
+        <v>942.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H245">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I245" t="str">
-        <v>1389.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
+        <v>256</v>
+      </c>
+      <c r="H246">
         <v>260</v>
       </c>
-      <c r="H246">
-        <v>274</v>
-      </c>
       <c r="I246" t="str">
-        <v>2290.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H247">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="I247" t="str">
-        <v>499.0</v>
+        <v>453.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="H248">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="I248" t="str">
-        <v>1135.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H249">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I249" t="str">
-        <v>715.0</v>
+        <v>696.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H250">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="I250" t="str">
-        <v>924.0</v>
+        <v>908.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H251">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I251" t="str">
-        <v>464.0</v>
+        <v>474.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H252">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="I252" t="str">
-        <v>244.0</v>
+        <v>271.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H253">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="I253" t="str">
-        <v>479.0</v>
+        <v>494.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H254">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="I254" t="str">
-        <v>922.0</v>
+        <v>927.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H255">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="I255" t="str">
-        <v>1388.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,10 +10109,10 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="H256">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="I256" t="str">
         <v>2297.0</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H257">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I257" t="str">
-        <v>475.0</v>
+        <v>483.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="H258">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="I258" t="str">
-        <v>1126.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H259">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I259" t="str">
-        <v>717.0</v>
+        <v>708.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H260">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="I260" t="str">
-        <v>905.0</v>
+        <v>909.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H261">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="I261" t="str">
-        <v>455.0</v>
+        <v>488.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H262">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="I262" t="str">
-        <v>251.0</v>
+        <v>243.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H263">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I263" t="str">
-        <v>451.0</v>
+        <v>483.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H264">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="I264" t="str">
-        <v>937.0</v>
+        <v>901.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="H265">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I265" t="str">
-        <v>1373.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="H266">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="I266" t="str">
-        <v>2296.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,10 +10527,10 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H267">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I267" t="str">
         <v>467.0</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H268">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="I268" t="str">
-        <v>1160.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H269">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I269" t="str">
-        <v>704.0</v>
+        <v>699.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H270">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="I270" t="str">
-        <v>936.0</v>
+        <v>906.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H271">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="I271" t="str">
-        <v>469.0</v>
+        <v>484.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H272">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I272" t="str">
-        <v>263.0</v>
+        <v>274.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H273">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I273" t="str">
-        <v>494.0</v>
+        <v>475.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="H274">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I274" t="str">
-        <v>914.0</v>
+        <v>936.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="H275">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I275" t="str">
-        <v>1374.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="H276">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I276" t="str">
-        <v>2251.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H277">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="I277" t="str">
-        <v>475.0</v>
+        <v>487.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H278">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="I278" t="str">
-        <v>1142.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H279">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="I279" t="str">
-        <v>711.0</v>
+        <v>682.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H280">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="I280" t="str">
-        <v>927.0</v>
+        <v>906.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="H281">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I281" t="str">
-        <v>460.0</v>
+        <v>466.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H282">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I282" t="str">
-        <v>260.0</v>
+        <v>239.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H283">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="I283" t="str">
-        <v>498.0</v>
+        <v>450.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="H284">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="I284" t="str">
-        <v>919.0</v>
+        <v>913.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="H285">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I285" t="str">
-        <v>1360.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="H286">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I286" t="str">
-        <v>2260.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H287">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="I287" t="str">
-        <v>493.0</v>
+        <v>499.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H288">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="I288" t="str">
-        <v>1129.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H289">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I289" t="str">
-        <v>694.0</v>
+        <v>723.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="H290">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I290" t="str">
-        <v>943.0</v>
+        <v>947.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H291">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="I291" t="str">
-        <v>496.0</v>
+        <v>486.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="H292">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I292" t="str">
-        <v>245.0</v>
+        <v>259.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H293">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I293" t="str">
-        <v>463.0</v>
+        <v>498.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H294">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="I294" t="str">
-        <v>941.0</v>
+        <v>931.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="H295">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I295" t="str">
-        <v>1384.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H296">
         <v>278</v>
       </c>
       <c r="I296" t="str">
-        <v>2267.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H297">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="I297" t="str">
-        <v>476.0</v>
+        <v>490.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H298">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="I298" t="str">
-        <v>1133.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H299">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="I299" t="str">
-        <v>692.0</v>
+        <v>679.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H300">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I300" t="str">
-        <v>918.0</v>
+        <v>913.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H301">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="I301" t="str">
-        <v>455.0</v>
+        <v>492.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="I2" t="str">
-        <v>260.0</v>
+        <v>259.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H3">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I3" t="str">
-        <v>479.0</v>
+        <v>452.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H4">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I4" t="str">
-        <v>900.0</v>
+        <v>942.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H5">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I5" t="str">
-        <v>1373.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="H6">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="I6" t="str">
-        <v>2298.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H7">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I7" t="str">
-        <v>496.0</v>
+        <v>464.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H8">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="I8" t="str">
-        <v>1156.0</v>
+        <v>1134.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="H9">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I9" t="str">
-        <v>717.0</v>
+        <v>677.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="H10">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I10" t="str">
-        <v>907.0</v>
+        <v>940.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H11">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="I11" t="str">
-        <v>465.0</v>
+        <v>486.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H12">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I12" t="str">
-        <v>232.0</v>
+        <v>252.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H13">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="I13" t="str">
-        <v>459.0</v>
+        <v>494.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H14">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I14" t="str">
-        <v>934.0</v>
+        <v>929.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H15">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="I15" t="str">
-        <v>1380.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="H16">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="I16" t="str">
-        <v>2271.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H17">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I17" t="str">
-        <v>471.0</v>
+        <v>496.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H18">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I18" t="str">
-        <v>1167.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H19">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="I19" t="str">
-        <v>717.0</v>
+        <v>685.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H20">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I20" t="str">
-        <v>936.0</v>
+        <v>940.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H21">
         <v>154</v>
       </c>
       <c r="I21" t="str">
-        <v>457.0</v>
+        <v>453.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H22">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="I22" t="str">
-        <v>257.0</v>
+        <v>228.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1258,10 +1258,10 @@
         <v>122</v>
       </c>
       <c r="H23">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I23" t="str">
-        <v>465.0</v>
+        <v>486.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H24">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="I24" t="str">
-        <v>926.0</v>
+        <v>925.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H25">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="I25" t="str">
-        <v>1390.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="H26">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I26" t="str">
-        <v>2288.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H27">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="I27" t="str">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H28">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I28" t="str">
-        <v>1168.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="H29">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I29" t="str">
-        <v>684.0</v>
+        <v>716.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H30">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I30" t="str">
-        <v>923.0</v>
+        <v>912.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H31">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I31" t="str">
-        <v>481.0</v>
+        <v>480.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H32">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="I32" t="str">
-        <v>258.0</v>
+        <v>244.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H33">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I33" t="str">
-        <v>466.0</v>
+        <v>455.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
+        <v>147</v>
+      </c>
+      <c r="H34">
         <v>161</v>
       </c>
-      <c r="H34">
-        <v>191</v>
-      </c>
       <c r="I34" t="str">
-        <v>913.0</v>
+        <v>928.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="H35">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="I35" t="str">
-        <v>1371.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H36">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="I36" t="str">
-        <v>2265.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H37">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="I37" t="str">
-        <v>497.0</v>
+        <v>482.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H38">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I38" t="str">
-        <v>1135.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H39">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I39" t="str">
-        <v>694.0</v>
+        <v>693.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H40">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="I40" t="str">
-        <v>949.0</v>
+        <v>931.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="H41">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="I41" t="str">
-        <v>483.0</v>
+        <v>460.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1980,10 +1980,10 @@
         <v>90</v>
       </c>
       <c r="H42">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="I42" t="str">
-        <v>232.0</v>
+        <v>237.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H43">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="I43" t="str">
-        <v>486.0</v>
+        <v>470.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H44">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="I44" t="str">
-        <v>933.0</v>
+        <v>940.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H45">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="I45" t="str">
-        <v>1372.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H46">
         <v>299</v>
       </c>
       <c r="I46" t="str">
-        <v>2282.0</v>
+        <v>2284.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2173,7 +2173,7 @@
         <v>145</v>
       </c>
       <c r="I47" t="str">
-        <v>489.0</v>
+        <v>460.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H48">
         <v>206</v>
       </c>
       <c r="I48" t="str">
-        <v>1125.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H49">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I49" t="str">
-        <v>700.0</v>
+        <v>689.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H50">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="I50" t="str">
-        <v>930.0</v>
+        <v>906.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H51">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I51" t="str">
-        <v>488.0</v>
+        <v>493.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H52">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="I52" t="str">
-        <v>240.0</v>
+        <v>249.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="H53">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I53" t="str">
-        <v>460.0</v>
+        <v>493.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H54">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I54" t="str">
-        <v>927.0</v>
+        <v>941.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2474,10 +2474,10 @@
         <v>210</v>
       </c>
       <c r="H55">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="I55" t="str">
-        <v>1369.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H56">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="I56" t="str">
-        <v>2282.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H57">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I57" t="str">
-        <v>463.0</v>
+        <v>485.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="H58">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="I58" t="str">
-        <v>1172.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="H59">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="I59" t="str">
-        <v>710.0</v>
+        <v>692.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2664,10 +2664,10 @@
         <v>112</v>
       </c>
       <c r="H60">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I60" t="str">
-        <v>908.0</v>
+        <v>932.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H61">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="I61" t="str">
-        <v>472.0</v>
+        <v>480.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H62">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I62" t="str">
-        <v>266.0</v>
+        <v>242.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H63">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="I63" t="str">
-        <v>485.0</v>
+        <v>463.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H64">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="I64" t="str">
-        <v>921.0</v>
+        <v>902.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H65">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="I65" t="str">
-        <v>1373.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H66">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="I66" t="str">
-        <v>2289.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H67">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="I67" t="str">
-        <v>464.0</v>
+        <v>473.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H68">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I68" t="str">
-        <v>1128.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H69">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I69" t="str">
-        <v>695.0</v>
+        <v>705.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,10 +3041,10 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H70">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I70" t="str">
         <v>943.0</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H71">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="I71" t="str">
-        <v>452.0</v>
+        <v>494.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H72">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="I72" t="str">
-        <v>261.0</v>
+        <v>248.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H73">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="I73" t="str">
-        <v>488.0</v>
+        <v>456.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H74">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I74" t="str">
-        <v>915.0</v>
+        <v>936.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="H75">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="I75" t="str">
-        <v>1389.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H76">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="I76" t="str">
-        <v>2270.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H77">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="I77" t="str">
-        <v>498.0</v>
+        <v>455.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H78">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I78" t="str">
-        <v>1131.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H79">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I79" t="str">
-        <v>712.0</v>
+        <v>699.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H80">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I80" t="str">
-        <v>926.0</v>
+        <v>901.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H81">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="I81" t="str">
-        <v>491.0</v>
+        <v>483.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="H82">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I82" t="str">
-        <v>225.0</v>
+        <v>232.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="H83">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="I83" t="str">
-        <v>472.0</v>
+        <v>474.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H84">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="I84" t="str">
-        <v>911.0</v>
+        <v>905.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="H85">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I85" t="str">
-        <v>1352.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H86">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="I86" t="str">
-        <v>2252.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="H87">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="I87" t="str">
-        <v>490.0</v>
+        <v>467.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H88">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="I88" t="str">
-        <v>1146.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3766,10 +3766,10 @@
         <v>131</v>
       </c>
       <c r="H89">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="I89" t="str">
-        <v>677.0</v>
+        <v>701.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H90">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I90" t="str">
-        <v>919.0</v>
+        <v>945.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="H91">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="I91" t="str">
-        <v>455.0</v>
+        <v>461.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H92">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I92" t="str">
-        <v>228.0</v>
+        <v>240.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H93">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I93" t="str">
-        <v>486.0</v>
+        <v>495.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H94">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I94" t="str">
-        <v>909.0</v>
+        <v>903.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="H95">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="I95" t="str">
-        <v>1355.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H96">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="I96" t="str">
-        <v>2253.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H97">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I97" t="str">
-        <v>490.0</v>
+        <v>498.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4108,10 +4108,10 @@
         <v>166</v>
       </c>
       <c r="H98">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I98" t="str">
-        <v>1138.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H99">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="I99" t="str">
-        <v>677.0</v>
+        <v>700.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H100">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I100" t="str">
-        <v>934.0</v>
+        <v>915.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="H101">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="I101" t="str">
-        <v>486.0</v>
+        <v>479.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H102">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I102" t="str">
-        <v>266.0</v>
+        <v>271.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H103">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I103" t="str">
-        <v>463.0</v>
+        <v>465.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4336,10 +4336,10 @@
         <v>162</v>
       </c>
       <c r="H104">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="I104" t="str">
-        <v>926.0</v>
+        <v>944.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H105">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="I105" t="str">
-        <v>1391.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="H106">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="I106" t="str">
-        <v>2284.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H107">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="I107" t="str">
-        <v>465.0</v>
+        <v>451.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H108">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I108" t="str">
-        <v>1154.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H109">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I109" t="str">
-        <v>678.0</v>
+        <v>695.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H110">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="I110" t="str">
-        <v>946.0</v>
+        <v>901.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="H111">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="I111" t="str">
-        <v>478.0</v>
+        <v>498.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H112">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="I112" t="str">
-        <v>238.0</v>
+        <v>271.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H113">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I113" t="str">
-        <v>450.0</v>
+        <v>489.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4716,10 +4716,10 @@
         <v>162</v>
       </c>
       <c r="H114">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="I114" t="str">
-        <v>928.0</v>
+        <v>936.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="H115">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="I115" t="str">
-        <v>1380.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="H116">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="I116" t="str">
-        <v>2255.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="H117">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="I117" t="str">
-        <v>455.0</v>
+        <v>462.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="H118">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="I118" t="str">
-        <v>1170.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H119">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I119" t="str">
-        <v>680.0</v>
+        <v>715.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H120">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="I120" t="str">
-        <v>949.0</v>
+        <v>932.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H121">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="I121" t="str">
-        <v>461.0</v>
+        <v>490.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H122">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="I122" t="str">
-        <v>240.0</v>
+        <v>239.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H123">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="I123" t="str">
-        <v>493.0</v>
+        <v>484.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="H124">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="I124" t="str">
-        <v>934.0</v>
+        <v>944.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H125">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="I125" t="str">
-        <v>1354.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H126">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="I126" t="str">
-        <v>2259.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H127">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="I127" t="str">
-        <v>499.0</v>
+        <v>481.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H128">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I128" t="str">
-        <v>1155.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="H129">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I129" t="str">
-        <v>687.0</v>
+        <v>694.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5324,10 +5324,10 @@
         <v>117</v>
       </c>
       <c r="H130">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="I130" t="str">
-        <v>936.0</v>
+        <v>924.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H131">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="I131" t="str">
-        <v>474.0</v>
+        <v>462.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H132">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I132" t="str">
-        <v>245.0</v>
+        <v>247.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5438,7 +5438,7 @@
         <v>126</v>
       </c>
       <c r="H133">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I133" t="str">
         <v>466.0</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="H134">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="I134" t="str">
-        <v>904.0</v>
+        <v>908.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,7 +5511,7 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="H135">
         <v>224</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
+        <v>256</v>
+      </c>
+      <c r="H136">
         <v>260</v>
       </c>
-      <c r="H136">
-        <v>282</v>
-      </c>
       <c r="I136" t="str">
-        <v>2263.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H137">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="I137" t="str">
-        <v>468.0</v>
+        <v>483.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H138">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I138" t="str">
-        <v>1140.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="H139">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="I139" t="str">
-        <v>689.0</v>
+        <v>676.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H140">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I140" t="str">
-        <v>925.0</v>
+        <v>900.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H141">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="I141" t="str">
-        <v>469.0</v>
+        <v>462.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H142">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I142" t="str">
-        <v>236.0</v>
+        <v>226.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H143">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I143" t="str">
-        <v>485.0</v>
+        <v>497.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H144">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="I144" t="str">
-        <v>916.0</v>
+        <v>946.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="H145">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="I145" t="str">
-        <v>1392.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H146">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="I146" t="str">
-        <v>2268.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H147">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I147" t="str">
-        <v>465.0</v>
+        <v>450.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H148">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="I148" t="str">
-        <v>1159.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="H149">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="I149" t="str">
-        <v>712.0</v>
+        <v>682.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H150">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="I150" t="str">
-        <v>924.0</v>
+        <v>921.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H151">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="I151" t="str">
-        <v>470.0</v>
+        <v>491.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H152">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="I152" t="str">
-        <v>271.0</v>
+        <v>262.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H153">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="I153" t="str">
-        <v>483.0</v>
+        <v>453.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H154">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I154" t="str">
-        <v>903.0</v>
+        <v>925.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H155">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="I155" t="str">
-        <v>1359.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H156">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="I156" t="str">
-        <v>2275.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H157">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I157" t="str">
-        <v>489.0</v>
+        <v>454.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H158">
         <v>181</v>
       </c>
       <c r="I158" t="str">
-        <v>1148.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H159">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I159" t="str">
-        <v>710.0</v>
+        <v>717.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="H160">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="I160" t="str">
-        <v>916.0</v>
+        <v>901.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H161">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I161" t="str">
-        <v>459.0</v>
+        <v>486.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H162">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="I162" t="str">
-        <v>246.0</v>
+        <v>272.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
+        <v>113</v>
+      </c>
+      <c r="H163">
         <v>128</v>
       </c>
-      <c r="H163">
-        <v>151</v>
-      </c>
       <c r="I163" t="str">
-        <v>470.0</v>
+        <v>483.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H164">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="I164" t="str">
-        <v>925.0</v>
+        <v>921.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H165">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="I165" t="str">
-        <v>1355.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H166">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="I166" t="str">
-        <v>2288.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H167">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="I167" t="str">
-        <v>496.0</v>
+        <v>454.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H168">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I168" t="str">
-        <v>1167.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H169">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I169" t="str">
-        <v>715.0</v>
+        <v>706.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H170">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I170" t="str">
-        <v>912.0</v>
+        <v>913.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H171">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I171" t="str">
-        <v>499.0</v>
+        <v>482.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H172">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="I172" t="str">
-        <v>257.0</v>
+        <v>265.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H173">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="I173" t="str">
-        <v>460.0</v>
+        <v>465.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H174">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="I174" t="str">
-        <v>902.0</v>
+        <v>901.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H175">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I175" t="str">
-        <v>1354.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H176">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="I176" t="str">
-        <v>2281.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H177">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="I177" t="str">
-        <v>492.0</v>
+        <v>451.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H178">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I178" t="str">
-        <v>1170.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H179">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="I179" t="str">
-        <v>675.0</v>
+        <v>693.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H180">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I180" t="str">
-        <v>945.0</v>
+        <v>912.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H181">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I181" t="str">
-        <v>455.0</v>
+        <v>450.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="H182">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I182" t="str">
-        <v>263.0</v>
+        <v>234.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H183">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="I183" t="str">
-        <v>486.0</v>
+        <v>461.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H184">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="I184" t="str">
-        <v>923.0</v>
+        <v>943.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H185">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="I185" t="str">
-        <v>1372.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H186">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="I186" t="str">
-        <v>2272.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H187">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="I187" t="str">
-        <v>470.0</v>
+        <v>473.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H188">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="I188" t="str">
-        <v>1163.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="H189">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I189" t="str">
-        <v>686.0</v>
+        <v>721.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H190">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="I190" t="str">
-        <v>923.0</v>
+        <v>907.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="H191">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="I191" t="str">
-        <v>460.0</v>
+        <v>464.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H192">
         <v>100</v>
       </c>
       <c r="I192" t="str">
-        <v>236.0</v>
+        <v>241.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H193">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="I193" t="str">
-        <v>495.0</v>
+        <v>488.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H194">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="I194" t="str">
-        <v>943.0</v>
+        <v>933.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="H195">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I195" t="str">
-        <v>1364.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H196">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="I196" t="str">
-        <v>2259.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H197">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="I197" t="str">
-        <v>474.0</v>
+        <v>456.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H198">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I198" t="str">
-        <v>1157.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H199">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="I199" t="str">
-        <v>685.0</v>
+        <v>696.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H200">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="I200" t="str">
-        <v>938.0</v>
+        <v>926.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H201">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I201" t="str">
-        <v>479.0</v>
+        <v>478.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8060,10 +8060,10 @@
         <v>89</v>
       </c>
       <c r="H202">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I202" t="str">
-        <v>266.0</v>
+        <v>270.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H203">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="I203" t="str">
-        <v>468.0</v>
+        <v>483.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H204">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="I204" t="str">
-        <v>922.0</v>
+        <v>933.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H205">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I205" t="str">
-        <v>1383.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H206">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="I206" t="str">
-        <v>2258.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8250,10 +8250,10 @@
         <v>111</v>
       </c>
       <c r="H207">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I207" t="str">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H208">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I208" t="str">
-        <v>1148.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H209">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="I209" t="str">
-        <v>703.0</v>
+        <v>680.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H210">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="I210" t="str">
-        <v>931.0</v>
+        <v>919.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H211">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I211" t="str">
-        <v>491.0</v>
+        <v>452.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H212">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="I212" t="str">
-        <v>229.0</v>
+        <v>239.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H213">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I213" t="str">
-        <v>488.0</v>
+        <v>494.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="H214">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="I214" t="str">
-        <v>935.0</v>
+        <v>901.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H215">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I215" t="str">
-        <v>1377.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H216">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="I216" t="str">
-        <v>2251.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H217">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="I217" t="str">
-        <v>480.0</v>
+        <v>489.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="H218">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="I218" t="str">
-        <v>1151.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H219">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="I219" t="str">
-        <v>675.0</v>
+        <v>703.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H220">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I220" t="str">
-        <v>944.0</v>
+        <v>904.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H221">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I221" t="str">
-        <v>489.0</v>
+        <v>467.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H222">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I222" t="str">
-        <v>266.0</v>
+        <v>261.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H223">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="I223" t="str">
-        <v>477.0</v>
+        <v>457.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="H224">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="I224" t="str">
-        <v>944.0</v>
+        <v>927.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="H225">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I225" t="str">
-        <v>1395.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H226">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="I226" t="str">
-        <v>2294.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H227">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I227" t="str">
-        <v>462.0</v>
+        <v>470.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H228">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I228" t="str">
-        <v>1165.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H229">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="I229" t="str">
-        <v>687.0</v>
+        <v>696.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H230">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I230" t="str">
-        <v>905.0</v>
+        <v>936.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H231">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I231" t="str">
-        <v>490.0</v>
+        <v>471.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="H232">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="I232" t="str">
-        <v>241.0</v>
+        <v>262.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H233">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="I233" t="str">
-        <v>470.0</v>
+        <v>484.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="H234">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I234" t="str">
-        <v>921.0</v>
+        <v>949.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="H235">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="I235" t="str">
-        <v>1374.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="H236">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="I236" t="str">
-        <v>2256.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="H237">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="I237" t="str">
-        <v>471.0</v>
+        <v>492.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H238">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="I238" t="str">
-        <v>1138.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H239">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="I239" t="str">
-        <v>693.0</v>
+        <v>706.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H240">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="I240" t="str">
-        <v>947.0</v>
+        <v>912.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="H241">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="I241" t="str">
-        <v>494.0</v>
+        <v>458.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H242">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="I242" t="str">
-        <v>239.0</v>
+        <v>253.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H243">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I243" t="str">
-        <v>494.0</v>
+        <v>475.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="H244">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I244" t="str">
-        <v>942.0</v>
+        <v>932.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H245">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I245" t="str">
-        <v>1386.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="H246">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="I246" t="str">
-        <v>2293.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H247">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I247" t="str">
-        <v>453.0</v>
+        <v>490.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="H248">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="I248" t="str">
-        <v>1161.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H249">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I249" t="str">
-        <v>696.0</v>
+        <v>701.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H250">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I250" t="str">
-        <v>908.0</v>
+        <v>940.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H251">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="I251" t="str">
-        <v>474.0</v>
+        <v>450.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="H252">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="I252" t="str">
-        <v>271.0</v>
+        <v>247.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H253">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="I253" t="str">
-        <v>494.0</v>
+        <v>462.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="H254">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="I254" t="str">
-        <v>927.0</v>
+        <v>925.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="H255">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="I255" t="str">
-        <v>1370.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="H256">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="I256" t="str">
-        <v>2297.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="H257">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="I257" t="str">
-        <v>483.0</v>
+        <v>499.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H258">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="I258" t="str">
-        <v>1149.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H259">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="I259" t="str">
-        <v>708.0</v>
+        <v>712.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H260">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="I260" t="str">
-        <v>909.0</v>
+        <v>906.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="H261">
         <v>163</v>
       </c>
       <c r="I261" t="str">
-        <v>488.0</v>
+        <v>489.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H262">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="I262" t="str">
-        <v>243.0</v>
+        <v>251.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H263">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="I263" t="str">
-        <v>483.0</v>
+        <v>465.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="H264">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="I264" t="str">
-        <v>901.0</v>
+        <v>902.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H265">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="I265" t="str">
-        <v>1387.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H266">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I266" t="str">
-        <v>2280.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H267">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="I267" t="str">
-        <v>467.0</v>
+        <v>479.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H268">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="I268" t="str">
-        <v>1137.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H269">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I269" t="str">
-        <v>699.0</v>
+        <v>692.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H270">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="I270" t="str">
-        <v>906.0</v>
+        <v>909.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H271">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I271" t="str">
-        <v>484.0</v>
+        <v>473.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H272">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I272" t="str">
-        <v>274.0</v>
+        <v>236.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="H273">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="I273" t="str">
-        <v>475.0</v>
+        <v>488.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H274">
         <v>173</v>
       </c>
       <c r="I274" t="str">
-        <v>936.0</v>
+        <v>934.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H275">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I275" t="str">
-        <v>1377.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="H276">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="I276" t="str">
-        <v>2266.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H277">
         <v>128</v>
       </c>
       <c r="I277" t="str">
-        <v>487.0</v>
+        <v>483.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H278">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="I278" t="str">
-        <v>1166.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H279">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I279" t="str">
-        <v>682.0</v>
+        <v>707.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H280">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I280" t="str">
-        <v>906.0</v>
+        <v>900.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H281">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="I281" t="str">
-        <v>466.0</v>
+        <v>455.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H282">
         <v>115</v>
       </c>
       <c r="I282" t="str">
-        <v>239.0</v>
+        <v>274.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H283">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="I283" t="str">
-        <v>450.0</v>
+        <v>457.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H284">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I284" t="str">
-        <v>913.0</v>
+        <v>909.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H285">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="I285" t="str">
-        <v>1384.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="H286">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="I286" t="str">
-        <v>2272.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H287">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I287" t="str">
-        <v>499.0</v>
+        <v>471.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H288">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I288" t="str">
-        <v>1164.0</v>
+        <v>1128.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H289">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I289" t="str">
-        <v>723.0</v>
+        <v>691.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H290">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I290" t="str">
-        <v>947.0</v>
+        <v>924.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H291">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I291" t="str">
-        <v>486.0</v>
+        <v>485.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11480,10 +11480,10 @@
         <v>102</v>
       </c>
       <c r="H292">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="I292" t="str">
-        <v>259.0</v>
+        <v>268.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H293">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I293" t="str">
-        <v>498.0</v>
+        <v>468.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H294">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="I294" t="str">
-        <v>931.0</v>
+        <v>935.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H295">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I295" t="str">
-        <v>1379.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11632,10 +11632,10 @@
         <v>259</v>
       </c>
       <c r="H296">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="I296" t="str">
-        <v>2250.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H297">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="I297" t="str">
-        <v>490.0</v>
+        <v>488.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H298">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="I298" t="str">
-        <v>1143.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="H299">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="I299" t="str">
-        <v>679.0</v>
+        <v>720.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H300">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I300" t="str">
-        <v>913.0</v>
+        <v>914.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H301">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="I301" t="str">
-        <v>492.0</v>
+        <v>479.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I2" t="str">
-        <v>259.0</v>
+        <v>270.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I3" t="str">
-        <v>452.0</v>
+        <v>463.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H4">
         <v>175</v>
       </c>
       <c r="I4" t="str">
-        <v>942.0</v>
+        <v>923.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -574,10 +574,10 @@
         <v>191</v>
       </c>
       <c r="H5">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I5" t="str">
-        <v>1399.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="H6">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I6" t="str">
-        <v>2274.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H7">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="I7" t="str">
-        <v>464.0</v>
+        <v>488.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H8">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="I8" t="str">
-        <v>1134.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H9">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I9" t="str">
-        <v>677.0</v>
+        <v>687.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H10">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I10" t="str">
-        <v>940.0</v>
+        <v>942.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H11">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="I11" t="str">
-        <v>486.0</v>
+        <v>488.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="H12">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I12" t="str">
-        <v>252.0</v>
+        <v>227.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H13">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I13" t="str">
-        <v>494.0</v>
+        <v>456.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H14">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="I14" t="str">
-        <v>929.0</v>
+        <v>901.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="H15">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="I15" t="str">
-        <v>1365.0</v>
+        <v>1382.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H16">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="I16" t="str">
-        <v>2275.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H17">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I17" t="str">
-        <v>496.0</v>
+        <v>459.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H18">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I18" t="str">
-        <v>1127.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H19">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="I19" t="str">
-        <v>685.0</v>
+        <v>719.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H20">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="I20" t="str">
-        <v>940.0</v>
+        <v>917.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H21">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I21" t="str">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H22">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="I22" t="str">
-        <v>228.0</v>
+        <v>262.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H23">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I23" t="str">
-        <v>486.0</v>
+        <v>493.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H24">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I24" t="str">
-        <v>925.0</v>
+        <v>937.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H25">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="I25" t="str">
-        <v>1353.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1372,10 +1372,10 @@
         <v>252</v>
       </c>
       <c r="H26">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I26" t="str">
-        <v>2268.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H27">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I27" t="str">
-        <v>462.0</v>
+        <v>470.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H28">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="I28" t="str">
-        <v>1133.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H29">
         <v>179</v>
       </c>
       <c r="I29" t="str">
-        <v>716.0</v>
+        <v>680.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H30">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="I30" t="str">
-        <v>912.0</v>
+        <v>915.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H31">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="I31" t="str">
-        <v>480.0</v>
+        <v>457.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H32">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I32" t="str">
-        <v>244.0</v>
+        <v>262.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H33">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="I33" t="str">
-        <v>455.0</v>
+        <v>453.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H34">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="I34" t="str">
-        <v>928.0</v>
+        <v>911.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="H35">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="I35" t="str">
-        <v>1388.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H36">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="I36" t="str">
-        <v>2252.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H37">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="I37" t="str">
-        <v>482.0</v>
+        <v>465.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H38">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I38" t="str">
-        <v>1171.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1869,7 +1869,7 @@
         <v>179</v>
       </c>
       <c r="I39" t="str">
-        <v>693.0</v>
+        <v>684.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H40">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="I40" t="str">
-        <v>931.0</v>
+        <v>930.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H41">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="I41" t="str">
-        <v>460.0</v>
+        <v>484.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H42">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I42" t="str">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,10 +2015,10 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H43">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I43" t="str">
         <v>470.0</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H44">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="I44" t="str">
-        <v>940.0</v>
+        <v>929.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,10 +2091,10 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H45">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I45" t="str">
         <v>1377.0</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="H46">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="I46" t="str">
-        <v>2284.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H47">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I47" t="str">
-        <v>460.0</v>
+        <v>481.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="H48">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="I48" t="str">
-        <v>1164.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H49">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="I49" t="str">
-        <v>689.0</v>
+        <v>678.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H50">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="I50" t="str">
-        <v>906.0</v>
+        <v>904.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="H51">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I51" t="str">
-        <v>493.0</v>
+        <v>460.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2360,10 +2360,10 @@
         <v>105</v>
       </c>
       <c r="H52">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I52" t="str">
-        <v>249.0</v>
+        <v>244.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H53">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="I53" t="str">
-        <v>493.0</v>
+        <v>479.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H54">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="I54" t="str">
-        <v>941.0</v>
+        <v>913.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2474,10 +2474,10 @@
         <v>210</v>
       </c>
       <c r="H55">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="I55" t="str">
-        <v>1377.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H56">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="I56" t="str">
-        <v>2298.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H57">
         <v>143</v>
       </c>
       <c r="I57" t="str">
-        <v>485.0</v>
+        <v>469.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H58">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I58" t="str">
-        <v>1170.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H59">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="I59" t="str">
-        <v>692.0</v>
+        <v>695.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H60">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="I60" t="str">
-        <v>932.0</v>
+        <v>942.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H61">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="I61" t="str">
-        <v>480.0</v>
+        <v>489.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H62">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="I62" t="str">
-        <v>242.0</v>
+        <v>225.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2778,10 +2778,10 @@
         <v>132</v>
       </c>
       <c r="H63">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I63" t="str">
-        <v>463.0</v>
+        <v>481.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="H64">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I64" t="str">
-        <v>902.0</v>
+        <v>912.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H65">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I65" t="str">
-        <v>1354.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="H66">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="I66" t="str">
-        <v>2297.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="H67">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="I67" t="str">
-        <v>473.0</v>
+        <v>499.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H68">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I68" t="str">
-        <v>1125.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="H69">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I69" t="str">
-        <v>705.0</v>
+        <v>695.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3044,10 +3044,10 @@
         <v>99</v>
       </c>
       <c r="H70">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I70" t="str">
-        <v>943.0</v>
+        <v>932.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H71">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I71" t="str">
-        <v>494.0</v>
+        <v>478.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H72">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I72" t="str">
-        <v>248.0</v>
+        <v>230.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H73">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="I73" t="str">
-        <v>456.0</v>
+        <v>454.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H74">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I74" t="str">
-        <v>936.0</v>
+        <v>905.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="H75">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I75" t="str">
-        <v>1363.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H76">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="I76" t="str">
-        <v>2297.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H77">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="I77" t="str">
-        <v>455.0</v>
+        <v>452.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H78">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="I78" t="str">
-        <v>1162.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H79">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I79" t="str">
-        <v>699.0</v>
+        <v>705.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="H80">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="I80" t="str">
-        <v>901.0</v>
+        <v>931.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H81">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="I81" t="str">
-        <v>483.0</v>
+        <v>452.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="H82">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I82" t="str">
-        <v>232.0</v>
+        <v>258.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H83">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="I83" t="str">
-        <v>474.0</v>
+        <v>452.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="H84">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="I84" t="str">
-        <v>905.0</v>
+        <v>903.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="H85">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="I85" t="str">
-        <v>1380.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H86">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="I86" t="str">
-        <v>2297.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="H87">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I87" t="str">
-        <v>467.0</v>
+        <v>475.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H88">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="I88" t="str">
-        <v>1148.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H89">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="I89" t="str">
-        <v>701.0</v>
+        <v>708.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H90">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I90" t="str">
-        <v>945.0</v>
+        <v>902.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="H91">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I91" t="str">
-        <v>461.0</v>
+        <v>478.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H92">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I92" t="str">
-        <v>240.0</v>
+        <v>247.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3918,10 +3918,10 @@
         <v>126</v>
       </c>
       <c r="H93">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I93" t="str">
-        <v>495.0</v>
+        <v>470.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H94">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="I94" t="str">
-        <v>903.0</v>
+        <v>937.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H95">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="I95" t="str">
-        <v>1362.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H96">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="I96" t="str">
-        <v>2273.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="H97">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I97" t="str">
-        <v>498.0</v>
+        <v>496.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H98">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="I98" t="str">
-        <v>1150.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H99">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="I99" t="str">
-        <v>700.0</v>
+        <v>720.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H100">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="I100" t="str">
-        <v>915.0</v>
+        <v>925.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H101">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="I101" t="str">
-        <v>479.0</v>
+        <v>451.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H102">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="I102" t="str">
-        <v>271.0</v>
+        <v>239.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H103">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I103" t="str">
-        <v>465.0</v>
+        <v>460.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H104">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I104" t="str">
-        <v>944.0</v>
+        <v>905.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H105">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I105" t="str">
-        <v>1385.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H106">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="I106" t="str">
-        <v>2296.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H107">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="I107" t="str">
-        <v>451.0</v>
+        <v>478.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H108">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="I108" t="str">
-        <v>1126.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H109">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I109" t="str">
-        <v>695.0</v>
+        <v>706.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H110">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="I110" t="str">
-        <v>901.0</v>
+        <v>943.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H111">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="I111" t="str">
-        <v>498.0</v>
+        <v>493.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H112">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="I112" t="str">
-        <v>271.0</v>
+        <v>243.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="H113">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="I113" t="str">
-        <v>489.0</v>
+        <v>465.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
+        <v>160</v>
+      </c>
+      <c r="H114">
         <v>162</v>
       </c>
-      <c r="H114">
-        <v>181</v>
-      </c>
       <c r="I114" t="str">
-        <v>936.0</v>
+        <v>929.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H115">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I115" t="str">
-        <v>1379.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="H116">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="I116" t="str">
-        <v>2282.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="H117">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="I117" t="str">
-        <v>462.0</v>
+        <v>495.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H118">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="I118" t="str">
-        <v>1149.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="H119">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="I119" t="str">
-        <v>715.0</v>
+        <v>704.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H120">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="I120" t="str">
-        <v>932.0</v>
+        <v>908.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H121">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="I121" t="str">
-        <v>490.0</v>
+        <v>483.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H122">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I122" t="str">
-        <v>239.0</v>
+        <v>232.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H123">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="I123" t="str">
-        <v>484.0</v>
+        <v>470.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H124">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I124" t="str">
-        <v>944.0</v>
+        <v>920.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H125">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="I125" t="str">
-        <v>1392.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H126">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="I126" t="str">
-        <v>2281.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,10 +5207,10 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H127">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="I127" t="str">
         <v>481.0</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H128">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="I128" t="str">
-        <v>1153.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H129">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I129" t="str">
-        <v>694.0</v>
+        <v>710.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="H130">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="I130" t="str">
-        <v>924.0</v>
+        <v>947.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,10 +5359,10 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H131">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="I131" t="str">
         <v>462.0</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H132">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I132" t="str">
-        <v>247.0</v>
+        <v>261.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H133">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I133" t="str">
-        <v>466.0</v>
+        <v>470.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H134">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I134" t="str">
-        <v>908.0</v>
+        <v>912.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H135">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I135" t="str">
-        <v>1351.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H136">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I136" t="str">
-        <v>2269.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H137">
         <v>140</v>
       </c>
       <c r="I137" t="str">
-        <v>483.0</v>
+        <v>457.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H138">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="I138" t="str">
-        <v>1138.0</v>
+        <v>1145.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H139">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I139" t="str">
-        <v>676.0</v>
+        <v>695.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H140">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="I140" t="str">
-        <v>900.0</v>
+        <v>916.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H141">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I141" t="str">
-        <v>462.0</v>
+        <v>476.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H142">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="I142" t="str">
-        <v>226.0</v>
+        <v>251.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5818,10 +5818,10 @@
         <v>111</v>
       </c>
       <c r="H143">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I143" t="str">
-        <v>497.0</v>
+        <v>452.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H144">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="I144" t="str">
-        <v>946.0</v>
+        <v>911.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H145">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I145" t="str">
-        <v>1358.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H146">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="I146" t="str">
-        <v>2282.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H147">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I147" t="str">
-        <v>450.0</v>
+        <v>495.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H148">
         <v>187</v>
       </c>
       <c r="I148" t="str">
-        <v>1141.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H149">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I149" t="str">
-        <v>682.0</v>
+        <v>678.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="H150">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="I150" t="str">
-        <v>921.0</v>
+        <v>947.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H151">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I151" t="str">
-        <v>491.0</v>
+        <v>452.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H152">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="I152" t="str">
-        <v>262.0</v>
+        <v>241.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6198,10 +6198,10 @@
         <v>128</v>
       </c>
       <c r="H153">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="I153" t="str">
-        <v>453.0</v>
+        <v>496.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H154">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="I154" t="str">
-        <v>925.0</v>
+        <v>938.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H155">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I155" t="str">
-        <v>1365.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6312,10 +6312,10 @@
         <v>244</v>
       </c>
       <c r="H156">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I156" t="str">
-        <v>2268.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H157">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="I157" t="str">
-        <v>454.0</v>
+        <v>458.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H158">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="I158" t="str">
-        <v>1169.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H159">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I159" t="str">
-        <v>717.0</v>
+        <v>719.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H160">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I160" t="str">
-        <v>901.0</v>
+        <v>947.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H161">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I161" t="str">
-        <v>486.0</v>
+        <v>493.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
+        <v>85</v>
+      </c>
+      <c r="H162">
         <v>104</v>
       </c>
-      <c r="H162">
-        <v>112</v>
-      </c>
       <c r="I162" t="str">
-        <v>272.0</v>
+        <v>269.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="H163">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="I163" t="str">
-        <v>483.0</v>
+        <v>452.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H164">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I164" t="str">
-        <v>921.0</v>
+        <v>907.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="H165">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="I165" t="str">
-        <v>1385.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H166">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="I166" t="str">
-        <v>2258.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H167">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="I167" t="str">
-        <v>454.0</v>
+        <v>475.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="H168">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I168" t="str">
-        <v>1139.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="H169">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I169" t="str">
-        <v>706.0</v>
+        <v>715.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H170">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I170" t="str">
-        <v>913.0</v>
+        <v>938.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H171">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I171" t="str">
-        <v>482.0</v>
+        <v>484.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H172">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I172" t="str">
-        <v>265.0</v>
+        <v>251.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H173">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I173" t="str">
-        <v>465.0</v>
+        <v>464.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="H174">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="I174" t="str">
-        <v>901.0</v>
+        <v>947.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H175">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="I175" t="str">
-        <v>1362.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7072,10 +7072,10 @@
         <v>252</v>
       </c>
       <c r="H176">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="I176" t="str">
-        <v>2266.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H177">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="I177" t="str">
-        <v>451.0</v>
+        <v>495.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="H178">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I178" t="str">
-        <v>1129.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="H179">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I179" t="str">
-        <v>693.0</v>
+        <v>677.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H180">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I180" t="str">
-        <v>912.0</v>
+        <v>928.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H181">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="I181" t="str">
-        <v>450.0</v>
+        <v>492.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H182">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="I182" t="str">
-        <v>234.0</v>
+        <v>259.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H183">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="I183" t="str">
-        <v>461.0</v>
+        <v>483.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="H184">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="I184" t="str">
-        <v>943.0</v>
+        <v>936.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H185">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I185" t="str">
-        <v>1388.0</v>
+        <v>1393.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H186">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I186" t="str">
-        <v>2273.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H187">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I187" t="str">
-        <v>473.0</v>
+        <v>479.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H188">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I188" t="str">
-        <v>1151.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H189">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="I189" t="str">
-        <v>721.0</v>
+        <v>722.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H190">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="I190" t="str">
-        <v>907.0</v>
+        <v>925.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="H191">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I191" t="str">
-        <v>464.0</v>
+        <v>468.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H192">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I192" t="str">
-        <v>241.0</v>
+        <v>263.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H193">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I193" t="str">
-        <v>488.0</v>
+        <v>474.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="H194">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I194" t="str">
-        <v>933.0</v>
+        <v>944.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7794,10 +7794,10 @@
         <v>206</v>
       </c>
       <c r="H195">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="I195" t="str">
-        <v>1368.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H196">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="I196" t="str">
-        <v>2299.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H197">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="I197" t="str">
-        <v>456.0</v>
+        <v>461.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H198">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I198" t="str">
-        <v>1159.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H199">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I199" t="str">
-        <v>696.0</v>
+        <v>675.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H200">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="I200" t="str">
-        <v>926.0</v>
+        <v>919.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H201">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="I201" t="str">
-        <v>478.0</v>
+        <v>463.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H202">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I202" t="str">
-        <v>270.0</v>
+        <v>266.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="H203">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I203" t="str">
-        <v>483.0</v>
+        <v>489.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H204">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="I204" t="str">
-        <v>933.0</v>
+        <v>935.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H205">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="I205" t="str">
-        <v>1391.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H206">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="I206" t="str">
-        <v>2296.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H207">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I207" t="str">
-        <v>471.0</v>
+        <v>489.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H208">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="I208" t="str">
-        <v>1174.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H209">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I209" t="str">
-        <v>680.0</v>
+        <v>714.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="H210">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="I210" t="str">
-        <v>919.0</v>
+        <v>935.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="H211">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="I211" t="str">
-        <v>452.0</v>
+        <v>499.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H212">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="I212" t="str">
-        <v>239.0</v>
+        <v>249.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H213">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="I213" t="str">
-        <v>494.0</v>
+        <v>459.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H214">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I214" t="str">
-        <v>901.0</v>
+        <v>941.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H215">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I215" t="str">
-        <v>1357.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H216">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="I216" t="str">
-        <v>2267.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8630,10 +8630,10 @@
         <v>105</v>
       </c>
       <c r="H217">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I217" t="str">
-        <v>489.0</v>
+        <v>455.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H218">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="I218" t="str">
-        <v>1136.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H219">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I219" t="str">
-        <v>703.0</v>
+        <v>709.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H220">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="I220" t="str">
-        <v>904.0</v>
+        <v>907.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H221">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="I221" t="str">
-        <v>467.0</v>
+        <v>466.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="H222">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I222" t="str">
-        <v>261.0</v>
+        <v>260.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H223">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="I223" t="str">
-        <v>457.0</v>
+        <v>461.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H224">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I224" t="str">
-        <v>927.0</v>
+        <v>928.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H225">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I225" t="str">
-        <v>1369.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H226">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I226" t="str">
-        <v>2267.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H227">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I227" t="str">
-        <v>470.0</v>
+        <v>489.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="H228">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="I228" t="str">
-        <v>1130.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9086,10 +9086,10 @@
         <v>132</v>
       </c>
       <c r="H229">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="I229" t="str">
-        <v>696.0</v>
+        <v>700.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="H230">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="I230" t="str">
-        <v>936.0</v>
+        <v>910.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9162,10 +9162,10 @@
         <v>134</v>
       </c>
       <c r="H231">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="I231" t="str">
-        <v>471.0</v>
+        <v>491.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9200,10 +9200,10 @@
         <v>105</v>
       </c>
       <c r="H232">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="I232" t="str">
-        <v>262.0</v>
+        <v>249.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H233">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I233" t="str">
-        <v>484.0</v>
+        <v>463.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9276,10 +9276,10 @@
         <v>167</v>
       </c>
       <c r="H234">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I234" t="str">
-        <v>949.0</v>
+        <v>930.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="H235">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="I235" t="str">
-        <v>1363.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="H236">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="I236" t="str">
-        <v>2263.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="H237">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="I237" t="str">
-        <v>492.0</v>
+        <v>498.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H238">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="I238" t="str">
-        <v>1149.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H239">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="I239" t="str">
-        <v>706.0</v>
+        <v>713.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H240">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I240" t="str">
-        <v>912.0</v>
+        <v>931.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H241">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="I241" t="str">
-        <v>458.0</v>
+        <v>462.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="H242">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I242" t="str">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H243">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I243" t="str">
-        <v>475.0</v>
+        <v>483.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="H244">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I244" t="str">
-        <v>932.0</v>
+        <v>944.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="H245">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I245" t="str">
-        <v>1370.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="H246">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="I246" t="str">
-        <v>2296.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H247">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I247" t="str">
-        <v>490.0</v>
+        <v>482.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
+        <v>163</v>
+      </c>
+      <c r="H248">
         <v>172</v>
       </c>
-      <c r="H248">
-        <v>207</v>
-      </c>
       <c r="I248" t="str">
-        <v>1164.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H249">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I249" t="str">
-        <v>701.0</v>
+        <v>703.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H250">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I250" t="str">
-        <v>940.0</v>
+        <v>947.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H251">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="I251" t="str">
-        <v>450.0</v>
+        <v>457.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="H252">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I252" t="str">
-        <v>247.0</v>
+        <v>232.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H253">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="I253" t="str">
-        <v>462.0</v>
+        <v>460.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H254">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I254" t="str">
-        <v>925.0</v>
+        <v>910.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H255">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="I255" t="str">
-        <v>1395.0</v>
+        <v>1398.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H256">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="I256" t="str">
-        <v>2292.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H257">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I257" t="str">
-        <v>499.0</v>
+        <v>458.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H258">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="I258" t="str">
-        <v>1147.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H259">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="I259" t="str">
-        <v>712.0</v>
+        <v>677.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H260">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I260" t="str">
-        <v>906.0</v>
+        <v>926.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="H261">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="I261" t="str">
-        <v>489.0</v>
+        <v>470.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H262">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I262" t="str">
-        <v>251.0</v>
+        <v>239.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H263">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="I263" t="str">
-        <v>465.0</v>
+        <v>497.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="H264">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="I264" t="str">
-        <v>902.0</v>
+        <v>927.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="H265">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="I265" t="str">
-        <v>1354.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10492,10 +10492,10 @@
         <v>240</v>
       </c>
       <c r="H266">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="I266" t="str">
-        <v>2286.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="H267">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="I267" t="str">
-        <v>479.0</v>
+        <v>493.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H268">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I268" t="str">
-        <v>1142.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H269">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I269" t="str">
-        <v>692.0</v>
+        <v>693.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H270">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I270" t="str">
-        <v>909.0</v>
+        <v>943.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H271">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="I271" t="str">
-        <v>473.0</v>
+        <v>468.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H272">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="I272" t="str">
-        <v>236.0</v>
+        <v>225.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10758,10 +10758,10 @@
         <v>131</v>
       </c>
       <c r="H273">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I273" t="str">
-        <v>488.0</v>
+        <v>469.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H274">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I274" t="str">
-        <v>934.0</v>
+        <v>936.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H275">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="I275" t="str">
-        <v>1356.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H276">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="I276" t="str">
-        <v>2272.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H277">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="I277" t="str">
-        <v>483.0</v>
+        <v>472.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
+        <v>167</v>
+      </c>
+      <c r="H278">
         <v>183</v>
       </c>
-      <c r="H278">
-        <v>202</v>
-      </c>
       <c r="I278" t="str">
-        <v>1142.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="H279">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="I279" t="str">
-        <v>707.0</v>
+        <v>706.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H280">
         <v>148</v>
       </c>
       <c r="I280" t="str">
-        <v>900.0</v>
+        <v>947.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H281">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I281" t="str">
-        <v>455.0</v>
+        <v>496.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H282">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I282" t="str">
-        <v>274.0</v>
+        <v>237.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H283">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I283" t="str">
-        <v>457.0</v>
+        <v>451.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H284">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I284" t="str">
-        <v>909.0</v>
+        <v>902.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H285">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I285" t="str">
-        <v>1381.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H286">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I286" t="str">
-        <v>2260.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H287">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="I287" t="str">
-        <v>471.0</v>
+        <v>498.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H288">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="I288" t="str">
-        <v>1128.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="H289">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="I289" t="str">
-        <v>691.0</v>
+        <v>706.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H290">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="I290" t="str">
-        <v>924.0</v>
+        <v>914.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H291">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I291" t="str">
-        <v>485.0</v>
+        <v>486.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H292">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="I292" t="str">
-        <v>268.0</v>
+        <v>253.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H293">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I293" t="str">
-        <v>468.0</v>
+        <v>460.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H294">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="I294" t="str">
-        <v>935.0</v>
+        <v>934.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H295">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I295" t="str">
-        <v>1361.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H296">
         <v>290</v>
       </c>
       <c r="I296" t="str">
-        <v>2254.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H297">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="I297" t="str">
-        <v>488.0</v>
+        <v>478.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="H298">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="I298" t="str">
-        <v>1144.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H299">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="I299" t="str">
-        <v>720.0</v>
+        <v>715.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H300">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I300" t="str">
-        <v>914.0</v>
+        <v>902.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="H301">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I301" t="str">
-        <v>479.0</v>
+        <v>470.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H2">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="I2" t="str">
-        <v>270.0</v>
+        <v>273.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="H3">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="I3" t="str">
-        <v>463.0</v>
+        <v>490.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H4">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="I4" t="str">
-        <v>923.0</v>
+        <v>944.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H5">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="I5" t="str">
-        <v>1371.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="H6">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="I6" t="str">
-        <v>2273.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H7">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="I7" t="str">
-        <v>488.0</v>
+        <v>458.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H8">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="I8" t="str">
-        <v>1159.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H9">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="I9" t="str">
-        <v>687.0</v>
+        <v>711.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H10">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I10" t="str">
-        <v>942.0</v>
+        <v>945.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -802,10 +802,10 @@
         <v>139</v>
       </c>
       <c r="H11">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="I11" t="str">
-        <v>488.0</v>
+        <v>469.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H12">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I12" t="str">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="H13">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="I13" t="str">
-        <v>456.0</v>
+        <v>484.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H14">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I14" t="str">
-        <v>901.0</v>
+        <v>931.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H15">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="I15" t="str">
-        <v>1382.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="H16">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="I16" t="str">
-        <v>2290.0</v>
+        <v>2262.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H17">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I17" t="str">
-        <v>459.0</v>
+        <v>461.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H18">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="I18" t="str">
-        <v>1141.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,10 +1103,10 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H19">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="I19" t="str">
         <v>719.0</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="H20">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I20" t="str">
-        <v>917.0</v>
+        <v>903.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H21">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I21" t="str">
-        <v>454.0</v>
+        <v>492.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H22">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I22" t="str">
-        <v>262.0</v>
+        <v>242.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H23">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I23" t="str">
-        <v>493.0</v>
+        <v>476.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H24">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I24" t="str">
-        <v>937.0</v>
+        <v>933.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="H25">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I25" t="str">
-        <v>1369.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H26">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="I26" t="str">
-        <v>2251.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H27">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="I27" t="str">
-        <v>470.0</v>
+        <v>469.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H28">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="I28" t="str">
-        <v>1152.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H29">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I29" t="str">
-        <v>680.0</v>
+        <v>703.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,10 +1521,10 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H30">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="I30" t="str">
         <v>915.0</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="H31">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="I31" t="str">
-        <v>457.0</v>
+        <v>495.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H32">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="I32" t="str">
-        <v>262.0</v>
+        <v>270.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H33">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="I33" t="str">
-        <v>453.0</v>
+        <v>459.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="H34">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I34" t="str">
-        <v>911.0</v>
+        <v>901.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H35">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="I35" t="str">
-        <v>1375.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H36">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I36" t="str">
-        <v>2292.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H37">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I37" t="str">
-        <v>465.0</v>
+        <v>458.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1828,10 +1828,10 @@
         <v>165</v>
       </c>
       <c r="H38">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="I38" t="str">
-        <v>1142.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H39">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="I39" t="str">
-        <v>684.0</v>
+        <v>706.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H40">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="I40" t="str">
-        <v>930.0</v>
+        <v>904.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="H41">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="I41" t="str">
-        <v>484.0</v>
+        <v>490.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="H42">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="I42" t="str">
-        <v>239.0</v>
+        <v>244.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H43">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I43" t="str">
-        <v>470.0</v>
+        <v>493.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H44">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="I44" t="str">
-        <v>929.0</v>
+        <v>921.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="H45">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="I45" t="str">
-        <v>1377.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H46">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I46" t="str">
-        <v>2282.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H47">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I47" t="str">
-        <v>481.0</v>
+        <v>499.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H48">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="I48" t="str">
-        <v>1170.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2246,10 +2246,10 @@
         <v>153</v>
       </c>
       <c r="H49">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="I49" t="str">
-        <v>678.0</v>
+        <v>710.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H50">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="I50" t="str">
-        <v>904.0</v>
+        <v>905.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="H51">
         <v>144</v>
       </c>
       <c r="I51" t="str">
-        <v>460.0</v>
+        <v>457.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H52">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="I52" t="str">
-        <v>244.0</v>
+        <v>235.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="H53">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="I53" t="str">
-        <v>479.0</v>
+        <v>456.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H54">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I54" t="str">
-        <v>913.0</v>
+        <v>944.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H55">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I55" t="str">
-        <v>1354.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H56">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="I56" t="str">
-        <v>2264.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H57">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I57" t="str">
-        <v>469.0</v>
+        <v>452.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="H58">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I58" t="str">
-        <v>1148.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2626,10 +2626,10 @@
         <v>133</v>
       </c>
       <c r="H59">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I59" t="str">
-        <v>695.0</v>
+        <v>710.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H60">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I60" t="str">
-        <v>942.0</v>
+        <v>927.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H61">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I61" t="str">
-        <v>489.0</v>
+        <v>454.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="H62">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I62" t="str">
-        <v>225.0</v>
+        <v>229.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H63">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="I63" t="str">
-        <v>481.0</v>
+        <v>484.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H64">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I64" t="str">
-        <v>912.0</v>
+        <v>900.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H65">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="I65" t="str">
-        <v>1377.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H66">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="I66" t="str">
-        <v>2257.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="H67">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="I67" t="str">
-        <v>499.0</v>
+        <v>492.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H68">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I68" t="str">
-        <v>1135.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H69">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I69" t="str">
-        <v>695.0</v>
+        <v>709.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H70">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="I70" t="str">
-        <v>932.0</v>
+        <v>923.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H71">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="I71" t="str">
-        <v>478.0</v>
+        <v>492.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H72">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="I72" t="str">
-        <v>230.0</v>
+        <v>238.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H73">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I73" t="str">
-        <v>454.0</v>
+        <v>466.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H74">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="I74" t="str">
-        <v>905.0</v>
+        <v>927.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H75">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I75" t="str">
-        <v>1375.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="H76">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I76" t="str">
-        <v>2251.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H77">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="I77" t="str">
-        <v>452.0</v>
+        <v>451.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="H78">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I78" t="str">
-        <v>1146.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,10 +3383,10 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="H79">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="I79" t="str">
         <v>705.0</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H80">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="I80" t="str">
-        <v>931.0</v>
+        <v>923.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H81">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="I81" t="str">
-        <v>452.0</v>
+        <v>465.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H82">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I82" t="str">
-        <v>258.0</v>
+        <v>235.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H83">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="I83" t="str">
-        <v>452.0</v>
+        <v>482.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H84">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="I84" t="str">
-        <v>903.0</v>
+        <v>949.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="H85">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="I85" t="str">
-        <v>1394.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="H86">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="I86" t="str">
-        <v>2299.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H87">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="I87" t="str">
-        <v>475.0</v>
+        <v>490.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="H88">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="I88" t="str">
-        <v>1126.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H89">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="I89" t="str">
-        <v>708.0</v>
+        <v>710.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H90">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I90" t="str">
-        <v>902.0</v>
+        <v>918.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H91">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I91" t="str">
-        <v>478.0</v>
+        <v>461.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H92">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="I92" t="str">
-        <v>247.0</v>
+        <v>252.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
+        <v>116</v>
+      </c>
+      <c r="H93">
         <v>126</v>
       </c>
-      <c r="H93">
-        <v>145</v>
-      </c>
       <c r="I93" t="str">
-        <v>470.0</v>
+        <v>481.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H94">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I94" t="str">
-        <v>937.0</v>
+        <v>908.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H95">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="I95" t="str">
-        <v>1373.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H96">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="I96" t="str">
-        <v>2296.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="H97">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="I97" t="str">
-        <v>496.0</v>
+        <v>494.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H98">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I98" t="str">
-        <v>1141.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="H99">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="I99" t="str">
-        <v>720.0</v>
+        <v>675.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H100">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I100" t="str">
-        <v>925.0</v>
+        <v>934.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H101">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I101" t="str">
-        <v>451.0</v>
+        <v>492.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H102">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="I102" t="str">
-        <v>239.0</v>
+        <v>249.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="H103">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="I103" t="str">
-        <v>460.0</v>
+        <v>468.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H104">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="I104" t="str">
-        <v>905.0</v>
+        <v>930.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H105">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="I105" t="str">
-        <v>1352.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H106">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="I106" t="str">
-        <v>2278.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,10 +4447,10 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H107">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I107" t="str">
         <v>478.0</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H108">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I108" t="str">
-        <v>1137.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="H109">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I109" t="str">
-        <v>706.0</v>
+        <v>710.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H110">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="I110" t="str">
-        <v>943.0</v>
+        <v>928.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H111">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I111" t="str">
-        <v>493.0</v>
+        <v>477.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H112">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I112" t="str">
-        <v>243.0</v>
+        <v>225.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H113">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I113" t="str">
-        <v>465.0</v>
+        <v>453.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="H114">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I114" t="str">
-        <v>929.0</v>
+        <v>937.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H115">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I115" t="str">
-        <v>1351.0</v>
+        <v>1383.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H116">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I116" t="str">
-        <v>2255.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H117">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="I117" t="str">
-        <v>495.0</v>
+        <v>487.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,10 +4865,10 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H118">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I118" t="str">
         <v>1147.0</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H119">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I119" t="str">
-        <v>704.0</v>
+        <v>691.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4944,10 +4944,10 @@
         <v>119</v>
       </c>
       <c r="H120">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="I120" t="str">
-        <v>908.0</v>
+        <v>944.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H121">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I121" t="str">
-        <v>483.0</v>
+        <v>466.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5020,10 +5020,10 @@
         <v>104</v>
       </c>
       <c r="H122">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I122" t="str">
-        <v>232.0</v>
+        <v>228.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H123">
         <v>124</v>
       </c>
       <c r="I123" t="str">
-        <v>470.0</v>
+        <v>479.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H124">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="I124" t="str">
-        <v>920.0</v>
+        <v>923.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H125">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="I125" t="str">
-        <v>1352.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H126">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I126" t="str">
-        <v>2274.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H127">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="I127" t="str">
-        <v>481.0</v>
+        <v>474.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H128">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="I128" t="str">
-        <v>1160.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H129">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I129" t="str">
-        <v>710.0</v>
+        <v>709.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H130">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I130" t="str">
-        <v>947.0</v>
+        <v>912.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H131">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="I131" t="str">
-        <v>462.0</v>
+        <v>498.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H132">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="I132" t="str">
-        <v>261.0</v>
+        <v>241.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H133">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I133" t="str">
-        <v>470.0</v>
+        <v>474.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H134">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I134" t="str">
-        <v>912.0</v>
+        <v>936.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H135">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="I135" t="str">
-        <v>1381.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H136">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I136" t="str">
-        <v>2287.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="H137">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="I137" t="str">
-        <v>457.0</v>
+        <v>468.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="H138">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I138" t="str">
-        <v>1145.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H139">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I139" t="str">
-        <v>695.0</v>
+        <v>694.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H140">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I140" t="str">
-        <v>916.0</v>
+        <v>917.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="H141">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I141" t="str">
-        <v>476.0</v>
+        <v>475.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H142">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I142" t="str">
-        <v>251.0</v>
+        <v>255.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="H143">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="I143" t="str">
-        <v>452.0</v>
+        <v>458.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H144">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I144" t="str">
-        <v>911.0</v>
+        <v>909.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="H145">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="I145" t="str">
-        <v>1379.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="H146">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="I146" t="str">
-        <v>2272.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H147">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I147" t="str">
-        <v>495.0</v>
+        <v>452.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="H148">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="I148" t="str">
-        <v>1136.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H149">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I149" t="str">
-        <v>678.0</v>
+        <v>710.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H150">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I150" t="str">
-        <v>947.0</v>
+        <v>940.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H151">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I151" t="str">
-        <v>452.0</v>
+        <v>480.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H152">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="I152" t="str">
-        <v>241.0</v>
+        <v>257.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H153">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="I153" t="str">
-        <v>496.0</v>
+        <v>483.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H154">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="I154" t="str">
-        <v>938.0</v>
+        <v>931.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H155">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I155" t="str">
-        <v>1390.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H156">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="I156" t="str">
-        <v>2279.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H157">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="I157" t="str">
-        <v>458.0</v>
+        <v>483.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6388,10 +6388,10 @@
         <v>180</v>
       </c>
       <c r="H158">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="I158" t="str">
-        <v>1147.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H159">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I159" t="str">
-        <v>719.0</v>
+        <v>716.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H160">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="I160" t="str">
-        <v>947.0</v>
+        <v>904.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="H161">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="I161" t="str">
-        <v>493.0</v>
+        <v>481.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H162">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I162" t="str">
-        <v>269.0</v>
+        <v>247.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H163">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I163" t="str">
-        <v>452.0</v>
+        <v>472.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H164">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I164" t="str">
-        <v>907.0</v>
+        <v>945.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="H165">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="I165" t="str">
-        <v>1381.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H166">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="I166" t="str">
-        <v>2291.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H167">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I167" t="str">
-        <v>475.0</v>
+        <v>477.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H168">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I168" t="str">
-        <v>1162.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="H169">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I169" t="str">
-        <v>715.0</v>
+        <v>720.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="H170">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I170" t="str">
-        <v>938.0</v>
+        <v>922.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H171">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="I171" t="str">
-        <v>484.0</v>
+        <v>474.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="H172">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="I172" t="str">
-        <v>251.0</v>
+        <v>241.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="H173">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="I173" t="str">
-        <v>464.0</v>
+        <v>475.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="H174">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="I174" t="str">
-        <v>947.0</v>
+        <v>944.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="H175">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I175" t="str">
-        <v>1390.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H176">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="I176" t="str">
-        <v>2251.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H177">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="I177" t="str">
-        <v>495.0</v>
+        <v>466.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H178">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I178" t="str">
-        <v>1141.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H179">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="I179" t="str">
-        <v>677.0</v>
+        <v>712.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H180">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I180" t="str">
-        <v>928.0</v>
+        <v>909.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="H181">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I181" t="str">
-        <v>492.0</v>
+        <v>487.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H182">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I182" t="str">
-        <v>259.0</v>
+        <v>270.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H183">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I183" t="str">
-        <v>483.0</v>
+        <v>459.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H184">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="I184" t="str">
-        <v>936.0</v>
+        <v>921.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H185">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I185" t="str">
-        <v>1393.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="H186">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="I186" t="str">
-        <v>2282.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H187">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I187" t="str">
-        <v>479.0</v>
+        <v>485.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H188">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="I188" t="str">
-        <v>1130.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H189">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="I189" t="str">
-        <v>722.0</v>
+        <v>724.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H190">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="I190" t="str">
-        <v>925.0</v>
+        <v>946.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="H191">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="I191" t="str">
-        <v>468.0</v>
+        <v>473.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H192">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="I192" t="str">
-        <v>263.0</v>
+        <v>250.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H193">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I193" t="str">
-        <v>474.0</v>
+        <v>459.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H194">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I194" t="str">
-        <v>944.0</v>
+        <v>935.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H195">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="I195" t="str">
-        <v>1375.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H196">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="I196" t="str">
-        <v>2294.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H197">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="I197" t="str">
-        <v>461.0</v>
+        <v>487.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="H198">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="I198" t="str">
-        <v>1153.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="H199">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I199" t="str">
-        <v>675.0</v>
+        <v>716.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H200">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="I200" t="str">
-        <v>919.0</v>
+        <v>933.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H201">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I201" t="str">
-        <v>463.0</v>
+        <v>499.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H202">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I202" t="str">
-        <v>266.0</v>
+        <v>249.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H203">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="I203" t="str">
-        <v>489.0</v>
+        <v>467.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H204">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I204" t="str">
-        <v>935.0</v>
+        <v>948.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="H205">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I205" t="str">
-        <v>1358.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H206">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I206" t="str">
-        <v>2276.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H207">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I207" t="str">
-        <v>489.0</v>
+        <v>451.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H208">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="I208" t="str">
-        <v>1147.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H209">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="I209" t="str">
-        <v>714.0</v>
+        <v>721.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H210">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I210" t="str">
-        <v>935.0</v>
+        <v>916.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8402,10 +8402,10 @@
         <v>144</v>
       </c>
       <c r="H211">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I211" t="str">
-        <v>499.0</v>
+        <v>459.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H212">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I212" t="str">
-        <v>249.0</v>
+        <v>244.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H213">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I213" t="str">
-        <v>459.0</v>
+        <v>477.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="H214">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="I214" t="str">
-        <v>941.0</v>
+        <v>904.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H215">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="I215" t="str">
-        <v>1395.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H216">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I216" t="str">
-        <v>2274.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H217">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I217" t="str">
-        <v>455.0</v>
+        <v>471.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H218">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="I218" t="str">
-        <v>1164.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8706,10 +8706,10 @@
         <v>146</v>
       </c>
       <c r="H219">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I219" t="str">
-        <v>709.0</v>
+        <v>706.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="H220">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I220" t="str">
-        <v>907.0</v>
+        <v>941.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H221">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="I221" t="str">
-        <v>466.0</v>
+        <v>481.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H222">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I222" t="str">
-        <v>260.0</v>
+        <v>227.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H223">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I223" t="str">
-        <v>461.0</v>
+        <v>457.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H224">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="I224" t="str">
-        <v>928.0</v>
+        <v>924.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H225">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="I225" t="str">
-        <v>1388.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H226">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="I226" t="str">
-        <v>2299.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H227">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I227" t="str">
-        <v>489.0</v>
+        <v>479.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H228">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="I228" t="str">
-        <v>1155.0</v>
+        <v>1128.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="H229">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I229" t="str">
-        <v>700.0</v>
+        <v>699.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H230">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="I230" t="str">
-        <v>910.0</v>
+        <v>931.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,10 +9159,10 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H231">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="I231" t="str">
         <v>491.0</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H232">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I232" t="str">
-        <v>249.0</v>
+        <v>274.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9238,10 +9238,10 @@
         <v>124</v>
       </c>
       <c r="H233">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="I233" t="str">
-        <v>463.0</v>
+        <v>455.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="H234">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="I234" t="str">
-        <v>930.0</v>
+        <v>942.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H235">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I235" t="str">
-        <v>1362.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H236">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="I236" t="str">
-        <v>2265.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="H237">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I237" t="str">
-        <v>498.0</v>
+        <v>460.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="H238">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I238" t="str">
-        <v>1130.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="H239">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="I239" t="str">
-        <v>713.0</v>
+        <v>718.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H240">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="I240" t="str">
-        <v>931.0</v>
+        <v>947.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H241">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="I241" t="str">
-        <v>462.0</v>
+        <v>456.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H242">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="I242" t="str">
-        <v>256.0</v>
+        <v>239.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H243">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="I243" t="str">
-        <v>483.0</v>
+        <v>493.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="H244">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I244" t="str">
-        <v>944.0</v>
+        <v>938.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="H245">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="I245" t="str">
-        <v>1376.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H246">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="I246" t="str">
-        <v>2258.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H247">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="I247" t="str">
-        <v>482.0</v>
+        <v>488.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="H248">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="I248" t="str">
-        <v>1166.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H249">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="I249" t="str">
-        <v>703.0</v>
+        <v>712.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H250">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I250" t="str">
-        <v>947.0</v>
+        <v>936.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H251">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I251" t="str">
-        <v>457.0</v>
+        <v>479.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H252">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="I252" t="str">
-        <v>232.0</v>
+        <v>243.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="H253">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I253" t="str">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="H254">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I254" t="str">
-        <v>910.0</v>
+        <v>907.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H255">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I255" t="str">
-        <v>1398.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H256">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="I256" t="str">
-        <v>2286.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H257">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I257" t="str">
-        <v>458.0</v>
+        <v>474.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H258">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="I258" t="str">
-        <v>1137.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="H259">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="I259" t="str">
-        <v>677.0</v>
+        <v>706.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H260">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I260" t="str">
-        <v>926.0</v>
+        <v>909.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H261">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="I261" t="str">
-        <v>470.0</v>
+        <v>493.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H262">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="I262" t="str">
-        <v>239.0</v>
+        <v>260.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H263">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I263" t="str">
-        <v>497.0</v>
+        <v>455.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="H264">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="I264" t="str">
-        <v>927.0</v>
+        <v>920.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H265">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="I265" t="str">
-        <v>1364.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="H266">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I266" t="str">
-        <v>2281.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H267">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="I267" t="str">
-        <v>493.0</v>
+        <v>450.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H268">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="I268" t="str">
-        <v>1174.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H269">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I269" t="str">
-        <v>693.0</v>
+        <v>715.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H270">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I270" t="str">
-        <v>943.0</v>
+        <v>934.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="H271">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I271" t="str">
-        <v>468.0</v>
+        <v>486.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H272">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I272" t="str">
-        <v>225.0</v>
+        <v>233.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H273">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="I273" t="str">
-        <v>469.0</v>
+        <v>490.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H274">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I274" t="str">
-        <v>936.0</v>
+        <v>931.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="H275">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="I275" t="str">
-        <v>1394.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H276">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="I276" t="str">
-        <v>2277.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H277">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="I277" t="str">
-        <v>472.0</v>
+        <v>481.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H278">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I278" t="str">
-        <v>1138.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10986,10 +10986,10 @@
         <v>131</v>
       </c>
       <c r="H279">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I279" t="str">
-        <v>706.0</v>
+        <v>678.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H280">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="I280" t="str">
-        <v>947.0</v>
+        <v>916.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="H281">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="I281" t="str">
-        <v>496.0</v>
+        <v>467.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H282">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I282" t="str">
-        <v>237.0</v>
+        <v>273.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H283">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="I283" t="str">
-        <v>451.0</v>
+        <v>486.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H284">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="I284" t="str">
-        <v>902.0</v>
+        <v>919.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="H285">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="I285" t="str">
-        <v>1357.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="H286">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I286" t="str">
-        <v>2297.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H287">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="I287" t="str">
-        <v>498.0</v>
+        <v>452.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="H288">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I288" t="str">
-        <v>1140.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11366,10 +11366,10 @@
         <v>130</v>
       </c>
       <c r="H289">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="I289" t="str">
-        <v>706.0</v>
+        <v>712.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H290">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I290" t="str">
-        <v>914.0</v>
+        <v>928.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11442,10 +11442,10 @@
         <v>134</v>
       </c>
       <c r="H291">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="I291" t="str">
-        <v>486.0</v>
+        <v>466.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H292">
         <v>114</v>
       </c>
       <c r="I292" t="str">
-        <v>253.0</v>
+        <v>250.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H293">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I293" t="str">
-        <v>460.0</v>
+        <v>464.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H294">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I294" t="str">
-        <v>934.0</v>
+        <v>925.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H295">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="I295" t="str">
-        <v>1352.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H296">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="I296" t="str">
-        <v>2261.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H297">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I297" t="str">
-        <v>478.0</v>
+        <v>459.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="H298">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="I298" t="str">
-        <v>1149.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="H299">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="I299" t="str">
-        <v>715.0</v>
+        <v>702.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H300">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I300" t="str">
-        <v>902.0</v>
+        <v>928.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="H301">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="I301" t="str">
-        <v>470.0</v>
+        <v>456.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H2">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="I2" t="str">
-        <v>273.0</v>
+        <v>272.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H3">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I3" t="str">
-        <v>490.0</v>
+        <v>482.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -536,10 +536,10 @@
         <v>158</v>
       </c>
       <c r="H4">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="I4" t="str">
-        <v>944.0</v>
+        <v>934.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H5">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I5" t="str">
-        <v>1363.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="H6">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="I6" t="str">
-        <v>2265.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H7">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I7" t="str">
-        <v>458.0</v>
+        <v>499.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H8">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="I8" t="str">
-        <v>1141.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H9">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="I9" t="str">
-        <v>711.0</v>
+        <v>713.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H10">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="I10" t="str">
-        <v>945.0</v>
+        <v>924.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -802,10 +802,10 @@
         <v>139</v>
       </c>
       <c r="H11">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="I11" t="str">
-        <v>469.0</v>
+        <v>485.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H12">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="I12" t="str">
-        <v>231.0</v>
+        <v>228.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H13">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I13" t="str">
-        <v>484.0</v>
+        <v>459.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H14">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I14" t="str">
-        <v>931.0</v>
+        <v>906.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H15">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I15" t="str">
-        <v>1352.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,10 +989,10 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="H16">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I16" t="str">
         <v>2262.0</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H17">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I17" t="str">
-        <v>461.0</v>
+        <v>462.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="H18">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="I18" t="str">
-        <v>1140.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="H19">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="I19" t="str">
-        <v>719.0</v>
+        <v>700.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H20">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I20" t="str">
-        <v>903.0</v>
+        <v>925.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H21">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I21" t="str">
-        <v>492.0</v>
+        <v>498.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H22">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="I22" t="str">
-        <v>242.0</v>
+        <v>272.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H23">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="I23" t="str">
-        <v>476.0</v>
+        <v>482.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H24">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I24" t="str">
-        <v>933.0</v>
+        <v>931.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H25">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I25" t="str">
-        <v>1355.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H26">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="I26" t="str">
-        <v>2279.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="H27">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="I27" t="str">
-        <v>469.0</v>
+        <v>468.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="H28">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I28" t="str">
-        <v>1135.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H29">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="I29" t="str">
-        <v>703.0</v>
+        <v>706.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H30">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I30" t="str">
-        <v>915.0</v>
+        <v>935.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H31">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="I31" t="str">
-        <v>495.0</v>
+        <v>453.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H32">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="I32" t="str">
-        <v>270.0</v>
+        <v>236.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H33">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I33" t="str">
-        <v>459.0</v>
+        <v>468.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H34">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I34" t="str">
-        <v>901.0</v>
+        <v>939.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H35">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="I35" t="str">
-        <v>1377.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="H36">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I36" t="str">
-        <v>2282.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1790,10 +1790,10 @@
         <v>122</v>
       </c>
       <c r="H37">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I37" t="str">
-        <v>458.0</v>
+        <v>459.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H38">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I38" t="str">
-        <v>1150.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H39">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I39" t="str">
-        <v>706.0</v>
+        <v>676.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H40">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="I40" t="str">
-        <v>904.0</v>
+        <v>928.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H41">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="I41" t="str">
-        <v>490.0</v>
+        <v>483.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H42">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I42" t="str">
-        <v>244.0</v>
+        <v>228.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H43">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I43" t="str">
-        <v>493.0</v>
+        <v>456.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H44">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="I44" t="str">
-        <v>921.0</v>
+        <v>925.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="H45">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="I45" t="str">
-        <v>1389.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H46">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="I46" t="str">
-        <v>2260.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="H47">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="I47" t="str">
-        <v>499.0</v>
+        <v>467.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I48" t="str">
-        <v>1152.0</v>
+        <v>1145.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H49">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="I49" t="str">
-        <v>710.0</v>
+        <v>682.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H50">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="I50" t="str">
-        <v>905.0</v>
+        <v>936.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H51">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I51" t="str">
-        <v>457.0</v>
+        <v>489.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H52">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I52" t="str">
-        <v>235.0</v>
+        <v>226.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H53">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="I53" t="str">
-        <v>456.0</v>
+        <v>478.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H54">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="I54" t="str">
-        <v>944.0</v>
+        <v>914.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H55">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="I55" t="str">
-        <v>1395.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H56">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="I56" t="str">
-        <v>2259.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H57">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="I57" t="str">
-        <v>452.0</v>
+        <v>470.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H58">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="I58" t="str">
-        <v>1153.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H59">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I59" t="str">
-        <v>710.0</v>
+        <v>687.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H60">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="I60" t="str">
-        <v>927.0</v>
+        <v>947.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="H61">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="I61" t="str">
-        <v>454.0</v>
+        <v>482.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H62">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I62" t="str">
-        <v>229.0</v>
+        <v>252.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H63">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="I63" t="str">
-        <v>484.0</v>
+        <v>450.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H64">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="I64" t="str">
-        <v>900.0</v>
+        <v>939.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H65">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="I65" t="str">
-        <v>1372.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="H66">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I66" t="str">
-        <v>2265.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H67">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I67" t="str">
-        <v>492.0</v>
+        <v>481.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="H68">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I68" t="str">
-        <v>1172.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H69">
         <v>165</v>
       </c>
       <c r="I69" t="str">
-        <v>709.0</v>
+        <v>679.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H70">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I70" t="str">
-        <v>923.0</v>
+        <v>945.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H71">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="I71" t="str">
-        <v>492.0</v>
+        <v>461.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="H72">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="I72" t="str">
-        <v>238.0</v>
+        <v>269.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="H73">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="I73" t="str">
-        <v>466.0</v>
+        <v>452.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H74">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I74" t="str">
-        <v>927.0</v>
+        <v>903.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="H75">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I75" t="str">
-        <v>1386.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H76">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I76" t="str">
-        <v>2258.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="H77">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="I77" t="str">
-        <v>451.0</v>
+        <v>461.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H78">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I78" t="str">
-        <v>1150.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H79">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I79" t="str">
-        <v>705.0</v>
+        <v>676.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H80">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="I80" t="str">
-        <v>923.0</v>
+        <v>939.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3462,10 +3462,10 @@
         <v>126</v>
       </c>
       <c r="H81">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="I81" t="str">
-        <v>465.0</v>
+        <v>493.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H82">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I82" t="str">
-        <v>235.0</v>
+        <v>255.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="H83">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I83" t="str">
-        <v>482.0</v>
+        <v>488.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H84">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="I84" t="str">
-        <v>949.0</v>
+        <v>931.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H85">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="I85" t="str">
-        <v>1384.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="H86">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="I86" t="str">
-        <v>2258.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="H87">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="I87" t="str">
-        <v>490.0</v>
+        <v>480.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H88">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="I88" t="str">
-        <v>1150.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H89">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="I89" t="str">
-        <v>710.0</v>
+        <v>676.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H90">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="I90" t="str">
-        <v>918.0</v>
+        <v>934.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H91">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I91" t="str">
-        <v>461.0</v>
+        <v>479.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H92">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I92" t="str">
-        <v>252.0</v>
+        <v>255.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="H93">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I93" t="str">
-        <v>481.0</v>
+        <v>492.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H94">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="I94" t="str">
-        <v>908.0</v>
+        <v>946.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="H95">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="I95" t="str">
-        <v>1371.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="H96">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="I96" t="str">
-        <v>2291.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H97">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="I97" t="str">
-        <v>494.0</v>
+        <v>488.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H98">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I98" t="str">
-        <v>1149.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H99">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="I99" t="str">
-        <v>675.0</v>
+        <v>716.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H100">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="I100" t="str">
-        <v>934.0</v>
+        <v>946.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H101">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I101" t="str">
-        <v>492.0</v>
+        <v>465.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H102">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I102" t="str">
-        <v>249.0</v>
+        <v>246.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H103">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="I103" t="str">
-        <v>468.0</v>
+        <v>465.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H104">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I104" t="str">
-        <v>930.0</v>
+        <v>945.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
+        <v>190</v>
+      </c>
+      <c r="H105">
         <v>200</v>
       </c>
-      <c r="H105">
-        <v>227</v>
-      </c>
       <c r="I105" t="str">
-        <v>1377.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H106">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="I106" t="str">
-        <v>2255.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H107">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I107" t="str">
-        <v>478.0</v>
+        <v>475.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H108">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="I108" t="str">
-        <v>1169.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="H109">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I109" t="str">
-        <v>710.0</v>
+        <v>708.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H110">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="I110" t="str">
-        <v>928.0</v>
+        <v>910.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H111">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I111" t="str">
-        <v>477.0</v>
+        <v>461.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H112">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="I112" t="str">
-        <v>225.0</v>
+        <v>230.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,10 +4675,10 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H113">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="I113" t="str">
         <v>453.0</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H114">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="I114" t="str">
-        <v>937.0</v>
+        <v>945.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
+        <v>199</v>
+      </c>
+      <c r="H115">
         <v>206</v>
       </c>
-      <c r="H115">
-        <v>242</v>
-      </c>
       <c r="I115" t="str">
-        <v>1383.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H116">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="I116" t="str">
-        <v>2280.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H117">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="I117" t="str">
-        <v>487.0</v>
+        <v>458.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H118">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="I118" t="str">
-        <v>1147.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H119">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I119" t="str">
-        <v>691.0</v>
+        <v>723.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,10 +4941,10 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="H120">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="I120" t="str">
         <v>944.0</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H121">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I121" t="str">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H122">
         <v>126</v>
       </c>
       <c r="I122" t="str">
-        <v>228.0</v>
+        <v>247.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H123">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I123" t="str">
-        <v>479.0</v>
+        <v>456.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H124">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I124" t="str">
-        <v>923.0</v>
+        <v>901.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
+        <v>199</v>
+      </c>
+      <c r="H125">
         <v>204</v>
       </c>
-      <c r="H125">
-        <v>206</v>
-      </c>
       <c r="I125" t="str">
-        <v>1369.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="H126">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="I126" t="str">
-        <v>2263.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="H127">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I127" t="str">
-        <v>474.0</v>
+        <v>484.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H128">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="I128" t="str">
-        <v>1139.0</v>
+        <v>1145.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H129">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="I129" t="str">
-        <v>709.0</v>
+        <v>701.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H130">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I130" t="str">
-        <v>912.0</v>
+        <v>913.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H131">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="I131" t="str">
-        <v>498.0</v>
+        <v>460.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H132">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I132" t="str">
-        <v>241.0</v>
+        <v>236.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H133">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I133" t="str">
-        <v>474.0</v>
+        <v>493.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="H134">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="I134" t="str">
-        <v>936.0</v>
+        <v>939.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="H135">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I135" t="str">
-        <v>1358.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="H136">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="I136" t="str">
-        <v>2276.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="H137">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I137" t="str">
-        <v>468.0</v>
+        <v>450.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H138">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="I138" t="str">
-        <v>1136.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H139">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="I139" t="str">
-        <v>694.0</v>
+        <v>693.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="H140">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I140" t="str">
-        <v>917.0</v>
+        <v>941.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="H141">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I141" t="str">
-        <v>475.0</v>
+        <v>497.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H142">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I142" t="str">
-        <v>255.0</v>
+        <v>237.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="H143">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="I143" t="str">
-        <v>458.0</v>
+        <v>468.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H144">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="I144" t="str">
-        <v>909.0</v>
+        <v>917.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H145">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="I145" t="str">
-        <v>1397.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="H146">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I146" t="str">
-        <v>2256.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H147">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="I147" t="str">
-        <v>452.0</v>
+        <v>489.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H148">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="I148" t="str">
-        <v>1146.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H149">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="I149" t="str">
-        <v>710.0</v>
+        <v>693.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H150">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="I150" t="str">
-        <v>940.0</v>
+        <v>924.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="H151">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="I151" t="str">
-        <v>480.0</v>
+        <v>498.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H152">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="I152" t="str">
-        <v>257.0</v>
+        <v>231.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H153">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I153" t="str">
-        <v>483.0</v>
+        <v>486.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H154">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I154" t="str">
-        <v>931.0</v>
+        <v>903.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H155">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I155" t="str">
-        <v>1387.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="H156">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="I156" t="str">
-        <v>2256.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H157">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I157" t="str">
-        <v>483.0</v>
+        <v>499.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H158">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="I158" t="str">
-        <v>1154.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H159">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="I159" t="str">
-        <v>716.0</v>
+        <v>710.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H160">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I160" t="str">
-        <v>904.0</v>
+        <v>947.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H161">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="I161" t="str">
-        <v>481.0</v>
+        <v>474.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6540,10 +6540,10 @@
         <v>86</v>
       </c>
       <c r="H162">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="I162" t="str">
-        <v>247.0</v>
+        <v>266.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H163">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="I163" t="str">
-        <v>472.0</v>
+        <v>471.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H164">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I164" t="str">
-        <v>945.0</v>
+        <v>900.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H165">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="I165" t="str">
-        <v>1353.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="H166">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I166" t="str">
-        <v>2255.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H167">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="I167" t="str">
-        <v>477.0</v>
+        <v>455.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H168">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="I168" t="str">
-        <v>1155.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H169">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I169" t="str">
-        <v>720.0</v>
+        <v>699.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H170">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I170" t="str">
-        <v>922.0</v>
+        <v>923.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H171">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="I171" t="str">
-        <v>474.0</v>
+        <v>457.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H172">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="I172" t="str">
-        <v>241.0</v>
+        <v>258.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,10 +6955,10 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H173">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I173" t="str">
         <v>475.0</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H174">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="I174" t="str">
-        <v>944.0</v>
+        <v>946.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H175">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="I175" t="str">
-        <v>1399.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="H176">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="I176" t="str">
-        <v>2292.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H177">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="I177" t="str">
-        <v>466.0</v>
+        <v>464.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="H178">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="I178" t="str">
-        <v>1131.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H179">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="I179" t="str">
-        <v>712.0</v>
+        <v>698.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H180">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I180" t="str">
-        <v>909.0</v>
+        <v>930.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H181">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="I181" t="str">
-        <v>487.0</v>
+        <v>457.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H182">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="I182" t="str">
-        <v>270.0</v>
+        <v>258.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H183">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I183" t="str">
-        <v>459.0</v>
+        <v>465.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H184">
         <v>172</v>
       </c>
       <c r="I184" t="str">
-        <v>921.0</v>
+        <v>919.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="H185">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I185" t="str">
-        <v>1358.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H186">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="I186" t="str">
-        <v>2265.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H187">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I187" t="str">
-        <v>485.0</v>
+        <v>455.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7531,7 +7531,7 @@
         <v>205</v>
       </c>
       <c r="I188" t="str">
-        <v>1135.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H189">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I189" t="str">
-        <v>724.0</v>
+        <v>698.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H190">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I190" t="str">
-        <v>946.0</v>
+        <v>923.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H191">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="I191" t="str">
-        <v>473.0</v>
+        <v>463.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7680,10 +7680,10 @@
         <v>107</v>
       </c>
       <c r="H192">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="I192" t="str">
-        <v>250.0</v>
+        <v>244.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H193">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I193" t="str">
-        <v>459.0</v>
+        <v>479.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H194">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I194" t="str">
-        <v>935.0</v>
+        <v>922.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="H195">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I195" t="str">
-        <v>1381.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="H196">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="I196" t="str">
-        <v>2297.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H197">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="I197" t="str">
-        <v>487.0</v>
+        <v>483.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H198">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I198" t="str">
-        <v>1137.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H199">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I199" t="str">
-        <v>716.0</v>
+        <v>723.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H200">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="I200" t="str">
-        <v>933.0</v>
+        <v>917.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H201">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I201" t="str">
-        <v>499.0</v>
+        <v>481.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="H202">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I202" t="str">
-        <v>249.0</v>
+        <v>271.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="H203">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="I203" t="str">
-        <v>467.0</v>
+        <v>489.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="H204">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="I204" t="str">
-        <v>948.0</v>
+        <v>914.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H205">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I205" t="str">
-        <v>1361.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="H206">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="I206" t="str">
-        <v>2270.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H207">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="I207" t="str">
-        <v>451.0</v>
+        <v>485.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="H208">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="I208" t="str">
-        <v>1146.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8326,10 +8326,10 @@
         <v>131</v>
       </c>
       <c r="H209">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="I209" t="str">
-        <v>721.0</v>
+        <v>703.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H210">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="I210" t="str">
-        <v>916.0</v>
+        <v>904.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="H211">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I211" t="str">
-        <v>459.0</v>
+        <v>497.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H212">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I212" t="str">
-        <v>244.0</v>
+        <v>250.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="H213">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="I213" t="str">
-        <v>477.0</v>
+        <v>490.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="H214">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="I214" t="str">
-        <v>904.0</v>
+        <v>918.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="H215">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="I215" t="str">
-        <v>1361.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="H216">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="I216" t="str">
-        <v>2260.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H217">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I217" t="str">
-        <v>471.0</v>
+        <v>491.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H218">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I218" t="str">
-        <v>1144.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H219">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="I219" t="str">
-        <v>706.0</v>
+        <v>708.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H220">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="I220" t="str">
-        <v>941.0</v>
+        <v>933.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H221">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I221" t="str">
-        <v>481.0</v>
+        <v>460.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H222">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I222" t="str">
-        <v>227.0</v>
+        <v>256.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8858,10 +8858,10 @@
         <v>128</v>
       </c>
       <c r="H223">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="I223" t="str">
-        <v>457.0</v>
+        <v>494.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H224">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="I224" t="str">
-        <v>924.0</v>
+        <v>914.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="H225">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I225" t="str">
-        <v>1375.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H226">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="I226" t="str">
-        <v>2289.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H227">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="I227" t="str">
-        <v>479.0</v>
+        <v>471.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H228">
         <v>206</v>
       </c>
       <c r="I228" t="str">
-        <v>1128.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H229">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="I229" t="str">
-        <v>699.0</v>
+        <v>697.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H230">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="I230" t="str">
-        <v>931.0</v>
+        <v>905.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H231">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="I231" t="str">
-        <v>491.0</v>
+        <v>480.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,10 +9197,10 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H232">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I232" t="str">
         <v>274.0</v>
@@ -9238,10 +9238,10 @@
         <v>124</v>
       </c>
       <c r="H233">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I233" t="str">
-        <v>455.0</v>
+        <v>490.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="H234">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I234" t="str">
-        <v>942.0</v>
+        <v>936.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H235">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="I235" t="str">
-        <v>1357.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="H236">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="I236" t="str">
-        <v>2261.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H237">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I237" t="str">
-        <v>460.0</v>
+        <v>454.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="H238">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="I238" t="str">
-        <v>1156.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H239">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="I239" t="str">
-        <v>718.0</v>
+        <v>723.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H240">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="I240" t="str">
-        <v>947.0</v>
+        <v>913.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H241">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="I241" t="str">
-        <v>456.0</v>
+        <v>462.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H242">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="I242" t="str">
-        <v>239.0</v>
+        <v>258.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H243">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="I243" t="str">
-        <v>493.0</v>
+        <v>484.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="H244">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I244" t="str">
-        <v>938.0</v>
+        <v>915.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H245">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="I245" t="str">
-        <v>1355.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H246">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I246" t="str">
-        <v>2292.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H247">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I247" t="str">
-        <v>488.0</v>
+        <v>479.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="H248">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="I248" t="str">
-        <v>1153.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,10 +9843,10 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H249">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I249" t="str">
         <v>712.0</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="H250">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I250" t="str">
-        <v>936.0</v>
+        <v>933.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H251">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="I251" t="str">
-        <v>479.0</v>
+        <v>482.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H252">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I252" t="str">
-        <v>243.0</v>
+        <v>262.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H253">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="I253" t="str">
-        <v>462.0</v>
+        <v>470.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H254">
         <v>162</v>
       </c>
       <c r="I254" t="str">
-        <v>907.0</v>
+        <v>900.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H255">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I255" t="str">
-        <v>1372.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="H256">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I256" t="str">
-        <v>2274.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H257">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I257" t="str">
-        <v>474.0</v>
+        <v>463.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="H258">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="I258" t="str">
-        <v>1152.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="H259">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I259" t="str">
-        <v>706.0</v>
+        <v>707.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H260">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="I260" t="str">
-        <v>909.0</v>
+        <v>906.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="H261">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="I261" t="str">
-        <v>493.0</v>
+        <v>495.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H262">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="I262" t="str">
-        <v>260.0</v>
+        <v>266.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="H263">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I263" t="str">
-        <v>455.0</v>
+        <v>453.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="H264">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I264" t="str">
-        <v>920.0</v>
+        <v>916.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="H265">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="I265" t="str">
-        <v>1371.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H266">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="I266" t="str">
-        <v>2287.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H267">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I267" t="str">
-        <v>450.0</v>
+        <v>479.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H268">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="I268" t="str">
-        <v>1131.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10606,10 +10606,10 @@
         <v>136</v>
       </c>
       <c r="H269">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I269" t="str">
-        <v>715.0</v>
+        <v>716.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H270">
         <v>134</v>
       </c>
       <c r="I270" t="str">
-        <v>934.0</v>
+        <v>913.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="H271">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="I271" t="str">
-        <v>486.0</v>
+        <v>482.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H272">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I272" t="str">
-        <v>233.0</v>
+        <v>269.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H273">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="I273" t="str">
-        <v>490.0</v>
+        <v>461.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H274">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="I274" t="str">
-        <v>931.0</v>
+        <v>907.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H275">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I275" t="str">
-        <v>1389.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="H276">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="I276" t="str">
-        <v>2290.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H277">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I277" t="str">
-        <v>481.0</v>
+        <v>478.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H278">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="I278" t="str">
-        <v>1156.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10986,10 +10986,10 @@
         <v>131</v>
       </c>
       <c r="H279">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I279" t="str">
-        <v>678.0</v>
+        <v>699.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="H280">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I280" t="str">
-        <v>916.0</v>
+        <v>908.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H281">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I281" t="str">
-        <v>467.0</v>
+        <v>466.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
+        <v>88</v>
+      </c>
+      <c r="H282">
         <v>92</v>
       </c>
-      <c r="H282">
-        <v>118</v>
-      </c>
       <c r="I282" t="str">
-        <v>273.0</v>
+        <v>266.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H283">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I283" t="str">
-        <v>486.0</v>
+        <v>477.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H284">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="I284" t="str">
-        <v>919.0</v>
+        <v>906.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H285">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="I285" t="str">
-        <v>1368.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H286">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I286" t="str">
-        <v>2261.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H287">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="I287" t="str">
-        <v>452.0</v>
+        <v>477.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H288">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I288" t="str">
-        <v>1143.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="H289">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="I289" t="str">
-        <v>712.0</v>
+        <v>686.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H290">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="I290" t="str">
-        <v>928.0</v>
+        <v>947.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H291">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="I291" t="str">
-        <v>466.0</v>
+        <v>498.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H292">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I292" t="str">
-        <v>250.0</v>
+        <v>269.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H293">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="I293" t="str">
-        <v>464.0</v>
+        <v>480.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H294">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I294" t="str">
-        <v>925.0</v>
+        <v>932.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H295">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="I295" t="str">
-        <v>1388.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H296">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I296" t="str">
-        <v>2265.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H297">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I297" t="str">
-        <v>459.0</v>
+        <v>493.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="H298">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="I298" t="str">
-        <v>1136.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="H299">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="I299" t="str">
-        <v>702.0</v>
+        <v>688.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H300">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I300" t="str">
-        <v>928.0</v>
+        <v>946.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H301">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="I301" t="str">
-        <v>456.0</v>
+        <v>472.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H2">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I2" t="str">
-        <v>272.0</v>
+        <v>225.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H3">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I3" t="str">
-        <v>482.0</v>
+        <v>465.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H4">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="I4" t="str">
-        <v>934.0</v>
+        <v>900.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H5">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="I5" t="str">
-        <v>1397.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="H6">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="I6" t="str">
-        <v>2282.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="H7">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="I7" t="str">
-        <v>499.0</v>
+        <v>495.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H8">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I8" t="str">
-        <v>1153.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H9">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="I9" t="str">
-        <v>713.0</v>
+        <v>718.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H10">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I10" t="str">
-        <v>924.0</v>
+        <v>916.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H11">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I11" t="str">
-        <v>485.0</v>
+        <v>482.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,10 +837,10 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H12">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I12" t="str">
         <v>228.0</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H13">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="I13" t="str">
-        <v>459.0</v>
+        <v>489.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H14">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="I14" t="str">
-        <v>906.0</v>
+        <v>923.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="H15">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="I15" t="str">
-        <v>1399.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="H16">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="I16" t="str">
-        <v>2262.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H17">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I17" t="str">
-        <v>462.0</v>
+        <v>464.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H18">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="I18" t="str">
-        <v>1154.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="H19">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I19" t="str">
-        <v>700.0</v>
+        <v>706.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H20">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I20" t="str">
-        <v>925.0</v>
+        <v>926.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H21">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="I21" t="str">
-        <v>498.0</v>
+        <v>473.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H22">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="I22" t="str">
-        <v>272.0</v>
+        <v>261.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="H23">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="I23" t="str">
-        <v>482.0</v>
+        <v>458.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H24">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I24" t="str">
-        <v>931.0</v>
+        <v>903.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H25">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I25" t="str">
-        <v>1353.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="H26">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="I26" t="str">
-        <v>2294.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1410,10 +1410,10 @@
         <v>105</v>
       </c>
       <c r="H27">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I27" t="str">
-        <v>468.0</v>
+        <v>483.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H28">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I28" t="str">
-        <v>1133.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H29">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I29" t="str">
-        <v>706.0</v>
+        <v>708.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H30">
         <v>116</v>
       </c>
       <c r="I30" t="str">
-        <v>935.0</v>
+        <v>919.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H31">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I31" t="str">
-        <v>453.0</v>
+        <v>471.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H32">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I32" t="str">
-        <v>236.0</v>
+        <v>263.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1638,10 +1638,10 @@
         <v>113</v>
       </c>
       <c r="H33">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="I33" t="str">
-        <v>468.0</v>
+        <v>484.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H34">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I34" t="str">
-        <v>939.0</v>
+        <v>904.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="H35">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="I35" t="str">
-        <v>1371.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H36">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I36" t="str">
-        <v>2299.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H37">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="I37" t="str">
-        <v>459.0</v>
+        <v>450.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H38">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I38" t="str">
-        <v>1126.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H39">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="I39" t="str">
-        <v>676.0</v>
+        <v>681.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H40">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I40" t="str">
-        <v>928.0</v>
+        <v>922.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H41">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="I41" t="str">
-        <v>483.0</v>
+        <v>470.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H42">
         <v>124</v>
       </c>
       <c r="I42" t="str">
-        <v>228.0</v>
+        <v>226.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H43">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I43" t="str">
-        <v>456.0</v>
+        <v>488.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H44">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="I44" t="str">
-        <v>925.0</v>
+        <v>941.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2094,10 +2094,10 @@
         <v>209</v>
       </c>
       <c r="H45">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="I45" t="str">
-        <v>1377.0</v>
+        <v>1398.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="H46">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="I46" t="str">
-        <v>2264.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="H47">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I47" t="str">
-        <v>467.0</v>
+        <v>453.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H48">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I48" t="str">
-        <v>1145.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="H49">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="I49" t="str">
-        <v>682.0</v>
+        <v>678.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H50">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="I50" t="str">
-        <v>936.0</v>
+        <v>939.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H51">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I51" t="str">
-        <v>489.0</v>
+        <v>453.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H52">
         <v>103</v>
       </c>
       <c r="I52" t="str">
-        <v>226.0</v>
+        <v>225.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H53">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I53" t="str">
-        <v>478.0</v>
+        <v>473.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H54">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I54" t="str">
-        <v>914.0</v>
+        <v>933.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="H55">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="I55" t="str">
-        <v>1389.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,10 +2509,10 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H56">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="I56" t="str">
         <v>2286.0</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H57">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="I57" t="str">
-        <v>470.0</v>
+        <v>498.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H58">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I58" t="str">
-        <v>1150.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2626,10 +2626,10 @@
         <v>148</v>
       </c>
       <c r="H59">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="I59" t="str">
-        <v>687.0</v>
+        <v>677.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H60">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="I60" t="str">
-        <v>947.0</v>
+        <v>932.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H61">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="I61" t="str">
-        <v>482.0</v>
+        <v>479.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H62">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="I62" t="str">
-        <v>252.0</v>
+        <v>225.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H63">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="I63" t="str">
-        <v>450.0</v>
+        <v>496.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H64">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="I64" t="str">
-        <v>939.0</v>
+        <v>913.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H65">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="I65" t="str">
-        <v>1364.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="H66">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="I66" t="str">
-        <v>2255.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H67">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I67" t="str">
-        <v>481.0</v>
+        <v>460.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H68">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="I68" t="str">
-        <v>1166.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H69">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I69" t="str">
-        <v>679.0</v>
+        <v>689.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="H70">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I70" t="str">
-        <v>945.0</v>
+        <v>933.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="H71">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I71" t="str">
-        <v>461.0</v>
+        <v>459.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H72">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I72" t="str">
-        <v>269.0</v>
+        <v>247.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H73">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I73" t="str">
-        <v>452.0</v>
+        <v>495.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H74">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="I74" t="str">
-        <v>903.0</v>
+        <v>930.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="H75">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="I75" t="str">
-        <v>1385.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="H76">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="I76" t="str">
-        <v>2270.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H77">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="I77" t="str">
-        <v>461.0</v>
+        <v>498.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H78">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="I78" t="str">
-        <v>1168.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H79">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I79" t="str">
-        <v>676.0</v>
+        <v>688.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="H80">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="I80" t="str">
-        <v>939.0</v>
+        <v>904.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H81">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I81" t="str">
-        <v>493.0</v>
+        <v>464.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H82">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I82" t="str">
-        <v>255.0</v>
+        <v>252.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H83">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I83" t="str">
-        <v>488.0</v>
+        <v>469.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="H84">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="I84" t="str">
-        <v>931.0</v>
+        <v>900.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H85">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="I85" t="str">
-        <v>1396.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H86">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="I86" t="str">
-        <v>2274.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H87">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I87" t="str">
-        <v>480.0</v>
+        <v>462.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H88">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="I88" t="str">
-        <v>1142.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="H89">
         <v>182</v>
       </c>
       <c r="I89" t="str">
-        <v>676.0</v>
+        <v>679.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H90">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="I90" t="str">
-        <v>934.0</v>
+        <v>943.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H91">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I91" t="str">
-        <v>479.0</v>
+        <v>491.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
+        <v>107</v>
+      </c>
+      <c r="H92">
         <v>109</v>
       </c>
-      <c r="H92">
-        <v>132</v>
-      </c>
       <c r="I92" t="str">
-        <v>255.0</v>
+        <v>250.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="H93">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I93" t="str">
-        <v>492.0</v>
+        <v>477.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H94">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="I94" t="str">
-        <v>946.0</v>
+        <v>906.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H95">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I95" t="str">
-        <v>1353.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4032,10 +4032,10 @@
         <v>263</v>
       </c>
       <c r="H96">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="I96" t="str">
-        <v>2282.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H97">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="I97" t="str">
-        <v>488.0</v>
+        <v>455.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="H98">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="I98" t="str">
-        <v>1144.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="H99">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="I99" t="str">
-        <v>716.0</v>
+        <v>692.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="H100">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I100" t="str">
-        <v>946.0</v>
+        <v>910.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H101">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I101" t="str">
-        <v>465.0</v>
+        <v>452.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H102">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="I102" t="str">
-        <v>246.0</v>
+        <v>258.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H103">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I103" t="str">
-        <v>465.0</v>
+        <v>451.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H104">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I104" t="str">
-        <v>945.0</v>
+        <v>942.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="H105">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="I105" t="str">
-        <v>1356.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H106">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I106" t="str">
-        <v>2258.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H107">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="I107" t="str">
-        <v>475.0</v>
+        <v>478.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H108">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I108" t="str">
-        <v>1155.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4526,10 +4526,10 @@
         <v>143</v>
       </c>
       <c r="H109">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I109" t="str">
-        <v>708.0</v>
+        <v>716.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H110">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I110" t="str">
-        <v>910.0</v>
+        <v>901.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H111">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="I111" t="str">
-        <v>461.0</v>
+        <v>454.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="H112">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="I112" t="str">
-        <v>230.0</v>
+        <v>234.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H113">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="I113" t="str">
-        <v>453.0</v>
+        <v>475.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H114">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I114" t="str">
-        <v>945.0</v>
+        <v>900.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H115">
         <v>206</v>
       </c>
       <c r="I115" t="str">
-        <v>1367.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="H116">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I116" t="str">
-        <v>2296.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H117">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I117" t="str">
-        <v>458.0</v>
+        <v>492.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H118">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I118" t="str">
-        <v>1133.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H119">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I119" t="str">
-        <v>723.0</v>
+        <v>713.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H120">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="I120" t="str">
-        <v>944.0</v>
+        <v>940.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H121">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I121" t="str">
-        <v>468.0</v>
+        <v>467.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H122">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I122" t="str">
-        <v>247.0</v>
+        <v>267.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H123">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="I123" t="str">
-        <v>456.0</v>
+        <v>462.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="H124">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="I124" t="str">
-        <v>901.0</v>
+        <v>929.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,10 +5131,10 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H125">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I125" t="str">
         <v>1367.0</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H126">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I126" t="str">
-        <v>2267.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="H127">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="I127" t="str">
-        <v>484.0</v>
+        <v>487.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H128">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="I128" t="str">
-        <v>1145.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H129">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="I129" t="str">
-        <v>701.0</v>
+        <v>677.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H130">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="I130" t="str">
-        <v>913.0</v>
+        <v>910.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="H131">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="I131" t="str">
-        <v>460.0</v>
+        <v>480.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H132">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I132" t="str">
-        <v>236.0</v>
+        <v>239.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H133">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I133" t="str">
-        <v>493.0</v>
+        <v>484.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H134">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I134" t="str">
-        <v>939.0</v>
+        <v>903.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="H135">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="I135" t="str">
-        <v>1394.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H136">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I136" t="str">
-        <v>2288.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H137">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="I137" t="str">
-        <v>450.0</v>
+        <v>461.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H138">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="I138" t="str">
-        <v>1161.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="H139">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="I139" t="str">
-        <v>693.0</v>
+        <v>692.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H140">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="I140" t="str">
-        <v>941.0</v>
+        <v>937.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="H141">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="I141" t="str">
-        <v>497.0</v>
+        <v>469.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H142">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I142" t="str">
-        <v>237.0</v>
+        <v>259.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H143">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="I143" t="str">
-        <v>468.0</v>
+        <v>473.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H144">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="I144" t="str">
-        <v>917.0</v>
+        <v>900.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="H145">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I145" t="str">
-        <v>1373.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H146">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="I146" t="str">
-        <v>2272.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H147">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="I147" t="str">
-        <v>489.0</v>
+        <v>477.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H148">
         <v>175</v>
       </c>
       <c r="I148" t="str">
-        <v>1158.0</v>
+        <v>1137.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H149">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I149" t="str">
-        <v>693.0</v>
+        <v>684.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H150">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I150" t="str">
-        <v>924.0</v>
+        <v>911.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="H151">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I151" t="str">
-        <v>498.0</v>
+        <v>468.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H152">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="I152" t="str">
-        <v>231.0</v>
+        <v>238.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H153">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="I153" t="str">
-        <v>486.0</v>
+        <v>481.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H154">
         <v>190</v>
       </c>
       <c r="I154" t="str">
-        <v>903.0</v>
+        <v>912.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6274,10 +6274,10 @@
         <v>190</v>
       </c>
       <c r="H155">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="I155" t="str">
-        <v>1380.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H156">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="I156" t="str">
-        <v>2272.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="H157">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I157" t="str">
-        <v>499.0</v>
+        <v>468.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="H158">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="I158" t="str">
-        <v>1153.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="H159">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I159" t="str">
-        <v>710.0</v>
+        <v>700.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H160">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="I160" t="str">
-        <v>947.0</v>
+        <v>925.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H161">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I161" t="str">
-        <v>474.0</v>
+        <v>463.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H162">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I162" t="str">
-        <v>266.0</v>
+        <v>225.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H163">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I163" t="str">
-        <v>471.0</v>
+        <v>473.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="H164">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="I164" t="str">
-        <v>900.0</v>
+        <v>937.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H165">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I165" t="str">
-        <v>1367.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H166">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="I166" t="str">
-        <v>2283.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H167">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="I167" t="str">
-        <v>455.0</v>
+        <v>486.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H168">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I168" t="str">
-        <v>1143.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6806,10 +6806,10 @@
         <v>130</v>
       </c>
       <c r="H169">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I169" t="str">
-        <v>699.0</v>
+        <v>722.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H170">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I170" t="str">
-        <v>923.0</v>
+        <v>938.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H171">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I171" t="str">
-        <v>457.0</v>
+        <v>460.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H172">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I172" t="str">
-        <v>258.0</v>
+        <v>260.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H173">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I173" t="str">
-        <v>475.0</v>
+        <v>481.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H174">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I174" t="str">
-        <v>946.0</v>
+        <v>941.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="H175">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="I175" t="str">
-        <v>1363.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H176">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="I176" t="str">
-        <v>2264.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H177">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I177" t="str">
-        <v>464.0</v>
+        <v>473.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H178">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I178" t="str">
-        <v>1156.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H179">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I179" t="str">
-        <v>698.0</v>
+        <v>677.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="H180">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="I180" t="str">
-        <v>930.0</v>
+        <v>928.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H181">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I181" t="str">
-        <v>457.0</v>
+        <v>488.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H182">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I182" t="str">
-        <v>258.0</v>
+        <v>241.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H183">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I183" t="str">
-        <v>465.0</v>
+        <v>462.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H184">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="I184" t="str">
-        <v>919.0</v>
+        <v>900.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H185">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="I185" t="str">
-        <v>1390.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="H186">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I186" t="str">
-        <v>2259.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H187">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I187" t="str">
-        <v>455.0</v>
+        <v>483.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="H188">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="I188" t="str">
-        <v>1139.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="H189">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="I189" t="str">
-        <v>698.0</v>
+        <v>685.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H190">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="I190" t="str">
-        <v>923.0</v>
+        <v>927.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
+        <v>125</v>
+      </c>
+      <c r="H191">
         <v>133</v>
       </c>
-      <c r="H191">
-        <v>171</v>
-      </c>
       <c r="I191" t="str">
-        <v>463.0</v>
+        <v>464.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H192">
         <v>129</v>
       </c>
       <c r="I192" t="str">
-        <v>244.0</v>
+        <v>261.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H193">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="I193" t="str">
-        <v>479.0</v>
+        <v>482.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="H194">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I194" t="str">
-        <v>922.0</v>
+        <v>938.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="H195">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I195" t="str">
-        <v>1387.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H196">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I196" t="str">
-        <v>2263.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H197">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I197" t="str">
-        <v>483.0</v>
+        <v>491.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="H198">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="I198" t="str">
-        <v>1170.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H199">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="I199" t="str">
-        <v>723.0</v>
+        <v>709.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H200">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I200" t="str">
-        <v>917.0</v>
+        <v>946.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="H201">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I201" t="str">
-        <v>481.0</v>
+        <v>455.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H202">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I202" t="str">
-        <v>271.0</v>
+        <v>226.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8098,10 +8098,10 @@
         <v>114</v>
       </c>
       <c r="H203">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="I203" t="str">
-        <v>489.0</v>
+        <v>469.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H204">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="I204" t="str">
-        <v>914.0</v>
+        <v>942.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="H205">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I205" t="str">
-        <v>1354.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H206">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="I206" t="str">
-        <v>2282.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8250,10 +8250,10 @@
         <v>126</v>
       </c>
       <c r="H207">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I207" t="str">
-        <v>485.0</v>
+        <v>461.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="H208">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="I208" t="str">
-        <v>1173.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="H209">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I209" t="str">
-        <v>703.0</v>
+        <v>682.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H210">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="I210" t="str">
-        <v>904.0</v>
+        <v>934.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H211">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I211" t="str">
-        <v>497.0</v>
+        <v>487.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H212">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="I212" t="str">
-        <v>250.0</v>
+        <v>256.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H213">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="I213" t="str">
-        <v>490.0</v>
+        <v>459.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H214">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="I214" t="str">
-        <v>918.0</v>
+        <v>917.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H215">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I215" t="str">
-        <v>1355.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="H216">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="I216" t="str">
-        <v>2290.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H217">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I217" t="str">
-        <v>491.0</v>
+        <v>470.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="H218">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="I218" t="str">
-        <v>1142.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H219">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="I219" t="str">
-        <v>708.0</v>
+        <v>677.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H220">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I220" t="str">
-        <v>933.0</v>
+        <v>912.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H221">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="I221" t="str">
-        <v>460.0</v>
+        <v>487.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H222">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="I222" t="str">
-        <v>256.0</v>
+        <v>265.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H223">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I223" t="str">
-        <v>494.0</v>
+        <v>476.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H224">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="I224" t="str">
-        <v>914.0</v>
+        <v>923.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,10 +8931,10 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H225">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="I225" t="str">
         <v>1384.0</v>
@@ -8969,10 +8969,10 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H226">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I226" t="str">
         <v>2280.0</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H227">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="I227" t="str">
-        <v>471.0</v>
+        <v>490.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="H228">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I228" t="str">
-        <v>1136.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="H229">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I229" t="str">
-        <v>697.0</v>
+        <v>714.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="H230">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="I230" t="str">
-        <v>905.0</v>
+        <v>921.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="H231">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I231" t="str">
-        <v>480.0</v>
+        <v>497.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H232">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="I232" t="str">
-        <v>274.0</v>
+        <v>261.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H233">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I233" t="str">
-        <v>490.0</v>
+        <v>496.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H234">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I234" t="str">
-        <v>936.0</v>
+        <v>947.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="H235">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I235" t="str">
-        <v>1362.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="H236">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="I236" t="str">
-        <v>2277.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H237">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="I237" t="str">
-        <v>454.0</v>
+        <v>498.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H238">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="I238" t="str">
-        <v>1164.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H239">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I239" t="str">
-        <v>723.0</v>
+        <v>709.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H240">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="I240" t="str">
-        <v>913.0</v>
+        <v>933.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H241">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I241" t="str">
-        <v>462.0</v>
+        <v>499.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="H242">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I242" t="str">
-        <v>258.0</v>
+        <v>256.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H243">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I243" t="str">
-        <v>484.0</v>
+        <v>465.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="H244">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="I244" t="str">
-        <v>915.0</v>
+        <v>906.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H245">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I245" t="str">
-        <v>1373.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H246">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="I246" t="str">
-        <v>2279.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H247">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I247" t="str">
-        <v>479.0</v>
+        <v>465.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H248">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I248" t="str">
-        <v>1170.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H249">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I249" t="str">
-        <v>712.0</v>
+        <v>675.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H250">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="I250" t="str">
-        <v>933.0</v>
+        <v>917.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H251">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I251" t="str">
-        <v>482.0</v>
+        <v>483.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H252">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="I252" t="str">
-        <v>262.0</v>
+        <v>272.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="H253">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I253" t="str">
-        <v>470.0</v>
+        <v>494.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H254">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="I254" t="str">
-        <v>900.0</v>
+        <v>925.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H255">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I255" t="str">
-        <v>1356.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H256">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="I256" t="str">
-        <v>2268.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H257">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="I257" t="str">
-        <v>463.0</v>
+        <v>485.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="H258">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I258" t="str">
-        <v>1170.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H259">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="I259" t="str">
-        <v>707.0</v>
+        <v>708.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H260">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="I260" t="str">
-        <v>906.0</v>
+        <v>934.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H261">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="I261" t="str">
-        <v>495.0</v>
+        <v>483.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H262">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I262" t="str">
-        <v>266.0</v>
+        <v>255.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="H263">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="I263" t="str">
-        <v>453.0</v>
+        <v>477.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H264">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="I264" t="str">
-        <v>916.0</v>
+        <v>905.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H265">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="I265" t="str">
-        <v>1350.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H266">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I266" t="str">
-        <v>2282.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H267">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I267" t="str">
-        <v>479.0</v>
+        <v>457.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H268">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I268" t="str">
-        <v>1143.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H269">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="I269" t="str">
-        <v>716.0</v>
+        <v>714.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H270">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="I270" t="str">
-        <v>913.0</v>
+        <v>945.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H271">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="I271" t="str">
-        <v>482.0</v>
+        <v>464.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="H272">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="I272" t="str">
-        <v>269.0</v>
+        <v>268.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H273">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I273" t="str">
-        <v>461.0</v>
+        <v>460.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="H274">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="I274" t="str">
-        <v>907.0</v>
+        <v>921.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H275">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I275" t="str">
-        <v>1399.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H276">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="I276" t="str">
-        <v>2292.0</v>
+        <v>2269.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H277">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="I277" t="str">
-        <v>478.0</v>
+        <v>461.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H278">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="I278" t="str">
-        <v>1171.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H279">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="I279" t="str">
-        <v>699.0</v>
+        <v>682.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="H280">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I280" t="str">
-        <v>908.0</v>
+        <v>944.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H281">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I281" t="str">
-        <v>466.0</v>
+        <v>469.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H282">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="I282" t="str">
-        <v>266.0</v>
+        <v>251.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H283">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I283" t="str">
-        <v>477.0</v>
+        <v>468.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="H284">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="I284" t="str">
-        <v>906.0</v>
+        <v>947.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H285">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I285" t="str">
-        <v>1394.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H286">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I286" t="str">
-        <v>2264.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H287">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="I287" t="str">
-        <v>477.0</v>
+        <v>481.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H288">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="I288" t="str">
-        <v>1147.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H289">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="I289" t="str">
-        <v>686.0</v>
+        <v>717.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H290">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="I290" t="str">
-        <v>947.0</v>
+        <v>932.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H291">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="I291" t="str">
-        <v>498.0</v>
+        <v>497.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H292">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="I292" t="str">
-        <v>269.0</v>
+        <v>242.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H293">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I293" t="str">
-        <v>480.0</v>
+        <v>450.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H294">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="I294" t="str">
-        <v>932.0</v>
+        <v>912.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H295">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="I295" t="str">
-        <v>1395.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H296">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="I296" t="str">
-        <v>2273.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H297">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="I297" t="str">
-        <v>493.0</v>
+        <v>498.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H298">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="I298" t="str">
-        <v>1161.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="H299">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I299" t="str">
-        <v>688.0</v>
+        <v>706.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H300">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I300" t="str">
-        <v>946.0</v>
+        <v>907.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H301">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="I301" t="str">
-        <v>472.0</v>
+        <v>481.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I2" t="str">
-        <v>225.0</v>
+        <v>256.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H3">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="I3" t="str">
-        <v>465.0</v>
+        <v>494.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H4">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="I4" t="str">
-        <v>900.0</v>
+        <v>949.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="H5">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="I5" t="str">
-        <v>1374.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="H6">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I6" t="str">
-        <v>2289.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="H7">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="I7" t="str">
-        <v>495.0</v>
+        <v>479.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H8">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="I8" t="str">
-        <v>1135.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H9">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I9" t="str">
-        <v>718.0</v>
+        <v>712.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H10">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="I10" t="str">
-        <v>916.0</v>
+        <v>918.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H11">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I11" t="str">
-        <v>482.0</v>
+        <v>497.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H12">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="I12" t="str">
-        <v>228.0</v>
+        <v>271.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H13">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I13" t="str">
-        <v>489.0</v>
+        <v>494.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H14">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="I14" t="str">
-        <v>923.0</v>
+        <v>922.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="H15">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="I15" t="str">
-        <v>1353.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
+        <v>242</v>
+      </c>
+      <c r="H16">
         <v>243</v>
       </c>
-      <c r="H16">
-        <v>244</v>
-      </c>
       <c r="I16" t="str">
-        <v>2276.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H17">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I17" t="str">
-        <v>464.0</v>
+        <v>492.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H18">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="I18" t="str">
-        <v>1171.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1106,10 +1106,10 @@
         <v>154</v>
       </c>
       <c r="H19">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="I19" t="str">
-        <v>706.0</v>
+        <v>702.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H20">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="I20" t="str">
-        <v>926.0</v>
+        <v>908.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="H21">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I21" t="str">
-        <v>473.0</v>
+        <v>456.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H22">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="I22" t="str">
-        <v>261.0</v>
+        <v>271.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H23">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I23" t="str">
-        <v>458.0</v>
+        <v>453.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="H24">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="I24" t="str">
-        <v>903.0</v>
+        <v>945.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H25">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="I25" t="str">
-        <v>1395.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="H26">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I26" t="str">
-        <v>2258.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1410,10 +1410,10 @@
         <v>105</v>
       </c>
       <c r="H27">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I27" t="str">
-        <v>483.0</v>
+        <v>498.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="H28">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="I28" t="str">
-        <v>1171.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="H29">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="I29" t="str">
-        <v>708.0</v>
+        <v>719.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H30">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I30" t="str">
-        <v>919.0</v>
+        <v>947.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="H31">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="I31" t="str">
-        <v>471.0</v>
+        <v>478.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H32">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I32" t="str">
-        <v>263.0</v>
+        <v>237.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H33">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I33" t="str">
-        <v>484.0</v>
+        <v>451.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H34">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="I34" t="str">
-        <v>904.0</v>
+        <v>945.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1714,10 +1714,10 @@
         <v>192</v>
       </c>
       <c r="H35">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I35" t="str">
-        <v>1375.0</v>
+        <v>1383.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="H36">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I36" t="str">
-        <v>2266.0</v>
+        <v>2284.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H37">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="I37" t="str">
-        <v>450.0</v>
+        <v>457.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H38">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="I38" t="str">
-        <v>1150.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H39">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="I39" t="str">
-        <v>681.0</v>
+        <v>705.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H40">
         <v>119</v>
       </c>
       <c r="I40" t="str">
-        <v>922.0</v>
+        <v>926.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H41">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="I41" t="str">
-        <v>470.0</v>
+        <v>493.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H42">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I42" t="str">
-        <v>226.0</v>
+        <v>230.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H43">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I43" t="str">
-        <v>488.0</v>
+        <v>484.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H44">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I44" t="str">
-        <v>941.0</v>
+        <v>945.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H45">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="I45" t="str">
-        <v>1398.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H46">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="I46" t="str">
-        <v>2252.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H47">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="I47" t="str">
-        <v>453.0</v>
+        <v>462.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H48">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I48" t="str">
-        <v>1129.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="H49">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I49" t="str">
-        <v>678.0</v>
+        <v>690.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H50">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="I50" t="str">
-        <v>939.0</v>
+        <v>909.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2322,10 +2322,10 @@
         <v>131</v>
       </c>
       <c r="H51">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="I51" t="str">
-        <v>453.0</v>
+        <v>463.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H52">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I52" t="str">
-        <v>225.0</v>
+        <v>273.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="H53">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="I53" t="str">
-        <v>473.0</v>
+        <v>450.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H54">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="I54" t="str">
-        <v>933.0</v>
+        <v>941.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="H55">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="I55" t="str">
-        <v>1364.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H56">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="I56" t="str">
-        <v>2286.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="H57">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I57" t="str">
-        <v>498.0</v>
+        <v>469.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H58">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="I58" t="str">
-        <v>1143.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H59">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="I59" t="str">
-        <v>677.0</v>
+        <v>695.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H60">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="I60" t="str">
-        <v>932.0</v>
+        <v>936.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H61">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="I61" t="str">
-        <v>479.0</v>
+        <v>491.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H62">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="I62" t="str">
-        <v>225.0</v>
+        <v>239.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H63">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="I63" t="str">
-        <v>496.0</v>
+        <v>499.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H64">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I64" t="str">
-        <v>913.0</v>
+        <v>940.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="H65">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="I65" t="str">
-        <v>1397.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="H66">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I66" t="str">
-        <v>2278.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H67">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="I67" t="str">
-        <v>460.0</v>
+        <v>476.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="H68">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="I68" t="str">
-        <v>1151.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="H69">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I69" t="str">
-        <v>689.0</v>
+        <v>708.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H70">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="I70" t="str">
-        <v>933.0</v>
+        <v>928.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H71">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="I71" t="str">
-        <v>459.0</v>
+        <v>462.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H72">
         <v>110</v>
       </c>
       <c r="I72" t="str">
-        <v>247.0</v>
+        <v>237.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H73">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="I73" t="str">
-        <v>495.0</v>
+        <v>471.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="H74">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I74" t="str">
-        <v>930.0</v>
+        <v>933.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H75">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="I75" t="str">
-        <v>1374.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="H76">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I76" t="str">
-        <v>2276.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H77">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="I77" t="str">
-        <v>498.0</v>
+        <v>454.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H78">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I78" t="str">
-        <v>1162.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H79">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I79" t="str">
-        <v>688.0</v>
+        <v>698.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H80">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I80" t="str">
-        <v>904.0</v>
+        <v>932.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H81">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I81" t="str">
-        <v>464.0</v>
+        <v>455.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H82">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="I82" t="str">
-        <v>252.0</v>
+        <v>225.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H83">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I83" t="str">
-        <v>469.0</v>
+        <v>489.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H84">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="I84" t="str">
-        <v>900.0</v>
+        <v>942.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H85">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="I85" t="str">
-        <v>1377.0</v>
+        <v>1382.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H86">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="I86" t="str">
-        <v>2264.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H87">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I87" t="str">
-        <v>462.0</v>
+        <v>487.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H88">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I88" t="str">
-        <v>1147.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="H89">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="I89" t="str">
-        <v>679.0</v>
+        <v>681.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H90">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="I90" t="str">
-        <v>943.0</v>
+        <v>912.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H91">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I91" t="str">
-        <v>491.0</v>
+        <v>468.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H92">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="I92" t="str">
-        <v>250.0</v>
+        <v>270.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H93">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I93" t="str">
-        <v>477.0</v>
+        <v>498.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="H94">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="I94" t="str">
-        <v>906.0</v>
+        <v>933.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="H95">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="I95" t="str">
-        <v>1350.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="H96">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="I96" t="str">
-        <v>2277.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H97">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="I97" t="str">
-        <v>455.0</v>
+        <v>490.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="H98">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="I98" t="str">
-        <v>1166.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H99">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="I99" t="str">
-        <v>692.0</v>
+        <v>704.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H100">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I100" t="str">
-        <v>910.0</v>
+        <v>935.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H101">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I101" t="str">
-        <v>452.0</v>
+        <v>491.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H102">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I102" t="str">
-        <v>258.0</v>
+        <v>233.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H103">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="I103" t="str">
-        <v>451.0</v>
+        <v>481.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H104">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I104" t="str">
-        <v>942.0</v>
+        <v>903.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H105">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I105" t="str">
-        <v>1355.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H106">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="I106" t="str">
-        <v>2266.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H107">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I107" t="str">
-        <v>478.0</v>
+        <v>469.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H108">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="I108" t="str">
-        <v>1125.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H109">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I109" t="str">
-        <v>716.0</v>
+        <v>697.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H110">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I110" t="str">
-        <v>901.0</v>
+        <v>942.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H111">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="I111" t="str">
-        <v>454.0</v>
+        <v>467.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H112">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="I112" t="str">
-        <v>234.0</v>
+        <v>226.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H113">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I113" t="str">
-        <v>475.0</v>
+        <v>462.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H114">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="I114" t="str">
-        <v>900.0</v>
+        <v>947.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4754,10 +4754,10 @@
         <v>195</v>
       </c>
       <c r="H115">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="I115" t="str">
-        <v>1399.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H116">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="I116" t="str">
-        <v>2299.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H117">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="I117" t="str">
-        <v>492.0</v>
+        <v>466.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H118">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="I118" t="str">
-        <v>1170.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H119">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I119" t="str">
-        <v>713.0</v>
+        <v>678.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H120">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="I120" t="str">
-        <v>940.0</v>
+        <v>932.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H121">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I121" t="str">
-        <v>467.0</v>
+        <v>491.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H122">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="I122" t="str">
-        <v>267.0</v>
+        <v>233.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H123">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I123" t="str">
-        <v>462.0</v>
+        <v>460.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H124">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="I124" t="str">
-        <v>929.0</v>
+        <v>908.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H125">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="I125" t="str">
-        <v>1367.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H126">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="I126" t="str">
-        <v>2252.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H127">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I127" t="str">
-        <v>487.0</v>
+        <v>488.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H128">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="I128" t="str">
-        <v>1162.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H129">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="I129" t="str">
-        <v>677.0</v>
+        <v>682.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H130">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="I130" t="str">
-        <v>910.0</v>
+        <v>903.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H131">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="I131" t="str">
-        <v>480.0</v>
+        <v>474.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H132">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I132" t="str">
-        <v>239.0</v>
+        <v>273.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H133">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="I133" t="str">
-        <v>484.0</v>
+        <v>488.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H134">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="I134" t="str">
-        <v>903.0</v>
+        <v>907.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="H135">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="I135" t="str">
-        <v>1389.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H136">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I136" t="str">
-        <v>2269.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H137">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I137" t="str">
-        <v>461.0</v>
+        <v>492.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H138">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I138" t="str">
-        <v>1142.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H139">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="I139" t="str">
-        <v>692.0</v>
+        <v>717.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="H140">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="I140" t="str">
-        <v>937.0</v>
+        <v>935.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H141">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="I141" t="str">
-        <v>469.0</v>
+        <v>455.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H142">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I142" t="str">
-        <v>259.0</v>
+        <v>242.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="H143">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="I143" t="str">
-        <v>473.0</v>
+        <v>482.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H144">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="I144" t="str">
-        <v>900.0</v>
+        <v>919.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H145">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="I145" t="str">
-        <v>1396.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="H146">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I146" t="str">
-        <v>2283.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H147">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I147" t="str">
-        <v>477.0</v>
+        <v>499.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H148">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="I148" t="str">
-        <v>1137.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="H149">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="I149" t="str">
-        <v>684.0</v>
+        <v>710.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H150">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="I150" t="str">
-        <v>911.0</v>
+        <v>937.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H151">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="I151" t="str">
-        <v>468.0</v>
+        <v>481.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H152">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I152" t="str">
-        <v>238.0</v>
+        <v>273.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H153">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="I153" t="str">
-        <v>481.0</v>
+        <v>489.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,7 +6233,7 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H154">
         <v>190</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H155">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="I155" t="str">
-        <v>1394.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H156">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="I156" t="str">
-        <v>2298.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="H157">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="I157" t="str">
-        <v>468.0</v>
+        <v>454.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H158">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I158" t="str">
-        <v>1164.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H159">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="I159" t="str">
-        <v>700.0</v>
+        <v>693.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H160">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="I160" t="str">
-        <v>925.0</v>
+        <v>946.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H161">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I161" t="str">
-        <v>463.0</v>
+        <v>468.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H162">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I162" t="str">
-        <v>225.0</v>
+        <v>242.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="H163">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="I163" t="str">
-        <v>473.0</v>
+        <v>454.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H164">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I164" t="str">
-        <v>937.0</v>
+        <v>933.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H165">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I165" t="str">
-        <v>1375.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="H166">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="I166" t="str">
-        <v>2273.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H167">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I167" t="str">
-        <v>486.0</v>
+        <v>480.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H168">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="I168" t="str">
-        <v>1138.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H169">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="I169" t="str">
-        <v>722.0</v>
+        <v>707.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H170">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="I170" t="str">
-        <v>938.0</v>
+        <v>943.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="H171">
         <v>154</v>
       </c>
       <c r="I171" t="str">
-        <v>460.0</v>
+        <v>483.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H172">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="I172" t="str">
-        <v>260.0</v>
+        <v>233.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H173">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="I173" t="str">
-        <v>481.0</v>
+        <v>469.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="H174">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="I174" t="str">
-        <v>941.0</v>
+        <v>934.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H175">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="I175" t="str">
-        <v>1388.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H176">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="I176" t="str">
-        <v>2299.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
+        <v>117</v>
+      </c>
+      <c r="H177">
         <v>118</v>
       </c>
-      <c r="H177">
-        <v>149</v>
-      </c>
       <c r="I177" t="str">
-        <v>473.0</v>
+        <v>458.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="H178">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="I178" t="str">
-        <v>1170.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H179">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="I179" t="str">
-        <v>677.0</v>
+        <v>721.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H180">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="I180" t="str">
-        <v>928.0</v>
+        <v>905.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="H181">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I181" t="str">
-        <v>488.0</v>
+        <v>472.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H182">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="I182" t="str">
-        <v>241.0</v>
+        <v>258.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H183">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I183" t="str">
-        <v>462.0</v>
+        <v>450.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H184">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="I184" t="str">
-        <v>900.0</v>
+        <v>929.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H185">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="I185" t="str">
-        <v>1353.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H186">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="I186" t="str">
-        <v>2274.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H187">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I187" t="str">
-        <v>483.0</v>
+        <v>471.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H188">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="I188" t="str">
-        <v>1146.0</v>
+        <v>1160.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H189">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I189" t="str">
-        <v>685.0</v>
+        <v>686.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H190">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="I190" t="str">
-        <v>927.0</v>
+        <v>929.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H191">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I191" t="str">
-        <v>464.0</v>
+        <v>482.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H192">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="I192" t="str">
-        <v>261.0</v>
+        <v>227.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H193">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="I193" t="str">
-        <v>482.0</v>
+        <v>475.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H194">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I194" t="str">
-        <v>938.0</v>
+        <v>943.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H195">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="I195" t="str">
-        <v>1362.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H196">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I196" t="str">
-        <v>2259.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H197">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I197" t="str">
-        <v>491.0</v>
+        <v>498.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="H198">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="I198" t="str">
-        <v>1151.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H199">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="I199" t="str">
-        <v>709.0</v>
+        <v>680.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H200">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="I200" t="str">
-        <v>946.0</v>
+        <v>933.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H201">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I201" t="str">
-        <v>455.0</v>
+        <v>452.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="H202">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I202" t="str">
-        <v>226.0</v>
+        <v>256.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H203">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I203" t="str">
-        <v>469.0</v>
+        <v>464.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H204">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="I204" t="str">
-        <v>942.0</v>
+        <v>936.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H205">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="I205" t="str">
-        <v>1366.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="H206">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="I206" t="str">
-        <v>2267.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H207">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I207" t="str">
-        <v>461.0</v>
+        <v>457.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H208">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I208" t="str">
-        <v>1163.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H209">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="I209" t="str">
-        <v>682.0</v>
+        <v>676.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H210">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I210" t="str">
-        <v>934.0</v>
+        <v>936.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H211">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="I211" t="str">
-        <v>487.0</v>
+        <v>474.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H212">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="I212" t="str">
-        <v>256.0</v>
+        <v>248.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H213">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="I213" t="str">
-        <v>459.0</v>
+        <v>499.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8516,10 +8516,10 @@
         <v>155</v>
       </c>
       <c r="H214">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I214" t="str">
-        <v>917.0</v>
+        <v>901.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H215">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I215" t="str">
-        <v>1369.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H216">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I216" t="str">
-        <v>2267.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H217">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I217" t="str">
-        <v>470.0</v>
+        <v>463.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="H218">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I218" t="str">
-        <v>1164.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H219">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="I219" t="str">
-        <v>677.0</v>
+        <v>690.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H220">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I220" t="str">
-        <v>912.0</v>
+        <v>928.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H221">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="I221" t="str">
-        <v>487.0</v>
+        <v>495.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H222">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="I222" t="str">
-        <v>265.0</v>
+        <v>269.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H223">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="I223" t="str">
-        <v>476.0</v>
+        <v>468.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H224">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="I224" t="str">
-        <v>923.0</v>
+        <v>903.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H225">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I225" t="str">
-        <v>1384.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="H226">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="I226" t="str">
-        <v>2280.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="H227">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="I227" t="str">
-        <v>490.0</v>
+        <v>459.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H228">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="I228" t="str">
-        <v>1144.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H229">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I229" t="str">
-        <v>714.0</v>
+        <v>702.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H230">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="I230" t="str">
-        <v>921.0</v>
+        <v>901.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H231">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="I231" t="str">
-        <v>497.0</v>
+        <v>493.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="H232">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="I232" t="str">
-        <v>261.0</v>
+        <v>230.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H233">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I233" t="str">
-        <v>496.0</v>
+        <v>487.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H234">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I234" t="str">
-        <v>947.0</v>
+        <v>941.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H235">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I235" t="str">
-        <v>1394.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="H236">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I236" t="str">
-        <v>2271.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H237">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I237" t="str">
-        <v>498.0</v>
+        <v>480.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H238">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="I238" t="str">
-        <v>1174.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H239">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="I239" t="str">
-        <v>709.0</v>
+        <v>677.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H240">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I240" t="str">
-        <v>933.0</v>
+        <v>915.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H241">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="I241" t="str">
-        <v>499.0</v>
+        <v>475.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="H242">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I242" t="str">
-        <v>256.0</v>
+        <v>242.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H243">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="I243" t="str">
-        <v>465.0</v>
+        <v>499.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H244">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="I244" t="str">
-        <v>906.0</v>
+        <v>936.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H245">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I245" t="str">
-        <v>1386.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H246">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I246" t="str">
-        <v>2296.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H247">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I247" t="str">
-        <v>465.0</v>
+        <v>490.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H248">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="I248" t="str">
-        <v>1158.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H249">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I249" t="str">
-        <v>675.0</v>
+        <v>711.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H250">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I250" t="str">
-        <v>917.0</v>
+        <v>944.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="H251">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I251" t="str">
-        <v>483.0</v>
+        <v>454.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H252">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="I252" t="str">
-        <v>272.0</v>
+        <v>244.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H253">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I253" t="str">
-        <v>494.0</v>
+        <v>467.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H254">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="I254" t="str">
-        <v>925.0</v>
+        <v>932.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H255">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="I255" t="str">
-        <v>1377.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H256">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I256" t="str">
-        <v>2257.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10150,10 +10150,10 @@
         <v>120</v>
       </c>
       <c r="H257">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I257" t="str">
-        <v>485.0</v>
+        <v>488.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
+        <v>160</v>
+      </c>
+      <c r="H258">
         <v>176</v>
       </c>
-      <c r="H258">
-        <v>190</v>
-      </c>
       <c r="I258" t="str">
-        <v>1144.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H259">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="I259" t="str">
-        <v>708.0</v>
+        <v>680.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H260">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I260" t="str">
-        <v>934.0</v>
+        <v>949.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H261">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I261" t="str">
-        <v>483.0</v>
+        <v>498.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H262">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="I262" t="str">
-        <v>255.0</v>
+        <v>273.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H263">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="I263" t="str">
-        <v>477.0</v>
+        <v>497.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="H264">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="I264" t="str">
-        <v>905.0</v>
+        <v>924.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="H265">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="I265" t="str">
-        <v>1351.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10492,10 +10492,10 @@
         <v>240</v>
       </c>
       <c r="H266">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="I266" t="str">
-        <v>2253.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H267">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="I267" t="str">
-        <v>457.0</v>
+        <v>491.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H268">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I268" t="str">
-        <v>1171.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H269">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="I269" t="str">
-        <v>714.0</v>
+        <v>711.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H270">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="I270" t="str">
-        <v>945.0</v>
+        <v>915.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,10 +10679,10 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H271">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I271" t="str">
         <v>464.0</v>
@@ -10717,10 +10717,10 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H272">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I272" t="str">
         <v>268.0</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H273">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I273" t="str">
-        <v>460.0</v>
+        <v>464.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H274">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="I274" t="str">
-        <v>921.0</v>
+        <v>905.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="H275">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I275" t="str">
-        <v>1362.0</v>
+        <v>1382.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H276">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I276" t="str">
-        <v>2269.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H277">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I277" t="str">
-        <v>461.0</v>
+        <v>487.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H278">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="I278" t="str">
-        <v>1133.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H279">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="I279" t="str">
-        <v>682.0</v>
+        <v>692.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="H280">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="I280" t="str">
-        <v>944.0</v>
+        <v>910.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H281">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I281" t="str">
-        <v>469.0</v>
+        <v>476.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="H282">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I282" t="str">
-        <v>251.0</v>
+        <v>237.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="H283">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="I283" t="str">
-        <v>468.0</v>
+        <v>471.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H284">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="I284" t="str">
-        <v>947.0</v>
+        <v>915.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11214,7 +11214,7 @@
         <v>190</v>
       </c>
       <c r="H285">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I285" t="str">
         <v>1359.0</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H286">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="I286" t="str">
-        <v>2252.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H287">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="I287" t="str">
-        <v>481.0</v>
+        <v>494.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H288">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I288" t="str">
-        <v>1131.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H289">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="I289" t="str">
-        <v>717.0</v>
+        <v>724.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H290">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I290" t="str">
-        <v>932.0</v>
+        <v>935.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H291">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I291" t="str">
-        <v>497.0</v>
+        <v>456.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H292">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="I292" t="str">
-        <v>242.0</v>
+        <v>229.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H293">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I293" t="str">
-        <v>450.0</v>
+        <v>499.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H294">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="I294" t="str">
-        <v>912.0</v>
+        <v>949.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H295">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="I295" t="str">
-        <v>1364.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="H296">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="I296" t="str">
-        <v>2264.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H297">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="I297" t="str">
-        <v>498.0</v>
+        <v>472.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="H298">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I298" t="str">
-        <v>1133.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H299">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="I299" t="str">
-        <v>706.0</v>
+        <v>692.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H300">
         <v>113</v>
       </c>
       <c r="I300" t="str">
-        <v>907.0</v>
+        <v>936.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="H301">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="I301" t="str">
-        <v>481.0</v>
+        <v>467.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I2" t="str">
-        <v>256.0</v>
+        <v>235.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I3" t="str">
-        <v>494.0</v>
+        <v>462.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H4">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I4" t="str">
-        <v>949.0</v>
+        <v>909.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H5">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I5" t="str">
-        <v>1351.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H6">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I6" t="str">
-        <v>2263.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="H7">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I7" t="str">
-        <v>479.0</v>
+        <v>492.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="H8">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I8" t="str">
-        <v>1138.0</v>
+        <v>1145.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H9">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I9" t="str">
-        <v>712.0</v>
+        <v>688.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H10">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="I10" t="str">
-        <v>918.0</v>
+        <v>926.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H11">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="I11" t="str">
-        <v>497.0</v>
+        <v>479.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H12">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="I12" t="str">
-        <v>271.0</v>
+        <v>243.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H13">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I13" t="str">
-        <v>494.0</v>
+        <v>478.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H14">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I14" t="str">
-        <v>922.0</v>
+        <v>904.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H15">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="I15" t="str">
-        <v>1392.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="H16">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="I16" t="str">
-        <v>2298.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H17">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="I17" t="str">
-        <v>492.0</v>
+        <v>468.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H18">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I18" t="str">
-        <v>1148.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H19">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I19" t="str">
-        <v>702.0</v>
+        <v>693.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H20">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="I20" t="str">
-        <v>908.0</v>
+        <v>920.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H21">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I21" t="str">
-        <v>456.0</v>
+        <v>466.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H22">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I22" t="str">
-        <v>271.0</v>
+        <v>225.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H23">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="I23" t="str">
-        <v>453.0</v>
+        <v>456.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H24">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="I24" t="str">
-        <v>945.0</v>
+        <v>923.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1334,10 +1334,10 @@
         <v>204</v>
       </c>
       <c r="H25">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="I25" t="str">
-        <v>1355.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H26">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="I26" t="str">
-        <v>2271.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H27">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I27" t="str">
-        <v>498.0</v>
+        <v>453.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="H28">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="I28" t="str">
-        <v>1158.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H29">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I29" t="str">
-        <v>719.0</v>
+        <v>689.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H30">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I30" t="str">
-        <v>947.0</v>
+        <v>908.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="H31">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="I31" t="str">
-        <v>478.0</v>
+        <v>488.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="H32">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I32" t="str">
-        <v>237.0</v>
+        <v>263.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H33">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="I33" t="str">
-        <v>451.0</v>
+        <v>484.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H34">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="I34" t="str">
-        <v>945.0</v>
+        <v>907.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H35">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="I35" t="str">
-        <v>1383.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H36">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="I36" t="str">
-        <v>2284.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H37">
         <v>124</v>
       </c>
       <c r="I37" t="str">
-        <v>457.0</v>
+        <v>465.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H38">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I38" t="str">
-        <v>1140.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H39">
         <v>152</v>
       </c>
       <c r="I39" t="str">
-        <v>705.0</v>
+        <v>685.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H40">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="I40" t="str">
-        <v>926.0</v>
+        <v>928.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H41">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="I41" t="str">
-        <v>493.0</v>
+        <v>484.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H42">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I42" t="str">
-        <v>230.0</v>
+        <v>259.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H43">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="I43" t="str">
-        <v>484.0</v>
+        <v>464.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H44">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="I44" t="str">
-        <v>945.0</v>
+        <v>948.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H45">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I45" t="str">
-        <v>1396.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H46">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="I46" t="str">
-        <v>2265.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H47">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="I47" t="str">
-        <v>462.0</v>
+        <v>476.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H48">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="I48" t="str">
-        <v>1127.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H49">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="I49" t="str">
-        <v>690.0</v>
+        <v>702.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H50">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="I50" t="str">
-        <v>909.0</v>
+        <v>907.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H51">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I51" t="str">
-        <v>463.0</v>
+        <v>465.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H52">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="I52" t="str">
-        <v>273.0</v>
+        <v>227.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="H53">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="I53" t="str">
-        <v>450.0</v>
+        <v>457.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2436,10 +2436,10 @@
         <v>154</v>
       </c>
       <c r="H54">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="I54" t="str">
-        <v>941.0</v>
+        <v>900.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="H55">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="I55" t="str">
-        <v>1397.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="H56">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="I56" t="str">
-        <v>2254.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H57">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I57" t="str">
-        <v>469.0</v>
+        <v>478.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H58">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="I58" t="str">
-        <v>1170.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="H59">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="I59" t="str">
-        <v>695.0</v>
+        <v>716.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H60">
         <v>139</v>
       </c>
       <c r="I60" t="str">
-        <v>936.0</v>
+        <v>935.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H61">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="I61" t="str">
-        <v>491.0</v>
+        <v>464.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="H62">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I62" t="str">
-        <v>239.0</v>
+        <v>256.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H63">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I63" t="str">
-        <v>499.0</v>
+        <v>480.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H64">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I64" t="str">
-        <v>940.0</v>
+        <v>921.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H65">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="I65" t="str">
-        <v>1355.0</v>
+        <v>1353.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="H66">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="I66" t="str">
-        <v>2260.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="H67">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="I67" t="str">
-        <v>476.0</v>
+        <v>451.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="H68">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="I68" t="str">
-        <v>1168.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H69">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I69" t="str">
-        <v>708.0</v>
+        <v>715.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="H70">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I70" t="str">
-        <v>928.0</v>
+        <v>941.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H71">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I71" t="str">
-        <v>462.0</v>
+        <v>454.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H72">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I72" t="str">
-        <v>237.0</v>
+        <v>259.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H73">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I73" t="str">
-        <v>471.0</v>
+        <v>498.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H74">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="I74" t="str">
-        <v>933.0</v>
+        <v>923.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H75">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="I75" t="str">
-        <v>1378.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H76">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I76" t="str">
-        <v>2259.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H77">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="I77" t="str">
-        <v>454.0</v>
+        <v>472.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H78">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="I78" t="str">
-        <v>1130.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H79">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="I79" t="str">
-        <v>698.0</v>
+        <v>723.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H80">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="I80" t="str">
-        <v>932.0</v>
+        <v>908.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="H81">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="I81" t="str">
-        <v>455.0</v>
+        <v>472.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H82">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="I82" t="str">
-        <v>225.0</v>
+        <v>263.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H83">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I83" t="str">
-        <v>489.0</v>
+        <v>499.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H84">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="I84" t="str">
-        <v>942.0</v>
+        <v>937.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="H85">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="I85" t="str">
-        <v>1382.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H86">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="I86" t="str">
-        <v>2265.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H87">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I87" t="str">
-        <v>487.0</v>
+        <v>497.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H88">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I88" t="str">
-        <v>1143.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H89">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="I89" t="str">
-        <v>681.0</v>
+        <v>717.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H90">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="I90" t="str">
-        <v>912.0</v>
+        <v>904.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="H91">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I91" t="str">
-        <v>468.0</v>
+        <v>493.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3880,10 +3880,10 @@
         <v>92</v>
       </c>
       <c r="H92">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="I92" t="str">
-        <v>270.0</v>
+        <v>240.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H93">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I93" t="str">
-        <v>498.0</v>
+        <v>451.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H94">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="I94" t="str">
-        <v>933.0</v>
+        <v>941.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H95">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I95" t="str">
-        <v>1366.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="H96">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="I96" t="str">
-        <v>2268.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H97">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="I97" t="str">
-        <v>490.0</v>
+        <v>480.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="H98">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="I98" t="str">
-        <v>1170.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H99">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I99" t="str">
-        <v>704.0</v>
+        <v>685.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
+        <v>98</v>
+      </c>
+      <c r="H100">
         <v>105</v>
       </c>
-      <c r="H100">
-        <v>121</v>
-      </c>
       <c r="I100" t="str">
-        <v>935.0</v>
+        <v>909.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H101">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="I101" t="str">
-        <v>491.0</v>
+        <v>497.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H102">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="I102" t="str">
-        <v>233.0</v>
+        <v>250.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,7 +4295,7 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H103">
         <v>142</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="H104">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I104" t="str">
-        <v>903.0</v>
+        <v>944.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H105">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="I105" t="str">
-        <v>1374.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H106">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I106" t="str">
-        <v>2296.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H107">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="I107" t="str">
-        <v>469.0</v>
+        <v>476.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="H108">
-        <v>212</v>
+        <v>170</v>
       </c>
       <c r="I108" t="str">
-        <v>1171.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H109">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I109" t="str">
-        <v>697.0</v>
+        <v>678.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="H110">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="I110" t="str">
-        <v>942.0</v>
+        <v>925.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H111">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I111" t="str">
-        <v>467.0</v>
+        <v>498.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H112">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="I112" t="str">
-        <v>226.0</v>
+        <v>243.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H113">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I113" t="str">
-        <v>462.0</v>
+        <v>474.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H114">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I114" t="str">
-        <v>947.0</v>
+        <v>948.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H115">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I115" t="str">
-        <v>1379.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="H116">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="I116" t="str">
-        <v>2258.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H117">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="I117" t="str">
-        <v>466.0</v>
+        <v>495.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H118">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I118" t="str">
-        <v>1173.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H119">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I119" t="str">
-        <v>678.0</v>
+        <v>681.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H120">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="I120" t="str">
-        <v>932.0</v>
+        <v>911.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="H121">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I121" t="str">
-        <v>491.0</v>
+        <v>458.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="H122">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="I122" t="str">
-        <v>233.0</v>
+        <v>258.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H123">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I123" t="str">
-        <v>460.0</v>
+        <v>488.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="H124">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="I124" t="str">
-        <v>908.0</v>
+        <v>930.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H125">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="I125" t="str">
-        <v>1353.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="H126">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="I126" t="str">
-        <v>2295.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="H127">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="I127" t="str">
-        <v>488.0</v>
+        <v>468.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H128">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="I128" t="str">
-        <v>1171.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H129">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I129" t="str">
-        <v>682.0</v>
+        <v>714.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H130">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I130" t="str">
-        <v>903.0</v>
+        <v>949.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H131">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="I131" t="str">
-        <v>474.0</v>
+        <v>489.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H132">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I132" t="str">
-        <v>273.0</v>
+        <v>238.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H133">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I133" t="str">
-        <v>488.0</v>
+        <v>454.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H134">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="I134" t="str">
-        <v>907.0</v>
+        <v>924.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,10 +5511,10 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H135">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="I135" t="str">
         <v>1373.0</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="H136">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I136" t="str">
-        <v>2254.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H137">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="I137" t="str">
-        <v>492.0</v>
+        <v>475.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="H138">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I138" t="str">
-        <v>1157.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H139">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="I139" t="str">
-        <v>717.0</v>
+        <v>723.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H140">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I140" t="str">
-        <v>935.0</v>
+        <v>942.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H141">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="I141" t="str">
-        <v>455.0</v>
+        <v>463.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H142">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I142" t="str">
-        <v>242.0</v>
+        <v>269.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5818,10 +5818,10 @@
         <v>132</v>
       </c>
       <c r="H143">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="I143" t="str">
-        <v>482.0</v>
+        <v>473.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H144">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="I144" t="str">
-        <v>919.0</v>
+        <v>920.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H145">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I145" t="str">
-        <v>1364.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="H146">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="I146" t="str">
-        <v>2294.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H147">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I147" t="str">
-        <v>499.0</v>
+        <v>457.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H148">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="I148" t="str">
-        <v>1153.0</v>
+        <v>1128.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H149">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="I149" t="str">
-        <v>710.0</v>
+        <v>682.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H150">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I150" t="str">
-        <v>937.0</v>
+        <v>944.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H151">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="I151" t="str">
-        <v>481.0</v>
+        <v>460.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H152">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="I152" t="str">
-        <v>273.0</v>
+        <v>243.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H153">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="I153" t="str">
-        <v>489.0</v>
+        <v>463.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="H154">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="I154" t="str">
-        <v>912.0</v>
+        <v>933.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="H155">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="I155" t="str">
-        <v>1380.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H156">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="I156" t="str">
-        <v>2261.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H157">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="I157" t="str">
-        <v>454.0</v>
+        <v>486.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H158">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I158" t="str">
-        <v>1174.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H159">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="I159" t="str">
-        <v>693.0</v>
+        <v>715.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H160">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I160" t="str">
-        <v>946.0</v>
+        <v>919.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,10 +6499,10 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="H161">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I161" t="str">
         <v>468.0</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H162">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I162" t="str">
-        <v>242.0</v>
+        <v>235.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H163">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="I163" t="str">
-        <v>454.0</v>
+        <v>475.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H164">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="I164" t="str">
-        <v>933.0</v>
+        <v>934.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H165">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="I165" t="str">
-        <v>1361.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H166">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I166" t="str">
-        <v>2283.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H167">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I167" t="str">
-        <v>480.0</v>
+        <v>499.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="H168">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="I168" t="str">
-        <v>1125.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H169">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="I169" t="str">
-        <v>707.0</v>
+        <v>696.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6844,10 +6844,10 @@
         <v>106</v>
       </c>
       <c r="H170">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="I170" t="str">
-        <v>943.0</v>
+        <v>928.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="H171">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I171" t="str">
-        <v>483.0</v>
+        <v>466.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H172">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="I172" t="str">
-        <v>233.0</v>
+        <v>267.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H173">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I173" t="str">
-        <v>469.0</v>
+        <v>491.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="H174">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="I174" t="str">
-        <v>934.0</v>
+        <v>927.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="H175">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="I175" t="str">
-        <v>1379.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="H176">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="I176" t="str">
-        <v>2285.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H177">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="I177" t="str">
-        <v>458.0</v>
+        <v>496.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H178">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="I178" t="str">
-        <v>1138.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H179">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I179" t="str">
-        <v>721.0</v>
+        <v>699.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H180">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I180" t="str">
-        <v>905.0</v>
+        <v>927.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H181">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="I181" t="str">
-        <v>472.0</v>
+        <v>455.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H182">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="I182" t="str">
-        <v>258.0</v>
+        <v>274.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H183">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I183" t="str">
-        <v>450.0</v>
+        <v>480.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="H184">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="I184" t="str">
-        <v>929.0</v>
+        <v>916.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H185">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I185" t="str">
-        <v>1357.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="H186">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I186" t="str">
-        <v>2289.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H187">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I187" t="str">
-        <v>471.0</v>
+        <v>463.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7528,7 +7528,7 @@
         <v>171</v>
       </c>
       <c r="H188">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="I188" t="str">
         <v>1160.0</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="H189">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="I189" t="str">
-        <v>686.0</v>
+        <v>705.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H190">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="I190" t="str">
-        <v>929.0</v>
+        <v>914.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="H191">
         <v>162</v>
       </c>
       <c r="I191" t="str">
-        <v>482.0</v>
+        <v>475.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H192">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I192" t="str">
-        <v>227.0</v>
+        <v>267.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H193">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="I193" t="str">
-        <v>475.0</v>
+        <v>464.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H194">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I194" t="str">
-        <v>943.0</v>
+        <v>930.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H195">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="I195" t="str">
-        <v>1350.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="H196">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="I196" t="str">
-        <v>2287.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,10 +7867,10 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H197">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="I197" t="str">
         <v>498.0</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H198">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I198" t="str">
-        <v>1157.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H199">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="I199" t="str">
-        <v>680.0</v>
+        <v>681.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H200">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I200" t="str">
-        <v>933.0</v>
+        <v>947.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H201">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="I201" t="str">
-        <v>452.0</v>
+        <v>487.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H202">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I202" t="str">
-        <v>256.0</v>
+        <v>260.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H203">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I203" t="str">
-        <v>464.0</v>
+        <v>470.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H204">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="I204" t="str">
-        <v>936.0</v>
+        <v>909.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="H205">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I205" t="str">
-        <v>1390.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H206">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="I206" t="str">
-        <v>2270.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H207">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I207" t="str">
-        <v>457.0</v>
+        <v>491.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H208">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="I208" t="str">
-        <v>1133.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H209">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I209" t="str">
-        <v>676.0</v>
+        <v>719.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="H210">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I210" t="str">
-        <v>936.0</v>
+        <v>905.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H211">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I211" t="str">
-        <v>474.0</v>
+        <v>498.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,10 +8437,10 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H212">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I212" t="str">
         <v>248.0</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H213">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I213" t="str">
-        <v>499.0</v>
+        <v>470.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H214">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I214" t="str">
-        <v>901.0</v>
+        <v>933.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="H215">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="I215" t="str">
-        <v>1361.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="H216">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="I216" t="str">
-        <v>2252.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H217">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="I217" t="str">
-        <v>463.0</v>
+        <v>462.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8668,10 +8668,10 @@
         <v>176</v>
       </c>
       <c r="H218">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="I218" t="str">
-        <v>1125.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="H219">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I219" t="str">
-        <v>690.0</v>
+        <v>687.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H220">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="I220" t="str">
-        <v>928.0</v>
+        <v>906.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H221">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="I221" t="str">
-        <v>495.0</v>
+        <v>481.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H222">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I222" t="str">
-        <v>269.0</v>
+        <v>227.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H223">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I223" t="str">
-        <v>468.0</v>
+        <v>465.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="H224">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="I224" t="str">
-        <v>903.0</v>
+        <v>928.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H225">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I225" t="str">
-        <v>1352.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="H226">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="I226" t="str">
-        <v>2263.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H227">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I227" t="str">
-        <v>459.0</v>
+        <v>472.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H228">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="I228" t="str">
-        <v>1142.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="H229">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="I229" t="str">
-        <v>702.0</v>
+        <v>716.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H230">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="I230" t="str">
-        <v>901.0</v>
+        <v>902.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H231">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="I231" t="str">
-        <v>493.0</v>
+        <v>479.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="H232">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I232" t="str">
-        <v>230.0</v>
+        <v>246.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
+        <v>132</v>
+      </c>
+      <c r="H233">
         <v>133</v>
       </c>
-      <c r="H233">
-        <v>136</v>
-      </c>
       <c r="I233" t="str">
-        <v>487.0</v>
+        <v>461.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="H234">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="I234" t="str">
-        <v>941.0</v>
+        <v>902.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H235">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="I235" t="str">
-        <v>1390.0</v>
+        <v>1355.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H236">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I236" t="str">
-        <v>2295.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H237">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I237" t="str">
-        <v>480.0</v>
+        <v>485.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H238">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="I238" t="str">
-        <v>1158.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H239">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I239" t="str">
-        <v>677.0</v>
+        <v>720.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="H240">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="I240" t="str">
-        <v>915.0</v>
+        <v>932.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H241">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="I241" t="str">
-        <v>475.0</v>
+        <v>474.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H242">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="I242" t="str">
-        <v>242.0</v>
+        <v>263.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H243">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I243" t="str">
-        <v>499.0</v>
+        <v>467.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H244">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="I244" t="str">
-        <v>936.0</v>
+        <v>927.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H245">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I245" t="str">
-        <v>1368.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H246">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="I246" t="str">
-        <v>2290.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
+        <v>117</v>
+      </c>
+      <c r="H247">
         <v>126</v>
       </c>
-      <c r="H247">
-        <v>136</v>
-      </c>
       <c r="I247" t="str">
-        <v>490.0</v>
+        <v>470.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="H248">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I248" t="str">
-        <v>1136.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H249">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I249" t="str">
-        <v>711.0</v>
+        <v>715.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H250">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="I250" t="str">
-        <v>944.0</v>
+        <v>921.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="H251">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="I251" t="str">
-        <v>454.0</v>
+        <v>451.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H252">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I252" t="str">
-        <v>244.0</v>
+        <v>232.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H253">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I253" t="str">
-        <v>467.0</v>
+        <v>497.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H254">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="I254" t="str">
-        <v>932.0</v>
+        <v>919.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H255">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="I255" t="str">
-        <v>1380.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10112,10 +10112,10 @@
         <v>250</v>
       </c>
       <c r="H256">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="I256" t="str">
-        <v>2255.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H257">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I257" t="str">
-        <v>488.0</v>
+        <v>479.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H258">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="I258" t="str">
-        <v>1157.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H259">
         <v>155</v>
       </c>
       <c r="I259" t="str">
-        <v>680.0</v>
+        <v>688.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H260">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I260" t="str">
-        <v>949.0</v>
+        <v>918.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H261">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="I261" t="str">
-        <v>498.0</v>
+        <v>478.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H262">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I262" t="str">
-        <v>273.0</v>
+        <v>232.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="H263">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="I263" t="str">
-        <v>497.0</v>
+        <v>476.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H264">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="I264" t="str">
-        <v>924.0</v>
+        <v>915.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H265">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="I265" t="str">
-        <v>1376.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H266">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I266" t="str">
-        <v>2289.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H267">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="I267" t="str">
-        <v>491.0</v>
+        <v>452.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H268">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="I268" t="str">
-        <v>1142.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="H269">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="I269" t="str">
-        <v>711.0</v>
+        <v>706.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H270">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I270" t="str">
-        <v>915.0</v>
+        <v>901.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H271">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="I271" t="str">
-        <v>464.0</v>
+        <v>453.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H272">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I272" t="str">
-        <v>268.0</v>
+        <v>238.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="H273">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="I273" t="str">
-        <v>464.0</v>
+        <v>482.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
+        <v>147</v>
+      </c>
+      <c r="H274">
         <v>157</v>
       </c>
-      <c r="H274">
-        <v>194</v>
-      </c>
       <c r="I274" t="str">
-        <v>905.0</v>
+        <v>939.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H275">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="I275" t="str">
-        <v>1382.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,10 +10869,10 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H276">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="I276" t="str">
         <v>2292.0</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="H277">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I277" t="str">
-        <v>487.0</v>
+        <v>486.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,10 +10945,10 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H278">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="I278" t="str">
         <v>1161.0</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="H279">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="I279" t="str">
-        <v>692.0</v>
+        <v>711.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="H280">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I280" t="str">
-        <v>910.0</v>
+        <v>942.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="H281">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="I281" t="str">
-        <v>476.0</v>
+        <v>497.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H282">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I282" t="str">
-        <v>237.0</v>
+        <v>228.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="H283">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="I283" t="str">
-        <v>471.0</v>
+        <v>478.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="H284">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="I284" t="str">
-        <v>915.0</v>
+        <v>917.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H285">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I285" t="str">
-        <v>1359.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="H286">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="I286" t="str">
-        <v>2265.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,10 +11287,10 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H287">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="I287" t="str">
         <v>494.0</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H288">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="I288" t="str">
-        <v>1126.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H289">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I289" t="str">
-        <v>724.0</v>
+        <v>697.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H290">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I290" t="str">
-        <v>935.0</v>
+        <v>901.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H291">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I291" t="str">
-        <v>456.0</v>
+        <v>478.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="H292">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I292" t="str">
-        <v>229.0</v>
+        <v>264.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H293">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I293" t="str">
-        <v>499.0</v>
+        <v>466.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H294">
         <v>194</v>
       </c>
       <c r="I294" t="str">
-        <v>949.0</v>
+        <v>913.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H295">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="I295" t="str">
-        <v>1371.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="H296">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="I296" t="str">
-        <v>2279.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H297">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="I297" t="str">
-        <v>472.0</v>
+        <v>468.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H298">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I298" t="str">
-        <v>1141.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H299">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="I299" t="str">
-        <v>692.0</v>
+        <v>722.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H300">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="I300" t="str">
-        <v>936.0</v>
+        <v>931.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H301">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I301" t="str">
-        <v>467.0</v>
+        <v>489.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H2">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I2" t="str">
-        <v>235.0</v>
+        <v>252.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="H3">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="I3" t="str">
-        <v>462.0</v>
+        <v>480.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H4">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I4" t="str">
-        <v>909.0</v>
+        <v>929.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="H5">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="I5" t="str">
-        <v>1388.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H6">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="I6" t="str">
-        <v>2251.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H7">
         <v>144</v>
       </c>
       <c r="I7" t="str">
-        <v>492.0</v>
+        <v>482.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H8">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I8" t="str">
-        <v>1145.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H9">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I9" t="str">
-        <v>688.0</v>
+        <v>700.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="H10">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="I10" t="str">
-        <v>926.0</v>
+        <v>912.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H11">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="I11" t="str">
-        <v>479.0</v>
+        <v>489.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H12">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I12" t="str">
-        <v>243.0</v>
+        <v>262.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H13">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I13" t="str">
-        <v>478.0</v>
+        <v>476.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H14">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I14" t="str">
-        <v>904.0</v>
+        <v>936.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="H15">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I15" t="str">
-        <v>1381.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H16">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="I16" t="str">
-        <v>2285.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H17">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="I17" t="str">
-        <v>468.0</v>
+        <v>450.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H18">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="I18" t="str">
-        <v>1133.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H19">
         <v>176</v>
       </c>
       <c r="I19" t="str">
-        <v>693.0</v>
+        <v>683.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H20">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I20" t="str">
-        <v>920.0</v>
+        <v>915.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="H21">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I21" t="str">
-        <v>466.0</v>
+        <v>455.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="H22">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="I22" t="str">
-        <v>225.0</v>
+        <v>260.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H23">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="I23" t="str">
-        <v>456.0</v>
+        <v>473.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,10 +1293,10 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H24">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="I24" t="str">
         <v>923.0</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H25">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="I25" t="str">
-        <v>1380.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1372,10 +1372,10 @@
         <v>243</v>
       </c>
       <c r="H26">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="I26" t="str">
-        <v>2290.0</v>
+        <v>2297.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H27">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I27" t="str">
-        <v>453.0</v>
+        <v>456.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H28">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="I28" t="str">
-        <v>1140.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H29">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="I29" t="str">
-        <v>689.0</v>
+        <v>680.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H30">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I30" t="str">
-        <v>908.0</v>
+        <v>926.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H31">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="I31" t="str">
-        <v>488.0</v>
+        <v>483.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="H32">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I32" t="str">
-        <v>263.0</v>
+        <v>229.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,10 +1635,10 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H33">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I33" t="str">
         <v>484.0</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H34">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I34" t="str">
-        <v>907.0</v>
+        <v>939.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1714,10 +1714,10 @@
         <v>199</v>
       </c>
       <c r="H35">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="I35" t="str">
-        <v>1358.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="H36">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="I36" t="str">
-        <v>2255.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H37">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="I37" t="str">
-        <v>465.0</v>
+        <v>497.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1828,10 +1828,10 @@
         <v>165</v>
       </c>
       <c r="H38">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I38" t="str">
-        <v>1164.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H39">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="I39" t="str">
-        <v>685.0</v>
+        <v>708.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H40">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="I40" t="str">
-        <v>928.0</v>
+        <v>916.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="H41">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I41" t="str">
-        <v>484.0</v>
+        <v>463.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H42">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I42" t="str">
-        <v>259.0</v>
+        <v>262.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H43">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I43" t="str">
-        <v>464.0</v>
+        <v>466.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H44">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="I44" t="str">
-        <v>948.0</v>
+        <v>946.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H45">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="I45" t="str">
-        <v>1390.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
+        <v>249</v>
+      </c>
+      <c r="H46">
         <v>255</v>
       </c>
-      <c r="H46">
-        <v>258</v>
-      </c>
       <c r="I46" t="str">
-        <v>2292.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="H47">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I47" t="str">
-        <v>476.0</v>
+        <v>474.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H48">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="I48" t="str">
-        <v>1162.0</v>
+        <v>1170.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="H49">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="I49" t="str">
-        <v>702.0</v>
+        <v>707.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H50">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="I50" t="str">
-        <v>907.0</v>
+        <v>936.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H51">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="I51" t="str">
-        <v>465.0</v>
+        <v>491.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H52">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="I52" t="str">
-        <v>227.0</v>
+        <v>274.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="H53">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I53" t="str">
-        <v>457.0</v>
+        <v>494.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H54">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I54" t="str">
-        <v>900.0</v>
+        <v>938.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="H55">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="I55" t="str">
-        <v>1354.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="H56">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="I56" t="str">
-        <v>2295.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H57">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="I57" t="str">
-        <v>478.0</v>
+        <v>465.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="H58">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="I58" t="str">
-        <v>1133.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H59">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="I59" t="str">
-        <v>716.0</v>
+        <v>719.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H60">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I60" t="str">
-        <v>935.0</v>
+        <v>918.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H61">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I61" t="str">
-        <v>464.0</v>
+        <v>496.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H62">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="I62" t="str">
-        <v>256.0</v>
+        <v>241.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="H63">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="I63" t="str">
-        <v>480.0</v>
+        <v>475.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="H64">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I64" t="str">
-        <v>921.0</v>
+        <v>936.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="H65">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="I65" t="str">
-        <v>1353.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H66">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I66" t="str">
-        <v>2261.0</v>
+        <v>2258.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="H67">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="I67" t="str">
-        <v>451.0</v>
+        <v>470.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H68">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="I68" t="str">
-        <v>1165.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3006,10 +3006,10 @@
         <v>150</v>
       </c>
       <c r="H69">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="I69" t="str">
-        <v>715.0</v>
+        <v>722.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="H70">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="I70" t="str">
-        <v>941.0</v>
+        <v>925.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="H71">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I71" t="str">
-        <v>454.0</v>
+        <v>485.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="H72">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I72" t="str">
-        <v>259.0</v>
+        <v>231.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H73">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="I73" t="str">
-        <v>498.0</v>
+        <v>489.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H74">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I74" t="str">
-        <v>923.0</v>
+        <v>901.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H75">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I75" t="str">
-        <v>1356.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H76">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I76" t="str">
-        <v>2298.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H77">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="I77" t="str">
-        <v>472.0</v>
+        <v>482.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H78">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I78" t="str">
-        <v>1159.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H79">
         <v>145</v>
       </c>
       <c r="I79" t="str">
-        <v>723.0</v>
+        <v>685.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H80">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="I80" t="str">
-        <v>908.0</v>
+        <v>911.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H81">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I81" t="str">
-        <v>472.0</v>
+        <v>459.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H82">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I82" t="str">
-        <v>263.0</v>
+        <v>269.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H83">
         <v>137</v>
       </c>
       <c r="I83" t="str">
-        <v>499.0</v>
+        <v>489.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H84">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="I84" t="str">
-        <v>937.0</v>
+        <v>908.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H85">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="I85" t="str">
-        <v>1359.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="H86">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="I86" t="str">
-        <v>2254.0</v>
+        <v>2273.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H87">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I87" t="str">
-        <v>497.0</v>
+        <v>494.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H88">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="I88" t="str">
-        <v>1156.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="H89">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="I89" t="str">
-        <v>717.0</v>
+        <v>696.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3804,10 +3804,10 @@
         <v>100</v>
       </c>
       <c r="H90">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I90" t="str">
-        <v>904.0</v>
+        <v>906.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="H91">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I91" t="str">
-        <v>493.0</v>
+        <v>483.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H92">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="I92" t="str">
-        <v>240.0</v>
+        <v>227.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H93">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I93" t="str">
-        <v>451.0</v>
+        <v>482.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3956,10 +3956,10 @@
         <v>162</v>
       </c>
       <c r="H94">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="I94" t="str">
-        <v>941.0</v>
+        <v>905.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H95">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="I95" t="str">
-        <v>1395.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="H96">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="I96" t="str">
-        <v>2297.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H97">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="I97" t="str">
-        <v>480.0</v>
+        <v>473.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="H98">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="I98" t="str">
-        <v>1132.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="H99">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="I99" t="str">
-        <v>685.0</v>
+        <v>684.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H100">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I100" t="str">
-        <v>909.0</v>
+        <v>926.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="H101">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="I101" t="str">
-        <v>497.0</v>
+        <v>486.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H102">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I102" t="str">
-        <v>250.0</v>
+        <v>229.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H103">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I103" t="str">
-        <v>481.0</v>
+        <v>451.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="H104">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I104" t="str">
-        <v>944.0</v>
+        <v>917.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H105">
         <v>214</v>
       </c>
       <c r="I105" t="str">
-        <v>1399.0</v>
+        <v>1375.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H106">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I106" t="str">
-        <v>2260.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H107">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="I107" t="str">
-        <v>476.0</v>
+        <v>456.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="H108">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="I108" t="str">
-        <v>1142.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H109">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I109" t="str">
-        <v>678.0</v>
+        <v>724.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H110">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="I110" t="str">
-        <v>925.0</v>
+        <v>941.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="H111">
         <v>152</v>
       </c>
       <c r="I111" t="str">
-        <v>498.0</v>
+        <v>471.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H112">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I112" t="str">
-        <v>243.0</v>
+        <v>260.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H113">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="I113" t="str">
-        <v>474.0</v>
+        <v>478.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H114">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="I114" t="str">
-        <v>948.0</v>
+        <v>905.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H115">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="I115" t="str">
-        <v>1384.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H116">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="I116" t="str">
-        <v>2293.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H117">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="I117" t="str">
-        <v>495.0</v>
+        <v>492.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H118">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="I118" t="str">
-        <v>1164.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="H119">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="I119" t="str">
-        <v>681.0</v>
+        <v>701.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H120">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="I120" t="str">
-        <v>911.0</v>
+        <v>949.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="H121">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="I121" t="str">
-        <v>458.0</v>
+        <v>468.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H122">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I122" t="str">
-        <v>258.0</v>
+        <v>235.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,10 +5055,10 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="H123">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I123" t="str">
         <v>488.0</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H124">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I124" t="str">
-        <v>930.0</v>
+        <v>947.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H125">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I125" t="str">
-        <v>1376.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H126">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="I126" t="str">
-        <v>2287.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="H127">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="I127" t="str">
-        <v>468.0</v>
+        <v>483.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H128">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="I128" t="str">
-        <v>1162.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H129">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="I129" t="str">
-        <v>714.0</v>
+        <v>707.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H130">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I130" t="str">
-        <v>949.0</v>
+        <v>917.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H131">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I131" t="str">
-        <v>489.0</v>
+        <v>486.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H132">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I132" t="str">
-        <v>238.0</v>
+        <v>259.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H133">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I133" t="str">
-        <v>454.0</v>
+        <v>453.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5476,10 +5476,10 @@
         <v>148</v>
       </c>
       <c r="H134">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I134" t="str">
-        <v>924.0</v>
+        <v>948.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="H135">
         <v>209</v>
       </c>
       <c r="I135" t="str">
-        <v>1373.0</v>
+        <v>1389.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="H136">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="I136" t="str">
-        <v>2282.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H137">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I137" t="str">
-        <v>475.0</v>
+        <v>482.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H138">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="I138" t="str">
-        <v>1163.0</v>
+        <v>1167.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H139">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I139" t="str">
-        <v>723.0</v>
+        <v>714.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H140">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I140" t="str">
-        <v>942.0</v>
+        <v>947.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H141">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="I141" t="str">
-        <v>463.0</v>
+        <v>461.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H142">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I142" t="str">
-        <v>269.0</v>
+        <v>230.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H143">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="I143" t="str">
-        <v>473.0</v>
+        <v>451.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H144">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I144" t="str">
-        <v>920.0</v>
+        <v>933.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H145">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="I145" t="str">
-        <v>1356.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H146">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="I146" t="str">
-        <v>2257.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H147">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I147" t="str">
-        <v>457.0</v>
+        <v>467.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="H148">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="I148" t="str">
-        <v>1128.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H149">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I149" t="str">
-        <v>682.0</v>
+        <v>690.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H150">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="I150" t="str">
-        <v>944.0</v>
+        <v>900.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H151">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I151" t="str">
-        <v>460.0</v>
+        <v>475.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H152">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I152" t="str">
-        <v>243.0</v>
+        <v>257.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="H153">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="I153" t="str">
-        <v>463.0</v>
+        <v>499.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H154">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I154" t="str">
-        <v>933.0</v>
+        <v>900.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H155">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I155" t="str">
-        <v>1354.0</v>
+        <v>1393.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="H156">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="I156" t="str">
-        <v>2280.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H157">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I157" t="str">
-        <v>486.0</v>
+        <v>482.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H158">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="I158" t="str">
-        <v>1171.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H159">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="I159" t="str">
-        <v>715.0</v>
+        <v>683.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H160">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I160" t="str">
-        <v>919.0</v>
+        <v>939.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H161">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I161" t="str">
-        <v>468.0</v>
+        <v>461.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H162">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="I162" t="str">
-        <v>235.0</v>
+        <v>250.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H163">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="I163" t="str">
-        <v>475.0</v>
+        <v>461.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="H164">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="I164" t="str">
-        <v>934.0</v>
+        <v>948.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H165">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="I165" t="str">
-        <v>1385.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H166">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I166" t="str">
-        <v>2268.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="H167">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="I167" t="str">
-        <v>499.0</v>
+        <v>471.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H168">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="I168" t="str">
-        <v>1151.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H169">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="I169" t="str">
-        <v>696.0</v>
+        <v>688.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H170">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I170" t="str">
-        <v>928.0</v>
+        <v>944.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H171">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="I171" t="str">
-        <v>466.0</v>
+        <v>453.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H172">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="I172" t="str">
-        <v>267.0</v>
+        <v>274.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H173">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="I173" t="str">
-        <v>491.0</v>
+        <v>476.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H174">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I174" t="str">
-        <v>927.0</v>
+        <v>931.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H175">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="I175" t="str">
-        <v>1390.0</v>
+        <v>1358.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="H176">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="I176" t="str">
-        <v>2274.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H177">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I177" t="str">
-        <v>496.0</v>
+        <v>487.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H178">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I178" t="str">
-        <v>1174.0</v>
+        <v>1141.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H179">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="I179" t="str">
-        <v>699.0</v>
+        <v>703.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H180">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I180" t="str">
-        <v>927.0</v>
+        <v>932.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="H181">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="I181" t="str">
-        <v>455.0</v>
+        <v>486.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H182">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="I182" t="str">
-        <v>274.0</v>
+        <v>237.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H183">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="I183" t="str">
-        <v>480.0</v>
+        <v>470.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H184">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="I184" t="str">
-        <v>916.0</v>
+        <v>947.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H185">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="I185" t="str">
-        <v>1364.0</v>
+        <v>1357.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H186">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="I186" t="str">
-        <v>2258.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H187">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="I187" t="str">
-        <v>463.0</v>
+        <v>453.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H188">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="I188" t="str">
-        <v>1160.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="H189">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="I189" t="str">
-        <v>705.0</v>
+        <v>694.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="H190">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="I190" t="str">
-        <v>914.0</v>
+        <v>910.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="H191">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I191" t="str">
-        <v>475.0</v>
+        <v>482.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H192">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I192" t="str">
-        <v>267.0</v>
+        <v>265.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H193">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I193" t="str">
-        <v>464.0</v>
+        <v>459.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H194">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="I194" t="str">
-        <v>930.0</v>
+        <v>929.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="H195">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="I195" t="str">
-        <v>1367.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H196">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I196" t="str">
-        <v>2264.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H197">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I197" t="str">
-        <v>498.0</v>
+        <v>457.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H198">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I198" t="str">
-        <v>1154.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H199">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="I199" t="str">
-        <v>681.0</v>
+        <v>691.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H200">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="I200" t="str">
-        <v>947.0</v>
+        <v>915.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H201">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="I201" t="str">
-        <v>487.0</v>
+        <v>478.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H202">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="I202" t="str">
-        <v>260.0</v>
+        <v>246.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H203">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="I203" t="str">
-        <v>470.0</v>
+        <v>499.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H204">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="I204" t="str">
-        <v>909.0</v>
+        <v>943.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H205">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="I205" t="str">
-        <v>1388.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="H206">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I206" t="str">
-        <v>2250.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H207">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="I207" t="str">
-        <v>491.0</v>
+        <v>496.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="H208">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I208" t="str">
-        <v>1168.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H209">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="I209" t="str">
-        <v>719.0</v>
+        <v>723.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H210">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I210" t="str">
-        <v>905.0</v>
+        <v>947.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H211">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="I211" t="str">
-        <v>498.0</v>
+        <v>457.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H212">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="I212" t="str">
-        <v>248.0</v>
+        <v>267.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="H213">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="I213" t="str">
-        <v>470.0</v>
+        <v>463.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H214">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="I214" t="str">
-        <v>933.0</v>
+        <v>901.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H215">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="I215" t="str">
-        <v>1356.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="H216">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="I216" t="str">
-        <v>2265.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H217">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="I217" t="str">
-        <v>462.0</v>
+        <v>468.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H218">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I218" t="str">
-        <v>1149.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="H219">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="I219" t="str">
-        <v>687.0</v>
+        <v>707.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="H220">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="I220" t="str">
-        <v>906.0</v>
+        <v>910.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H221">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="I221" t="str">
-        <v>481.0</v>
+        <v>456.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H222">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="I222" t="str">
-        <v>227.0</v>
+        <v>254.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H223">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="I223" t="str">
-        <v>465.0</v>
+        <v>476.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H224">
         <v>166</v>
       </c>
       <c r="I224" t="str">
-        <v>928.0</v>
+        <v>906.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H225">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="I225" t="str">
-        <v>1390.0</v>
+        <v>1392.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H226">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I226" t="str">
-        <v>2256.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H227">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="I227" t="str">
-        <v>472.0</v>
+        <v>493.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H228">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="I228" t="str">
-        <v>1167.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="H229">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="I229" t="str">
-        <v>716.0</v>
+        <v>689.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="H230">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I230" t="str">
-        <v>902.0</v>
+        <v>905.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H231">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I231" t="str">
-        <v>479.0</v>
+        <v>464.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H232">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="I232" t="str">
-        <v>246.0</v>
+        <v>225.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H233">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="I233" t="str">
-        <v>461.0</v>
+        <v>458.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="H234">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I234" t="str">
-        <v>902.0</v>
+        <v>919.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H235">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="I235" t="str">
-        <v>1355.0</v>
+        <v>1384.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H236">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="I236" t="str">
-        <v>2299.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H237">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I237" t="str">
-        <v>485.0</v>
+        <v>488.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="H238">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I238" t="str">
-        <v>1167.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="H239">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I239" t="str">
-        <v>720.0</v>
+        <v>695.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="H240">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="I240" t="str">
-        <v>932.0</v>
+        <v>914.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H241">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I241" t="str">
-        <v>474.0</v>
+        <v>493.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H242">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="I242" t="str">
-        <v>263.0</v>
+        <v>255.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H243">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="I243" t="str">
-        <v>467.0</v>
+        <v>462.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H244">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="I244" t="str">
-        <v>927.0</v>
+        <v>914.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="H245">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="I245" t="str">
-        <v>1351.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="H246">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="I246" t="str">
-        <v>2251.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H247">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I247" t="str">
-        <v>470.0</v>
+        <v>485.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="H248">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="I248" t="str">
-        <v>1173.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H249">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="I249" t="str">
-        <v>715.0</v>
+        <v>724.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="H250">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I250" t="str">
-        <v>921.0</v>
+        <v>900.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="H251">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="I251" t="str">
-        <v>451.0</v>
+        <v>491.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="H252">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I252" t="str">
-        <v>232.0</v>
+        <v>228.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H253">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I253" t="str">
-        <v>497.0</v>
+        <v>459.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="H254">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I254" t="str">
-        <v>919.0</v>
+        <v>932.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H255">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="I255" t="str">
-        <v>1362.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="H256">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="I256" t="str">
-        <v>2297.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H257">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I257" t="str">
-        <v>479.0</v>
+        <v>453.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H258">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="I258" t="str">
-        <v>1161.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H259">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I259" t="str">
-        <v>688.0</v>
+        <v>724.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="H260">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="I260" t="str">
-        <v>918.0</v>
+        <v>936.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H261">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="I261" t="str">
-        <v>478.0</v>
+        <v>468.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H262">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I262" t="str">
-        <v>232.0</v>
+        <v>257.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="H263">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I263" t="str">
-        <v>476.0</v>
+        <v>465.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H264">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="I264" t="str">
-        <v>915.0</v>
+        <v>916.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H265">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="I265" t="str">
-        <v>1384.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H266">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I266" t="str">
-        <v>2292.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H267">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I267" t="str">
-        <v>452.0</v>
+        <v>456.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H268">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="I268" t="str">
-        <v>1157.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H269">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="I269" t="str">
-        <v>706.0</v>
+        <v>690.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H270">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="I270" t="str">
-        <v>901.0</v>
+        <v>916.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H271">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="I271" t="str">
-        <v>453.0</v>
+        <v>455.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H272">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I272" t="str">
-        <v>238.0</v>
+        <v>274.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,10 +10755,10 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H273">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="I273" t="str">
         <v>482.0</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H274">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I274" t="str">
-        <v>939.0</v>
+        <v>913.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H275">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="I275" t="str">
-        <v>1388.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H276">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I276" t="str">
-        <v>2292.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H277">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="I277" t="str">
-        <v>486.0</v>
+        <v>450.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H278">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="I278" t="str">
-        <v>1161.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H279">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I279" t="str">
-        <v>711.0</v>
+        <v>714.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="H280">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I280" t="str">
-        <v>942.0</v>
+        <v>947.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H281">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I281" t="str">
-        <v>497.0</v>
+        <v>495.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H282">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I282" t="str">
-        <v>228.0</v>
+        <v>236.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="H283">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="I283" t="str">
-        <v>478.0</v>
+        <v>467.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="H284">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="I284" t="str">
-        <v>917.0</v>
+        <v>912.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H285">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="I285" t="str">
-        <v>1381.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="H286">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I286" t="str">
-        <v>2272.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H287">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="I287" t="str">
-        <v>494.0</v>
+        <v>460.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H288">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="I288" t="str">
-        <v>1155.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H289">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="I289" t="str">
-        <v>697.0</v>
+        <v>704.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H290">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="I290" t="str">
-        <v>901.0</v>
+        <v>927.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H291">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="I291" t="str">
-        <v>478.0</v>
+        <v>453.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H292">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="I292" t="str">
-        <v>264.0</v>
+        <v>229.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H293">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="I293" t="str">
-        <v>466.0</v>
+        <v>469.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H294">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="I294" t="str">
-        <v>913.0</v>
+        <v>921.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="H295">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="I295" t="str">
-        <v>1390.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="H296">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="I296" t="str">
-        <v>2298.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H297">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="I297" t="str">
-        <v>468.0</v>
+        <v>474.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H298">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I298" t="str">
-        <v>1133.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H299">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="I299" t="str">
-        <v>722.0</v>
+        <v>711.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H300">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I300" t="str">
-        <v>931.0</v>
+        <v>930.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H301">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I301" t="str">
-        <v>489.0</v>
+        <v>486.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H2">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I2" t="str">
-        <v>252.0</v>
+        <v>273.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H3">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="I3" t="str">
-        <v>480.0</v>
+        <v>491.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="H4">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I4" t="str">
-        <v>929.0</v>
+        <v>926.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="H5">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="I5" t="str">
-        <v>1369.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H6">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="I6" t="str">
-        <v>2286.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H7">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I7" t="str">
-        <v>482.0</v>
+        <v>458.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H8">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I8" t="str">
-        <v>1169.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H9">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I9" t="str">
-        <v>700.0</v>
+        <v>698.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H10">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I10" t="str">
-        <v>912.0</v>
+        <v>935.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H11">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="I11" t="str">
-        <v>489.0</v>
+        <v>473.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="I12" t="str">
-        <v>262.0</v>
+        <v>233.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="H13">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I13" t="str">
-        <v>476.0</v>
+        <v>467.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H14">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="I14" t="str">
-        <v>936.0</v>
+        <v>900.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="H15">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="I15" t="str">
-        <v>1375.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H16">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="I16" t="str">
-        <v>2286.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H17">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I17" t="str">
-        <v>450.0</v>
+        <v>499.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H18">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I18" t="str">
-        <v>1144.0</v>
+        <v>1157.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H19">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="I19" t="str">
-        <v>683.0</v>
+        <v>681.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H20">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="I20" t="str">
-        <v>915.0</v>
+        <v>937.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H21">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="I21" t="str">
-        <v>455.0</v>
+        <v>479.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="I22" t="str">
-        <v>260.0</v>
+        <v>259.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H23">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="I23" t="str">
-        <v>473.0</v>
+        <v>456.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H24">
         <v>175</v>
       </c>
       <c r="I24" t="str">
-        <v>923.0</v>
+        <v>926.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H25">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="I25" t="str">
-        <v>1354.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H26">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I26" t="str">
-        <v>2297.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H27">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I27" t="str">
-        <v>456.0</v>
+        <v>474.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H28">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I28" t="str">
-        <v>1162.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H29">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="I29" t="str">
-        <v>680.0</v>
+        <v>686.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H30">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="I30" t="str">
-        <v>926.0</v>
+        <v>908.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H31">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="I31" t="str">
-        <v>483.0</v>
+        <v>499.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H32">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I32" t="str">
-        <v>229.0</v>
+        <v>234.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H33">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I33" t="str">
-        <v>484.0</v>
+        <v>469.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="H34">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="I34" t="str">
-        <v>939.0</v>
+        <v>911.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H35">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I35" t="str">
-        <v>1395.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="H36">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="I36" t="str">
-        <v>2291.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H37">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I37" t="str">
-        <v>497.0</v>
+        <v>490.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H38">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I38" t="str">
-        <v>1166.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H39">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I39" t="str">
-        <v>708.0</v>
+        <v>724.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H40">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I40" t="str">
-        <v>916.0</v>
+        <v>905.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H41">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I41" t="str">
-        <v>463.0</v>
+        <v>466.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H42">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="I42" t="str">
-        <v>262.0</v>
+        <v>254.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H43">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="I43" t="str">
-        <v>466.0</v>
+        <v>477.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H44">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="I44" t="str">
-        <v>946.0</v>
+        <v>936.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="H45">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="I45" t="str">
-        <v>1394.0</v>
+        <v>1398.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H46">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I46" t="str">
-        <v>2253.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H47">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I47" t="str">
-        <v>474.0</v>
+        <v>465.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H48">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I48" t="str">
-        <v>1170.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
+        <v>140</v>
+      </c>
+      <c r="H49">
         <v>154</v>
       </c>
-      <c r="H49">
-        <v>163</v>
-      </c>
       <c r="I49" t="str">
-        <v>707.0</v>
+        <v>717.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H50">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="I50" t="str">
-        <v>936.0</v>
+        <v>908.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H51">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I51" t="str">
-        <v>491.0</v>
+        <v>481.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="H52">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="I52" t="str">
-        <v>274.0</v>
+        <v>262.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H53">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="I53" t="str">
-        <v>494.0</v>
+        <v>467.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H54">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="I54" t="str">
-        <v>938.0</v>
+        <v>939.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
+        <v>202</v>
+      </c>
+      <c r="H55">
         <v>213</v>
       </c>
-      <c r="H55">
-        <v>252</v>
-      </c>
       <c r="I55" t="str">
-        <v>1376.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H56">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="I56" t="str">
-        <v>2261.0</v>
+        <v>2289.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H57">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I57" t="str">
-        <v>465.0</v>
+        <v>484.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H58">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="I58" t="str">
-        <v>1156.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H59">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="I59" t="str">
-        <v>719.0</v>
+        <v>678.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H60">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I60" t="str">
-        <v>918.0</v>
+        <v>909.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="H61">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="I61" t="str">
-        <v>496.0</v>
+        <v>490.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H62">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I62" t="str">
-        <v>241.0</v>
+        <v>264.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H63">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="I63" t="str">
-        <v>475.0</v>
+        <v>462.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H64">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I64" t="str">
-        <v>936.0</v>
+        <v>928.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H65">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="I65" t="str">
-        <v>1387.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H66">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="I66" t="str">
-        <v>2258.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H67">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="I67" t="str">
-        <v>470.0</v>
+        <v>481.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H68">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="I68" t="str">
-        <v>1163.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H69">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="I69" t="str">
-        <v>722.0</v>
+        <v>709.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H70">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="I70" t="str">
-        <v>925.0</v>
+        <v>902.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H71">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I71" t="str">
-        <v>485.0</v>
+        <v>498.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H72">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I72" t="str">
-        <v>231.0</v>
+        <v>274.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H73">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="I73" t="str">
-        <v>489.0</v>
+        <v>458.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="H74">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="I74" t="str">
-        <v>901.0</v>
+        <v>909.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,10 +3231,10 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="H75">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="I75" t="str">
         <v>1391.0</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H76">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="I76" t="str">
-        <v>2250.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H77">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="I77" t="str">
-        <v>482.0</v>
+        <v>486.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H78">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="I78" t="str">
-        <v>1158.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H79">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I79" t="str">
-        <v>685.0</v>
+        <v>704.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H80">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I80" t="str">
-        <v>911.0</v>
+        <v>909.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H81">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="I81" t="str">
-        <v>459.0</v>
+        <v>493.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H82">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="I82" t="str">
-        <v>269.0</v>
+        <v>250.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="H83">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="I83" t="str">
-        <v>489.0</v>
+        <v>467.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
+        <v>150</v>
+      </c>
+      <c r="H84">
         <v>161</v>
       </c>
-      <c r="H84">
-        <v>183</v>
-      </c>
       <c r="I84" t="str">
-        <v>908.0</v>
+        <v>940.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3614,10 +3614,10 @@
         <v>207</v>
       </c>
       <c r="H85">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="I85" t="str">
-        <v>1361.0</v>
+        <v>1377.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H86">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I86" t="str">
-        <v>2273.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H87">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="I87" t="str">
-        <v>494.0</v>
+        <v>458.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="H88">
         <v>186</v>
       </c>
       <c r="I88" t="str">
-        <v>1153.0</v>
+        <v>1171.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H89">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="I89" t="str">
-        <v>696.0</v>
+        <v>715.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="H90">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="I90" t="str">
-        <v>906.0</v>
+        <v>948.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H91">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I91" t="str">
-        <v>483.0</v>
+        <v>463.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H92">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="I92" t="str">
-        <v>227.0</v>
+        <v>266.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H93">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I93" t="str">
-        <v>482.0</v>
+        <v>465.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H94">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I94" t="str">
-        <v>905.0</v>
+        <v>943.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H95">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="I95" t="str">
-        <v>1372.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="H96">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I96" t="str">
-        <v>2287.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H97">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I97" t="str">
-        <v>473.0</v>
+        <v>481.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H98">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="I98" t="str">
-        <v>1147.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H99">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="I99" t="str">
-        <v>684.0</v>
+        <v>698.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4184,10 +4184,10 @@
         <v>104</v>
       </c>
       <c r="H100">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I100" t="str">
-        <v>926.0</v>
+        <v>939.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H101">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="I101" t="str">
-        <v>486.0</v>
+        <v>473.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H102">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="I102" t="str">
-        <v>229.0</v>
+        <v>237.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="H103">
         <v>148</v>
       </c>
       <c r="I103" t="str">
-        <v>451.0</v>
+        <v>496.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="H104">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="I104" t="str">
-        <v>917.0</v>
+        <v>924.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H105">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="I105" t="str">
-        <v>1375.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H106">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="I106" t="str">
-        <v>2281.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4450,10 +4450,10 @@
         <v>119</v>
       </c>
       <c r="H107">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="I107" t="str">
-        <v>456.0</v>
+        <v>484.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H108">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I108" t="str">
-        <v>1144.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H109">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I109" t="str">
-        <v>724.0</v>
+        <v>703.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H110">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I110" t="str">
-        <v>941.0</v>
+        <v>939.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,10 +4599,10 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H111">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I111" t="str">
         <v>471.0</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H112">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I112" t="str">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,10 +4675,10 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="H113">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="I113" t="str">
         <v>478.0</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H114">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I114" t="str">
-        <v>905.0</v>
+        <v>931.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H115">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="I115" t="str">
-        <v>1369.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="H116">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="I116" t="str">
-        <v>2277.0</v>
+        <v>2279.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H117">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I117" t="str">
-        <v>492.0</v>
+        <v>485.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H118">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="I118" t="str">
-        <v>1125.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,10 +4903,10 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H119">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="I119" t="str">
         <v>701.0</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H120">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="I120" t="str">
-        <v>949.0</v>
+        <v>921.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H121">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="I121" t="str">
-        <v>468.0</v>
+        <v>472.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
+        <v>98</v>
+      </c>
+      <c r="H122">
         <v>101</v>
       </c>
-      <c r="H122">
-        <v>107</v>
-      </c>
       <c r="I122" t="str">
-        <v>235.0</v>
+        <v>246.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H123">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I123" t="str">
-        <v>488.0</v>
+        <v>487.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H124">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I124" t="str">
-        <v>947.0</v>
+        <v>921.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H125">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I125" t="str">
-        <v>1390.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="H126">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="I126" t="str">
-        <v>2299.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="H127">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I127" t="str">
-        <v>483.0</v>
+        <v>486.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H128">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="I128" t="str">
-        <v>1151.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="H129">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I129" t="str">
-        <v>707.0</v>
+        <v>679.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H130">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I130" t="str">
-        <v>917.0</v>
+        <v>937.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H131">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="I131" t="str">
-        <v>486.0</v>
+        <v>494.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H132">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I132" t="str">
-        <v>259.0</v>
+        <v>246.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="H133">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="I133" t="str">
-        <v>453.0</v>
+        <v>467.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="H134">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I134" t="str">
-        <v>948.0</v>
+        <v>922.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,10 +5511,10 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H135">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I135" t="str">
         <v>1389.0</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H136">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I136" t="str">
-        <v>2274.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H137">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I137" t="str">
-        <v>482.0</v>
+        <v>470.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H138">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="I138" t="str">
-        <v>1167.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="H139">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I139" t="str">
-        <v>714.0</v>
+        <v>710.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H140">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="I140" t="str">
-        <v>947.0</v>
+        <v>926.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H141">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="I141" t="str">
-        <v>461.0</v>
+        <v>460.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H142">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="I142" t="str">
-        <v>230.0</v>
+        <v>257.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H143">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I143" t="str">
-        <v>451.0</v>
+        <v>477.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H144">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="I144" t="str">
-        <v>933.0</v>
+        <v>932.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H145">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="I145" t="str">
-        <v>1387.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H146">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="I146" t="str">
-        <v>2289.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H147">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I147" t="str">
-        <v>467.0</v>
+        <v>499.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H148">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I148" t="str">
-        <v>1130.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H149">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I149" t="str">
-        <v>690.0</v>
+        <v>688.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="H150">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="I150" t="str">
-        <v>900.0</v>
+        <v>940.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H151">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="I151" t="str">
-        <v>475.0</v>
+        <v>495.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H152">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="I152" t="str">
-        <v>257.0</v>
+        <v>240.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="H153">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I153" t="str">
-        <v>499.0</v>
+        <v>452.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H154">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I154" t="str">
-        <v>900.0</v>
+        <v>912.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H155">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I155" t="str">
-        <v>1393.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="H156">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="I156" t="str">
-        <v>2275.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H157">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I157" t="str">
-        <v>482.0</v>
+        <v>470.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H158">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="I158" t="str">
-        <v>1140.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H159">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="I159" t="str">
-        <v>683.0</v>
+        <v>721.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H160">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="I160" t="str">
-        <v>939.0</v>
+        <v>923.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H161">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I161" t="str">
-        <v>461.0</v>
+        <v>473.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H162">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="I162" t="str">
-        <v>250.0</v>
+        <v>254.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H163">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="I163" t="str">
-        <v>461.0</v>
+        <v>458.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="H164">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="I164" t="str">
-        <v>948.0</v>
+        <v>913.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H165">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I165" t="str">
-        <v>1365.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H166">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="I166" t="str">
-        <v>2271.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H167">
         <v>108</v>
       </c>
       <c r="I167" t="str">
-        <v>471.0</v>
+        <v>496.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,10 +6765,10 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="H168">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="I168" t="str">
         <v>1155.0</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="H169">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="I169" t="str">
-        <v>688.0</v>
+        <v>690.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H170">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="I170" t="str">
-        <v>944.0</v>
+        <v>928.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="H171">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I171" t="str">
-        <v>453.0</v>
+        <v>496.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H172">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="I172" t="str">
-        <v>274.0</v>
+        <v>270.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H173">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I173" t="str">
-        <v>476.0</v>
+        <v>454.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H174">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="I174" t="str">
-        <v>931.0</v>
+        <v>902.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H175">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I175" t="str">
-        <v>1358.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H176">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="I176" t="str">
-        <v>2270.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H177">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="I177" t="str">
-        <v>487.0</v>
+        <v>499.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H178">
         <v>187</v>
       </c>
       <c r="I178" t="str">
-        <v>1141.0</v>
+        <v>1142.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H179">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I179" t="str">
-        <v>703.0</v>
+        <v>681.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="H180">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="I180" t="str">
-        <v>932.0</v>
+        <v>938.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="H181">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="I181" t="str">
-        <v>486.0</v>
+        <v>477.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H182">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="I182" t="str">
-        <v>237.0</v>
+        <v>228.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7341,7 +7341,7 @@
         <v>136</v>
       </c>
       <c r="I183" t="str">
-        <v>470.0</v>
+        <v>454.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="H184">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I184" t="str">
-        <v>947.0</v>
+        <v>901.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H185">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="I185" t="str">
-        <v>1357.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H186">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I186" t="str">
-        <v>2275.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H187">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="I187" t="str">
-        <v>453.0</v>
+        <v>496.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H188">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="I188" t="str">
-        <v>1164.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H189">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="I189" t="str">
-        <v>694.0</v>
+        <v>677.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H190">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I190" t="str">
-        <v>910.0</v>
+        <v>948.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H191">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I191" t="str">
-        <v>482.0</v>
+        <v>467.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,10 +7677,10 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H192">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="I192" t="str">
         <v>265.0</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H193">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I193" t="str">
-        <v>459.0</v>
+        <v>499.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="H194">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="I194" t="str">
-        <v>929.0</v>
+        <v>942.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H195">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I195" t="str">
-        <v>1352.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H196">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I196" t="str">
-        <v>2296.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="H197">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I197" t="str">
-        <v>457.0</v>
+        <v>471.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="H198">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="I198" t="str">
-        <v>1168.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H199">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="I199" t="str">
-        <v>691.0</v>
+        <v>697.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H200">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I200" t="str">
-        <v>915.0</v>
+        <v>945.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H201">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="I201" t="str">
-        <v>478.0</v>
+        <v>498.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H202">
         <v>100</v>
       </c>
       <c r="I202" t="str">
-        <v>246.0</v>
+        <v>254.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,10 +8095,10 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H203">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I203" t="str">
         <v>499.0</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H204">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="I204" t="str">
-        <v>943.0</v>
+        <v>935.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H205">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I205" t="str">
-        <v>1384.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="H206">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I206" t="str">
-        <v>2282.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H207">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="I207" t="str">
-        <v>496.0</v>
+        <v>495.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H208">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="I208" t="str">
-        <v>1131.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8326,10 +8326,10 @@
         <v>131</v>
       </c>
       <c r="H209">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="I209" t="str">
-        <v>723.0</v>
+        <v>709.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H210">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I210" t="str">
-        <v>947.0</v>
+        <v>906.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="H211">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I211" t="str">
-        <v>457.0</v>
+        <v>458.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8440,10 +8440,10 @@
         <v>92</v>
       </c>
       <c r="H212">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I212" t="str">
-        <v>267.0</v>
+        <v>245.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H213">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I213" t="str">
-        <v>463.0</v>
+        <v>451.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="H214">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I214" t="str">
-        <v>901.0</v>
+        <v>902.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H215">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="I215" t="str">
-        <v>1397.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H216">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="I216" t="str">
-        <v>2257.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H217">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="I217" t="str">
-        <v>468.0</v>
+        <v>494.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H218">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="I218" t="str">
-        <v>1163.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H219">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="I219" t="str">
-        <v>707.0</v>
+        <v>718.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H220">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="I220" t="str">
-        <v>910.0</v>
+        <v>928.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8782,10 +8782,10 @@
         <v>127</v>
       </c>
       <c r="H221">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I221" t="str">
-        <v>456.0</v>
+        <v>490.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H222">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I222" t="str">
-        <v>254.0</v>
+        <v>226.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H223">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="I223" t="str">
-        <v>476.0</v>
+        <v>483.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H224">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="I224" t="str">
-        <v>906.0</v>
+        <v>912.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="H225">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="I225" t="str">
-        <v>1392.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H226">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="I226" t="str">
-        <v>2252.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="H227">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I227" t="str">
-        <v>493.0</v>
+        <v>457.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9048,10 +9048,10 @@
         <v>184</v>
       </c>
       <c r="H228">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="I228" t="str">
-        <v>1131.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H229">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I229" t="str">
-        <v>689.0</v>
+        <v>690.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H230">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I230" t="str">
-        <v>905.0</v>
+        <v>914.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H231">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="I231" t="str">
-        <v>464.0</v>
+        <v>458.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H232">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I232" t="str">
-        <v>225.0</v>
+        <v>235.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H233">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I233" t="str">
-        <v>458.0</v>
+        <v>492.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="H234">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="I234" t="str">
-        <v>919.0</v>
+        <v>937.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H235">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I235" t="str">
-        <v>1384.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="H236">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="I236" t="str">
-        <v>2259.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H237">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="I237" t="str">
-        <v>488.0</v>
+        <v>474.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H238">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I238" t="str">
-        <v>1140.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="H239">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I239" t="str">
-        <v>695.0</v>
+        <v>698.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H240">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="I240" t="str">
-        <v>914.0</v>
+        <v>942.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H241">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I241" t="str">
-        <v>493.0</v>
+        <v>458.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H242">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I242" t="str">
-        <v>255.0</v>
+        <v>258.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H243">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="I243" t="str">
-        <v>462.0</v>
+        <v>477.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H244">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I244" t="str">
-        <v>914.0</v>
+        <v>919.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="H245">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="I245" t="str">
-        <v>1388.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H246">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I246" t="str">
-        <v>2295.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H247">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I247" t="str">
-        <v>485.0</v>
+        <v>478.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H248">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="I248" t="str">
-        <v>1130.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H249">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I249" t="str">
-        <v>724.0</v>
+        <v>679.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="H250">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="I250" t="str">
-        <v>900.0</v>
+        <v>908.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="H251">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="I251" t="str">
-        <v>491.0</v>
+        <v>499.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H252">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I252" t="str">
-        <v>228.0</v>
+        <v>245.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H253">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="I253" t="str">
-        <v>459.0</v>
+        <v>467.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H254">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="I254" t="str">
-        <v>932.0</v>
+        <v>917.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H255">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="I255" t="str">
-        <v>1397.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="H256">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="I256" t="str">
-        <v>2260.0</v>
+        <v>2293.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="H257">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="I257" t="str">
-        <v>453.0</v>
+        <v>479.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H258">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="I258" t="str">
-        <v>1149.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H259">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I259" t="str">
-        <v>724.0</v>
+        <v>706.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H260">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I260" t="str">
-        <v>936.0</v>
+        <v>908.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H261">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I261" t="str">
-        <v>468.0</v>
+        <v>451.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H262">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I262" t="str">
-        <v>257.0</v>
+        <v>268.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H263">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I263" t="str">
-        <v>465.0</v>
+        <v>497.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H264">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="I264" t="str">
-        <v>916.0</v>
+        <v>917.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H265">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="I265" t="str">
-        <v>1350.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H266">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I266" t="str">
-        <v>2288.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H267">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I267" t="str">
-        <v>456.0</v>
+        <v>459.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H268">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="I268" t="str">
-        <v>1165.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H269">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="I269" t="str">
-        <v>690.0</v>
+        <v>700.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10644,10 +10644,10 @@
         <v>98</v>
       </c>
       <c r="H270">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I270" t="str">
-        <v>916.0</v>
+        <v>923.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H271">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="I271" t="str">
-        <v>455.0</v>
+        <v>465.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H272">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="I272" t="str">
-        <v>274.0</v>
+        <v>238.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10758,10 +10758,10 @@
         <v>125</v>
       </c>
       <c r="H273">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="I273" t="str">
-        <v>482.0</v>
+        <v>466.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H274">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="I274" t="str">
-        <v>913.0</v>
+        <v>940.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10834,10 +10834,10 @@
         <v>204</v>
       </c>
       <c r="H275">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I275" t="str">
-        <v>1371.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="H276">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I276" t="str">
-        <v>2299.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H277">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="I277" t="str">
-        <v>450.0</v>
+        <v>471.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H278">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="I278" t="str">
-        <v>1125.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H279">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I279" t="str">
-        <v>714.0</v>
+        <v>688.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H280">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I280" t="str">
-        <v>947.0</v>
+        <v>922.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H281">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="I281" t="str">
-        <v>495.0</v>
+        <v>492.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H282">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I282" t="str">
-        <v>236.0</v>
+        <v>233.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H283">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="I283" t="str">
-        <v>467.0</v>
+        <v>451.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="H284">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="I284" t="str">
-        <v>912.0</v>
+        <v>926.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H285">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I285" t="str">
-        <v>1363.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H286">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I286" t="str">
-        <v>2270.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H287">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I287" t="str">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H288">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="I288" t="str">
-        <v>1157.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H289">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="I289" t="str">
-        <v>704.0</v>
+        <v>713.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H290">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I290" t="str">
-        <v>927.0</v>
+        <v>919.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H291">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I291" t="str">
-        <v>453.0</v>
+        <v>481.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H292">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="I292" t="str">
-        <v>229.0</v>
+        <v>259.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H293">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="I293" t="str">
-        <v>469.0</v>
+        <v>499.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="H294">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I294" t="str">
-        <v>921.0</v>
+        <v>910.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="H295">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="I295" t="str">
-        <v>1367.0</v>
+        <v>1382.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11632,10 +11632,10 @@
         <v>243</v>
       </c>
       <c r="H296">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I296" t="str">
-        <v>2290.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H297">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="I297" t="str">
-        <v>474.0</v>
+        <v>491.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H298">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I298" t="str">
-        <v>1153.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H299">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I299" t="str">
-        <v>711.0</v>
+        <v>694.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H300">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="I300" t="str">
-        <v>930.0</v>
+        <v>928.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H301">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I301" t="str">
-        <v>486.0</v>
+        <v>499.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I2" t="str">
-        <v>273.0</v>
+        <v>270.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -498,10 +498,10 @@
         <v>126</v>
       </c>
       <c r="H3">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="I3" t="str">
-        <v>491.0</v>
+        <v>464.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="H4">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="I4" t="str">
-        <v>926.0</v>
+        <v>907.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H5">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="I5" t="str">
-        <v>1371.0</v>
+        <v>1383.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -612,10 +612,10 @@
         <v>243</v>
       </c>
       <c r="H6">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="I6" t="str">
-        <v>2259.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H7">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="I7" t="str">
-        <v>458.0</v>
+        <v>496.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="H8">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="I8" t="str">
-        <v>1142.0</v>
+        <v>1139.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H9">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I9" t="str">
-        <v>698.0</v>
+        <v>691.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H10">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I10" t="str">
-        <v>935.0</v>
+        <v>912.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H11">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I11" t="str">
-        <v>473.0</v>
+        <v>454.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H12">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I12" t="str">
-        <v>233.0</v>
+        <v>249.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H13">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I13" t="str">
-        <v>467.0</v>
+        <v>453.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H14">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="I14" t="str">
-        <v>900.0</v>
+        <v>915.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H15">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="I15" t="str">
-        <v>1395.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H16">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="I16" t="str">
-        <v>2295.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H17">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="I17" t="str">
-        <v>499.0</v>
+        <v>461.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H18">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I18" t="str">
-        <v>1157.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H19">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I19" t="str">
-        <v>681.0</v>
+        <v>680.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H20">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="I20" t="str">
-        <v>937.0</v>
+        <v>901.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="H21">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="I21" t="str">
-        <v>479.0</v>
+        <v>454.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H22">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I22" t="str">
-        <v>259.0</v>
+        <v>250.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H23">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I23" t="str">
-        <v>456.0</v>
+        <v>496.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H24">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I24" t="str">
-        <v>926.0</v>
+        <v>912.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H25">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="I25" t="str">
-        <v>1368.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H26">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="I26" t="str">
-        <v>2282.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="H27">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I27" t="str">
-        <v>474.0</v>
+        <v>487.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="H28">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="I28" t="str">
-        <v>1130.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H29">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="I29" t="str">
-        <v>686.0</v>
+        <v>705.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H30">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I30" t="str">
-        <v>908.0</v>
+        <v>906.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="H31">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="I31" t="str">
-        <v>499.0</v>
+        <v>494.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="H32">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="I32" t="str">
-        <v>234.0</v>
+        <v>254.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1638,10 +1638,10 @@
         <v>121</v>
       </c>
       <c r="H33">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="I33" t="str">
-        <v>469.0</v>
+        <v>495.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H34">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I34" t="str">
-        <v>911.0</v>
+        <v>943.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H35">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="I35" t="str">
-        <v>1378.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="H36">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="I36" t="str">
-        <v>2270.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H37">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I37" t="str">
-        <v>490.0</v>
+        <v>461.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1828,10 +1828,10 @@
         <v>163</v>
       </c>
       <c r="H38">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="I38" t="str">
-        <v>1164.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="H39">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I39" t="str">
-        <v>724.0</v>
+        <v>720.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,10 +1901,10 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H40">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I40" t="str">
         <v>905.0</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H41">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="I41" t="str">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H42">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I42" t="str">
-        <v>254.0</v>
+        <v>267.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H43">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I43" t="str">
-        <v>477.0</v>
+        <v>450.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="H44">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="I44" t="str">
-        <v>936.0</v>
+        <v>949.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H45">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I45" t="str">
-        <v>1398.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="H46">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="I46" t="str">
-        <v>2254.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H47">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I47" t="str">
-        <v>465.0</v>
+        <v>479.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H48">
         <v>204</v>
       </c>
       <c r="I48" t="str">
-        <v>1143.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H49">
         <v>154</v>
       </c>
       <c r="I49" t="str">
-        <v>717.0</v>
+        <v>703.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H50">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="I50" t="str">
-        <v>908.0</v>
+        <v>928.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H51">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="I51" t="str">
-        <v>481.0</v>
+        <v>483.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="H52">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I52" t="str">
-        <v>262.0</v>
+        <v>233.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="H53">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="I53" t="str">
-        <v>467.0</v>
+        <v>494.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2436,10 +2436,10 @@
         <v>166</v>
       </c>
       <c r="H54">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="I54" t="str">
-        <v>939.0</v>
+        <v>926.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H55">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="I55" t="str">
-        <v>1387.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H56">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="I56" t="str">
-        <v>2289.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H57">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I57" t="str">
-        <v>484.0</v>
+        <v>458.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="H58">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="I58" t="str">
-        <v>1136.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H59">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="I59" t="str">
-        <v>678.0</v>
+        <v>707.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H60">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="I60" t="str">
-        <v>909.0</v>
+        <v>914.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H61">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I61" t="str">
-        <v>490.0</v>
+        <v>497.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H62">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="I62" t="str">
-        <v>264.0</v>
+        <v>259.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2778,10 +2778,10 @@
         <v>125</v>
       </c>
       <c r="H63">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I63" t="str">
-        <v>462.0</v>
+        <v>468.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="H64">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="I64" t="str">
-        <v>928.0</v>
+        <v>921.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H65">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="I65" t="str">
-        <v>1351.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H66">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I66" t="str">
-        <v>2251.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H67">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="I67" t="str">
-        <v>481.0</v>
+        <v>455.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H68">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I68" t="str">
-        <v>1162.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H69">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="I69" t="str">
-        <v>709.0</v>
+        <v>701.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H70">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="I70" t="str">
-        <v>902.0</v>
+        <v>948.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H71">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="I71" t="str">
-        <v>498.0</v>
+        <v>489.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H72">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I72" t="str">
-        <v>274.0</v>
+        <v>245.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H73">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I73" t="str">
-        <v>458.0</v>
+        <v>494.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H74">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="I74" t="str">
-        <v>909.0</v>
+        <v>908.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H75">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="I75" t="str">
-        <v>1391.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="H76">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="I76" t="str">
-        <v>2256.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H77">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="I77" t="str">
-        <v>486.0</v>
+        <v>460.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H78">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="I78" t="str">
-        <v>1156.0</v>
+        <v>1131.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H79">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I79" t="str">
-        <v>704.0</v>
+        <v>705.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="H80">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="I80" t="str">
-        <v>909.0</v>
+        <v>902.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H81">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="I81" t="str">
-        <v>493.0</v>
+        <v>494.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="H82">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="I82" t="str">
-        <v>250.0</v>
+        <v>227.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H83">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I83" t="str">
-        <v>467.0</v>
+        <v>476.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H84">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="I84" t="str">
-        <v>940.0</v>
+        <v>943.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H85">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I85" t="str">
-        <v>1377.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H86">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I86" t="str">
-        <v>2280.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3690,10 +3690,10 @@
         <v>108</v>
       </c>
       <c r="H87">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="I87" t="str">
-        <v>458.0</v>
+        <v>497.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="H88">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="I88" t="str">
-        <v>1171.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H89">
         <v>160</v>
       </c>
       <c r="I89" t="str">
-        <v>715.0</v>
+        <v>710.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H90">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="I90" t="str">
-        <v>948.0</v>
+        <v>918.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H91">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="I91" t="str">
-        <v>463.0</v>
+        <v>495.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H92">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I92" t="str">
-        <v>266.0</v>
+        <v>273.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H93">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I93" t="str">
-        <v>465.0</v>
+        <v>455.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H94">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I94" t="str">
-        <v>943.0</v>
+        <v>942.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H95">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="I95" t="str">
-        <v>1366.0</v>
+        <v>1373.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="H96">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="I96" t="str">
-        <v>2263.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H97">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I97" t="str">
-        <v>481.0</v>
+        <v>469.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H98">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="I98" t="str">
-        <v>1129.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H99">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="I99" t="str">
-        <v>698.0</v>
+        <v>684.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H100">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I100" t="str">
-        <v>939.0</v>
+        <v>930.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H101">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="I101" t="str">
-        <v>473.0</v>
+        <v>494.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H102">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="I102" t="str">
-        <v>237.0</v>
+        <v>254.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,10 +4295,10 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H103">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I103" t="str">
         <v>496.0</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="H104">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I104" t="str">
-        <v>924.0</v>
+        <v>918.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H105">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="I105" t="str">
-        <v>1387.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="H106">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="I106" t="str">
-        <v>2271.0</v>
+        <v>2276.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H107">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="I107" t="str">
-        <v>484.0</v>
+        <v>468.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H108">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I108" t="str">
-        <v>1172.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="H109">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I109" t="str">
-        <v>703.0</v>
+        <v>699.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H110">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="I110" t="str">
-        <v>939.0</v>
+        <v>938.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="H111">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I111" t="str">
-        <v>471.0</v>
+        <v>481.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H112">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I112" t="str">
-        <v>261.0</v>
+        <v>268.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H113">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I113" t="str">
-        <v>478.0</v>
+        <v>454.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H114">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I114" t="str">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,13 +4751,13 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H115">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="I115" t="str">
-        <v>1399.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4792,10 +4792,10 @@
         <v>263</v>
       </c>
       <c r="H116">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I116" t="str">
-        <v>2279.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H117">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I117" t="str">
-        <v>485.0</v>
+        <v>452.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4868,10 +4868,10 @@
         <v>166</v>
       </c>
       <c r="H118">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I118" t="str">
-        <v>1133.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H119">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="I119" t="str">
-        <v>701.0</v>
+        <v>682.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H120">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="I120" t="str">
-        <v>921.0</v>
+        <v>916.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H121">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="I121" t="str">
-        <v>472.0</v>
+        <v>475.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H122">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="I122" t="str">
-        <v>246.0</v>
+        <v>269.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H123">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I123" t="str">
-        <v>487.0</v>
+        <v>481.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H124">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="I124" t="str">
-        <v>921.0</v>
+        <v>900.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5134,10 +5134,10 @@
         <v>191</v>
       </c>
       <c r="H125">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I125" t="str">
-        <v>1368.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H126">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="I126" t="str">
-        <v>2298.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="H127">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I127" t="str">
-        <v>486.0</v>
+        <v>452.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H128">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="I128" t="str">
-        <v>1172.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H129">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I129" t="str">
-        <v>679.0</v>
+        <v>711.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H130">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="I130" t="str">
-        <v>937.0</v>
+        <v>923.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H131">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="I131" t="str">
-        <v>494.0</v>
+        <v>460.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H132">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I132" t="str">
-        <v>246.0</v>
+        <v>258.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H133">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I133" t="str">
-        <v>467.0</v>
+        <v>452.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="H134">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="I134" t="str">
-        <v>922.0</v>
+        <v>910.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H135">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="I135" t="str">
-        <v>1389.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H136">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I136" t="str">
-        <v>2290.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H137">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="I137" t="str">
-        <v>470.0</v>
+        <v>468.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H138">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="I138" t="str">
-        <v>1168.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="H139">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="I139" t="str">
-        <v>710.0</v>
+        <v>680.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H140">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I140" t="str">
-        <v>926.0</v>
+        <v>922.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H141">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I141" t="str">
-        <v>460.0</v>
+        <v>499.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5780,10 +5780,10 @@
         <v>105</v>
       </c>
       <c r="H142">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I142" t="str">
-        <v>257.0</v>
+        <v>269.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H143">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="I143" t="str">
-        <v>477.0</v>
+        <v>486.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,10 +5853,10 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H144">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I144" t="str">
         <v>932.0</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H145">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="I145" t="str">
-        <v>1368.0</v>
+        <v>1387.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H146">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="I146" t="str">
-        <v>2268.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H147">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I147" t="str">
-        <v>499.0</v>
+        <v>480.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6008,10 +6008,10 @@
         <v>168</v>
       </c>
       <c r="H148">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="I148" t="str">
-        <v>1136.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H149">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I149" t="str">
-        <v>688.0</v>
+        <v>720.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H150">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I150" t="str">
-        <v>940.0</v>
+        <v>931.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H151">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="I151" t="str">
-        <v>495.0</v>
+        <v>472.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H152">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I152" t="str">
-        <v>240.0</v>
+        <v>270.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H153">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I153" t="str">
-        <v>452.0</v>
+        <v>471.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H154">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I154" t="str">
-        <v>912.0</v>
+        <v>909.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H155">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="I155" t="str">
-        <v>1365.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H156">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I156" t="str">
-        <v>2265.0</v>
+        <v>2275.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H157">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="I157" t="str">
-        <v>470.0</v>
+        <v>454.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H158">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I158" t="str">
-        <v>1169.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H159">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="I159" t="str">
-        <v>721.0</v>
+        <v>678.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H160">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="I160" t="str">
-        <v>923.0</v>
+        <v>924.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H161">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I161" t="str">
-        <v>473.0</v>
+        <v>452.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H162">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="I162" t="str">
-        <v>254.0</v>
+        <v>247.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H163">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="I163" t="str">
-        <v>458.0</v>
+        <v>485.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H164">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="I164" t="str">
-        <v>913.0</v>
+        <v>946.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="H165">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="I165" t="str">
-        <v>1396.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H166">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="I166" t="str">
-        <v>2293.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H167">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I167" t="str">
-        <v>496.0</v>
+        <v>477.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H168">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="I168" t="str">
-        <v>1155.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H169">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I169" t="str">
-        <v>690.0</v>
+        <v>692.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H170">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I170" t="str">
-        <v>928.0</v>
+        <v>901.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H171">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="I171" t="str">
-        <v>496.0</v>
+        <v>467.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H172">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I172" t="str">
-        <v>270.0</v>
+        <v>248.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H173">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="I173" t="str">
-        <v>454.0</v>
+        <v>474.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H174">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="I174" t="str">
-        <v>902.0</v>
+        <v>926.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H175">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="I175" t="str">
-        <v>1390.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="H176">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="I176" t="str">
-        <v>2288.0</v>
+        <v>2291.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="H177">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="I177" t="str">
-        <v>499.0</v>
+        <v>474.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H178">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="I178" t="str">
-        <v>1142.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="H179">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="I179" t="str">
-        <v>681.0</v>
+        <v>687.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H180">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I180" t="str">
-        <v>938.0</v>
+        <v>944.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H181">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I181" t="str">
-        <v>477.0</v>
+        <v>452.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H182">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="I182" t="str">
-        <v>228.0</v>
+        <v>244.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H183">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I183" t="str">
-        <v>454.0</v>
+        <v>480.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H184">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="I184" t="str">
-        <v>901.0</v>
+        <v>915.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H185">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="I185" t="str">
-        <v>1385.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H186">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I186" t="str">
-        <v>2263.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7490,10 +7490,10 @@
         <v>112</v>
       </c>
       <c r="H187">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I187" t="str">
-        <v>496.0</v>
+        <v>483.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H188">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I188" t="str">
-        <v>1139.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H189">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="I189" t="str">
-        <v>677.0</v>
+        <v>681.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H190">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I190" t="str">
-        <v>948.0</v>
+        <v>942.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,10 +7639,10 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H191">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I191" t="str">
         <v>467.0</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H192">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="I192" t="str">
-        <v>265.0</v>
+        <v>230.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="H193">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="I193" t="str">
-        <v>499.0</v>
+        <v>484.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="H194">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I194" t="str">
-        <v>942.0</v>
+        <v>940.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H195">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="I195" t="str">
-        <v>1379.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H196">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="I196" t="str">
-        <v>2292.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H197">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I197" t="str">
-        <v>471.0</v>
+        <v>458.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="H198">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I198" t="str">
-        <v>1147.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="H199">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="I199" t="str">
-        <v>697.0</v>
+        <v>703.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H200">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I200" t="str">
-        <v>945.0</v>
+        <v>915.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H201">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="I201" t="str">
-        <v>498.0</v>
+        <v>452.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H202">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I202" t="str">
-        <v>254.0</v>
+        <v>238.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H203">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="I203" t="str">
-        <v>499.0</v>
+        <v>493.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H204">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I204" t="str">
-        <v>935.0</v>
+        <v>925.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H205">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="I205" t="str">
-        <v>1371.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H206">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I206" t="str">
-        <v>2250.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H207">
         <v>143</v>
       </c>
       <c r="I207" t="str">
-        <v>495.0</v>
+        <v>466.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H208">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="I208" t="str">
-        <v>1174.0</v>
+        <v>1127.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H209">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="I209" t="str">
-        <v>709.0</v>
+        <v>715.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H210">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I210" t="str">
-        <v>906.0</v>
+        <v>940.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H211">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I211" t="str">
-        <v>458.0</v>
+        <v>477.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H212">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="I212" t="str">
-        <v>245.0</v>
+        <v>237.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="H213">
         <v>153</v>
       </c>
       <c r="I213" t="str">
-        <v>451.0</v>
+        <v>497.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="H214">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I214" t="str">
-        <v>902.0</v>
+        <v>944.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="H215">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="I215" t="str">
-        <v>1369.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H216">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="I216" t="str">
-        <v>2270.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H217">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="I217" t="str">
-        <v>494.0</v>
+        <v>479.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H218">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I218" t="str">
-        <v>1139.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H219">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I219" t="str">
-        <v>718.0</v>
+        <v>692.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H220">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="I220" t="str">
-        <v>928.0</v>
+        <v>939.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H221">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I221" t="str">
-        <v>490.0</v>
+        <v>484.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H222">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I222" t="str">
-        <v>226.0</v>
+        <v>230.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H223">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="I223" t="str">
-        <v>483.0</v>
+        <v>465.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="H224">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="I224" t="str">
-        <v>912.0</v>
+        <v>930.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H225">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="I225" t="str">
-        <v>1381.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H226">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="I226" t="str">
-        <v>2253.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H227">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I227" t="str">
-        <v>457.0</v>
+        <v>450.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H228">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="I228" t="str">
-        <v>1159.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H229">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="I229" t="str">
-        <v>690.0</v>
+        <v>685.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9124,10 +9124,10 @@
         <v>96</v>
       </c>
       <c r="H230">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I230" t="str">
-        <v>914.0</v>
+        <v>929.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="H231">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="I231" t="str">
-        <v>458.0</v>
+        <v>483.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H232">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I232" t="str">
-        <v>235.0</v>
+        <v>237.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H233">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="I233" t="str">
-        <v>492.0</v>
+        <v>499.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="H234">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="I234" t="str">
-        <v>937.0</v>
+        <v>923.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,10 +9311,10 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H235">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="I235" t="str">
         <v>1374.0</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H236">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I236" t="str">
-        <v>2282.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="H237">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I237" t="str">
-        <v>474.0</v>
+        <v>465.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H238">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="I238" t="str">
-        <v>1162.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="H239">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I239" t="str">
-        <v>698.0</v>
+        <v>707.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H240">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="I240" t="str">
-        <v>942.0</v>
+        <v>949.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="H241">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I241" t="str">
-        <v>458.0</v>
+        <v>465.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H242">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I242" t="str">
-        <v>258.0</v>
+        <v>254.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H243">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="I243" t="str">
-        <v>477.0</v>
+        <v>498.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,10 +9653,10 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="H244">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I244" t="str">
         <v>919.0</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="H245">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="I245" t="str">
-        <v>1364.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="H246">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="I246" t="str">
-        <v>2277.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H247">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="I247" t="str">
-        <v>478.0</v>
+        <v>471.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H248">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="I248" t="str">
-        <v>1173.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H249">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="I249" t="str">
-        <v>679.0</v>
+        <v>710.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H250">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I250" t="str">
-        <v>908.0</v>
+        <v>918.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H251">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I251" t="str">
-        <v>499.0</v>
+        <v>460.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H252">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="I252" t="str">
-        <v>245.0</v>
+        <v>241.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H253">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I253" t="str">
-        <v>467.0</v>
+        <v>453.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="H254">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="I254" t="str">
-        <v>917.0</v>
+        <v>910.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H255">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I255" t="str">
-        <v>1378.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="H256">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="I256" t="str">
-        <v>2293.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H257">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="I257" t="str">
-        <v>479.0</v>
+        <v>485.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H258">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="I258" t="str">
-        <v>1155.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H259">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I259" t="str">
-        <v>706.0</v>
+        <v>711.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H260">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="I260" t="str">
-        <v>908.0</v>
+        <v>934.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10302,10 +10302,10 @@
         <v>124</v>
       </c>
       <c r="H261">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I261" t="str">
-        <v>451.0</v>
+        <v>465.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H262">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I262" t="str">
-        <v>268.0</v>
+        <v>234.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="H263">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I263" t="str">
-        <v>497.0</v>
+        <v>475.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H264">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="I264" t="str">
-        <v>917.0</v>
+        <v>913.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H265">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="I265" t="str">
-        <v>1370.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H266">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="I266" t="str">
-        <v>2277.0</v>
+        <v>2295.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H267">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I267" t="str">
-        <v>459.0</v>
+        <v>497.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H268">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="I268" t="str">
-        <v>1129.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H269">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I269" t="str">
-        <v>700.0</v>
+        <v>682.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H270">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="I270" t="str">
-        <v>923.0</v>
+        <v>900.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="H271">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I271" t="str">
-        <v>465.0</v>
+        <v>477.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H272">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="I272" t="str">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H273">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="I273" t="str">
-        <v>466.0</v>
+        <v>481.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H274">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I274" t="str">
-        <v>940.0</v>
+        <v>925.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H275">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I275" t="str">
-        <v>1368.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H276">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="I276" t="str">
-        <v>2260.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H277">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="I277" t="str">
-        <v>471.0</v>
+        <v>493.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H278">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I278" t="str">
-        <v>1159.0</v>
+        <v>1148.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="H279">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="I279" t="str">
-        <v>688.0</v>
+        <v>705.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H280">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I280" t="str">
-        <v>922.0</v>
+        <v>917.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H281">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="I281" t="str">
-        <v>492.0</v>
+        <v>472.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H282">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I282" t="str">
-        <v>233.0</v>
+        <v>236.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H283">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="I283" t="str">
-        <v>451.0</v>
+        <v>475.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H284">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I284" t="str">
-        <v>926.0</v>
+        <v>923.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H285">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="I285" t="str">
-        <v>1387.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H286">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="I286" t="str">
-        <v>2255.0</v>
+        <v>2274.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="H287">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I287" t="str">
-        <v>461.0</v>
+        <v>484.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H288">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I288" t="str">
-        <v>1125.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H289">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I289" t="str">
-        <v>713.0</v>
+        <v>684.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="H290">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="I290" t="str">
-        <v>919.0</v>
+        <v>901.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H291">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I291" t="str">
-        <v>481.0</v>
+        <v>452.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H292">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I292" t="str">
-        <v>259.0</v>
+        <v>256.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H293">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="I293" t="str">
-        <v>499.0</v>
+        <v>464.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H294">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I294" t="str">
-        <v>910.0</v>
+        <v>917.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H295">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I295" t="str">
-        <v>1382.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="H296">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="I296" t="str">
-        <v>2287.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H297">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I297" t="str">
-        <v>491.0</v>
+        <v>457.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H298">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="I298" t="str">
-        <v>1168.0</v>
+        <v>1135.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H299">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I299" t="str">
-        <v>694.0</v>
+        <v>699.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H300">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="I300" t="str">
-        <v>928.0</v>
+        <v>929.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="H301">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="I301" t="str">
-        <v>499.0</v>
+        <v>461.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I2" t="str">
-        <v>270.0</v>
+        <v>227.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H3">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I3" t="str">
-        <v>464.0</v>
+        <v>480.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H4">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="I4" t="str">
-        <v>907.0</v>
+        <v>917.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H5">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="I5" t="str">
-        <v>1383.0</v>
+        <v>1354.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H6">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="I6" t="str">
-        <v>2280.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="H7">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="I7" t="str">
-        <v>496.0</v>
+        <v>451.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="H8">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I8" t="str">
-        <v>1139.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H9">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I9" t="str">
-        <v>691.0</v>
+        <v>687.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H10">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="I10" t="str">
-        <v>912.0</v>
+        <v>934.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H11">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="I11" t="str">
-        <v>454.0</v>
+        <v>492.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H12">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I12" t="str">
-        <v>249.0</v>
+        <v>244.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H13">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="I13" t="str">
-        <v>453.0</v>
+        <v>472.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H14">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="I14" t="str">
-        <v>915.0</v>
+        <v>941.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="H15">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="I15" t="str">
-        <v>1368.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="H16">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="I16" t="str">
-        <v>2275.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H17">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="I17" t="str">
-        <v>461.0</v>
+        <v>467.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H18">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I18" t="str">
-        <v>1129.0</v>
+        <v>1143.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="H19">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I19" t="str">
-        <v>680.0</v>
+        <v>691.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H20">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I20" t="str">
-        <v>901.0</v>
+        <v>930.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H21">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="I21" t="str">
-        <v>454.0</v>
+        <v>463.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="H22">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="I22" t="str">
-        <v>250.0</v>
+        <v>272.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="H23">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I23" t="str">
-        <v>496.0</v>
+        <v>469.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H24">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I24" t="str">
-        <v>912.0</v>
+        <v>928.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="H25">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I25" t="str">
-        <v>1351.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="H26">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="I26" t="str">
-        <v>2275.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1410,10 +1410,10 @@
         <v>106</v>
       </c>
       <c r="H27">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I27" t="str">
-        <v>487.0</v>
+        <v>463.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H28">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I28" t="str">
-        <v>1163.0</v>
+        <v>1172.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H29">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I29" t="str">
-        <v>705.0</v>
+        <v>680.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H30">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="I30" t="str">
-        <v>906.0</v>
+        <v>918.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="H31">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="I31" t="str">
-        <v>494.0</v>
+        <v>451.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H32">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="I32" t="str">
-        <v>254.0</v>
+        <v>269.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H33">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="I33" t="str">
-        <v>495.0</v>
+        <v>498.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
+        <v>148</v>
+      </c>
+      <c r="H34">
         <v>152</v>
       </c>
-      <c r="H34">
-        <v>177</v>
-      </c>
       <c r="I34" t="str">
-        <v>943.0</v>
+        <v>937.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="H35">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I35" t="str">
-        <v>1356.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H36">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="I36" t="str">
-        <v>2266.0</v>
+        <v>2257.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="H37">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I37" t="str">
-        <v>461.0</v>
+        <v>470.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H38">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="I38" t="str">
-        <v>1158.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H39">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="I39" t="str">
-        <v>720.0</v>
+        <v>679.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H40">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="I40" t="str">
-        <v>905.0</v>
+        <v>921.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="H41">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="I41" t="str">
-        <v>468.0</v>
+        <v>477.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="H42">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="I42" t="str">
-        <v>267.0</v>
+        <v>244.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,10 +2015,10 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H43">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="I43" t="str">
         <v>450.0</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H44">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="I44" t="str">
-        <v>949.0</v>
+        <v>922.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H45">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="I45" t="str">
-        <v>1386.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="H46">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I46" t="str">
-        <v>2253.0</v>
+        <v>2262.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H47">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="I47" t="str">
-        <v>479.0</v>
+        <v>465.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H48">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I48" t="str">
-        <v>1169.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H49">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I49" t="str">
-        <v>703.0</v>
+        <v>713.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H50">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="I50" t="str">
-        <v>928.0</v>
+        <v>945.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H51">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I51" t="str">
-        <v>483.0</v>
+        <v>496.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H52">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I52" t="str">
-        <v>233.0</v>
+        <v>241.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H53">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="I53" t="str">
-        <v>494.0</v>
+        <v>465.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H54">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="I54" t="str">
-        <v>926.0</v>
+        <v>937.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H55">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="I55" t="str">
-        <v>1399.0</v>
+        <v>1379.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
+        <v>248</v>
+      </c>
+      <c r="H56">
         <v>250</v>
       </c>
-      <c r="H56">
-        <v>278</v>
-      </c>
       <c r="I56" t="str">
-        <v>2250.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H57">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="I57" t="str">
-        <v>458.0</v>
+        <v>497.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H58">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I58" t="str">
-        <v>1162.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="H59">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="I59" t="str">
-        <v>707.0</v>
+        <v>708.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H60">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I60" t="str">
-        <v>914.0</v>
+        <v>931.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="H61">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I61" t="str">
-        <v>497.0</v>
+        <v>453.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H62">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I62" t="str">
-        <v>259.0</v>
+        <v>244.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H63">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="I63" t="str">
-        <v>468.0</v>
+        <v>473.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H64">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I64" t="str">
-        <v>921.0</v>
+        <v>938.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H65">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="I65" t="str">
-        <v>1371.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H66">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="I66" t="str">
-        <v>2298.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H67">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="I67" t="str">
-        <v>455.0</v>
+        <v>457.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H68">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="I68" t="str">
-        <v>1136.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H69">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="I69" t="str">
-        <v>701.0</v>
+        <v>716.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3041,13 +3041,13 @@
         <v>20</v>
       </c>
       <c r="G70">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="H70">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="I70" t="str">
-        <v>948.0</v>
+        <v>900.0</v>
       </c>
       <c r="J70" t="str">
         <v>100.00%</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="H71">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="I71" t="str">
-        <v>489.0</v>
+        <v>492.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H72">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I72" t="str">
-        <v>245.0</v>
+        <v>241.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="H73">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="I73" t="str">
-        <v>494.0</v>
+        <v>477.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H74">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="I74" t="str">
-        <v>908.0</v>
+        <v>912.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H75">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="I75" t="str">
-        <v>1365.0</v>
+        <v>1394.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="H76">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="I76" t="str">
-        <v>2299.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3307,13 +3307,13 @@
         <v>10</v>
       </c>
       <c r="G77">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H77">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="I77" t="str">
-        <v>460.0</v>
+        <v>450.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="H78">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I78" t="str">
-        <v>1131.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H79">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="I79" t="str">
-        <v>705.0</v>
+        <v>702.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H80">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="I80" t="str">
-        <v>902.0</v>
+        <v>916.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="H81">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="I81" t="str">
-        <v>494.0</v>
+        <v>462.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="H82">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="I82" t="str">
-        <v>227.0</v>
+        <v>232.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H83">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="I83" t="str">
-        <v>476.0</v>
+        <v>452.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H84">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="I84" t="str">
-        <v>943.0</v>
+        <v>933.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="H85">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="I85" t="str">
-        <v>1362.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="H86">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="I86" t="str">
-        <v>2286.0</v>
+        <v>2277.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H87">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="I87" t="str">
-        <v>497.0</v>
+        <v>474.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="H88">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="I88" t="str">
-        <v>1135.0</v>
+        <v>1146.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="H89">
         <v>160</v>
       </c>
       <c r="I89" t="str">
-        <v>710.0</v>
+        <v>680.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H90">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I90" t="str">
-        <v>918.0</v>
+        <v>943.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H91">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="I91" t="str">
-        <v>495.0</v>
+        <v>459.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,10 +3877,10 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H92">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I92" t="str">
         <v>273.0</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="H93">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I93" t="str">
-        <v>455.0</v>
+        <v>491.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H94">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I94" t="str">
-        <v>942.0</v>
+        <v>943.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H95">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="I95" t="str">
-        <v>1373.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="H96">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I96" t="str">
-        <v>2276.0</v>
+        <v>2265.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H97">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I97" t="str">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H98">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="I98" t="str">
-        <v>1143.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H99">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="I99" t="str">
-        <v>684.0</v>
+        <v>675.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H100">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I100" t="str">
-        <v>930.0</v>
+        <v>909.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4219,13 +4219,13 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="H101">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="I101" t="str">
-        <v>494.0</v>
+        <v>480.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H102">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I102" t="str">
-        <v>254.0</v>
+        <v>258.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="H103">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I103" t="str">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H104">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I104" t="str">
-        <v>918.0</v>
+        <v>901.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="H105">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I105" t="str">
-        <v>1363.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H106">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="I106" t="str">
-        <v>2276.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,13 +4447,13 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H107">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="I107" t="str">
-        <v>468.0</v>
+        <v>493.0</v>
       </c>
       <c r="J107" t="str">
         <v>100.00%</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="H108">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="I108" t="str">
-        <v>1136.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,7 +4523,7 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H109">
         <v>166</v>
@@ -4564,10 +4564,10 @@
         <v>117</v>
       </c>
       <c r="H110">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I110" t="str">
-        <v>938.0</v>
+        <v>933.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H111">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="I111" t="str">
-        <v>481.0</v>
+        <v>497.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H112">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="I112" t="str">
-        <v>268.0</v>
+        <v>230.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H113">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="I113" t="str">
-        <v>454.0</v>
+        <v>485.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H114">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="I114" t="str">
-        <v>933.0</v>
+        <v>927.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4751,10 +4751,10 @@
         <v>30</v>
       </c>
       <c r="G115">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H115">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="I115" t="str">
         <v>1360.0</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H116">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="I116" t="str">
-        <v>2290.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="H117">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I117" t="str">
-        <v>452.0</v>
+        <v>486.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4868,10 +4868,10 @@
         <v>166</v>
       </c>
       <c r="H118">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I118" t="str">
-        <v>1150.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="H119">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I119" t="str">
-        <v>682.0</v>
+        <v>716.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H120">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="I120" t="str">
-        <v>916.0</v>
+        <v>910.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
+        <v>124</v>
+      </c>
+      <c r="H121">
         <v>125</v>
       </c>
-      <c r="H121">
-        <v>126</v>
-      </c>
       <c r="I121" t="str">
-        <v>475.0</v>
+        <v>479.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="H122">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="I122" t="str">
-        <v>269.0</v>
+        <v>240.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H123">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I123" t="str">
-        <v>481.0</v>
+        <v>466.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5096,10 +5096,10 @@
         <v>164</v>
       </c>
       <c r="H124">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="I124" t="str">
-        <v>900.0</v>
+        <v>944.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H125">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I125" t="str">
-        <v>1374.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H126">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="I126" t="str">
-        <v>2294.0</v>
+        <v>2271.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="H127">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I127" t="str">
-        <v>452.0</v>
+        <v>498.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H128">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="I128" t="str">
-        <v>1130.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="H129">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="I129" t="str">
-        <v>711.0</v>
+        <v>697.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5324,10 +5324,10 @@
         <v>100</v>
       </c>
       <c r="H130">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I130" t="str">
-        <v>923.0</v>
+        <v>900.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H131">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="I131" t="str">
-        <v>460.0</v>
+        <v>469.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H132">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="I132" t="str">
-        <v>258.0</v>
+        <v>254.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H133">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="I133" t="str">
-        <v>452.0</v>
+        <v>480.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H134">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I134" t="str">
-        <v>910.0</v>
+        <v>928.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5514,10 +5514,10 @@
         <v>203</v>
       </c>
       <c r="H135">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I135" t="str">
-        <v>1362.0</v>
+        <v>1395.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H136">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="I136" t="str">
-        <v>2260.0</v>
+        <v>2252.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,10 +5587,10 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="H137">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="I137" t="str">
         <v>468.0</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="H138">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I138" t="str">
-        <v>1143.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="H139">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="I139" t="str">
-        <v>680.0</v>
+        <v>713.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H140">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="I140" t="str">
-        <v>922.0</v>
+        <v>911.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,10 +5739,10 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="H141">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I141" t="str">
         <v>499.0</v>
@@ -5777,13 +5777,13 @@
         <v>5</v>
       </c>
       <c r="G142">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H142">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I142" t="str">
-        <v>269.0</v>
+        <v>258.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H143">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="I143" t="str">
-        <v>486.0</v>
+        <v>461.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="H144">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="I144" t="str">
-        <v>932.0</v>
+        <v>925.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="H145">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I145" t="str">
-        <v>1387.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="H146">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="I146" t="str">
-        <v>2263.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H147">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="I147" t="str">
-        <v>480.0</v>
+        <v>498.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,10 +6005,10 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H148">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I148" t="str">
         <v>1152.0</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H149">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="I149" t="str">
-        <v>720.0</v>
+        <v>724.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H150">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="I150" t="str">
-        <v>931.0</v>
+        <v>946.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H151">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I151" t="str">
-        <v>472.0</v>
+        <v>479.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H152">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I152" t="str">
-        <v>270.0</v>
+        <v>229.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6198,10 +6198,10 @@
         <v>118</v>
       </c>
       <c r="H153">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="I153" t="str">
-        <v>471.0</v>
+        <v>491.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6236,10 +6236,10 @@
         <v>155</v>
       </c>
       <c r="H154">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I154" t="str">
-        <v>909.0</v>
+        <v>944.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="H155">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I155" t="str">
-        <v>1376.0</v>
+        <v>1381.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H156">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="I156" t="str">
-        <v>2275.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H157">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I157" t="str">
-        <v>454.0</v>
+        <v>496.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H158">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I158" t="str">
-        <v>1165.0</v>
+        <v>1173.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H159">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I159" t="str">
-        <v>678.0</v>
+        <v>712.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H160">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I160" t="str">
-        <v>924.0</v>
+        <v>943.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H161">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I161" t="str">
-        <v>452.0</v>
+        <v>471.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H162">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="I162" t="str">
-        <v>247.0</v>
+        <v>255.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H163">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I163" t="str">
-        <v>485.0</v>
+        <v>452.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H164">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="I164" t="str">
-        <v>946.0</v>
+        <v>940.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6651,13 +6651,13 @@
         <v>30</v>
       </c>
       <c r="G165">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H165">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I165" t="str">
-        <v>1376.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H166">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="I166" t="str">
-        <v>2256.0</v>
+        <v>2253.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="H167">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="I167" t="str">
-        <v>477.0</v>
+        <v>485.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H168">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="I168" t="str">
-        <v>1153.0</v>
+        <v>1159.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H169">
         <v>183</v>
       </c>
       <c r="I169" t="str">
-        <v>692.0</v>
+        <v>679.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H170">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I170" t="str">
-        <v>901.0</v>
+        <v>943.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H171">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I171" t="str">
-        <v>467.0</v>
+        <v>490.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H172">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I172" t="str">
-        <v>248.0</v>
+        <v>239.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H173">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="I173" t="str">
-        <v>474.0</v>
+        <v>483.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="H174">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="I174" t="str">
-        <v>926.0</v>
+        <v>937.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H175">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="I175" t="str">
-        <v>1368.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7069,13 +7069,13 @@
         <v>50</v>
       </c>
       <c r="G176">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H176">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I176" t="str">
-        <v>2291.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H177">
         <v>138</v>
       </c>
       <c r="I177" t="str">
-        <v>474.0</v>
+        <v>452.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="H178">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I178" t="str">
-        <v>1158.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H179">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="I179" t="str">
-        <v>687.0</v>
+        <v>683.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H180">
         <v>130</v>
       </c>
       <c r="I180" t="str">
-        <v>944.0</v>
+        <v>934.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H181">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="I181" t="str">
-        <v>452.0</v>
+        <v>489.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H182">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I182" t="str">
-        <v>244.0</v>
+        <v>265.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
+        <v>119</v>
+      </c>
+      <c r="H183">
         <v>122</v>
       </c>
-      <c r="H183">
-        <v>141</v>
-      </c>
       <c r="I183" t="str">
-        <v>480.0</v>
+        <v>459.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H184">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="I184" t="str">
-        <v>915.0</v>
+        <v>949.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H185">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I185" t="str">
-        <v>1374.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7449,13 +7449,13 @@
         <v>50</v>
       </c>
       <c r="G186">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H186">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I186" t="str">
-        <v>2295.0</v>
+        <v>2283.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H187">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="I187" t="str">
-        <v>483.0</v>
+        <v>475.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7525,13 +7525,13 @@
         <v>25</v>
       </c>
       <c r="G188">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H188">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="I188" t="str">
-        <v>1132.0</v>
+        <v>1134.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H189">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I189" t="str">
-        <v>681.0</v>
+        <v>691.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H190">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="I190" t="str">
-        <v>942.0</v>
+        <v>916.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H191">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I191" t="str">
-        <v>467.0</v>
+        <v>457.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H192">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I192" t="str">
-        <v>230.0</v>
+        <v>269.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H193">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I193" t="str">
-        <v>484.0</v>
+        <v>454.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H194">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I194" t="str">
-        <v>940.0</v>
+        <v>901.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H195">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="I195" t="str">
-        <v>1380.0</v>
+        <v>1376.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H196">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="I196" t="str">
-        <v>2253.0</v>
+        <v>2294.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="H197">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="I197" t="str">
-        <v>458.0</v>
+        <v>494.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H198">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="I198" t="str">
-        <v>1159.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H199">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="I199" t="str">
-        <v>703.0</v>
+        <v>687.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H200">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I200" t="str">
-        <v>915.0</v>
+        <v>942.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H201">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="I201" t="str">
-        <v>452.0</v>
+        <v>474.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H202">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="I202" t="str">
-        <v>238.0</v>
+        <v>231.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H203">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I203" t="str">
-        <v>493.0</v>
+        <v>459.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,10 +8133,10 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="H204">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="I204" t="str">
         <v>925.0</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="H205">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I205" t="str">
-        <v>1361.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H206">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="I206" t="str">
-        <v>2287.0</v>
+        <v>2266.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="H207">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I207" t="str">
-        <v>466.0</v>
+        <v>481.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H208">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="I208" t="str">
-        <v>1127.0</v>
+        <v>1136.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H209">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I209" t="str">
-        <v>715.0</v>
+        <v>684.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,13 +8361,13 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H210">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="I210" t="str">
-        <v>940.0</v>
+        <v>943.0</v>
       </c>
       <c r="J210" t="str">
         <v>100.00%</v>
@@ -8402,10 +8402,10 @@
         <v>134</v>
       </c>
       <c r="H211">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I211" t="str">
-        <v>477.0</v>
+        <v>474.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H212">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="I212" t="str">
-        <v>237.0</v>
+        <v>228.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="H213">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I213" t="str">
-        <v>497.0</v>
+        <v>472.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,13 +8513,13 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="H214">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="I214" t="str">
-        <v>944.0</v>
+        <v>926.0</v>
       </c>
       <c r="J214" t="str">
         <v>100.00%</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H215">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="I215" t="str">
-        <v>1350.0</v>
+        <v>1385.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8589,13 +8589,13 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="H216">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="I216" t="str">
-        <v>2277.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="H217">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="I217" t="str">
-        <v>479.0</v>
+        <v>483.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="H218">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="I218" t="str">
-        <v>1154.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8703,13 +8703,13 @@
         <v>15</v>
       </c>
       <c r="G219">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="H219">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="I219" t="str">
-        <v>692.0</v>
+        <v>675.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H220">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="I220" t="str">
-        <v>939.0</v>
+        <v>908.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H221">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I221" t="str">
-        <v>484.0</v>
+        <v>478.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H222">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="I222" t="str">
-        <v>230.0</v>
+        <v>261.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H223">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="I223" t="str">
-        <v>465.0</v>
+        <v>462.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="H224">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="I224" t="str">
-        <v>930.0</v>
+        <v>927.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="H225">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I225" t="str">
-        <v>1351.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H226">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="I226" t="str">
-        <v>2256.0</v>
+        <v>2285.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H227">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="I227" t="str">
-        <v>450.0</v>
+        <v>458.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H228">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I228" t="str">
-        <v>1148.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="H229">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="I229" t="str">
-        <v>685.0</v>
+        <v>675.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="H230">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="I230" t="str">
-        <v>929.0</v>
+        <v>911.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="H231">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="I231" t="str">
-        <v>483.0</v>
+        <v>456.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H232">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I232" t="str">
-        <v>237.0</v>
+        <v>270.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H233">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="I233" t="str">
-        <v>499.0</v>
+        <v>467.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H234">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="I234" t="str">
-        <v>923.0</v>
+        <v>931.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H235">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I235" t="str">
-        <v>1374.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,10 +9349,10 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H236">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I236" t="str">
         <v>2254.0</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H237">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I237" t="str">
-        <v>465.0</v>
+        <v>455.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H238">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="I238" t="str">
-        <v>1156.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,13 +9463,13 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="H239">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="I239" t="str">
-        <v>707.0</v>
+        <v>677.0</v>
       </c>
       <c r="J239" t="str">
         <v>100.00%</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H240">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I240" t="str">
-        <v>949.0</v>
+        <v>914.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H241">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="I241" t="str">
-        <v>465.0</v>
+        <v>455.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H242">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I242" t="str">
-        <v>254.0</v>
+        <v>260.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H243">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I243" t="str">
-        <v>498.0</v>
+        <v>454.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H244">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="I244" t="str">
-        <v>919.0</v>
+        <v>940.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="H245">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="I245" t="str">
-        <v>1390.0</v>
+        <v>1382.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="H246">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="I246" t="str">
-        <v>2267.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H247">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I247" t="str">
-        <v>471.0</v>
+        <v>459.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H248">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I248" t="str">
-        <v>1161.0</v>
+        <v>1138.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="H249">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="I249" t="str">
-        <v>710.0</v>
+        <v>677.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9881,13 +9881,13 @@
         <v>20</v>
       </c>
       <c r="G250">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="H250">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="I250" t="str">
-        <v>918.0</v>
+        <v>928.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H251">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="I251" t="str">
-        <v>460.0</v>
+        <v>453.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9960,10 +9960,10 @@
         <v>97</v>
       </c>
       <c r="H252">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I252" t="str">
-        <v>241.0</v>
+        <v>272.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H253">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="I253" t="str">
-        <v>453.0</v>
+        <v>452.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H254">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I254" t="str">
-        <v>910.0</v>
+        <v>937.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H255">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="I255" t="str">
-        <v>1386.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H256">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="I256" t="str">
-        <v>2271.0</v>
+        <v>2255.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H257">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I257" t="str">
-        <v>485.0</v>
+        <v>460.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10185,13 +10185,13 @@
         <v>25</v>
       </c>
       <c r="G258">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H258">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="I258" t="str">
-        <v>1158.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="H259">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="I259" t="str">
-        <v>711.0</v>
+        <v>680.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H260">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I260" t="str">
-        <v>934.0</v>
+        <v>901.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="H261">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="I261" t="str">
-        <v>465.0</v>
+        <v>471.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H262">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I262" t="str">
-        <v>234.0</v>
+        <v>255.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="H263">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="I263" t="str">
-        <v>475.0</v>
+        <v>460.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="H264">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I264" t="str">
-        <v>913.0</v>
+        <v>933.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H265">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="I265" t="str">
-        <v>1374.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10489,13 +10489,13 @@
         <v>50</v>
       </c>
       <c r="G266">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H266">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I266" t="str">
-        <v>2295.0</v>
+        <v>2296.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H267">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I267" t="str">
-        <v>497.0</v>
+        <v>494.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H268">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="I268" t="str">
-        <v>1140.0</v>
+        <v>1130.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H269">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="I269" t="str">
-        <v>682.0</v>
+        <v>681.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10641,13 +10641,13 @@
         <v>20</v>
       </c>
       <c r="G270">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H270">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I270" t="str">
-        <v>900.0</v>
+        <v>933.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H271">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I271" t="str">
-        <v>477.0</v>
+        <v>499.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="H272">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="I272" t="str">
-        <v>239.0</v>
+        <v>262.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H273">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I273" t="str">
-        <v>481.0</v>
+        <v>488.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H274">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I274" t="str">
-        <v>925.0</v>
+        <v>912.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="H275">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="I275" t="str">
-        <v>1354.0</v>
+        <v>1350.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="H276">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="I276" t="str">
-        <v>2266.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H277">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I277" t="str">
-        <v>493.0</v>
+        <v>485.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H278">
         <v>205</v>
       </c>
       <c r="I278" t="str">
-        <v>1148.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H279">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I279" t="str">
-        <v>705.0</v>
+        <v>720.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H280">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="I280" t="str">
-        <v>917.0</v>
+        <v>948.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H281">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I281" t="str">
-        <v>472.0</v>
+        <v>474.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H282">
         <v>127</v>
       </c>
       <c r="I282" t="str">
-        <v>236.0</v>
+        <v>232.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,10 +11135,10 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H283">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I283" t="str">
         <v>475.0</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H284">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I284" t="str">
-        <v>923.0</v>
+        <v>927.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H285">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="I285" t="str">
-        <v>1369.0</v>
+        <v>1386.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="H286">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I286" t="str">
-        <v>2274.0</v>
+        <v>2278.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="H287">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="I287" t="str">
-        <v>484.0</v>
+        <v>474.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H288">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="I288" t="str">
-        <v>1135.0</v>
+        <v>1151.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="H289">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I289" t="str">
-        <v>684.0</v>
+        <v>678.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="H290">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="I290" t="str">
-        <v>901.0</v>
+        <v>921.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H291">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="I291" t="str">
-        <v>452.0</v>
+        <v>480.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H292">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="I292" t="str">
-        <v>256.0</v>
+        <v>252.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11518,10 +11518,10 @@
         <v>112</v>
       </c>
       <c r="H293">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I293" t="str">
-        <v>464.0</v>
+        <v>466.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H294">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I294" t="str">
-        <v>917.0</v>
+        <v>946.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H295">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I295" t="str">
-        <v>1391.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="H296">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I296" t="str">
-        <v>2277.0</v>
+        <v>2299.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H297">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="I297" t="str">
-        <v>457.0</v>
+        <v>495.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H298">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="I298" t="str">
-        <v>1135.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H299">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I299" t="str">
-        <v>699.0</v>
+        <v>681.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H300">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I300" t="str">
-        <v>929.0</v>
+        <v>941.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="H301">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I301" t="str">
-        <v>461.0</v>
+        <v>490.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I2" t="str">
-        <v>227.0</v>
+        <v>270.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H3">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="I3" t="str">
-        <v>480.0</v>
+        <v>456.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="H4">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I4" t="str">
-        <v>917.0</v>
+        <v>911.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="H5">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="I5" t="str">
-        <v>1354.0</v>
+        <v>1363.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="H6">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I6" t="str">
-        <v>2260.0</v>
+        <v>2259.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I7" t="str">
-        <v>451.0</v>
+        <v>493.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H8">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I8" t="str">
-        <v>1166.0</v>
+        <v>1153.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H9">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I9" t="str">
-        <v>687.0</v>
+        <v>708.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H10">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="I10" t="str">
-        <v>934.0</v>
+        <v>911.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H11">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I11" t="str">
-        <v>492.0</v>
+        <v>472.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -837,13 +837,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H12">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="I12" t="str">
-        <v>244.0</v>
+        <v>236.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
+        <v>112</v>
+      </c>
+      <c r="H13">
         <v>126</v>
       </c>
-      <c r="H13">
-        <v>156</v>
-      </c>
       <c r="I13" t="str">
-        <v>472.0</v>
+        <v>473.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H14">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I14" t="str">
-        <v>941.0</v>
+        <v>907.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H15">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="I15" t="str">
-        <v>1359.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H16">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="I16" t="str">
-        <v>2251.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H17">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="I17" t="str">
-        <v>467.0</v>
+        <v>454.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="H18">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I18" t="str">
-        <v>1143.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H19">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I19" t="str">
-        <v>691.0</v>
+        <v>721.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H20">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="I20" t="str">
-        <v>930.0</v>
+        <v>932.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="H21">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="I21" t="str">
-        <v>463.0</v>
+        <v>461.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H22">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I22" t="str">
-        <v>272.0</v>
+        <v>260.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H23">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I23" t="str">
-        <v>469.0</v>
+        <v>466.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H24">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="I24" t="str">
-        <v>928.0</v>
+        <v>936.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H25">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="I25" t="str">
-        <v>1360.0</v>
+        <v>1372.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H26">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="I26" t="str">
-        <v>2254.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,13 +1407,13 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H27">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="I27" t="str">
-        <v>463.0</v>
+        <v>480.0</v>
       </c>
       <c r="J27" t="str">
         <v>100.00%</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="H28">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="I28" t="str">
-        <v>1172.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H29">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I29" t="str">
-        <v>680.0</v>
+        <v>704.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H30">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I30" t="str">
-        <v>918.0</v>
+        <v>922.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="H31">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="I31" t="str">
-        <v>451.0</v>
+        <v>484.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I32" t="str">
-        <v>269.0</v>
+        <v>225.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H33">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I33" t="str">
-        <v>498.0</v>
+        <v>465.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H34">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="I34" t="str">
-        <v>937.0</v>
+        <v>948.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="H35">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="I35" t="str">
-        <v>1368.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="H36">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I36" t="str">
-        <v>2257.0</v>
+        <v>2254.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H37">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I37" t="str">
-        <v>470.0</v>
+        <v>467.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H38">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I38" t="str">
-        <v>1125.0</v>
+        <v>1129.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="I39" t="str">
-        <v>679.0</v>
+        <v>722.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H40">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="I40" t="str">
-        <v>921.0</v>
+        <v>906.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H41">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="I41" t="str">
-        <v>477.0</v>
+        <v>486.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H42">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I42" t="str">
-        <v>244.0</v>
+        <v>269.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,10 +2015,10 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H43">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I43" t="str">
         <v>450.0</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H44">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="I44" t="str">
-        <v>922.0</v>
+        <v>926.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H45">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="I45" t="str">
-        <v>1385.0</v>
+        <v>1369.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="H46">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="I46" t="str">
-        <v>2262.0</v>
+        <v>2280.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H47">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I47" t="str">
-        <v>465.0</v>
+        <v>491.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H48">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I48" t="str">
-        <v>1132.0</v>
+        <v>1174.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H49">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="I49" t="str">
-        <v>713.0</v>
+        <v>685.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H50">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I50" t="str">
-        <v>945.0</v>
+        <v>932.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H51">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="I51" t="str">
-        <v>496.0</v>
+        <v>497.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H52">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I52" t="str">
-        <v>241.0</v>
+        <v>256.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="H53">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="I53" t="str">
-        <v>465.0</v>
+        <v>463.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H54">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I54" t="str">
-        <v>937.0</v>
+        <v>912.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H55">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="I55" t="str">
-        <v>1379.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H56">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I56" t="str">
-        <v>2263.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H57">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I57" t="str">
-        <v>497.0</v>
+        <v>453.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,10 +2585,10 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H58">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I58" t="str">
         <v>1144.0</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H59">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I59" t="str">
-        <v>708.0</v>
+        <v>723.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H60">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I60" t="str">
-        <v>931.0</v>
+        <v>915.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H61">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I61" t="str">
-        <v>453.0</v>
+        <v>452.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H62">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I62" t="str">
-        <v>244.0</v>
+        <v>226.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H63">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I63" t="str">
-        <v>473.0</v>
+        <v>486.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="H64">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="I64" t="str">
-        <v>938.0</v>
+        <v>929.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H65">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="I65" t="str">
-        <v>1391.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -2889,13 +2889,13 @@
         <v>50</v>
       </c>
       <c r="G66">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H66">
         <v>266</v>
       </c>
       <c r="I66" t="str">
-        <v>2267.0</v>
+        <v>2290.0</v>
       </c>
       <c r="J66" t="str">
         <v>100.00%</v>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="G67">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H67">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I67" t="str">
-        <v>457.0</v>
+        <v>488.0</v>
       </c>
       <c r="J67" t="str">
         <v>100.00%</v>
@@ -2965,13 +2965,13 @@
         <v>25</v>
       </c>
       <c r="G68">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H68">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="I68" t="str">
-        <v>1163.0</v>
+        <v>1147.0</v>
       </c>
       <c r="J68" t="str">
         <v>100.00%</v>
@@ -3003,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G69">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H69">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I69" t="str">
-        <v>716.0</v>
+        <v>686.0</v>
       </c>
       <c r="J69" t="str">
         <v>100.00%</v>
@@ -3044,7 +3044,7 @@
         <v>102</v>
       </c>
       <c r="H70">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I70" t="str">
         <v>900.0</v>
@@ -3079,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="G71">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H71">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I71" t="str">
-        <v>492.0</v>
+        <v>485.0</v>
       </c>
       <c r="J71" t="str">
         <v>100.00%</v>
@@ -3117,13 +3117,13 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H72">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="I72" t="str">
-        <v>241.0</v>
+        <v>250.0</v>
       </c>
       <c r="J72" t="str">
         <v>100.00%</v>
@@ -3155,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="G73">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H73">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="I73" t="str">
-        <v>477.0</v>
+        <v>472.0</v>
       </c>
       <c r="J73" t="str">
         <v>100.00%</v>
@@ -3193,13 +3193,13 @@
         <v>20</v>
       </c>
       <c r="G74">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="H74">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="I74" t="str">
-        <v>912.0</v>
+        <v>900.0</v>
       </c>
       <c r="J74" t="str">
         <v>100.00%</v>
@@ -3231,13 +3231,13 @@
         <v>30</v>
       </c>
       <c r="G75">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H75">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I75" t="str">
-        <v>1394.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J75" t="str">
         <v>100.00%</v>
@@ -3269,13 +3269,13 @@
         <v>50</v>
       </c>
       <c r="G76">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H76">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="I76" t="str">
-        <v>2281.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J76" t="str">
         <v>100.00%</v>
@@ -3310,10 +3310,10 @@
         <v>106</v>
       </c>
       <c r="H77">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I77" t="str">
-        <v>450.0</v>
+        <v>474.0</v>
       </c>
       <c r="J77" t="str">
         <v>100.00%</v>
@@ -3345,13 +3345,13 @@
         <v>25</v>
       </c>
       <c r="G78">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H78">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I78" t="str">
-        <v>1149.0</v>
+        <v>1161.0</v>
       </c>
       <c r="J78" t="str">
         <v>100.00%</v>
@@ -3383,13 +3383,13 @@
         <v>15</v>
       </c>
       <c r="G79">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H79">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="I79" t="str">
-        <v>702.0</v>
+        <v>687.0</v>
       </c>
       <c r="J79" t="str">
         <v>100.00%</v>
@@ -3421,13 +3421,13 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H80">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="I80" t="str">
-        <v>916.0</v>
+        <v>936.0</v>
       </c>
       <c r="J80" t="str">
         <v>100.00%</v>
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="G81">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H81">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I81" t="str">
-        <v>462.0</v>
+        <v>468.0</v>
       </c>
       <c r="J81" t="str">
         <v>100.00%</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="G82">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H82">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="I82" t="str">
-        <v>232.0</v>
+        <v>234.0</v>
       </c>
       <c r="J82" t="str">
         <v>100.00%</v>
@@ -3535,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="G83">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H83">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="I83" t="str">
-        <v>452.0</v>
+        <v>463.0</v>
       </c>
       <c r="J83" t="str">
         <v>100.00%</v>
@@ -3573,13 +3573,13 @@
         <v>20</v>
       </c>
       <c r="G84">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="H84">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I84" t="str">
-        <v>933.0</v>
+        <v>904.0</v>
       </c>
       <c r="J84" t="str">
         <v>100.00%</v>
@@ -3611,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="G85">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H85">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I85" t="str">
-        <v>1390.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J85" t="str">
         <v>100.00%</v>
@@ -3649,13 +3649,13 @@
         <v>50</v>
       </c>
       <c r="G86">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="H86">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I86" t="str">
-        <v>2277.0</v>
+        <v>2281.0</v>
       </c>
       <c r="J86" t="str">
         <v>100.00%</v>
@@ -3687,13 +3687,13 @@
         <v>10</v>
       </c>
       <c r="G87">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="H87">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I87" t="str">
-        <v>474.0</v>
+        <v>481.0</v>
       </c>
       <c r="J87" t="str">
         <v>100.00%</v>
@@ -3725,13 +3725,13 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="H88">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I88" t="str">
-        <v>1146.0</v>
+        <v>1140.0</v>
       </c>
       <c r="J88" t="str">
         <v>100.00%</v>
@@ -3763,13 +3763,13 @@
         <v>15</v>
       </c>
       <c r="G89">
+        <v>146</v>
+      </c>
+      <c r="H89">
         <v>150</v>
       </c>
-      <c r="H89">
-        <v>160</v>
-      </c>
       <c r="I89" t="str">
-        <v>680.0</v>
+        <v>700.0</v>
       </c>
       <c r="J89" t="str">
         <v>100.00%</v>
@@ -3801,13 +3801,13 @@
         <v>20</v>
       </c>
       <c r="G90">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H90">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="I90" t="str">
-        <v>943.0</v>
+        <v>913.0</v>
       </c>
       <c r="J90" t="str">
         <v>100.00%</v>
@@ -3839,13 +3839,13 @@
         <v>10</v>
       </c>
       <c r="G91">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H91">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I91" t="str">
-        <v>459.0</v>
+        <v>492.0</v>
       </c>
       <c r="J91" t="str">
         <v>100.00%</v>
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="G92">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H92">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="I92" t="str">
-        <v>273.0</v>
+        <v>244.0</v>
       </c>
       <c r="J92" t="str">
         <v>100.00%</v>
@@ -3915,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H93">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="I93" t="str">
-        <v>491.0</v>
+        <v>450.0</v>
       </c>
       <c r="J93" t="str">
         <v>100.00%</v>
@@ -3953,13 +3953,13 @@
         <v>20</v>
       </c>
       <c r="G94">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="H94">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="I94" t="str">
-        <v>943.0</v>
+        <v>922.0</v>
       </c>
       <c r="J94" t="str">
         <v>100.00%</v>
@@ -3991,13 +3991,13 @@
         <v>30</v>
       </c>
       <c r="G95">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="H95">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I95" t="str">
-        <v>1356.0</v>
+        <v>1360.0</v>
       </c>
       <c r="J95" t="str">
         <v>100.00%</v>
@@ -4029,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="G96">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="H96">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="I96" t="str">
-        <v>2265.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J96" t="str">
         <v>100.00%</v>
@@ -4067,13 +4067,13 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H97">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="I97" t="str">
-        <v>470.0</v>
+        <v>498.0</v>
       </c>
       <c r="J97" t="str">
         <v>100.00%</v>
@@ -4105,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="G98">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H98">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="I98" t="str">
-        <v>1125.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J98" t="str">
         <v>100.00%</v>
@@ -4143,13 +4143,13 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H99">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I99" t="str">
-        <v>675.0</v>
+        <v>679.0</v>
       </c>
       <c r="J99" t="str">
         <v>100.00%</v>
@@ -4181,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H100">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I100" t="str">
-        <v>909.0</v>
+        <v>905.0</v>
       </c>
       <c r="J100" t="str">
         <v>100.00%</v>
@@ -4222,10 +4222,10 @@
         <v>121</v>
       </c>
       <c r="H101">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I101" t="str">
-        <v>480.0</v>
+        <v>450.0</v>
       </c>
       <c r="J101" t="str">
         <v>100.00%</v>
@@ -4257,13 +4257,13 @@
         <v>5</v>
       </c>
       <c r="G102">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="H102">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="I102" t="str">
-        <v>258.0</v>
+        <v>242.0</v>
       </c>
       <c r="J102" t="str">
         <v>100.00%</v>
@@ -4295,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="H103">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="I103" t="str">
-        <v>498.0</v>
+        <v>471.0</v>
       </c>
       <c r="J103" t="str">
         <v>100.00%</v>
@@ -4333,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="G104">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H104">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="I104" t="str">
-        <v>901.0</v>
+        <v>918.0</v>
       </c>
       <c r="J104" t="str">
         <v>100.00%</v>
@@ -4371,13 +4371,13 @@
         <v>30</v>
       </c>
       <c r="G105">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="H105">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I105" t="str">
-        <v>1350.0</v>
+        <v>1356.0</v>
       </c>
       <c r="J105" t="str">
         <v>100.00%</v>
@@ -4409,13 +4409,13 @@
         <v>50</v>
       </c>
       <c r="G106">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="H106">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="I106" t="str">
-        <v>2254.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J106" t="str">
         <v>100.00%</v>
@@ -4447,10 +4447,10 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="H107">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="I107" t="str">
         <v>493.0</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="G108">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H108">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="I108" t="str">
-        <v>1150.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J108" t="str">
         <v>100.00%</v>
@@ -4523,13 +4523,13 @@
         <v>15</v>
       </c>
       <c r="G109">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H109">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I109" t="str">
-        <v>699.0</v>
+        <v>684.0</v>
       </c>
       <c r="J109" t="str">
         <v>100.00%</v>
@@ -4561,13 +4561,13 @@
         <v>20</v>
       </c>
       <c r="G110">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="H110">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="I110" t="str">
-        <v>933.0</v>
+        <v>943.0</v>
       </c>
       <c r="J110" t="str">
         <v>100.00%</v>
@@ -4599,13 +4599,13 @@
         <v>10</v>
       </c>
       <c r="G111">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="H111">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="I111" t="str">
-        <v>497.0</v>
+        <v>457.0</v>
       </c>
       <c r="J111" t="str">
         <v>100.00%</v>
@@ -4637,13 +4637,13 @@
         <v>5</v>
       </c>
       <c r="G112">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H112">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I112" t="str">
-        <v>230.0</v>
+        <v>250.0</v>
       </c>
       <c r="J112" t="str">
         <v>100.00%</v>
@@ -4675,13 +4675,13 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H113">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="I113" t="str">
-        <v>485.0</v>
+        <v>460.0</v>
       </c>
       <c r="J113" t="str">
         <v>100.00%</v>
@@ -4713,13 +4713,13 @@
         <v>20</v>
       </c>
       <c r="G114">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H114">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="I114" t="str">
-        <v>927.0</v>
+        <v>930.0</v>
       </c>
       <c r="J114" t="str">
         <v>100.00%</v>
@@ -4754,10 +4754,10 @@
         <v>211</v>
       </c>
       <c r="H115">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I115" t="str">
-        <v>1360.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J115" t="str">
         <v>100.00%</v>
@@ -4789,13 +4789,13 @@
         <v>50</v>
       </c>
       <c r="G116">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H116">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="I116" t="str">
-        <v>2268.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J116" t="str">
         <v>100.00%</v>
@@ -4827,13 +4827,13 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H117">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="I117" t="str">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="J117" t="str">
         <v>100.00%</v>
@@ -4865,13 +4865,13 @@
         <v>25</v>
       </c>
       <c r="G118">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="H118">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="I118" t="str">
-        <v>1173.0</v>
+        <v>1169.0</v>
       </c>
       <c r="J118" t="str">
         <v>100.00%</v>
@@ -4903,13 +4903,13 @@
         <v>15</v>
       </c>
       <c r="G119">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H119">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I119" t="str">
-        <v>716.0</v>
+        <v>690.0</v>
       </c>
       <c r="J119" t="str">
         <v>100.00%</v>
@@ -4941,13 +4941,13 @@
         <v>20</v>
       </c>
       <c r="G120">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H120">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I120" t="str">
-        <v>910.0</v>
+        <v>908.0</v>
       </c>
       <c r="J120" t="str">
         <v>100.00%</v>
@@ -4979,13 +4979,13 @@
         <v>10</v>
       </c>
       <c r="G121">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H121">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="I121" t="str">
-        <v>479.0</v>
+        <v>463.0</v>
       </c>
       <c r="J121" t="str">
         <v>100.00%</v>
@@ -5017,13 +5017,13 @@
         <v>5</v>
       </c>
       <c r="G122">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="H122">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="I122" t="str">
-        <v>240.0</v>
+        <v>247.0</v>
       </c>
       <c r="J122" t="str">
         <v>100.00%</v>
@@ -5055,13 +5055,13 @@
         <v>10</v>
       </c>
       <c r="G123">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="H123">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I123" t="str">
-        <v>466.0</v>
+        <v>494.0</v>
       </c>
       <c r="J123" t="str">
         <v>100.00%</v>
@@ -5093,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="G124">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H124">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="I124" t="str">
-        <v>944.0</v>
+        <v>928.0</v>
       </c>
       <c r="J124" t="str">
         <v>100.00%</v>
@@ -5131,13 +5131,13 @@
         <v>30</v>
       </c>
       <c r="G125">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H125">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="I125" t="str">
-        <v>1362.0</v>
+        <v>1366.0</v>
       </c>
       <c r="J125" t="str">
         <v>100.00%</v>
@@ -5169,13 +5169,13 @@
         <v>50</v>
       </c>
       <c r="G126">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H126">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="I126" t="str">
-        <v>2271.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J126" t="str">
         <v>100.00%</v>
@@ -5207,13 +5207,13 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H127">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I127" t="str">
-        <v>498.0</v>
+        <v>492.0</v>
       </c>
       <c r="J127" t="str">
         <v>100.00%</v>
@@ -5245,13 +5245,13 @@
         <v>25</v>
       </c>
       <c r="G128">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H128">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="I128" t="str">
-        <v>1162.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J128" t="str">
         <v>100.00%</v>
@@ -5283,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H129">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I129" t="str">
-        <v>697.0</v>
+        <v>717.0</v>
       </c>
       <c r="J129" t="str">
         <v>100.00%</v>
@@ -5321,13 +5321,13 @@
         <v>20</v>
       </c>
       <c r="G130">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H130">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I130" t="str">
-        <v>900.0</v>
+        <v>946.0</v>
       </c>
       <c r="J130" t="str">
         <v>100.00%</v>
@@ -5359,13 +5359,13 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H131">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="I131" t="str">
-        <v>469.0</v>
+        <v>462.0</v>
       </c>
       <c r="J131" t="str">
         <v>100.00%</v>
@@ -5397,13 +5397,13 @@
         <v>5</v>
       </c>
       <c r="G132">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H132">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="I132" t="str">
-        <v>254.0</v>
+        <v>245.0</v>
       </c>
       <c r="J132" t="str">
         <v>100.00%</v>
@@ -5435,13 +5435,13 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H133">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I133" t="str">
-        <v>480.0</v>
+        <v>462.0</v>
       </c>
       <c r="J133" t="str">
         <v>100.00%</v>
@@ -5473,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="G134">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H134">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I134" t="str">
-        <v>928.0</v>
+        <v>906.0</v>
       </c>
       <c r="J134" t="str">
         <v>100.00%</v>
@@ -5511,13 +5511,13 @@
         <v>30</v>
       </c>
       <c r="G135">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H135">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="I135" t="str">
-        <v>1395.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J135" t="str">
         <v>100.00%</v>
@@ -5549,13 +5549,13 @@
         <v>50</v>
       </c>
       <c r="G136">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H136">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="I136" t="str">
-        <v>2252.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J136" t="str">
         <v>100.00%</v>
@@ -5587,13 +5587,13 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="H137">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I137" t="str">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="J137" t="str">
         <v>100.00%</v>
@@ -5625,13 +5625,13 @@
         <v>25</v>
       </c>
       <c r="G138">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H138">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="I138" t="str">
-        <v>1132.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J138" t="str">
         <v>100.00%</v>
@@ -5663,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H139">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I139" t="str">
-        <v>713.0</v>
+        <v>717.0</v>
       </c>
       <c r="J139" t="str">
         <v>100.00%</v>
@@ -5701,13 +5701,13 @@
         <v>20</v>
       </c>
       <c r="G140">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H140">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="I140" t="str">
-        <v>911.0</v>
+        <v>921.0</v>
       </c>
       <c r="J140" t="str">
         <v>100.00%</v>
@@ -5739,13 +5739,13 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H141">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="I141" t="str">
-        <v>499.0</v>
+        <v>473.0</v>
       </c>
       <c r="J141" t="str">
         <v>100.00%</v>
@@ -5780,10 +5780,10 @@
         <v>95</v>
       </c>
       <c r="H142">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I142" t="str">
-        <v>258.0</v>
+        <v>266.0</v>
       </c>
       <c r="J142" t="str">
         <v>100.00%</v>
@@ -5815,13 +5815,13 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H143">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="I143" t="str">
-        <v>461.0</v>
+        <v>490.0</v>
       </c>
       <c r="J143" t="str">
         <v>100.00%</v>
@@ -5853,13 +5853,13 @@
         <v>20</v>
       </c>
       <c r="G144">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="H144">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="I144" t="str">
-        <v>925.0</v>
+        <v>921.0</v>
       </c>
       <c r="J144" t="str">
         <v>100.00%</v>
@@ -5891,13 +5891,13 @@
         <v>30</v>
       </c>
       <c r="G145">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="H145">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I145" t="str">
-        <v>1365.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J145" t="str">
         <v>100.00%</v>
@@ -5929,13 +5929,13 @@
         <v>50</v>
       </c>
       <c r="G146">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H146">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I146" t="str">
-        <v>2255.0</v>
+        <v>2286.0</v>
       </c>
       <c r="J146" t="str">
         <v>100.00%</v>
@@ -5967,13 +5967,13 @@
         <v>10</v>
       </c>
       <c r="G147">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H147">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I147" t="str">
-        <v>498.0</v>
+        <v>487.0</v>
       </c>
       <c r="J147" t="str">
         <v>100.00%</v>
@@ -6005,13 +6005,13 @@
         <v>25</v>
       </c>
       <c r="G148">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="H148">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="I148" t="str">
-        <v>1152.0</v>
+        <v>1150.0</v>
       </c>
       <c r="J148" t="str">
         <v>100.00%</v>
@@ -6043,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H149">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="I149" t="str">
-        <v>724.0</v>
+        <v>698.0</v>
       </c>
       <c r="J149" t="str">
         <v>100.00%</v>
@@ -6081,13 +6081,13 @@
         <v>20</v>
       </c>
       <c r="G150">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H150">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="I150" t="str">
-        <v>946.0</v>
+        <v>901.0</v>
       </c>
       <c r="J150" t="str">
         <v>100.00%</v>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H151">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I151" t="str">
-        <v>479.0</v>
+        <v>487.0</v>
       </c>
       <c r="J151" t="str">
         <v>100.00%</v>
@@ -6157,13 +6157,13 @@
         <v>5</v>
       </c>
       <c r="G152">
+        <v>101</v>
+      </c>
+      <c r="H152">
         <v>107</v>
       </c>
-      <c r="H152">
-        <v>109</v>
-      </c>
       <c r="I152" t="str">
-        <v>229.0</v>
+        <v>236.0</v>
       </c>
       <c r="J152" t="str">
         <v>100.00%</v>
@@ -6195,13 +6195,13 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H153">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I153" t="str">
-        <v>491.0</v>
+        <v>486.0</v>
       </c>
       <c r="J153" t="str">
         <v>100.00%</v>
@@ -6233,13 +6233,13 @@
         <v>20</v>
       </c>
       <c r="G154">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H154">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="I154" t="str">
-        <v>944.0</v>
+        <v>946.0</v>
       </c>
       <c r="J154" t="str">
         <v>100.00%</v>
@@ -6271,13 +6271,13 @@
         <v>30</v>
       </c>
       <c r="G155">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H155">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I155" t="str">
-        <v>1381.0</v>
+        <v>1374.0</v>
       </c>
       <c r="J155" t="str">
         <v>100.00%</v>
@@ -6309,13 +6309,13 @@
         <v>50</v>
       </c>
       <c r="G156">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H156">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="I156" t="str">
-        <v>2288.0</v>
+        <v>2270.0</v>
       </c>
       <c r="J156" t="str">
         <v>100.00%</v>
@@ -6347,13 +6347,13 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="H157">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="I157" t="str">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="J157" t="str">
         <v>100.00%</v>
@@ -6385,13 +6385,13 @@
         <v>25</v>
       </c>
       <c r="G158">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H158">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="I158" t="str">
-        <v>1173.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J158" t="str">
         <v>100.00%</v>
@@ -6423,13 +6423,13 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="H159">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="I159" t="str">
-        <v>712.0</v>
+        <v>681.0</v>
       </c>
       <c r="J159" t="str">
         <v>100.00%</v>
@@ -6461,13 +6461,13 @@
         <v>20</v>
       </c>
       <c r="G160">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="H160">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="I160" t="str">
-        <v>943.0</v>
+        <v>907.0</v>
       </c>
       <c r="J160" t="str">
         <v>100.00%</v>
@@ -6499,13 +6499,13 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H161">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="I161" t="str">
-        <v>471.0</v>
+        <v>463.0</v>
       </c>
       <c r="J161" t="str">
         <v>100.00%</v>
@@ -6537,13 +6537,13 @@
         <v>5</v>
       </c>
       <c r="G162">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H162">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="I162" t="str">
-        <v>255.0</v>
+        <v>254.0</v>
       </c>
       <c r="J162" t="str">
         <v>100.00%</v>
@@ -6575,13 +6575,13 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H163">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I163" t="str">
-        <v>452.0</v>
+        <v>474.0</v>
       </c>
       <c r="J163" t="str">
         <v>100.00%</v>
@@ -6613,13 +6613,13 @@
         <v>20</v>
       </c>
       <c r="G164">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H164">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="I164" t="str">
-        <v>940.0</v>
+        <v>912.0</v>
       </c>
       <c r="J164" t="str">
         <v>100.00%</v>
@@ -6654,10 +6654,10 @@
         <v>208</v>
       </c>
       <c r="H165">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="I165" t="str">
-        <v>1362.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J165" t="str">
         <v>100.00%</v>
@@ -6689,13 +6689,13 @@
         <v>50</v>
       </c>
       <c r="G166">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="H166">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I166" t="str">
-        <v>2253.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J166" t="str">
         <v>100.00%</v>
@@ -6727,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H167">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I167" t="str">
-        <v>485.0</v>
+        <v>469.0</v>
       </c>
       <c r="J167" t="str">
         <v>100.00%</v>
@@ -6765,13 +6765,13 @@
         <v>25</v>
       </c>
       <c r="G168">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="H168">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I168" t="str">
-        <v>1159.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J168" t="str">
         <v>100.00%</v>
@@ -6803,13 +6803,13 @@
         <v>15</v>
       </c>
       <c r="G169">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H169">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I169" t="str">
-        <v>679.0</v>
+        <v>703.0</v>
       </c>
       <c r="J169" t="str">
         <v>100.00%</v>
@@ -6841,13 +6841,13 @@
         <v>20</v>
       </c>
       <c r="G170">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H170">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="I170" t="str">
-        <v>943.0</v>
+        <v>947.0</v>
       </c>
       <c r="J170" t="str">
         <v>100.00%</v>
@@ -6879,13 +6879,13 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H171">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I171" t="str">
-        <v>490.0</v>
+        <v>470.0</v>
       </c>
       <c r="J171" t="str">
         <v>100.00%</v>
@@ -6917,13 +6917,13 @@
         <v>5</v>
       </c>
       <c r="G172">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H172">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I172" t="str">
-        <v>239.0</v>
+        <v>226.0</v>
       </c>
       <c r="J172" t="str">
         <v>100.00%</v>
@@ -6955,13 +6955,13 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H173">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="I173" t="str">
-        <v>483.0</v>
+        <v>481.0</v>
       </c>
       <c r="J173" t="str">
         <v>100.00%</v>
@@ -6993,13 +6993,13 @@
         <v>20</v>
       </c>
       <c r="G174">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H174">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="I174" t="str">
-        <v>937.0</v>
+        <v>923.0</v>
       </c>
       <c r="J174" t="str">
         <v>100.00%</v>
@@ -7031,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="G175">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H175">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="I175" t="str">
-        <v>1360.0</v>
+        <v>1359.0</v>
       </c>
       <c r="J175" t="str">
         <v>100.00%</v>
@@ -7072,10 +7072,10 @@
         <v>250</v>
       </c>
       <c r="H176">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I176" t="str">
-        <v>2299.0</v>
+        <v>2287.0</v>
       </c>
       <c r="J176" t="str">
         <v>100.00%</v>
@@ -7107,13 +7107,13 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H177">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I177" t="str">
-        <v>452.0</v>
+        <v>484.0</v>
       </c>
       <c r="J177" t="str">
         <v>100.00%</v>
@@ -7145,13 +7145,13 @@
         <v>25</v>
       </c>
       <c r="G178">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H178">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="I178" t="str">
-        <v>1163.0</v>
+        <v>1126.0</v>
       </c>
       <c r="J178" t="str">
         <v>100.00%</v>
@@ -7183,13 +7183,13 @@
         <v>15</v>
       </c>
       <c r="G179">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="H179">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="I179" t="str">
-        <v>683.0</v>
+        <v>675.0</v>
       </c>
       <c r="J179" t="str">
         <v>100.00%</v>
@@ -7221,13 +7221,13 @@
         <v>20</v>
       </c>
       <c r="G180">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H180">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I180" t="str">
-        <v>934.0</v>
+        <v>913.0</v>
       </c>
       <c r="J180" t="str">
         <v>100.00%</v>
@@ -7259,13 +7259,13 @@
         <v>10</v>
       </c>
       <c r="G181">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H181">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="I181" t="str">
-        <v>489.0</v>
+        <v>457.0</v>
       </c>
       <c r="J181" t="str">
         <v>100.00%</v>
@@ -7297,13 +7297,13 @@
         <v>5</v>
       </c>
       <c r="G182">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="H182">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="I182" t="str">
-        <v>265.0</v>
+        <v>262.0</v>
       </c>
       <c r="J182" t="str">
         <v>100.00%</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H183">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I183" t="str">
-        <v>459.0</v>
+        <v>452.0</v>
       </c>
       <c r="J183" t="str">
         <v>100.00%</v>
@@ -7373,13 +7373,13 @@
         <v>20</v>
       </c>
       <c r="G184">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H184">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I184" t="str">
-        <v>949.0</v>
+        <v>937.0</v>
       </c>
       <c r="J184" t="str">
         <v>100.00%</v>
@@ -7411,13 +7411,13 @@
         <v>30</v>
       </c>
       <c r="G185">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H185">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="I185" t="str">
-        <v>1370.0</v>
+        <v>1364.0</v>
       </c>
       <c r="J185" t="str">
         <v>100.00%</v>
@@ -7452,10 +7452,10 @@
         <v>243</v>
       </c>
       <c r="H186">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I186" t="str">
-        <v>2283.0</v>
+        <v>2263.0</v>
       </c>
       <c r="J186" t="str">
         <v>100.00%</v>
@@ -7487,13 +7487,13 @@
         <v>10</v>
       </c>
       <c r="G187">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H187">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I187" t="str">
-        <v>475.0</v>
+        <v>455.0</v>
       </c>
       <c r="J187" t="str">
         <v>100.00%</v>
@@ -7528,10 +7528,10 @@
         <v>168</v>
       </c>
       <c r="H188">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="I188" t="str">
-        <v>1134.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J188" t="str">
         <v>100.00%</v>
@@ -7563,13 +7563,13 @@
         <v>15</v>
       </c>
       <c r="G189">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="H189">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="I189" t="str">
-        <v>691.0</v>
+        <v>712.0</v>
       </c>
       <c r="J189" t="str">
         <v>100.00%</v>
@@ -7601,13 +7601,13 @@
         <v>20</v>
       </c>
       <c r="G190">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H190">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="I190" t="str">
-        <v>916.0</v>
+        <v>934.0</v>
       </c>
       <c r="J190" t="str">
         <v>100.00%</v>
@@ -7639,13 +7639,13 @@
         <v>10</v>
       </c>
       <c r="G191">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H191">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I191" t="str">
-        <v>457.0</v>
+        <v>498.0</v>
       </c>
       <c r="J191" t="str">
         <v>100.00%</v>
@@ -7677,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="G192">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H192">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I192" t="str">
-        <v>269.0</v>
+        <v>254.0</v>
       </c>
       <c r="J192" t="str">
         <v>100.00%</v>
@@ -7715,13 +7715,13 @@
         <v>10</v>
       </c>
       <c r="G193">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H193">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="I193" t="str">
-        <v>454.0</v>
+        <v>456.0</v>
       </c>
       <c r="J193" t="str">
         <v>100.00%</v>
@@ -7753,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="G194">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H194">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="I194" t="str">
-        <v>901.0</v>
+        <v>903.0</v>
       </c>
       <c r="J194" t="str">
         <v>100.00%</v>
@@ -7791,13 +7791,13 @@
         <v>30</v>
       </c>
       <c r="G195">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H195">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="I195" t="str">
-        <v>1376.0</v>
+        <v>1388.0</v>
       </c>
       <c r="J195" t="str">
         <v>100.00%</v>
@@ -7829,13 +7829,13 @@
         <v>50</v>
       </c>
       <c r="G196">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="H196">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="I196" t="str">
-        <v>2294.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J196" t="str">
         <v>100.00%</v>
@@ -7867,13 +7867,13 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H197">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I197" t="str">
-        <v>494.0</v>
+        <v>474.0</v>
       </c>
       <c r="J197" t="str">
         <v>100.00%</v>
@@ -7905,13 +7905,13 @@
         <v>25</v>
       </c>
       <c r="G198">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H198">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I198" t="str">
-        <v>1153.0</v>
+        <v>1164.0</v>
       </c>
       <c r="J198" t="str">
         <v>100.00%</v>
@@ -7943,13 +7943,13 @@
         <v>15</v>
       </c>
       <c r="G199">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="H199">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="I199" t="str">
-        <v>687.0</v>
+        <v>718.0</v>
       </c>
       <c r="J199" t="str">
         <v>100.00%</v>
@@ -7981,13 +7981,13 @@
         <v>20</v>
       </c>
       <c r="G200">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H200">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I200" t="str">
-        <v>942.0</v>
+        <v>929.0</v>
       </c>
       <c r="J200" t="str">
         <v>100.00%</v>
@@ -8019,13 +8019,13 @@
         <v>10</v>
       </c>
       <c r="G201">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H201">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="I201" t="str">
-        <v>474.0</v>
+        <v>464.0</v>
       </c>
       <c r="J201" t="str">
         <v>100.00%</v>
@@ -8057,13 +8057,13 @@
         <v>5</v>
       </c>
       <c r="G202">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H202">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="I202" t="str">
-        <v>231.0</v>
+        <v>250.0</v>
       </c>
       <c r="J202" t="str">
         <v>100.00%</v>
@@ -8095,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="G203">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="H203">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="I203" t="str">
-        <v>459.0</v>
+        <v>466.0</v>
       </c>
       <c r="J203" t="str">
         <v>100.00%</v>
@@ -8133,13 +8133,13 @@
         <v>20</v>
       </c>
       <c r="G204">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H204">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="I204" t="str">
-        <v>925.0</v>
+        <v>911.0</v>
       </c>
       <c r="J204" t="str">
         <v>100.00%</v>
@@ -8171,13 +8171,13 @@
         <v>30</v>
       </c>
       <c r="G205">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="H205">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I205" t="str">
-        <v>1367.0</v>
+        <v>1397.0</v>
       </c>
       <c r="J205" t="str">
         <v>100.00%</v>
@@ -8209,13 +8209,13 @@
         <v>50</v>
       </c>
       <c r="G206">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H206">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="I206" t="str">
-        <v>2266.0</v>
+        <v>2298.0</v>
       </c>
       <c r="J206" t="str">
         <v>100.00%</v>
@@ -8247,13 +8247,13 @@
         <v>10</v>
       </c>
       <c r="G207">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H207">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I207" t="str">
-        <v>481.0</v>
+        <v>453.0</v>
       </c>
       <c r="J207" t="str">
         <v>100.00%</v>
@@ -8285,13 +8285,13 @@
         <v>25</v>
       </c>
       <c r="G208">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H208">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I208" t="str">
-        <v>1136.0</v>
+        <v>1158.0</v>
       </c>
       <c r="J208" t="str">
         <v>100.00%</v>
@@ -8323,13 +8323,13 @@
         <v>15</v>
       </c>
       <c r="G209">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H209">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="I209" t="str">
-        <v>684.0</v>
+        <v>679.0</v>
       </c>
       <c r="J209" t="str">
         <v>100.00%</v>
@@ -8361,10 +8361,10 @@
         <v>20</v>
       </c>
       <c r="G210">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H210">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="I210" t="str">
         <v>943.0</v>
@@ -8399,13 +8399,13 @@
         <v>10</v>
       </c>
       <c r="G211">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="H211">
         <v>153</v>
       </c>
       <c r="I211" t="str">
-        <v>474.0</v>
+        <v>491.0</v>
       </c>
       <c r="J211" t="str">
         <v>100.00%</v>
@@ -8437,13 +8437,13 @@
         <v>5</v>
       </c>
       <c r="G212">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H212">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="I212" t="str">
-        <v>228.0</v>
+        <v>226.0</v>
       </c>
       <c r="J212" t="str">
         <v>100.00%</v>
@@ -8475,13 +8475,13 @@
         <v>10</v>
       </c>
       <c r="G213">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="H213">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I213" t="str">
-        <v>472.0</v>
+        <v>497.0</v>
       </c>
       <c r="J213" t="str">
         <v>100.00%</v>
@@ -8513,10 +8513,10 @@
         <v>20</v>
       </c>
       <c r="G214">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H214">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="I214" t="str">
         <v>926.0</v>
@@ -8551,13 +8551,13 @@
         <v>30</v>
       </c>
       <c r="G215">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H215">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I215" t="str">
-        <v>1385.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J215" t="str">
         <v>100.00%</v>
@@ -8592,10 +8592,10 @@
         <v>249</v>
       </c>
       <c r="H216">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="I216" t="str">
-        <v>2278.0</v>
+        <v>2267.0</v>
       </c>
       <c r="J216" t="str">
         <v>100.00%</v>
@@ -8627,13 +8627,13 @@
         <v>10</v>
       </c>
       <c r="G217">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H217">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="I217" t="str">
-        <v>483.0</v>
+        <v>492.0</v>
       </c>
       <c r="J217" t="str">
         <v>100.00%</v>
@@ -8665,13 +8665,13 @@
         <v>25</v>
       </c>
       <c r="G218">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="H218">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="I218" t="str">
-        <v>1155.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J218" t="str">
         <v>100.00%</v>
@@ -8706,10 +8706,10 @@
         <v>130</v>
       </c>
       <c r="H219">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I219" t="str">
-        <v>675.0</v>
+        <v>683.0</v>
       </c>
       <c r="J219" t="str">
         <v>100.00%</v>
@@ -8741,13 +8741,13 @@
         <v>20</v>
       </c>
       <c r="G220">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H220">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I220" t="str">
-        <v>908.0</v>
+        <v>919.0</v>
       </c>
       <c r="J220" t="str">
         <v>100.00%</v>
@@ -8779,13 +8779,13 @@
         <v>10</v>
       </c>
       <c r="G221">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H221">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="I221" t="str">
-        <v>478.0</v>
+        <v>495.0</v>
       </c>
       <c r="J221" t="str">
         <v>100.00%</v>
@@ -8817,13 +8817,13 @@
         <v>5</v>
       </c>
       <c r="G222">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="H222">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="I222" t="str">
-        <v>261.0</v>
+        <v>252.0</v>
       </c>
       <c r="J222" t="str">
         <v>100.00%</v>
@@ -8855,13 +8855,13 @@
         <v>10</v>
       </c>
       <c r="G223">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="H223">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="I223" t="str">
-        <v>462.0</v>
+        <v>469.0</v>
       </c>
       <c r="J223" t="str">
         <v>100.00%</v>
@@ -8893,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="G224">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H224">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="I224" t="str">
-        <v>927.0</v>
+        <v>911.0</v>
       </c>
       <c r="J224" t="str">
         <v>100.00%</v>
@@ -8931,13 +8931,13 @@
         <v>30</v>
       </c>
       <c r="G225">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="H225">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="I225" t="str">
-        <v>1364.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J225" t="str">
         <v>100.00%</v>
@@ -8969,13 +8969,13 @@
         <v>50</v>
       </c>
       <c r="G226">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="H226">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I226" t="str">
-        <v>2285.0</v>
+        <v>2264.0</v>
       </c>
       <c r="J226" t="str">
         <v>100.00%</v>
@@ -9007,13 +9007,13 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H227">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I227" t="str">
-        <v>458.0</v>
+        <v>471.0</v>
       </c>
       <c r="J227" t="str">
         <v>100.00%</v>
@@ -9045,13 +9045,13 @@
         <v>25</v>
       </c>
       <c r="G228">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H228">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="I228" t="str">
-        <v>1164.0</v>
+        <v>1156.0</v>
       </c>
       <c r="J228" t="str">
         <v>100.00%</v>
@@ -9083,13 +9083,13 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H229">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I229" t="str">
-        <v>675.0</v>
+        <v>717.0</v>
       </c>
       <c r="J229" t="str">
         <v>100.00%</v>
@@ -9121,13 +9121,13 @@
         <v>20</v>
       </c>
       <c r="G230">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H230">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="I230" t="str">
-        <v>911.0</v>
+        <v>930.0</v>
       </c>
       <c r="J230" t="str">
         <v>100.00%</v>
@@ -9159,13 +9159,13 @@
         <v>10</v>
       </c>
       <c r="G231">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="H231">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="I231" t="str">
-        <v>456.0</v>
+        <v>487.0</v>
       </c>
       <c r="J231" t="str">
         <v>100.00%</v>
@@ -9197,13 +9197,13 @@
         <v>5</v>
       </c>
       <c r="G232">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H232">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I232" t="str">
-        <v>270.0</v>
+        <v>254.0</v>
       </c>
       <c r="J232" t="str">
         <v>100.00%</v>
@@ -9235,13 +9235,13 @@
         <v>10</v>
       </c>
       <c r="G233">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H233">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I233" t="str">
-        <v>467.0</v>
+        <v>471.0</v>
       </c>
       <c r="J233" t="str">
         <v>100.00%</v>
@@ -9273,13 +9273,13 @@
         <v>20</v>
       </c>
       <c r="G234">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H234">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I234" t="str">
-        <v>931.0</v>
+        <v>914.0</v>
       </c>
       <c r="J234" t="str">
         <v>100.00%</v>
@@ -9311,13 +9311,13 @@
         <v>30</v>
       </c>
       <c r="G235">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="H235">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="I235" t="str">
-        <v>1397.0</v>
+        <v>1396.0</v>
       </c>
       <c r="J235" t="str">
         <v>100.00%</v>
@@ -9349,13 +9349,13 @@
         <v>50</v>
       </c>
       <c r="G236">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H236">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I236" t="str">
-        <v>2254.0</v>
+        <v>2268.0</v>
       </c>
       <c r="J236" t="str">
         <v>100.00%</v>
@@ -9387,13 +9387,13 @@
         <v>10</v>
       </c>
       <c r="G237">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="H237">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="I237" t="str">
-        <v>455.0</v>
+        <v>460.0</v>
       </c>
       <c r="J237" t="str">
         <v>100.00%</v>
@@ -9425,13 +9425,13 @@
         <v>25</v>
       </c>
       <c r="G238">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="H238">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I238" t="str">
-        <v>1144.0</v>
+        <v>1155.0</v>
       </c>
       <c r="J238" t="str">
         <v>100.00%</v>
@@ -9463,10 +9463,10 @@
         <v>15</v>
       </c>
       <c r="G239">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H239">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="I239" t="str">
         <v>677.0</v>
@@ -9501,13 +9501,13 @@
         <v>20</v>
       </c>
       <c r="G240">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H240">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I240" t="str">
-        <v>914.0</v>
+        <v>934.0</v>
       </c>
       <c r="J240" t="str">
         <v>100.00%</v>
@@ -9539,13 +9539,13 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="H241">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="I241" t="str">
-        <v>455.0</v>
+        <v>491.0</v>
       </c>
       <c r="J241" t="str">
         <v>100.00%</v>
@@ -9577,13 +9577,13 @@
         <v>5</v>
       </c>
       <c r="G242">
+        <v>92</v>
+      </c>
+      <c r="H242">
         <v>96</v>
       </c>
-      <c r="H242">
-        <v>118</v>
-      </c>
       <c r="I242" t="str">
-        <v>260.0</v>
+        <v>235.0</v>
       </c>
       <c r="J242" t="str">
         <v>100.00%</v>
@@ -9615,13 +9615,13 @@
         <v>10</v>
       </c>
       <c r="G243">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H243">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="I243" t="str">
-        <v>454.0</v>
+        <v>461.0</v>
       </c>
       <c r="J243" t="str">
         <v>100.00%</v>
@@ -9653,13 +9653,13 @@
         <v>20</v>
       </c>
       <c r="G244">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H244">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="I244" t="str">
-        <v>940.0</v>
+        <v>948.0</v>
       </c>
       <c r="J244" t="str">
         <v>100.00%</v>
@@ -9691,13 +9691,13 @@
         <v>30</v>
       </c>
       <c r="G245">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H245">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="I245" t="str">
-        <v>1382.0</v>
+        <v>1378.0</v>
       </c>
       <c r="J245" t="str">
         <v>100.00%</v>
@@ -9729,13 +9729,13 @@
         <v>50</v>
       </c>
       <c r="G246">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H246">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="I246" t="str">
-        <v>2278.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J246" t="str">
         <v>100.00%</v>
@@ -9767,13 +9767,13 @@
         <v>10</v>
       </c>
       <c r="G247">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H247">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I247" t="str">
-        <v>459.0</v>
+        <v>467.0</v>
       </c>
       <c r="J247" t="str">
         <v>100.00%</v>
@@ -9805,13 +9805,13 @@
         <v>25</v>
       </c>
       <c r="G248">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H248">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="I248" t="str">
-        <v>1138.0</v>
+        <v>1168.0</v>
       </c>
       <c r="J248" t="str">
         <v>100.00%</v>
@@ -9843,13 +9843,13 @@
         <v>15</v>
       </c>
       <c r="G249">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H249">
         <v>157</v>
       </c>
       <c r="I249" t="str">
-        <v>677.0</v>
+        <v>719.0</v>
       </c>
       <c r="J249" t="str">
         <v>100.00%</v>
@@ -9884,10 +9884,10 @@
         <v>99</v>
       </c>
       <c r="H250">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I250" t="str">
-        <v>928.0</v>
+        <v>906.0</v>
       </c>
       <c r="J250" t="str">
         <v>100.00%</v>
@@ -9919,13 +9919,13 @@
         <v>10</v>
       </c>
       <c r="G251">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H251">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="I251" t="str">
-        <v>453.0</v>
+        <v>462.0</v>
       </c>
       <c r="J251" t="str">
         <v>100.00%</v>
@@ -9957,13 +9957,13 @@
         <v>5</v>
       </c>
       <c r="G252">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H252">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="I252" t="str">
-        <v>272.0</v>
+        <v>264.0</v>
       </c>
       <c r="J252" t="str">
         <v>100.00%</v>
@@ -9995,13 +9995,13 @@
         <v>10</v>
       </c>
       <c r="G253">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H253">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I253" t="str">
-        <v>452.0</v>
+        <v>483.0</v>
       </c>
       <c r="J253" t="str">
         <v>100.00%</v>
@@ -10033,13 +10033,13 @@
         <v>20</v>
       </c>
       <c r="G254">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="H254">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I254" t="str">
-        <v>937.0</v>
+        <v>923.0</v>
       </c>
       <c r="J254" t="str">
         <v>100.00%</v>
@@ -10071,13 +10071,13 @@
         <v>30</v>
       </c>
       <c r="G255">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H255">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="I255" t="str">
-        <v>1361.0</v>
+        <v>1368.0</v>
       </c>
       <c r="J255" t="str">
         <v>100.00%</v>
@@ -10109,13 +10109,13 @@
         <v>50</v>
       </c>
       <c r="G256">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H256">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I256" t="str">
-        <v>2255.0</v>
+        <v>2282.0</v>
       </c>
       <c r="J256" t="str">
         <v>100.00%</v>
@@ -10147,13 +10147,13 @@
         <v>10</v>
       </c>
       <c r="G257">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H257">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="I257" t="str">
-        <v>460.0</v>
+        <v>469.0</v>
       </c>
       <c r="J257" t="str">
         <v>100.00%</v>
@@ -10188,10 +10188,10 @@
         <v>180</v>
       </c>
       <c r="H258">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I258" t="str">
-        <v>1133.0</v>
+        <v>1132.0</v>
       </c>
       <c r="J258" t="str">
         <v>100.00%</v>
@@ -10223,13 +10223,13 @@
         <v>15</v>
       </c>
       <c r="G259">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H259">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="I259" t="str">
-        <v>680.0</v>
+        <v>715.0</v>
       </c>
       <c r="J259" t="str">
         <v>100.00%</v>
@@ -10261,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="G260">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H260">
         <v>138</v>
       </c>
       <c r="I260" t="str">
-        <v>901.0</v>
+        <v>903.0</v>
       </c>
       <c r="J260" t="str">
         <v>100.00%</v>
@@ -10299,13 +10299,13 @@
         <v>10</v>
       </c>
       <c r="G261">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="H261">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="I261" t="str">
-        <v>471.0</v>
+        <v>453.0</v>
       </c>
       <c r="J261" t="str">
         <v>100.00%</v>
@@ -10337,13 +10337,13 @@
         <v>5</v>
       </c>
       <c r="G262">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="H262">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I262" t="str">
-        <v>255.0</v>
+        <v>267.0</v>
       </c>
       <c r="J262" t="str">
         <v>100.00%</v>
@@ -10375,13 +10375,13 @@
         <v>10</v>
       </c>
       <c r="G263">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H263">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I263" t="str">
-        <v>460.0</v>
+        <v>491.0</v>
       </c>
       <c r="J263" t="str">
         <v>100.00%</v>
@@ -10413,13 +10413,13 @@
         <v>20</v>
       </c>
       <c r="G264">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H264">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I264" t="str">
-        <v>933.0</v>
+        <v>917.0</v>
       </c>
       <c r="J264" t="str">
         <v>100.00%</v>
@@ -10451,13 +10451,13 @@
         <v>30</v>
       </c>
       <c r="G265">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="H265">
         <v>220</v>
       </c>
       <c r="I265" t="str">
-        <v>1360.0</v>
+        <v>1370.0</v>
       </c>
       <c r="J265" t="str">
         <v>100.00%</v>
@@ -10492,10 +10492,10 @@
         <v>244</v>
       </c>
       <c r="H266">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I266" t="str">
-        <v>2296.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J266" t="str">
         <v>100.00%</v>
@@ -10527,13 +10527,13 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="H267">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="I267" t="str">
-        <v>494.0</v>
+        <v>458.0</v>
       </c>
       <c r="J267" t="str">
         <v>100.00%</v>
@@ -10565,13 +10565,13 @@
         <v>25</v>
       </c>
       <c r="G268">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="H268">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="I268" t="str">
-        <v>1130.0</v>
+        <v>1162.0</v>
       </c>
       <c r="J268" t="str">
         <v>100.00%</v>
@@ -10603,13 +10603,13 @@
         <v>15</v>
       </c>
       <c r="G269">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H269">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="I269" t="str">
-        <v>681.0</v>
+        <v>677.0</v>
       </c>
       <c r="J269" t="str">
         <v>100.00%</v>
@@ -10644,10 +10644,10 @@
         <v>104</v>
       </c>
       <c r="H270">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="I270" t="str">
-        <v>933.0</v>
+        <v>906.0</v>
       </c>
       <c r="J270" t="str">
         <v>100.00%</v>
@@ -10679,13 +10679,13 @@
         <v>10</v>
       </c>
       <c r="G271">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H271">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I271" t="str">
-        <v>499.0</v>
+        <v>456.0</v>
       </c>
       <c r="J271" t="str">
         <v>100.00%</v>
@@ -10717,13 +10717,13 @@
         <v>5</v>
       </c>
       <c r="G272">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H272">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I272" t="str">
-        <v>262.0</v>
+        <v>241.0</v>
       </c>
       <c r="J272" t="str">
         <v>100.00%</v>
@@ -10755,13 +10755,13 @@
         <v>10</v>
       </c>
       <c r="G273">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H273">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="I273" t="str">
-        <v>488.0</v>
+        <v>483.0</v>
       </c>
       <c r="J273" t="str">
         <v>100.00%</v>
@@ -10793,13 +10793,13 @@
         <v>20</v>
       </c>
       <c r="G274">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="H274">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I274" t="str">
-        <v>912.0</v>
+        <v>934.0</v>
       </c>
       <c r="J274" t="str">
         <v>100.00%</v>
@@ -10831,13 +10831,13 @@
         <v>30</v>
       </c>
       <c r="G275">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="H275">
-        <v>199</v>
+        <v>244</v>
       </c>
       <c r="I275" t="str">
-        <v>1350.0</v>
+        <v>1367.0</v>
       </c>
       <c r="J275" t="str">
         <v>100.00%</v>
@@ -10869,13 +10869,13 @@
         <v>50</v>
       </c>
       <c r="G276">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="H276">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I276" t="str">
-        <v>2278.0</v>
+        <v>2288.0</v>
       </c>
       <c r="J276" t="str">
         <v>100.00%</v>
@@ -10907,13 +10907,13 @@
         <v>10</v>
       </c>
       <c r="G277">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H277">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I277" t="str">
-        <v>485.0</v>
+        <v>469.0</v>
       </c>
       <c r="J277" t="str">
         <v>100.00%</v>
@@ -10945,13 +10945,13 @@
         <v>25</v>
       </c>
       <c r="G278">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H278">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="I278" t="str">
-        <v>1174.0</v>
+        <v>1133.0</v>
       </c>
       <c r="J278" t="str">
         <v>100.00%</v>
@@ -10983,13 +10983,13 @@
         <v>15</v>
       </c>
       <c r="G279">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="H279">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I279" t="str">
-        <v>720.0</v>
+        <v>700.0</v>
       </c>
       <c r="J279" t="str">
         <v>100.00%</v>
@@ -11021,13 +11021,13 @@
         <v>20</v>
       </c>
       <c r="G280">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H280">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="I280" t="str">
-        <v>948.0</v>
+        <v>918.0</v>
       </c>
       <c r="J280" t="str">
         <v>100.00%</v>
@@ -11059,13 +11059,13 @@
         <v>10</v>
       </c>
       <c r="G281">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H281">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="I281" t="str">
-        <v>474.0</v>
+        <v>485.0</v>
       </c>
       <c r="J281" t="str">
         <v>100.00%</v>
@@ -11097,13 +11097,13 @@
         <v>5</v>
       </c>
       <c r="G282">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H282">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="I282" t="str">
-        <v>232.0</v>
+        <v>243.0</v>
       </c>
       <c r="J282" t="str">
         <v>100.00%</v>
@@ -11135,13 +11135,13 @@
         <v>10</v>
       </c>
       <c r="G283">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H283">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I283" t="str">
-        <v>475.0</v>
+        <v>480.0</v>
       </c>
       <c r="J283" t="str">
         <v>100.00%</v>
@@ -11173,13 +11173,13 @@
         <v>20</v>
       </c>
       <c r="G284">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H284">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="I284" t="str">
-        <v>927.0</v>
+        <v>936.0</v>
       </c>
       <c r="J284" t="str">
         <v>100.00%</v>
@@ -11211,13 +11211,13 @@
         <v>30</v>
       </c>
       <c r="G285">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="H285">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="I285" t="str">
-        <v>1386.0</v>
+        <v>1351.0</v>
       </c>
       <c r="J285" t="str">
         <v>100.00%</v>
@@ -11249,13 +11249,13 @@
         <v>50</v>
       </c>
       <c r="G286">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H286">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I286" t="str">
-        <v>2278.0</v>
+        <v>2292.0</v>
       </c>
       <c r="J286" t="str">
         <v>100.00%</v>
@@ -11287,13 +11287,13 @@
         <v>10</v>
       </c>
       <c r="G287">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H287">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="I287" t="str">
-        <v>474.0</v>
+        <v>456.0</v>
       </c>
       <c r="J287" t="str">
         <v>100.00%</v>
@@ -11325,13 +11325,13 @@
         <v>25</v>
       </c>
       <c r="G288">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H288">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="I288" t="str">
-        <v>1151.0</v>
+        <v>1165.0</v>
       </c>
       <c r="J288" t="str">
         <v>100.00%</v>
@@ -11363,13 +11363,13 @@
         <v>15</v>
       </c>
       <c r="G289">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H289">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="I289" t="str">
-        <v>678.0</v>
+        <v>705.0</v>
       </c>
       <c r="J289" t="str">
         <v>100.00%</v>
@@ -11401,13 +11401,13 @@
         <v>20</v>
       </c>
       <c r="G290">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H290">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I290" t="str">
-        <v>921.0</v>
+        <v>946.0</v>
       </c>
       <c r="J290" t="str">
         <v>100.00%</v>
@@ -11439,13 +11439,13 @@
         <v>10</v>
       </c>
       <c r="G291">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H291">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="I291" t="str">
-        <v>480.0</v>
+        <v>466.0</v>
       </c>
       <c r="J291" t="str">
         <v>100.00%</v>
@@ -11477,13 +11477,13 @@
         <v>5</v>
       </c>
       <c r="G292">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H292">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I292" t="str">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="J292" t="str">
         <v>100.00%</v>
@@ -11515,13 +11515,13 @@
         <v>10</v>
       </c>
       <c r="G293">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="H293">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I293" t="str">
-        <v>466.0</v>
+        <v>461.0</v>
       </c>
       <c r="J293" t="str">
         <v>100.00%</v>
@@ -11553,13 +11553,13 @@
         <v>20</v>
       </c>
       <c r="G294">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H294">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I294" t="str">
-        <v>946.0</v>
+        <v>940.0</v>
       </c>
       <c r="J294" t="str">
         <v>100.00%</v>
@@ -11591,13 +11591,13 @@
         <v>30</v>
       </c>
       <c r="G295">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="H295">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I295" t="str">
-        <v>1378.0</v>
+        <v>1391.0</v>
       </c>
       <c r="J295" t="str">
         <v>100.00%</v>
@@ -11629,13 +11629,13 @@
         <v>50</v>
       </c>
       <c r="G296">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="H296">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="I296" t="str">
-        <v>2299.0</v>
+        <v>2251.0</v>
       </c>
       <c r="J296" t="str">
         <v>100.00%</v>
@@ -11667,13 +11667,13 @@
         <v>10</v>
       </c>
       <c r="G297">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H297">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="I297" t="str">
-        <v>495.0</v>
+        <v>491.0</v>
       </c>
       <c r="J297" t="str">
         <v>100.00%</v>
@@ -11705,13 +11705,13 @@
         <v>25</v>
       </c>
       <c r="G298">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="H298">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I298" t="str">
-        <v>1155.0</v>
+        <v>1163.0</v>
       </c>
       <c r="J298" t="str">
         <v>100.00%</v>
@@ -11743,13 +11743,13 @@
         <v>15</v>
       </c>
       <c r="G299">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H299">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I299" t="str">
-        <v>681.0</v>
+        <v>721.0</v>
       </c>
       <c r="J299" t="str">
         <v>100.00%</v>
@@ -11781,13 +11781,13 @@
         <v>20</v>
       </c>
       <c r="G300">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H300">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="I300" t="str">
-        <v>941.0</v>
+        <v>928.0</v>
       </c>
       <c r="J300" t="str">
         <v>100.00%</v>
@@ -11819,13 +11819,13 @@
         <v>10</v>
       </c>
       <c r="G301">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H301">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I301" t="str">
-        <v>490.0</v>
+        <v>454.0</v>
       </c>
       <c r="J301" t="str">
         <v>100.00%</v>

--- a/EventSphere_k6_Load_Testing_300_Report.xlsx
+++ b/EventSphere_k6_Load_Testing_300_Report.xlsx
@@ -457,13 +457,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I2" t="str">
-        <v>270.0</v>
+        <v>266.0</v>
       </c>
       <c r="J2" t="str">
         <v>100.00%</v>
@@ -495,13 +495,13 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H3">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I3" t="str">
-        <v>456.0</v>
+        <v>482.0</v>
       </c>
       <c r="J3" t="str">
         <v>100.00%</v>
@@ -533,13 +533,13 @@
         <v>20</v>
       </c>
       <c r="G4">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H4">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I4" t="str">
-        <v>911.0</v>
+        <v>935.0</v>
       </c>
       <c r="J4" t="str">
         <v>100.00%</v>
@@ -571,13 +571,13 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H5">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I5" t="str">
-        <v>1363.0</v>
+        <v>1361.0</v>
       </c>
       <c r="J5" t="str">
         <v>100.00%</v>
@@ -609,13 +609,13 @@
         <v>50</v>
       </c>
       <c r="G6">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H6">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I6" t="str">
-        <v>2259.0</v>
+        <v>2261.0</v>
       </c>
       <c r="J6" t="str">
         <v>100.00%</v>
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H7">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="I7" t="str">
-        <v>493.0</v>
+        <v>484.0</v>
       </c>
       <c r="J7" t="str">
         <v>100.00%</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="H8">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="I8" t="str">
-        <v>1153.0</v>
+        <v>1144.0</v>
       </c>
       <c r="J8" t="str">
         <v>100.00%</v>
@@ -723,13 +723,13 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H9">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I9" t="str">
-        <v>708.0</v>
+        <v>722.0</v>
       </c>
       <c r="J9" t="str">
         <v>100.00%</v>
@@ -761,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="G10">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H10">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="I10" t="str">
-        <v>911.0</v>
+        <v>928.0</v>
       </c>
       <c r="J10" t="str">
         <v>100.00%</v>
@@ -799,13 +799,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="H11">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I11" t="str">
-        <v>472.0</v>
+        <v>491.0</v>
       </c>
       <c r="J11" t="str">
         <v>100.00%</v>
@@ -840,10 +840,10 @@
         <v>93</v>
       </c>
       <c r="H12">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I12" t="str">
-        <v>236.0</v>
+        <v>270.0</v>
       </c>
       <c r="J12" t="str">
         <v>100.00%</v>
@@ -875,13 +875,13 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H13">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I13" t="str">
-        <v>473.0</v>
+        <v>458.0</v>
       </c>
       <c r="J13" t="str">
         <v>100.00%</v>
@@ -913,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G14">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H14">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="I14" t="str">
-        <v>907.0</v>
+        <v>902.0</v>
       </c>
       <c r="J14" t="str">
         <v>100.00%</v>
@@ -951,13 +951,13 @@
         <v>30</v>
       </c>
       <c r="G15">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H15">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I15" t="str">
-        <v>1366.0</v>
+        <v>1371.0</v>
       </c>
       <c r="J15" t="str">
         <v>100.00%</v>
@@ -989,13 +989,13 @@
         <v>50</v>
       </c>
       <c r="G16">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H16">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I16" t="str">
-        <v>2263.0</v>
+        <v>2284.0</v>
       </c>
       <c r="J16" t="str">
         <v>100.00%</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I17" t="str">
-        <v>454.0</v>
+        <v>493.0</v>
       </c>
       <c r="J17" t="str">
         <v>100.00%</v>
@@ -1065,13 +1065,13 @@
         <v>25</v>
       </c>
       <c r="G18">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="H18">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I18" t="str">
-        <v>1162.0</v>
+        <v>1154.0</v>
       </c>
       <c r="J18" t="str">
         <v>100.00%</v>
@@ -1103,13 +1103,13 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H19">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I19" t="str">
-        <v>721.0</v>
+        <v>699.0</v>
       </c>
       <c r="J19" t="str">
         <v>100.00%</v>
@@ -1141,13 +1141,13 @@
         <v>20</v>
       </c>
       <c r="G20">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H20">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I20" t="str">
-        <v>932.0</v>
+        <v>947.0</v>
       </c>
       <c r="J20" t="str">
         <v>100.00%</v>
@@ -1179,13 +1179,13 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="H21">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="I21" t="str">
-        <v>461.0</v>
+        <v>451.0</v>
       </c>
       <c r="J21" t="str">
         <v>100.00%</v>
@@ -1217,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I22" t="str">
-        <v>260.0</v>
+        <v>232.0</v>
       </c>
       <c r="J22" t="str">
         <v>100.00%</v>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H23">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I23" t="str">
-        <v>466.0</v>
+        <v>491.0</v>
       </c>
       <c r="J23" t="str">
         <v>100.00%</v>
@@ -1293,13 +1293,13 @@
         <v>20</v>
       </c>
       <c r="G24">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="H24">
         <v>178</v>
       </c>
       <c r="I24" t="str">
-        <v>936.0</v>
+        <v>902.0</v>
       </c>
       <c r="J24" t="str">
         <v>100.00%</v>
@@ -1331,13 +1331,13 @@
         <v>30</v>
       </c>
       <c r="G25">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="H25">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I25" t="str">
-        <v>1372.0</v>
+        <v>1399.0</v>
       </c>
       <c r="J25" t="str">
         <v>100.00%</v>
@@ -1369,13 +1369,13 @@
         <v>50</v>
       </c>
       <c r="G26">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H26">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I26" t="str">
-        <v>2250.0</v>
+        <v>2260.0</v>
       </c>
       <c r="J26" t="str">
         <v>100.00%</v>
@@ -1407,10 +1407,10 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H27">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I27" t="str">
         <v>480.0</v>
@@ -1445,13 +1445,13 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="H28">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="I28" t="str">
-        <v>1144.0</v>
+        <v>1166.0</v>
       </c>
       <c r="J28" t="str">
         <v>100.00%</v>
@@ -1483,13 +1483,13 @@
         <v>15</v>
       </c>
       <c r="G29">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H29">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="I29" t="str">
-        <v>704.0</v>
+        <v>677.0</v>
       </c>
       <c r="J29" t="str">
         <v>100.00%</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G30">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H30">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I30" t="str">
-        <v>922.0</v>
+        <v>914.0</v>
       </c>
       <c r="J30" t="str">
         <v>100.00%</v>
@@ -1559,13 +1559,13 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H31">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="I31" t="str">
-        <v>484.0</v>
+        <v>462.0</v>
       </c>
       <c r="J31" t="str">
         <v>100.00%</v>
@@ -1597,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H32">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="I32" t="str">
-        <v>225.0</v>
+        <v>237.0</v>
       </c>
       <c r="J32" t="str">
         <v>100.00%</v>
@@ -1635,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H33">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="I33" t="str">
-        <v>465.0</v>
+        <v>495.0</v>
       </c>
       <c r="J33" t="str">
         <v>100.00%</v>
@@ -1673,13 +1673,13 @@
         <v>20</v>
       </c>
       <c r="G34">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H34">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="I34" t="str">
-        <v>948.0</v>
+        <v>920.0</v>
       </c>
       <c r="J34" t="str">
         <v>100.00%</v>
@@ -1711,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="G35">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="H35">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I35" t="str">
-        <v>1378.0</v>
+        <v>1365.0</v>
       </c>
       <c r="J35" t="str">
         <v>100.00%</v>
@@ -1749,13 +1749,13 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H36">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I36" t="str">
-        <v>2254.0</v>
+        <v>2272.0</v>
       </c>
       <c r="J36" t="str">
         <v>100.00%</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="G37">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H37">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="I37" t="str">
-        <v>467.0</v>
+        <v>461.0</v>
       </c>
       <c r="J37" t="str">
         <v>100.00%</v>
@@ -1825,13 +1825,13 @@
         <v>25</v>
       </c>
       <c r="G38">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H38">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I38" t="str">
-        <v>1129.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J38" t="str">
         <v>100.00%</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H39">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I39" t="str">
-        <v>722.0</v>
+        <v>720.0</v>
       </c>
       <c r="J39" t="str">
         <v>100.00%</v>
@@ -1901,13 +1901,13 @@
         <v>20</v>
       </c>
       <c r="G40">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H40">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="I40" t="str">
-        <v>906.0</v>
+        <v>940.0</v>
       </c>
       <c r="J40" t="str">
         <v>100.00%</v>
@@ -1939,13 +1939,13 @@
         <v>10</v>
       </c>
       <c r="G41">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H41">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I41" t="str">
-        <v>486.0</v>
+        <v>468.0</v>
       </c>
       <c r="J41" t="str">
         <v>100.00%</v>
@@ -1977,13 +1977,13 @@
         <v>5</v>
       </c>
       <c r="G42">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="H42">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I42" t="str">
-        <v>269.0</v>
+        <v>247.0</v>
       </c>
       <c r="J42" t="str">
         <v>100.00%</v>
@@ -2015,13 +2015,13 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="H43">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="I43" t="str">
-        <v>450.0</v>
+        <v>461.0</v>
       </c>
       <c r="J43" t="str">
         <v>100.00%</v>
@@ -2053,13 +2053,13 @@
         <v>20</v>
       </c>
       <c r="G44">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H44">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="I44" t="str">
-        <v>926.0</v>
+        <v>907.0</v>
       </c>
       <c r="J44" t="str">
         <v>100.00%</v>
@@ -2091,13 +2091,13 @@
         <v>30</v>
       </c>
       <c r="G45">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="H45">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="I45" t="str">
-        <v>1369.0</v>
+        <v>1352.0</v>
       </c>
       <c r="J45" t="str">
         <v>100.00%</v>
@@ -2129,13 +2129,13 @@
         <v>50</v>
       </c>
       <c r="G46">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="H46">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="I46" t="str">
-        <v>2280.0</v>
+        <v>2256.0</v>
       </c>
       <c r="J46" t="str">
         <v>100.00%</v>
@@ -2167,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="G47">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H47">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="I47" t="str">
-        <v>491.0</v>
+        <v>479.0</v>
       </c>
       <c r="J47" t="str">
         <v>100.00%</v>
@@ -2205,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="G48">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H48">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I48" t="str">
-        <v>1174.0</v>
+        <v>1125.0</v>
       </c>
       <c r="J48" t="str">
         <v>100.00%</v>
@@ -2243,13 +2243,13 @@
         <v>15</v>
       </c>
       <c r="G49">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H49">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I49" t="str">
-        <v>685.0</v>
+        <v>706.0</v>
       </c>
       <c r="J49" t="str">
         <v>100.00%</v>
@@ -2281,13 +2281,13 @@
         <v>20</v>
       </c>
       <c r="G50">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H50">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I50" t="str">
-        <v>932.0</v>
+        <v>948.0</v>
       </c>
       <c r="J50" t="str">
         <v>100.00%</v>
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="G51">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H51">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I51" t="str">
-        <v>497.0</v>
+        <v>489.0</v>
       </c>
       <c r="J51" t="str">
         <v>100.00%</v>
@@ -2357,13 +2357,13 @@
         <v>5</v>
       </c>
       <c r="G52">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H52">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="I52" t="str">
-        <v>256.0</v>
+        <v>239.0</v>
       </c>
       <c r="J52" t="str">
         <v>100.00%</v>
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="G53">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H53">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="I53" t="str">
-        <v>463.0</v>
+        <v>499.0</v>
       </c>
       <c r="J53" t="str">
         <v>100.00%</v>
@@ -2433,13 +2433,13 @@
         <v>20</v>
       </c>
       <c r="G54">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H54">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I54" t="str">
-        <v>912.0</v>
+        <v>931.0</v>
       </c>
       <c r="J54" t="str">
         <v>100.00%</v>
@@ -2471,13 +2471,13 @@
         <v>30</v>
       </c>
       <c r="G55">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H55">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="I55" t="str">
-        <v>1366.0</v>
+        <v>1390.0</v>
       </c>
       <c r="J55" t="str">
         <v>100.00%</v>
@@ -2509,13 +2509,13 @@
         <v>50</v>
       </c>
       <c r="G56">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H56">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="I56" t="str">
-        <v>2281.0</v>
+        <v>2250.0</v>
       </c>
       <c r="J56" t="str">
         <v>100.00%</v>
@@ -2547,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="G57">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H57">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="I57" t="str">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="J57" t="str">
         <v>100.00%</v>
@@ -2585,13 +2585,13 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="H58">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="I58" t="str">
-        <v>1144.0</v>
+        <v>1152.0</v>
       </c>
       <c r="J58" t="str">
         <v>100.00%</v>
@@ -2623,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="G59">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H59">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I59" t="str">
-        <v>723.0</v>
+        <v>698.0</v>
       </c>
       <c r="J59" t="str">
         <v>100.00%</v>
@@ -2661,13 +2661,13 @@
         <v>20</v>
       </c>
       <c r="G60">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="H60">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="I60" t="str">
-        <v>915.0</v>
+        <v>933.0</v>
       </c>
       <c r="J60" t="str">
         <v>100.00%</v>
@@ -2699,13 +2699,13 @@
         <v>10</v>
       </c>
       <c r="G61">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H61">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I61" t="str">
-        <v>452.0</v>
+        <v>469.0</v>
       </c>
       <c r="J61" t="str">
         <v>100.00%</v>
@@ -2737,13 +2737,13 @@
         <v>5</v>
       </c>
       <c r="G62">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H62">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="I62" t="str">
-        <v>226.0</v>
+        <v>247.0</v>
       </c>
       <c r="J62" t="str">
         <v>100.00%</v>
@@ -2775,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="G63">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H63">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="I63" t="str">
-        <v>486.0</v>
+        <v>465.0</v>
       </c>
       <c r="J63" t="str">
         <v>100.00%</v>
@@ -2813,13 +2813,13 @@
         <v>20</v>
       </c>
       <c r="G64">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H64">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I64" t="str">
-        <v>929.0</v>
+        <v>919.0</v>
       </c>
       <c r="J64" t="str">
         <v>100.00%</v>
@@ -2851,13 +2851,13 @@
         <v>30</v>
       </c>
       <c r="G65">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H65">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I65" t="str">
-        <v>1365.0</v>
+        <v>1362.0</v>
       </c>
       <c r="J65" t="str">
         <v>100.00%</v>
@@ -288